--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="281">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -608,6 +608,9 @@
   </si>
   <si>
     <t>['34', '87']</t>
+  </si>
+  <si>
+    <t>['43']</t>
   </si>
   <si>
     <t>['3', '15', '45+3']</t>
@@ -1215,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1471,7 +1474,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1755,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3">
         <v>2.2</v>
@@ -2089,7 +2092,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2501,7 +2504,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2707,7 +2710,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2788,7 +2791,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3119,7 +3122,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3325,7 +3328,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3531,7 +3534,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4355,7 +4358,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4433,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -4973,7 +4976,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5672,7 +5675,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ22">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6003,7 +6006,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6621,7 +6624,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6827,7 +6830,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7445,7 +7448,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7651,7 +7654,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8063,7 +8066,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8553,7 +8556,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36">
         <v>0.6</v>
@@ -8887,7 +8890,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -8968,7 +8971,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ38">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
         <v>1.63</v>
@@ -9505,7 +9508,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9711,7 +9714,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9917,7 +9920,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10123,7 +10126,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10329,7 +10332,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10947,7 +10950,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11025,7 +11028,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48">
         <v>2</v>
@@ -11359,7 +11362,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11565,7 +11568,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11852,7 +11855,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ52">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR52">
         <v>1.32</v>
@@ -12389,7 +12392,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12801,7 +12804,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13007,7 +13010,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13213,7 +13216,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13419,7 +13422,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13625,7 +13628,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13831,7 +13834,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -14037,7 +14040,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14243,7 +14246,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14321,7 +14324,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ64">
         <v>1.9</v>
@@ -14449,7 +14452,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14530,7 +14533,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR65">
         <v>1.31</v>
@@ -14655,7 +14658,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15273,7 +15276,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15685,7 +15688,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15891,7 +15894,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16303,7 +16306,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16715,7 +16718,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17127,7 +17130,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17333,7 +17336,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17745,7 +17748,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17951,7 +17954,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18157,7 +18160,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18235,7 +18238,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83">
         <v>1.1</v>
@@ -18363,7 +18366,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18569,7 +18572,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18650,7 +18653,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ85">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>1.12</v>
@@ -18981,7 +18984,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19393,7 +19396,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19805,7 +19808,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20092,7 +20095,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ92">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20423,7 +20426,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21453,7 +21456,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21659,7 +21662,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21865,7 +21868,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -21943,7 +21946,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -22071,7 +22074,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22277,7 +22280,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22976,7 +22979,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ106">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR106">
         <v>2.08</v>
@@ -23101,7 +23104,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23513,7 +23516,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23925,7 +23928,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24131,7 +24134,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24827,7 +24830,7 @@
         <v>0.14</v>
       </c>
       <c r="AP115">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ115">
         <v>0.1</v>
@@ -24955,7 +24958,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25161,7 +25164,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25367,7 +25370,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25573,7 +25576,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25779,7 +25782,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26603,7 +26606,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26809,7 +26812,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -26890,7 +26893,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ125">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27015,7 +27018,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27427,7 +27430,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27505,7 +27508,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27633,7 +27636,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28045,7 +28048,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28663,7 +28666,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29075,7 +29078,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29693,7 +29696,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29899,7 +29902,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30105,7 +30108,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30311,7 +30314,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30517,7 +30520,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31135,7 +31138,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31213,7 +31216,7 @@
         <v>0.78</v>
       </c>
       <c r="AP146">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ146">
         <v>0.7</v>
@@ -31341,7 +31344,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31547,7 +31550,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31753,7 +31756,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -31834,7 +31837,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ149">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR149">
         <v>2.02</v>
@@ -32165,7 +32168,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32371,7 +32374,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32577,7 +32580,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32989,7 +32992,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33607,7 +33610,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33813,7 +33816,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34019,7 +34022,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34225,7 +34228,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34382,6 +34385,212 @@
       </c>
       <c r="BP161">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7453843</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45688.54166666666</v>
+      </c>
+      <c r="F162">
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>71</v>
+      </c>
+      <c r="H162" t="s">
+        <v>85</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>2</v>
+      </c>
+      <c r="O162" t="s">
+        <v>198</v>
+      </c>
+      <c r="P162" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q162">
+        <v>4</v>
+      </c>
+      <c r="R162">
+        <v>2.05</v>
+      </c>
+      <c r="S162">
+        <v>2.63</v>
+      </c>
+      <c r="T162">
+        <v>1.44</v>
+      </c>
+      <c r="U162">
+        <v>2.63</v>
+      </c>
+      <c r="V162">
+        <v>3.25</v>
+      </c>
+      <c r="W162">
+        <v>1.33</v>
+      </c>
+      <c r="X162">
+        <v>7.5</v>
+      </c>
+      <c r="Y162">
+        <v>1.07</v>
+      </c>
+      <c r="Z162">
+        <v>3.97</v>
+      </c>
+      <c r="AA162">
+        <v>3.48</v>
+      </c>
+      <c r="AB162">
+        <v>1.84</v>
+      </c>
+      <c r="AC162">
+        <v>1.06</v>
+      </c>
+      <c r="AD162">
+        <v>8</v>
+      </c>
+      <c r="AE162">
+        <v>1.33</v>
+      </c>
+      <c r="AF162">
+        <v>3.15</v>
+      </c>
+      <c r="AG162">
+        <v>1.96</v>
+      </c>
+      <c r="AH162">
+        <v>1.76</v>
+      </c>
+      <c r="AI162">
+        <v>1.91</v>
+      </c>
+      <c r="AJ162">
+        <v>1.8</v>
+      </c>
+      <c r="AK162">
+        <v>1.84</v>
+      </c>
+      <c r="AL162">
+        <v>1.27</v>
+      </c>
+      <c r="AM162">
+        <v>1.22</v>
+      </c>
+      <c r="AN162">
+        <v>1.3</v>
+      </c>
+      <c r="AO162">
+        <v>1.8</v>
+      </c>
+      <c r="AP162">
+        <v>1.27</v>
+      </c>
+      <c r="AQ162">
+        <v>1.73</v>
+      </c>
+      <c r="AR162">
+        <v>1.35</v>
+      </c>
+      <c r="AS162">
+        <v>1.68</v>
+      </c>
+      <c r="AT162">
+        <v>3.03</v>
+      </c>
+      <c r="AU162">
+        <v>3</v>
+      </c>
+      <c r="AV162">
+        <v>6</v>
+      </c>
+      <c r="AW162">
+        <v>6</v>
+      </c>
+      <c r="AX162">
+        <v>8</v>
+      </c>
+      <c r="AY162">
+        <v>9</v>
+      </c>
+      <c r="AZ162">
+        <v>14</v>
+      </c>
+      <c r="BA162">
+        <v>2</v>
+      </c>
+      <c r="BB162">
+        <v>5</v>
+      </c>
+      <c r="BC162">
+        <v>7</v>
+      </c>
+      <c r="BD162">
+        <v>2.9</v>
+      </c>
+      <c r="BE162">
+        <v>8</v>
+      </c>
+      <c r="BF162">
+        <v>1.59</v>
+      </c>
+      <c r="BG162">
+        <v>1.4</v>
+      </c>
+      <c r="BH162">
+        <v>2.82</v>
+      </c>
+      <c r="BI162">
+        <v>1.68</v>
+      </c>
+      <c r="BJ162">
+        <v>2.11</v>
+      </c>
+      <c r="BK162">
+        <v>2.11</v>
+      </c>
+      <c r="BL162">
+        <v>1.68</v>
+      </c>
+      <c r="BM162">
+        <v>2.75</v>
+      </c>
+      <c r="BN162">
+        <v>1.42</v>
+      </c>
+      <c r="BO162">
+        <v>3.82</v>
+      </c>
+      <c r="BP162">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,6 +613,12 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['21', '49']</t>
+  </si>
+  <si>
+    <t>['74', '88']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -857,6 +863,12 @@
   </si>
   <si>
     <t>['18', '42']</t>
+  </si>
+  <si>
+    <t>['8', '43', '53']</t>
+  </si>
+  <si>
+    <t>['28', '38']</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1486,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2092,7 +2104,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2376,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ6">
         <v>0.7</v>
@@ -2504,7 +2516,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2582,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2710,7 +2722,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3122,7 +3134,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3328,7 +3340,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3534,7 +3546,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3615,7 +3627,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR12">
         <v>2.33</v>
@@ -4233,7 +4245,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ15">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4358,7 +4370,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4642,7 +4654,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17">
         <v>2</v>
@@ -4976,7 +4988,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5263,7 +5275,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5466,7 +5478,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21">
         <v>1.3</v>
@@ -5672,7 +5684,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22">
         <v>1.73</v>
@@ -6006,7 +6018,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6624,7 +6636,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6705,7 +6717,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ27">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6830,7 +6842,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7448,7 +7460,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7654,7 +7666,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7732,7 +7744,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -8066,7 +8078,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8144,10 +8156,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ34">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR34">
         <v>1.89</v>
@@ -8559,7 +8571,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ36">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR36">
         <v>1.22</v>
@@ -8890,7 +8902,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9508,7 +9520,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9714,7 +9726,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9920,7 +9932,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10126,7 +10138,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10332,7 +10344,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10616,10 +10628,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR46">
         <v>0.99</v>
@@ -10822,7 +10834,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
         <v>0.1</v>
@@ -10950,7 +10962,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11237,7 +11249,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR49">
         <v>1.36</v>
@@ -11362,7 +11374,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11443,7 +11455,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ50">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11568,7 +11580,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11852,7 +11864,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52">
         <v>1.73</v>
@@ -12392,7 +12404,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12804,7 +12816,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -12882,7 +12894,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ57">
         <v>1.1</v>
@@ -13010,7 +13022,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13216,7 +13228,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13422,7 +13434,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13628,7 +13640,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13834,7 +13846,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -13912,7 +13924,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ62">
         <v>0.1</v>
@@ -14040,7 +14052,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14246,7 +14258,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14327,7 +14339,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ64">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR64">
         <v>1.12</v>
@@ -14452,7 +14464,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14658,7 +14670,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14739,7 +14751,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ66">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15151,7 +15163,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ68">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -15276,7 +15288,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15354,7 +15366,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ69">
         <v>3</v>
@@ -15688,7 +15700,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15894,7 +15906,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15972,7 +15984,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ72">
         <v>1.5</v>
@@ -16178,7 +16190,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ73">
         <v>1.4</v>
@@ -16306,7 +16318,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16718,7 +16730,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17005,7 +17017,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ77">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR77">
         <v>0.96</v>
@@ -17130,7 +17142,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17336,7 +17348,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17748,7 +17760,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17829,7 +17841,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ81">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR81">
         <v>1.32</v>
@@ -17954,7 +17966,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18032,10 +18044,10 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18160,7 +18172,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18366,7 +18378,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18572,7 +18584,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18984,7 +18996,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19268,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19396,7 +19408,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19683,7 +19695,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19808,7 +19820,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20426,7 +20438,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20504,7 +20516,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ94">
         <v>2.2</v>
@@ -20713,7 +20725,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ95">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR95">
         <v>1.17</v>
@@ -21122,7 +21134,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ97">
         <v>1.1</v>
@@ -21456,7 +21468,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21662,7 +21674,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21868,7 +21880,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22074,7 +22086,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22155,7 +22167,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR102">
         <v>1.61</v>
@@ -22280,7 +22292,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22564,7 +22576,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>0.8</v>
@@ -23104,7 +23116,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23391,7 +23403,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ108">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
         <v>0.6899999999999999</v>
@@ -23516,7 +23528,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23800,7 +23812,7 @@
         <v>1.29</v>
       </c>
       <c r="AP110">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ110">
         <v>1.3</v>
@@ -23928,7 +23940,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24134,7 +24146,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24421,7 +24433,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR113">
         <v>1.01</v>
@@ -24627,7 +24639,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ114">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24958,7 +24970,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25036,7 +25048,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ116">
         <v>1.4</v>
@@ -25164,7 +25176,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25370,7 +25382,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25576,7 +25588,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25782,7 +25794,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26069,7 +26081,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ121">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR121">
         <v>1.85</v>
@@ -26275,7 +26287,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ122">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR122">
         <v>1.45</v>
@@ -26478,7 +26490,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26606,7 +26618,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26812,7 +26824,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -26890,7 +26902,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ125">
         <v>1.73</v>
@@ -27018,7 +27030,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27096,10 +27108,10 @@
         <v>0.38</v>
       </c>
       <c r="AP126">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ126">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR126">
         <v>1.56</v>
@@ -27430,7 +27442,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27636,7 +27648,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27920,7 +27932,7 @@
         <v>0.13</v>
       </c>
       <c r="AP130">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ130">
         <v>0.1</v>
@@ -28048,7 +28060,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28538,7 +28550,7 @@
         <v>0.88</v>
       </c>
       <c r="AP133">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ133">
         <v>0.7</v>
@@ -28666,7 +28678,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -28953,7 +28965,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ135">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR135">
         <v>1.93</v>
@@ -29078,7 +29090,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29159,7 +29171,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ136">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR136">
         <v>1.2</v>
@@ -29696,7 +29708,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29902,7 +29914,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30108,7 +30120,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30314,7 +30326,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30520,7 +30532,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30807,7 +30819,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ144">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR144">
         <v>1.18</v>
@@ -31138,7 +31150,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31344,7 +31356,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31422,7 +31434,7 @@
         <v>1.89</v>
       </c>
       <c r="AP147">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147">
         <v>2</v>
@@ -31550,7 +31562,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31628,7 +31640,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ148">
         <v>3</v>
@@ -31756,7 +31768,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32043,7 +32055,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ150">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR150">
         <v>1.62</v>
@@ -32168,7 +32180,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32246,7 +32258,7 @@
         <v>0.78</v>
       </c>
       <c r="AP151">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ151">
         <v>0.8</v>
@@ -32374,7 +32386,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32580,7 +32592,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32992,7 +33004,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33485,7 +33497,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ157">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR157">
         <v>1.13</v>
@@ -33610,7 +33622,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33816,7 +33828,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34022,7 +34034,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34228,7 +34240,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34590,6 +34602,624 @@
         <v>3.82</v>
       </c>
       <c r="BP162">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7453846</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45689.41666666666</v>
+      </c>
+      <c r="F163">
+        <v>21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>74</v>
+      </c>
+      <c r="H163" t="s">
+        <v>73</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
+        <v>87</v>
+      </c>
+      <c r="P163" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q163">
+        <v>0</v>
+      </c>
+      <c r="R163">
+        <v>0</v>
+      </c>
+      <c r="S163">
+        <v>0</v>
+      </c>
+      <c r="T163">
+        <v>0</v>
+      </c>
+      <c r="U163">
+        <v>0</v>
+      </c>
+      <c r="V163">
+        <v>0</v>
+      </c>
+      <c r="W163">
+        <v>0</v>
+      </c>
+      <c r="X163">
+        <v>0</v>
+      </c>
+      <c r="Y163">
+        <v>0</v>
+      </c>
+      <c r="Z163">
+        <v>1.59</v>
+      </c>
+      <c r="AA163">
+        <v>3.92</v>
+      </c>
+      <c r="AB163">
+        <v>5.4</v>
+      </c>
+      <c r="AC163">
+        <v>0</v>
+      </c>
+      <c r="AD163">
+        <v>0</v>
+      </c>
+      <c r="AE163">
+        <v>0</v>
+      </c>
+      <c r="AF163">
+        <v>0</v>
+      </c>
+      <c r="AG163">
+        <v>1.83</v>
+      </c>
+      <c r="AH163">
+        <v>1.91</v>
+      </c>
+      <c r="AI163">
+        <v>0</v>
+      </c>
+      <c r="AJ163">
+        <v>0</v>
+      </c>
+      <c r="AK163">
+        <v>0</v>
+      </c>
+      <c r="AL163">
+        <v>0</v>
+      </c>
+      <c r="AM163">
+        <v>0</v>
+      </c>
+      <c r="AN163">
+        <v>1.6</v>
+      </c>
+      <c r="AO163">
+        <v>1.9</v>
+      </c>
+      <c r="AP163">
+        <v>1.55</v>
+      </c>
+      <c r="AQ163">
+        <v>1.82</v>
+      </c>
+      <c r="AR163">
+        <v>1.69</v>
+      </c>
+      <c r="AS163">
+        <v>0.75</v>
+      </c>
+      <c r="AT163">
+        <v>2.44</v>
+      </c>
+      <c r="AU163">
+        <v>-1</v>
+      </c>
+      <c r="AV163">
+        <v>-1</v>
+      </c>
+      <c r="AW163">
+        <v>-1</v>
+      </c>
+      <c r="AX163">
+        <v>-1</v>
+      </c>
+      <c r="AY163">
+        <v>-1</v>
+      </c>
+      <c r="AZ163">
+        <v>-1</v>
+      </c>
+      <c r="BA163">
+        <v>-1</v>
+      </c>
+      <c r="BB163">
+        <v>-1</v>
+      </c>
+      <c r="BC163">
+        <v>-1</v>
+      </c>
+      <c r="BD163">
+        <v>0</v>
+      </c>
+      <c r="BE163">
+        <v>0</v>
+      </c>
+      <c r="BF163">
+        <v>0</v>
+      </c>
+      <c r="BG163">
+        <v>0</v>
+      </c>
+      <c r="BH163">
+        <v>0</v>
+      </c>
+      <c r="BI163">
+        <v>0</v>
+      </c>
+      <c r="BJ163">
+        <v>0</v>
+      </c>
+      <c r="BK163">
+        <v>0</v>
+      </c>
+      <c r="BL163">
+        <v>0</v>
+      </c>
+      <c r="BM163">
+        <v>0</v>
+      </c>
+      <c r="BN163">
+        <v>0</v>
+      </c>
+      <c r="BO163">
+        <v>0</v>
+      </c>
+      <c r="BP163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7453847</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F164">
+        <v>21</v>
+      </c>
+      <c r="G164" t="s">
+        <v>75</v>
+      </c>
+      <c r="H164" t="s">
+        <v>76</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>2</v>
+      </c>
+      <c r="K164">
+        <v>3</v>
+      </c>
+      <c r="L164">
+        <v>2</v>
+      </c>
+      <c r="M164">
+        <v>3</v>
+      </c>
+      <c r="N164">
+        <v>5</v>
+      </c>
+      <c r="O164" t="s">
+        <v>199</v>
+      </c>
+      <c r="P164" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q164">
+        <v>2.1</v>
+      </c>
+      <c r="R164">
+        <v>2.2</v>
+      </c>
+      <c r="S164">
+        <v>5.5</v>
+      </c>
+      <c r="T164">
+        <v>1.36</v>
+      </c>
+      <c r="U164">
+        <v>3</v>
+      </c>
+      <c r="V164">
+        <v>2.75</v>
+      </c>
+      <c r="W164">
+        <v>1.4</v>
+      </c>
+      <c r="X164">
+        <v>6.5</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>1.92</v>
+      </c>
+      <c r="AA164">
+        <v>3.47</v>
+      </c>
+      <c r="AB164">
+        <v>3.85</v>
+      </c>
+      <c r="AC164">
+        <v>1.05</v>
+      </c>
+      <c r="AD164">
+        <v>8.5</v>
+      </c>
+      <c r="AE164">
+        <v>1.3</v>
+      </c>
+      <c r="AF164">
+        <v>3.1</v>
+      </c>
+      <c r="AG164">
+        <v>1.85</v>
+      </c>
+      <c r="AH164">
+        <v>1.75</v>
+      </c>
+      <c r="AI164">
+        <v>1.83</v>
+      </c>
+      <c r="AJ164">
+        <v>1.83</v>
+      </c>
+      <c r="AK164">
+        <v>1.12</v>
+      </c>
+      <c r="AL164">
+        <v>1.22</v>
+      </c>
+      <c r="AM164">
+        <v>2.12</v>
+      </c>
+      <c r="AN164">
+        <v>1.4</v>
+      </c>
+      <c r="AO164">
+        <v>0.4</v>
+      </c>
+      <c r="AP164">
+        <v>1.27</v>
+      </c>
+      <c r="AQ164">
+        <v>0.64</v>
+      </c>
+      <c r="AR164">
+        <v>1.67</v>
+      </c>
+      <c r="AS164">
+        <v>0.96</v>
+      </c>
+      <c r="AT164">
+        <v>2.63</v>
+      </c>
+      <c r="AU164">
+        <v>9</v>
+      </c>
+      <c r="AV164">
+        <v>8</v>
+      </c>
+      <c r="AW164">
+        <v>4</v>
+      </c>
+      <c r="AX164">
+        <v>5</v>
+      </c>
+      <c r="AY164">
+        <v>15</v>
+      </c>
+      <c r="AZ164">
+        <v>14</v>
+      </c>
+      <c r="BA164">
+        <v>7</v>
+      </c>
+      <c r="BB164">
+        <v>5</v>
+      </c>
+      <c r="BC164">
+        <v>12</v>
+      </c>
+      <c r="BD164">
+        <v>1.69</v>
+      </c>
+      <c r="BE164">
+        <v>7.5</v>
+      </c>
+      <c r="BF164">
+        <v>2.66</v>
+      </c>
+      <c r="BG164">
+        <v>1.51</v>
+      </c>
+      <c r="BH164">
+        <v>2.45</v>
+      </c>
+      <c r="BI164">
+        <v>1.87</v>
+      </c>
+      <c r="BJ164">
+        <v>1.87</v>
+      </c>
+      <c r="BK164">
+        <v>2.42</v>
+      </c>
+      <c r="BL164">
+        <v>1.53</v>
+      </c>
+      <c r="BM164">
+        <v>3.3</v>
+      </c>
+      <c r="BN164">
+        <v>1.3</v>
+      </c>
+      <c r="BO164">
+        <v>4.65</v>
+      </c>
+      <c r="BP164">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7453842</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45689.60416666666</v>
+      </c>
+      <c r="F165">
+        <v>21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>83</v>
+      </c>
+      <c r="H165" t="s">
+        <v>81</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>2</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>2</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>4</v>
+      </c>
+      <c r="O165" t="s">
+        <v>200</v>
+      </c>
+      <c r="P165" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q165">
+        <v>1.8</v>
+      </c>
+      <c r="R165">
+        <v>2.4</v>
+      </c>
+      <c r="S165">
+        <v>7</v>
+      </c>
+      <c r="T165">
+        <v>1.3</v>
+      </c>
+      <c r="U165">
+        <v>3.4</v>
+      </c>
+      <c r="V165">
+        <v>2.5</v>
+      </c>
+      <c r="W165">
+        <v>1.5</v>
+      </c>
+      <c r="X165">
+        <v>5.5</v>
+      </c>
+      <c r="Y165">
+        <v>1.13</v>
+      </c>
+      <c r="Z165">
+        <v>1.36</v>
+      </c>
+      <c r="AA165">
+        <v>5.3</v>
+      </c>
+      <c r="AB165">
+        <v>6.9</v>
+      </c>
+      <c r="AC165">
+        <v>1.03</v>
+      </c>
+      <c r="AD165">
+        <v>10</v>
+      </c>
+      <c r="AE165">
+        <v>1.2</v>
+      </c>
+      <c r="AF165">
+        <v>4.3</v>
+      </c>
+      <c r="AG165">
+        <v>1.57</v>
+      </c>
+      <c r="AH165">
+        <v>2.15</v>
+      </c>
+      <c r="AI165">
+        <v>2</v>
+      </c>
+      <c r="AJ165">
+        <v>1.73</v>
+      </c>
+      <c r="AK165">
+        <v>1.04</v>
+      </c>
+      <c r="AL165">
+        <v>1.09</v>
+      </c>
+      <c r="AM165">
+        <v>3.35</v>
+      </c>
+      <c r="AN165">
+        <v>1.9</v>
+      </c>
+      <c r="AO165">
+        <v>0.6</v>
+      </c>
+      <c r="AP165">
+        <v>1.82</v>
+      </c>
+      <c r="AQ165">
+        <v>0.64</v>
+      </c>
+      <c r="AR165">
+        <v>1.65</v>
+      </c>
+      <c r="AS165">
+        <v>1.38</v>
+      </c>
+      <c r="AT165">
+        <v>3.03</v>
+      </c>
+      <c r="AU165">
+        <v>5</v>
+      </c>
+      <c r="AV165">
+        <v>6</v>
+      </c>
+      <c r="AW165">
+        <v>10</v>
+      </c>
+      <c r="AX165">
+        <v>1</v>
+      </c>
+      <c r="AY165">
+        <v>17</v>
+      </c>
+      <c r="AZ165">
+        <v>8</v>
+      </c>
+      <c r="BA165">
+        <v>3</v>
+      </c>
+      <c r="BB165">
+        <v>6</v>
+      </c>
+      <c r="BC165">
+        <v>9</v>
+      </c>
+      <c r="BD165">
+        <v>1.41</v>
+      </c>
+      <c r="BE165">
+        <v>8.5</v>
+      </c>
+      <c r="BF165">
+        <v>3.59</v>
+      </c>
+      <c r="BG165">
+        <v>1.4</v>
+      </c>
+      <c r="BH165">
+        <v>2.82</v>
+      </c>
+      <c r="BI165">
+        <v>1.68</v>
+      </c>
+      <c r="BJ165">
+        <v>2.11</v>
+      </c>
+      <c r="BK165">
+        <v>2.11</v>
+      </c>
+      <c r="BL165">
+        <v>1.68</v>
+      </c>
+      <c r="BM165">
+        <v>2.75</v>
+      </c>
+      <c r="BN165">
+        <v>1.42</v>
+      </c>
+      <c r="BO165">
+        <v>3.82</v>
+      </c>
+      <c r="BP165">
         <v>1.24</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="288">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,12 @@
     <t>['74', '88']</t>
   </si>
   <si>
+    <t>['39', '67']</t>
+  </si>
+  <si>
+    <t>['73', '77']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -869,6 +875,9 @@
   </si>
   <si>
     <t>['28', '38']</t>
+  </si>
+  <si>
+    <t>['29', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1486,7 +1495,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1564,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2">
         <v>1.3</v>
@@ -1979,7 +1988,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ4">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2104,7 +2113,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2185,7 +2194,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2391,7 +2400,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ6">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2516,7 +2525,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2722,7 +2731,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3006,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
         <v>0.8</v>
@@ -3134,7 +3143,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3340,7 +3349,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3418,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3546,7 +3555,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4370,7 +4379,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4657,7 +4666,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -4863,7 +4872,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ18">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4988,7 +4997,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5272,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20">
         <v>0.64</v>
@@ -5890,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ23">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
         <v>1.76</v>
@@ -6018,7 +6027,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6636,7 +6645,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6842,7 +6851,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7332,7 +7341,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30">
         <v>2.2</v>
@@ -7460,7 +7469,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7666,7 +7675,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7950,10 +7959,10 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ33">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR33">
         <v>1.82</v>
@@ -8078,7 +8087,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8365,7 +8374,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ35">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -8774,7 +8783,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ37">
         <v>0.8</v>
@@ -8902,7 +8911,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -8980,7 +8989,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ38">
         <v>1.73</v>
@@ -9520,7 +9529,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9726,7 +9735,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9932,7 +9941,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10138,7 +10147,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10344,7 +10353,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10422,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -10837,7 +10846,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR47">
         <v>1.89</v>
@@ -10962,7 +10971,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11043,7 +11052,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ48">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR48">
         <v>1.07</v>
@@ -11246,7 +11255,7 @@
         <v>0.33</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
         <v>0.64</v>
@@ -11374,7 +11383,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11452,7 +11461,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ50">
         <v>1.82</v>
@@ -11580,7 +11589,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11658,7 +11667,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ51">
         <v>3</v>
@@ -12404,7 +12413,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12816,7 +12825,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13022,7 +13031,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13228,7 +13237,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13434,7 +13443,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13515,7 +13524,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ60">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR60">
         <v>0.73</v>
@@ -13640,7 +13649,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13718,7 +13727,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61">
         <v>1.4</v>
@@ -13846,7 +13855,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -13927,7 +13936,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ62">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -14052,7 +14061,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14130,7 +14139,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ63">
         <v>1.1</v>
@@ -14258,7 +14267,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14464,7 +14473,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14542,7 +14551,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>1.73</v>
@@ -14670,7 +14679,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14954,10 +14963,10 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR67">
         <v>1.33</v>
@@ -15160,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ68">
         <v>0.64</v>
@@ -15288,7 +15297,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15700,7 +15709,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15906,7 +15915,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16318,7 +16327,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16399,7 +16408,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ74">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR74">
         <v>1.34</v>
@@ -16730,7 +16739,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17142,7 +17151,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17348,7 +17357,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17429,7 +17438,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR79">
         <v>1.64</v>
@@ -17632,7 +17641,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ80">
         <v>1.1</v>
@@ -17760,7 +17769,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17838,7 +17847,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ81">
         <v>1.82</v>
@@ -17966,7 +17975,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18172,7 +18181,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18378,7 +18387,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18456,7 +18465,7 @@
         <v>3</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>3</v>
@@ -18584,7 +18593,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18868,10 +18877,10 @@
         <v>0.2</v>
       </c>
       <c r="AP86">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -18996,7 +19005,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19077,7 +19086,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ87">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
         <v>2.4</v>
@@ -19408,7 +19417,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19486,7 +19495,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
         <v>1.4</v>
@@ -19820,7 +19829,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20438,7 +20447,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20722,7 +20731,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>0.64</v>
@@ -20928,10 +20937,10 @@
         <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21340,7 +21349,7 @@
         <v>0.6</v>
       </c>
       <c r="AP98">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ98">
         <v>1.1</v>
@@ -21468,7 +21477,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21674,7 +21683,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21755,7 +21764,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR100">
         <v>1.66</v>
@@ -21880,7 +21889,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22086,7 +22095,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22292,7 +22301,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22373,7 +22382,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ103">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -22782,7 +22791,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105">
         <v>1</v>
@@ -23116,7 +23125,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23194,7 +23203,7 @@
         <v>2.17</v>
       </c>
       <c r="AP107">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ107">
         <v>2.2</v>
@@ -23528,7 +23537,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23609,7 +23618,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ109">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR109">
         <v>1.11</v>
@@ -23940,7 +23949,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24146,7 +24155,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24224,7 +24233,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ112">
         <v>1.1</v>
@@ -24845,7 +24854,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ115">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -24970,7 +24979,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25176,7 +25185,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25254,7 +25263,7 @@
         <v>1.8</v>
       </c>
       <c r="AP117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ117">
         <v>1.5</v>
@@ -25382,7 +25391,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25588,7 +25597,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25794,7 +25803,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26618,7 +26627,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26696,7 +26705,7 @@
         <v>1.43</v>
       </c>
       <c r="AP124">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ124">
         <v>1.4</v>
@@ -26824,7 +26833,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27030,7 +27039,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27317,7 +27326,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27442,7 +27451,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27648,7 +27657,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27726,7 +27735,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ129">
         <v>0.8</v>
@@ -27935,7 +27944,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ130">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28060,7 +28069,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28344,10 +28353,10 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ132">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR132">
         <v>1.95</v>
@@ -28553,7 +28562,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ133">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28678,7 +28687,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29090,7 +29099,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29708,7 +29717,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29786,7 +29795,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ139">
         <v>2.2</v>
@@ -29914,7 +29923,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30120,7 +30129,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30198,7 +30207,7 @@
         <v>0.88</v>
       </c>
       <c r="AP141">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30326,7 +30335,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30532,7 +30541,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31022,10 +31031,10 @@
         <v>0.11</v>
       </c>
       <c r="AP145">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ145">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31150,7 +31159,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31231,7 +31240,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ146">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31356,7 +31365,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31437,7 +31446,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ147">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31562,7 +31571,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31768,7 +31777,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -31846,7 +31855,7 @@
         <v>1.67</v>
       </c>
       <c r="AP149">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32052,7 +32061,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ150">
         <v>0.64</v>
@@ -32180,7 +32189,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32386,7 +32395,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32592,7 +32601,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32876,7 +32885,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.3</v>
@@ -33004,7 +33013,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33622,7 +33631,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33828,7 +33837,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34034,7 +34043,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34240,7 +34249,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34318,7 +34327,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ161">
         <v>1.5</v>
@@ -34745,31 +34754,31 @@
         <v>2.44</v>
       </c>
       <c r="AU163">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV163">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW163">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX163">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY163">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ163">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BA163">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB163">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC163">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD163">
         <v>0</v>
@@ -34858,7 +34867,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35064,7 +35073,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35221,6 +35230,830 @@
       </c>
       <c r="BP165">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7453840</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45690.41666666666</v>
+      </c>
+      <c r="F166">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>84</v>
+      </c>
+      <c r="H166" t="s">
+        <v>78</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>2</v>
+      </c>
+      <c r="O166" t="s">
+        <v>201</v>
+      </c>
+      <c r="P166" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q166">
+        <v>1.95</v>
+      </c>
+      <c r="R166">
+        <v>2.25</v>
+      </c>
+      <c r="S166">
+        <v>6.5</v>
+      </c>
+      <c r="T166">
+        <v>1.36</v>
+      </c>
+      <c r="U166">
+        <v>3</v>
+      </c>
+      <c r="V166">
+        <v>2.75</v>
+      </c>
+      <c r="W166">
+        <v>1.4</v>
+      </c>
+      <c r="X166">
+        <v>6.5</v>
+      </c>
+      <c r="Y166">
+        <v>1.1</v>
+      </c>
+      <c r="Z166">
+        <v>1.39</v>
+      </c>
+      <c r="AA166">
+        <v>4.15</v>
+      </c>
+      <c r="AB166">
+        <v>6.92</v>
+      </c>
+      <c r="AC166">
+        <v>1.05</v>
+      </c>
+      <c r="AD166">
+        <v>8.5</v>
+      </c>
+      <c r="AE166">
+        <v>1.28</v>
+      </c>
+      <c r="AF166">
+        <v>3.5</v>
+      </c>
+      <c r="AG166">
+        <v>1.83</v>
+      </c>
+      <c r="AH166">
+        <v>1.87</v>
+      </c>
+      <c r="AI166">
+        <v>2.1</v>
+      </c>
+      <c r="AJ166">
+        <v>1.67</v>
+      </c>
+      <c r="AK166">
+        <v>1.09</v>
+      </c>
+      <c r="AL166">
+        <v>1.17</v>
+      </c>
+      <c r="AM166">
+        <v>2.46</v>
+      </c>
+      <c r="AN166">
+        <v>1.2</v>
+      </c>
+      <c r="AO166">
+        <v>0.1</v>
+      </c>
+      <c r="AP166">
+        <v>1.36</v>
+      </c>
+      <c r="AQ166">
+        <v>0.09</v>
+      </c>
+      <c r="AR166">
+        <v>1.38</v>
+      </c>
+      <c r="AS166">
+        <v>1.02</v>
+      </c>
+      <c r="AT166">
+        <v>2.4</v>
+      </c>
+      <c r="AU166">
+        <v>6</v>
+      </c>
+      <c r="AV166">
+        <v>5</v>
+      </c>
+      <c r="AW166">
+        <v>9</v>
+      </c>
+      <c r="AX166">
+        <v>6</v>
+      </c>
+      <c r="AY166">
+        <v>19</v>
+      </c>
+      <c r="AZ166">
+        <v>12</v>
+      </c>
+      <c r="BA166">
+        <v>4</v>
+      </c>
+      <c r="BB166">
+        <v>3</v>
+      </c>
+      <c r="BC166">
+        <v>7</v>
+      </c>
+      <c r="BD166">
+        <v>1.18</v>
+      </c>
+      <c r="BE166">
+        <v>11</v>
+      </c>
+      <c r="BF166">
+        <v>6.16</v>
+      </c>
+      <c r="BG166">
+        <v>1.37</v>
+      </c>
+      <c r="BH166">
+        <v>2.66</v>
+      </c>
+      <c r="BI166">
+        <v>1.69</v>
+      </c>
+      <c r="BJ166">
+        <v>2</v>
+      </c>
+      <c r="BK166">
+        <v>2.14</v>
+      </c>
+      <c r="BL166">
+        <v>1.57</v>
+      </c>
+      <c r="BM166">
+        <v>2.88</v>
+      </c>
+      <c r="BN166">
+        <v>1.32</v>
+      </c>
+      <c r="BO166">
+        <v>4.05</v>
+      </c>
+      <c r="BP166">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7453845</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F167">
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>77</v>
+      </c>
+      <c r="H167" t="s">
+        <v>72</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>2</v>
+      </c>
+      <c r="N167">
+        <v>3</v>
+      </c>
+      <c r="O167" t="s">
+        <v>97</v>
+      </c>
+      <c r="P167" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q167">
+        <v>6.5</v>
+      </c>
+      <c r="R167">
+        <v>2.4</v>
+      </c>
+      <c r="S167">
+        <v>1.83</v>
+      </c>
+      <c r="T167">
+        <v>1.3</v>
+      </c>
+      <c r="U167">
+        <v>3.4</v>
+      </c>
+      <c r="V167">
+        <v>2.38</v>
+      </c>
+      <c r="W167">
+        <v>1.53</v>
+      </c>
+      <c r="X167">
+        <v>5.5</v>
+      </c>
+      <c r="Y167">
+        <v>1.13</v>
+      </c>
+      <c r="Z167">
+        <v>6.5</v>
+      </c>
+      <c r="AA167">
+        <v>5</v>
+      </c>
+      <c r="AB167">
+        <v>1.36</v>
+      </c>
+      <c r="AC167">
+        <v>1.03</v>
+      </c>
+      <c r="AD167">
+        <v>10</v>
+      </c>
+      <c r="AE167">
+        <v>1.18</v>
+      </c>
+      <c r="AF167">
+        <v>4.5</v>
+      </c>
+      <c r="AG167">
+        <v>1.53</v>
+      </c>
+      <c r="AH167">
+        <v>2.34</v>
+      </c>
+      <c r="AI167">
+        <v>1.83</v>
+      </c>
+      <c r="AJ167">
+        <v>1.83</v>
+      </c>
+      <c r="AK167">
+        <v>3.2</v>
+      </c>
+      <c r="AL167">
+        <v>1.09</v>
+      </c>
+      <c r="AM167">
+        <v>1.05</v>
+      </c>
+      <c r="AN167">
+        <v>1.3</v>
+      </c>
+      <c r="AO167">
+        <v>3</v>
+      </c>
+      <c r="AP167">
+        <v>1.18</v>
+      </c>
+      <c r="AQ167">
+        <v>3</v>
+      </c>
+      <c r="AR167">
+        <v>2.02</v>
+      </c>
+      <c r="AS167">
+        <v>2.2</v>
+      </c>
+      <c r="AT167">
+        <v>4.22</v>
+      </c>
+      <c r="AU167">
+        <v>4</v>
+      </c>
+      <c r="AV167">
+        <v>7</v>
+      </c>
+      <c r="AW167">
+        <v>8</v>
+      </c>
+      <c r="AX167">
+        <v>6</v>
+      </c>
+      <c r="AY167">
+        <v>14</v>
+      </c>
+      <c r="AZ167">
+        <v>15</v>
+      </c>
+      <c r="BA167">
+        <v>3</v>
+      </c>
+      <c r="BB167">
+        <v>7</v>
+      </c>
+      <c r="BC167">
+        <v>10</v>
+      </c>
+      <c r="BD167">
+        <v>3.83</v>
+      </c>
+      <c r="BE167">
+        <v>9</v>
+      </c>
+      <c r="BF167">
+        <v>1.37</v>
+      </c>
+      <c r="BG167">
+        <v>1.4</v>
+      </c>
+      <c r="BH167">
+        <v>2.82</v>
+      </c>
+      <c r="BI167">
+        <v>1.68</v>
+      </c>
+      <c r="BJ167">
+        <v>2.11</v>
+      </c>
+      <c r="BK167">
+        <v>2.11</v>
+      </c>
+      <c r="BL167">
+        <v>1.68</v>
+      </c>
+      <c r="BM167">
+        <v>2.75</v>
+      </c>
+      <c r="BN167">
+        <v>1.42</v>
+      </c>
+      <c r="BO167">
+        <v>3.82</v>
+      </c>
+      <c r="BP167">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7453841</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45690.54166666666</v>
+      </c>
+      <c r="F168">
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>79</v>
+      </c>
+      <c r="H168" t="s">
+        <v>80</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168" t="s">
+        <v>87</v>
+      </c>
+      <c r="P168" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q168">
+        <v>2.75</v>
+      </c>
+      <c r="R168">
+        <v>2.05</v>
+      </c>
+      <c r="S168">
+        <v>4</v>
+      </c>
+      <c r="T168">
+        <v>1.44</v>
+      </c>
+      <c r="U168">
+        <v>2.63</v>
+      </c>
+      <c r="V168">
+        <v>3.25</v>
+      </c>
+      <c r="W168">
+        <v>1.33</v>
+      </c>
+      <c r="X168">
+        <v>7.5</v>
+      </c>
+      <c r="Y168">
+        <v>1.07</v>
+      </c>
+      <c r="Z168">
+        <v>1.9</v>
+      </c>
+      <c r="AA168">
+        <v>3.3</v>
+      </c>
+      <c r="AB168">
+        <v>3.63</v>
+      </c>
+      <c r="AC168">
+        <v>1.06</v>
+      </c>
+      <c r="AD168">
+        <v>8</v>
+      </c>
+      <c r="AE168">
+        <v>1.36</v>
+      </c>
+      <c r="AF168">
+        <v>3</v>
+      </c>
+      <c r="AG168">
+        <v>2.06</v>
+      </c>
+      <c r="AH168">
+        <v>1.68</v>
+      </c>
+      <c r="AI168">
+        <v>1.83</v>
+      </c>
+      <c r="AJ168">
+        <v>1.83</v>
+      </c>
+      <c r="AK168">
+        <v>1.3</v>
+      </c>
+      <c r="AL168">
+        <v>1.28</v>
+      </c>
+      <c r="AM168">
+        <v>1.67</v>
+      </c>
+      <c r="AN168">
+        <v>1.2</v>
+      </c>
+      <c r="AO168">
+        <v>0.7</v>
+      </c>
+      <c r="AP168">
+        <v>1.18</v>
+      </c>
+      <c r="AQ168">
+        <v>0.73</v>
+      </c>
+      <c r="AR168">
+        <v>1.49</v>
+      </c>
+      <c r="AS168">
+        <v>1.44</v>
+      </c>
+      <c r="AT168">
+        <v>2.93</v>
+      </c>
+      <c r="AU168">
+        <v>4</v>
+      </c>
+      <c r="AV168">
+        <v>4</v>
+      </c>
+      <c r="AW168">
+        <v>3</v>
+      </c>
+      <c r="AX168">
+        <v>5</v>
+      </c>
+      <c r="AY168">
+        <v>7</v>
+      </c>
+      <c r="AZ168">
+        <v>10</v>
+      </c>
+      <c r="BA168">
+        <v>1</v>
+      </c>
+      <c r="BB168">
+        <v>3</v>
+      </c>
+      <c r="BC168">
+        <v>4</v>
+      </c>
+      <c r="BD168">
+        <v>1.91</v>
+      </c>
+      <c r="BE168">
+        <v>7.5</v>
+      </c>
+      <c r="BF168">
+        <v>2.2</v>
+      </c>
+      <c r="BG168">
+        <v>1.44</v>
+      </c>
+      <c r="BH168">
+        <v>2.43</v>
+      </c>
+      <c r="BI168">
+        <v>1.88</v>
+      </c>
+      <c r="BJ168">
+        <v>1.92</v>
+      </c>
+      <c r="BK168">
+        <v>2.35</v>
+      </c>
+      <c r="BL168">
+        <v>1.47</v>
+      </c>
+      <c r="BM168">
+        <v>3.2</v>
+      </c>
+      <c r="BN168">
+        <v>1.26</v>
+      </c>
+      <c r="BO168">
+        <v>4.65</v>
+      </c>
+      <c r="BP168">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7453844</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45691.54166666666</v>
+      </c>
+      <c r="F169">
+        <v>21</v>
+      </c>
+      <c r="G169" t="s">
+        <v>70</v>
+      </c>
+      <c r="H169" t="s">
+        <v>82</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>202</v>
+      </c>
+      <c r="P169" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q169">
+        <v>2.4</v>
+      </c>
+      <c r="R169">
+        <v>2.2</v>
+      </c>
+      <c r="S169">
+        <v>4.33</v>
+      </c>
+      <c r="T169">
+        <v>1.36</v>
+      </c>
+      <c r="U169">
+        <v>3</v>
+      </c>
+      <c r="V169">
+        <v>2.75</v>
+      </c>
+      <c r="W169">
+        <v>1.4</v>
+      </c>
+      <c r="X169">
+        <v>6.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.1</v>
+      </c>
+      <c r="Z169">
+        <v>1.82</v>
+      </c>
+      <c r="AA169">
+        <v>3.65</v>
+      </c>
+      <c r="AB169">
+        <v>4</v>
+      </c>
+      <c r="AC169">
+        <v>1.05</v>
+      </c>
+      <c r="AD169">
+        <v>8.5</v>
+      </c>
+      <c r="AE169">
+        <v>1.25</v>
+      </c>
+      <c r="AF169">
+        <v>3.6</v>
+      </c>
+      <c r="AG169">
+        <v>1.77</v>
+      </c>
+      <c r="AH169">
+        <v>1.98</v>
+      </c>
+      <c r="AI169">
+        <v>1.73</v>
+      </c>
+      <c r="AJ169">
+        <v>2</v>
+      </c>
+      <c r="AK169">
+        <v>1.22</v>
+      </c>
+      <c r="AL169">
+        <v>1.25</v>
+      </c>
+      <c r="AM169">
+        <v>1.89</v>
+      </c>
+      <c r="AN169">
+        <v>1.7</v>
+      </c>
+      <c r="AO169">
+        <v>2</v>
+      </c>
+      <c r="AP169">
+        <v>1.82</v>
+      </c>
+      <c r="AQ169">
+        <v>1.82</v>
+      </c>
+      <c r="AR169">
+        <v>1.61</v>
+      </c>
+      <c r="AS169">
+        <v>1.36</v>
+      </c>
+      <c r="AT169">
+        <v>2.97</v>
+      </c>
+      <c r="AU169">
+        <v>6</v>
+      </c>
+      <c r="AV169">
+        <v>7</v>
+      </c>
+      <c r="AW169">
+        <v>7</v>
+      </c>
+      <c r="AX169">
+        <v>11</v>
+      </c>
+      <c r="AY169">
+        <v>13</v>
+      </c>
+      <c r="AZ169">
+        <v>23</v>
+      </c>
+      <c r="BA169">
+        <v>4</v>
+      </c>
+      <c r="BB169">
+        <v>8</v>
+      </c>
+      <c r="BC169">
+        <v>12</v>
+      </c>
+      <c r="BD169">
+        <v>1.64</v>
+      </c>
+      <c r="BE169">
+        <v>8</v>
+      </c>
+      <c r="BF169">
+        <v>2.67</v>
+      </c>
+      <c r="BG169">
+        <v>1.35</v>
+      </c>
+      <c r="BH169">
+        <v>2.74</v>
+      </c>
+      <c r="BI169">
+        <v>1.67</v>
+      </c>
+      <c r="BJ169">
+        <v>2.03</v>
+      </c>
+      <c r="BK169">
+        <v>2.1</v>
+      </c>
+      <c r="BL169">
+        <v>1.59</v>
+      </c>
+      <c r="BM169">
+        <v>2.83</v>
+      </c>
+      <c r="BN169">
+        <v>1.33</v>
+      </c>
+      <c r="BO169">
+        <v>3.9</v>
+      </c>
+      <c r="BP169">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="289">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -879,6 +879,9 @@
   <si>
     <t>['29', '90+8']</t>
   </si>
+  <si>
+    <t>['13']</t>
+  </si>
 </sst>
 </file>
 
@@ -1239,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2809,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8">
         <v>1.73</v>
@@ -4048,7 +4051,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5075,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -6108,7 +6111,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ24">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR24">
         <v>0.98</v>
@@ -8371,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35">
         <v>0.09</v>
@@ -9198,7 +9201,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ39">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9607,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
         <v>1.1</v>
@@ -12906,7 +12909,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ57">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR57">
         <v>1.94</v>
@@ -13315,7 +13318,7 @@
         <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -16611,7 +16614,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17644,7 +17647,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ80">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -19907,7 +19910,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
         <v>1.3</v>
@@ -21146,7 +21149,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ97">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR97">
         <v>1.33</v>
@@ -22379,7 +22382,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103">
         <v>0.73</v>
@@ -24236,7 +24239,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ112">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
         <v>1.19</v>
@@ -25678,7 +25681,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ119">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR119">
         <v>1.78</v>
@@ -27323,7 +27326,7 @@
         <v>2.13</v>
       </c>
       <c r="AP127">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ127">
         <v>1.82</v>
@@ -29386,7 +29389,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ137">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR137">
         <v>1.8</v>
@@ -30825,7 +30828,7 @@
         <v>2.11</v>
       </c>
       <c r="AP144">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ144">
         <v>1.82</v>
@@ -33712,7 +33715,7 @@
         <v>2.8</v>
       </c>
       <c r="AQ158">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR158">
         <v>2</v>
@@ -36054,6 +36057,212 @@
       </c>
       <c r="BP169">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7453849</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45695.45833333334</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>76</v>
+      </c>
+      <c r="H170" t="s">
+        <v>74</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>87</v>
+      </c>
+      <c r="P170" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q170">
+        <v>3.75</v>
+      </c>
+      <c r="R170">
+        <v>2.2</v>
+      </c>
+      <c r="S170">
+        <v>2.63</v>
+      </c>
+      <c r="T170">
+        <v>1.36</v>
+      </c>
+      <c r="U170">
+        <v>3</v>
+      </c>
+      <c r="V170">
+        <v>2.75</v>
+      </c>
+      <c r="W170">
+        <v>1.4</v>
+      </c>
+      <c r="X170">
+        <v>6.5</v>
+      </c>
+      <c r="Y170">
+        <v>1.1</v>
+      </c>
+      <c r="Z170">
+        <v>3.55</v>
+      </c>
+      <c r="AA170">
+        <v>3.3</v>
+      </c>
+      <c r="AB170">
+        <v>1.94</v>
+      </c>
+      <c r="AC170">
+        <v>1.05</v>
+      </c>
+      <c r="AD170">
+        <v>8.5</v>
+      </c>
+      <c r="AE170">
+        <v>1.25</v>
+      </c>
+      <c r="AF170">
+        <v>3.7</v>
+      </c>
+      <c r="AG170">
+        <v>1.78</v>
+      </c>
+      <c r="AH170">
+        <v>1.93</v>
+      </c>
+      <c r="AI170">
+        <v>1.73</v>
+      </c>
+      <c r="AJ170">
+        <v>2</v>
+      </c>
+      <c r="AK170">
+        <v>1.75</v>
+      </c>
+      <c r="AL170">
+        <v>1.28</v>
+      </c>
+      <c r="AM170">
+        <v>1.26</v>
+      </c>
+      <c r="AN170">
+        <v>1.4</v>
+      </c>
+      <c r="AO170">
+        <v>1.1</v>
+      </c>
+      <c r="AP170">
+        <v>1.27</v>
+      </c>
+      <c r="AQ170">
+        <v>1.27</v>
+      </c>
+      <c r="AR170">
+        <v>1.25</v>
+      </c>
+      <c r="AS170">
+        <v>1.35</v>
+      </c>
+      <c r="AT170">
+        <v>2.6</v>
+      </c>
+      <c r="AU170">
+        <v>2</v>
+      </c>
+      <c r="AV170">
+        <v>5</v>
+      </c>
+      <c r="AW170">
+        <v>3</v>
+      </c>
+      <c r="AX170">
+        <v>9</v>
+      </c>
+      <c r="AY170">
+        <v>7</v>
+      </c>
+      <c r="AZ170">
+        <v>17</v>
+      </c>
+      <c r="BA170">
+        <v>3</v>
+      </c>
+      <c r="BB170">
+        <v>2</v>
+      </c>
+      <c r="BC170">
+        <v>5</v>
+      </c>
+      <c r="BD170">
+        <v>2.29</v>
+      </c>
+      <c r="BE170">
+        <v>7.5</v>
+      </c>
+      <c r="BF170">
+        <v>1.85</v>
+      </c>
+      <c r="BG170">
+        <v>1.55</v>
+      </c>
+      <c r="BH170">
+        <v>2.37</v>
+      </c>
+      <c r="BI170">
+        <v>1.92</v>
+      </c>
+      <c r="BJ170">
+        <v>1.82</v>
+      </c>
+      <c r="BK170">
+        <v>2.5</v>
+      </c>
+      <c r="BL170">
+        <v>1.49</v>
+      </c>
+      <c r="BM170">
+        <v>3.45</v>
+      </c>
+      <c r="BN170">
+        <v>1.28</v>
+      </c>
+      <c r="BO170">
+        <v>4.85</v>
+      </c>
+      <c r="BP170">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -623,6 +623,12 @@
   </si>
   <si>
     <t>['73', '77']</t>
+  </si>
+  <si>
+    <t>['32', '49', '58', '78']</t>
+  </si>
+  <si>
+    <t>['32', '40', '48', '56', '62', '65']</t>
   </si>
   <si>
     <t>['3', '15', '45+3']</t>
@@ -1242,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP170"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1498,7 +1504,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1785,7 +1791,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ3">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1988,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ4">
         <v>0.09</v>
@@ -2116,7 +2122,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2194,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ5">
         <v>1.82</v>
@@ -2528,7 +2534,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2734,7 +2740,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3146,7 +3152,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3227,7 +3233,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ10">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3352,7 +3358,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3558,7 +3564,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3636,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ12">
         <v>1.82</v>
@@ -3845,7 +3851,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4382,7 +4388,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4872,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ18">
         <v>0.09</v>
@@ -5000,7 +5006,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6030,7 +6036,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6523,7 +6529,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6648,7 +6654,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6726,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ27">
         <v>0.64</v>
@@ -6854,7 +6860,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -6932,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ28">
         <v>1.1</v>
@@ -7347,7 +7353,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ30">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7472,7 +7478,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7550,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7678,7 +7684,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8090,7 +8096,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8914,7 +8920,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9198,7 +9204,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ39">
         <v>1.27</v>
@@ -9532,7 +9538,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9738,7 +9744,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9944,7 +9950,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10025,7 +10031,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ43">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR43">
         <v>1.47</v>
@@ -10150,7 +10156,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10228,7 +10234,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10356,7 +10362,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10974,7 +10980,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11386,7 +11392,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11592,7 +11598,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12288,7 +12294,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ54">
         <v>1.3</v>
@@ -12416,7 +12422,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12494,10 +12500,10 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ55">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>0</v>
@@ -12700,7 +12706,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -12828,7 +12834,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13034,7 +13040,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13115,7 +13121,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ58">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13240,7 +13246,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13321,7 +13327,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13446,7 +13452,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13652,7 +13658,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13733,7 +13739,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ61">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.36</v>
@@ -13858,7 +13864,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -14064,7 +14070,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14270,7 +14276,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14476,7 +14482,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14682,7 +14688,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15300,7 +15306,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15584,7 +15590,7 @@
         <v>1.2</v>
       </c>
       <c r="AP70">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ70">
         <v>1.3</v>
@@ -15712,7 +15718,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15918,7 +15924,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15999,7 +16005,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ72">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
         <v>1.46</v>
@@ -16205,7 +16211,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR73">
         <v>1.97</v>
@@ -16330,7 +16336,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16408,7 +16414,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ74">
         <v>0.73</v>
@@ -16742,7 +16748,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16820,10 +16826,10 @@
         <v>1.75</v>
       </c>
       <c r="AP76">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ76">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -17154,7 +17160,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17232,7 +17238,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ78">
         <v>1.1</v>
@@ -17360,7 +17366,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17772,7 +17778,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17978,7 +17984,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18184,7 +18190,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18390,7 +18396,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18596,7 +18602,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19008,7 +19014,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19086,7 +19092,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ87">
         <v>0.73</v>
@@ -19420,7 +19426,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19501,7 +19507,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR89">
         <v>1.92</v>
@@ -19832,7 +19838,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20322,7 +20328,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ93">
         <v>0.8</v>
@@ -20450,7 +20456,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20531,7 +20537,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ94">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR94">
         <v>1.84</v>
@@ -21480,7 +21486,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21686,7 +21692,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21764,7 +21770,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ100">
         <v>1.82</v>
@@ -21892,7 +21898,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -21973,7 +21979,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22098,7 +22104,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22304,7 +22310,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23000,7 +23006,7 @@
         <v>1.71</v>
       </c>
       <c r="AP106">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ106">
         <v>1.73</v>
@@ -23128,7 +23134,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23209,7 +23215,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR107">
         <v>1.95</v>
@@ -23412,7 +23418,7 @@
         <v>0.29</v>
       </c>
       <c r="AP108">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108">
         <v>0.64</v>
@@ -23540,7 +23546,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23952,7 +23958,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24158,7 +24164,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24648,7 +24654,7 @@
         <v>2.33</v>
       </c>
       <c r="AP114">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ114">
         <v>1.82</v>
@@ -24982,7 +24988,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25063,7 +25069,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ116">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25188,7 +25194,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25269,7 +25275,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ117">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25394,7 +25400,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25600,7 +25606,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25806,7 +25812,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26090,7 +26096,7 @@
         <v>0.43</v>
       </c>
       <c r="AP121">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ121">
         <v>0.64</v>
@@ -26630,7 +26636,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26711,7 +26717,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ124">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR124">
         <v>1.33</v>
@@ -26836,7 +26842,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27042,7 +27048,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27454,7 +27460,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27660,7 +27666,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28072,7 +28078,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28150,7 +28156,7 @@
         <v>3</v>
       </c>
       <c r="AP131">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ131">
         <v>3</v>
@@ -28690,7 +28696,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -28768,10 +28774,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ134">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR134">
         <v>2.03</v>
@@ -28974,7 +28980,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ135">
         <v>0.64</v>
@@ -29102,7 +29108,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29386,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
         <v>1.27</v>
@@ -29595,7 +29601,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR138">
         <v>1.06</v>
@@ -29720,7 +29726,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29801,7 +29807,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ139">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR139">
         <v>1.32</v>
@@ -29926,7 +29932,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30132,7 +30138,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30338,7 +30344,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30419,7 +30425,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ142">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30544,7 +30550,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30625,7 +30631,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ143">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR143">
         <v>1.05</v>
@@ -31162,7 +31168,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31368,7 +31374,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31574,7 +31580,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31780,7 +31786,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32192,7 +32198,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32398,7 +32404,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32604,7 +32610,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32682,7 +32688,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ153">
         <v>1.1</v>
@@ -33016,7 +33022,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33094,10 +33100,10 @@
         <v>1.56</v>
       </c>
       <c r="AP155">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ155">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR155">
         <v>1.77</v>
@@ -33303,7 +33309,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ156">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR156">
         <v>1.72</v>
@@ -33634,7 +33640,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33712,7 +33718,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -33840,7 +33846,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34046,7 +34052,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34127,7 +34133,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ160">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR160">
         <v>1.53</v>
@@ -34252,7 +34258,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34333,7 +34339,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ161">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34870,7 +34876,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35076,7 +35082,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35488,7 +35494,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36106,7 +36112,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36263,6 +36269,624 @@
       </c>
       <c r="BP170">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7453850</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45696.41666666666</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>73</v>
+      </c>
+      <c r="H171" t="s">
+        <v>77</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>4</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>5</v>
+      </c>
+      <c r="O171" t="s">
+        <v>203</v>
+      </c>
+      <c r="P171" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>0</v>
+      </c>
+      <c r="X171">
+        <v>0</v>
+      </c>
+      <c r="Y171">
+        <v>0</v>
+      </c>
+      <c r="Z171">
+        <v>2.71</v>
+      </c>
+      <c r="AA171">
+        <v>3.13</v>
+      </c>
+      <c r="AB171">
+        <v>2.37</v>
+      </c>
+      <c r="AC171">
+        <v>0</v>
+      </c>
+      <c r="AD171">
+        <v>0</v>
+      </c>
+      <c r="AE171">
+        <v>0</v>
+      </c>
+      <c r="AF171">
+        <v>0</v>
+      </c>
+      <c r="AG171">
+        <v>1.94</v>
+      </c>
+      <c r="AH171">
+        <v>1.74</v>
+      </c>
+      <c r="AI171">
+        <v>0</v>
+      </c>
+      <c r="AJ171">
+        <v>0</v>
+      </c>
+      <c r="AK171">
+        <v>0</v>
+      </c>
+      <c r="AL171">
+        <v>0</v>
+      </c>
+      <c r="AM171">
+        <v>0</v>
+      </c>
+      <c r="AN171">
+        <v>1.3</v>
+      </c>
+      <c r="AO171">
+        <v>1.5</v>
+      </c>
+      <c r="AP171">
+        <v>1.45</v>
+      </c>
+      <c r="AQ171">
+        <v>1.36</v>
+      </c>
+      <c r="AR171">
+        <v>1.13</v>
+      </c>
+      <c r="AS171">
+        <v>1.49</v>
+      </c>
+      <c r="AT171">
+        <v>2.62</v>
+      </c>
+      <c r="AU171">
+        <v>-1</v>
+      </c>
+      <c r="AV171">
+        <v>-1</v>
+      </c>
+      <c r="AW171">
+        <v>-1</v>
+      </c>
+      <c r="AX171">
+        <v>-1</v>
+      </c>
+      <c r="AY171">
+        <v>-1</v>
+      </c>
+      <c r="AZ171">
+        <v>-1</v>
+      </c>
+      <c r="BA171">
+        <v>-1</v>
+      </c>
+      <c r="BB171">
+        <v>-1</v>
+      </c>
+      <c r="BC171">
+        <v>-1</v>
+      </c>
+      <c r="BD171">
+        <v>0</v>
+      </c>
+      <c r="BE171">
+        <v>0</v>
+      </c>
+      <c r="BF171">
+        <v>0</v>
+      </c>
+      <c r="BG171">
+        <v>0</v>
+      </c>
+      <c r="BH171">
+        <v>0</v>
+      </c>
+      <c r="BI171">
+        <v>0</v>
+      </c>
+      <c r="BJ171">
+        <v>0</v>
+      </c>
+      <c r="BK171">
+        <v>0</v>
+      </c>
+      <c r="BL171">
+        <v>0</v>
+      </c>
+      <c r="BM171">
+        <v>0</v>
+      </c>
+      <c r="BN171">
+        <v>0</v>
+      </c>
+      <c r="BO171">
+        <v>0</v>
+      </c>
+      <c r="BP171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7453851</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>72</v>
+      </c>
+      <c r="H172" t="s">
+        <v>70</v>
+      </c>
+      <c r="I172">
+        <v>2</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>2</v>
+      </c>
+      <c r="L172">
+        <v>6</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>6</v>
+      </c>
+      <c r="O172" t="s">
+        <v>204</v>
+      </c>
+      <c r="P172" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q172">
+        <v>1.53</v>
+      </c>
+      <c r="R172">
+        <v>2.88</v>
+      </c>
+      <c r="S172">
+        <v>9.5</v>
+      </c>
+      <c r="T172">
+        <v>1.22</v>
+      </c>
+      <c r="U172">
+        <v>4</v>
+      </c>
+      <c r="V172">
+        <v>2.1</v>
+      </c>
+      <c r="W172">
+        <v>1.67</v>
+      </c>
+      <c r="X172">
+        <v>4.33</v>
+      </c>
+      <c r="Y172">
+        <v>1.2</v>
+      </c>
+      <c r="Z172">
+        <v>1.14</v>
+      </c>
+      <c r="AA172">
+        <v>6.78</v>
+      </c>
+      <c r="AB172">
+        <v>11.81</v>
+      </c>
+      <c r="AC172">
+        <v>1.01</v>
+      </c>
+      <c r="AD172">
+        <v>17</v>
+      </c>
+      <c r="AE172">
+        <v>1.11</v>
+      </c>
+      <c r="AF172">
+        <v>5.8</v>
+      </c>
+      <c r="AG172">
+        <v>1.44</v>
+      </c>
+      <c r="AH172">
+        <v>2.63</v>
+      </c>
+      <c r="AI172">
+        <v>2.1</v>
+      </c>
+      <c r="AJ172">
+        <v>1.67</v>
+      </c>
+      <c r="AK172">
+        <v>1.03</v>
+      </c>
+      <c r="AL172">
+        <v>1.06</v>
+      </c>
+      <c r="AM172">
+        <v>4.6</v>
+      </c>
+      <c r="AN172">
+        <v>2.8</v>
+      </c>
+      <c r="AO172">
+        <v>1.4</v>
+      </c>
+      <c r="AP172">
+        <v>2.82</v>
+      </c>
+      <c r="AQ172">
+        <v>1.27</v>
+      </c>
+      <c r="AR172">
+        <v>2.01</v>
+      </c>
+      <c r="AS172">
+        <v>1.74</v>
+      </c>
+      <c r="AT172">
+        <v>3.75</v>
+      </c>
+      <c r="AU172">
+        <v>18</v>
+      </c>
+      <c r="AV172">
+        <v>4</v>
+      </c>
+      <c r="AW172">
+        <v>9</v>
+      </c>
+      <c r="AX172">
+        <v>9</v>
+      </c>
+      <c r="AY172">
+        <v>31</v>
+      </c>
+      <c r="AZ172">
+        <v>17</v>
+      </c>
+      <c r="BA172">
+        <v>3</v>
+      </c>
+      <c r="BB172">
+        <v>4</v>
+      </c>
+      <c r="BC172">
+        <v>7</v>
+      </c>
+      <c r="BD172">
+        <v>1.1</v>
+      </c>
+      <c r="BE172">
+        <v>13</v>
+      </c>
+      <c r="BF172">
+        <v>8</v>
+      </c>
+      <c r="BG172">
+        <v>1.4</v>
+      </c>
+      <c r="BH172">
+        <v>2.82</v>
+      </c>
+      <c r="BI172">
+        <v>1.68</v>
+      </c>
+      <c r="BJ172">
+        <v>2.12</v>
+      </c>
+      <c r="BK172">
+        <v>2.11</v>
+      </c>
+      <c r="BL172">
+        <v>1.68</v>
+      </c>
+      <c r="BM172">
+        <v>2.75</v>
+      </c>
+      <c r="BN172">
+        <v>1.42</v>
+      </c>
+      <c r="BO172">
+        <v>3.8</v>
+      </c>
+      <c r="BP172">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7453853</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45696.60416666666</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>85</v>
+      </c>
+      <c r="H173" t="s">
+        <v>83</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173" t="s">
+        <v>87</v>
+      </c>
+      <c r="P173" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q173">
+        <v>3.25</v>
+      </c>
+      <c r="R173">
+        <v>2.2</v>
+      </c>
+      <c r="S173">
+        <v>3</v>
+      </c>
+      <c r="T173">
+        <v>1.36</v>
+      </c>
+      <c r="U173">
+        <v>3</v>
+      </c>
+      <c r="V173">
+        <v>2.75</v>
+      </c>
+      <c r="W173">
+        <v>1.4</v>
+      </c>
+      <c r="X173">
+        <v>6.5</v>
+      </c>
+      <c r="Y173">
+        <v>1.1</v>
+      </c>
+      <c r="Z173">
+        <v>2.79</v>
+      </c>
+      <c r="AA173">
+        <v>3.25</v>
+      </c>
+      <c r="AB173">
+        <v>2.25</v>
+      </c>
+      <c r="AC173">
+        <v>1.05</v>
+      </c>
+      <c r="AD173">
+        <v>8.5</v>
+      </c>
+      <c r="AE173">
+        <v>1.24</v>
+      </c>
+      <c r="AF173">
+        <v>3.8</v>
+      </c>
+      <c r="AG173">
+        <v>1.83</v>
+      </c>
+      <c r="AH173">
+        <v>1.98</v>
+      </c>
+      <c r="AI173">
+        <v>1.67</v>
+      </c>
+      <c r="AJ173">
+        <v>2.1</v>
+      </c>
+      <c r="AK173">
+        <v>1.55</v>
+      </c>
+      <c r="AL173">
+        <v>1.29</v>
+      </c>
+      <c r="AM173">
+        <v>1.38</v>
+      </c>
+      <c r="AN173">
+        <v>1.2</v>
+      </c>
+      <c r="AO173">
+        <v>2.2</v>
+      </c>
+      <c r="AP173">
+        <v>1.18</v>
+      </c>
+      <c r="AQ173">
+        <v>2.09</v>
+      </c>
+      <c r="AR173">
+        <v>1.77</v>
+      </c>
+      <c r="AS173">
+        <v>1.36</v>
+      </c>
+      <c r="AT173">
+        <v>3.13</v>
+      </c>
+      <c r="AU173">
+        <v>6</v>
+      </c>
+      <c r="AV173">
+        <v>6</v>
+      </c>
+      <c r="AW173">
+        <v>8</v>
+      </c>
+      <c r="AX173">
+        <v>2</v>
+      </c>
+      <c r="AY173">
+        <v>16</v>
+      </c>
+      <c r="AZ173">
+        <v>9</v>
+      </c>
+      <c r="BA173">
+        <v>5</v>
+      </c>
+      <c r="BB173">
+        <v>4</v>
+      </c>
+      <c r="BC173">
+        <v>9</v>
+      </c>
+      <c r="BD173">
+        <v>1.91</v>
+      </c>
+      <c r="BE173">
+        <v>8</v>
+      </c>
+      <c r="BF173">
+        <v>2.2</v>
+      </c>
+      <c r="BG173">
+        <v>1.32</v>
+      </c>
+      <c r="BH173">
+        <v>3.22</v>
+      </c>
+      <c r="BI173">
+        <v>1.56</v>
+      </c>
+      <c r="BJ173">
+        <v>2.33</v>
+      </c>
+      <c r="BK173">
+        <v>2</v>
+      </c>
+      <c r="BL173">
+        <v>1.8</v>
+      </c>
+      <c r="BM173">
+        <v>2.47</v>
+      </c>
+      <c r="BN173">
+        <v>1.51</v>
+      </c>
+      <c r="BO173">
+        <v>3.35</v>
+      </c>
+      <c r="BP173">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,9 @@
     <t>['32', '40', '48', '56', '62', '65']</t>
   </si>
   <si>
+    <t>['66', '83', '90+6']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -887,6 +890,12 @@
   </si>
   <si>
     <t>['13']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['76', '80']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1585,7 +1594,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2122,7 +2131,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2534,7 +2543,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2740,7 +2749,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3027,7 +3036,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ9">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3152,7 +3161,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3230,7 +3239,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ10">
         <v>2.09</v>
@@ -3358,7 +3367,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3439,7 +3448,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3564,7 +3573,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3848,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ13">
         <v>1.36</v>
@@ -4054,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ14">
         <v>1.27</v>
@@ -4260,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ15">
         <v>0.64</v>
@@ -4388,7 +4397,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4469,7 +4478,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR16">
         <v>1.02</v>
@@ -5006,7 +5015,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5499,7 +5508,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6036,7 +6045,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6114,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24">
         <v>1.27</v>
@@ -6320,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR25">
         <v>1.68</v>
@@ -6526,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ26">
         <v>1.27</v>
@@ -6654,7 +6663,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6860,7 +6869,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -6941,7 +6950,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>2.33</v>
@@ -7144,10 +7153,10 @@
         <v>1.5</v>
       </c>
       <c r="AP29">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ29">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR29">
         <v>0.53</v>
@@ -7478,7 +7487,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7684,7 +7693,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8096,7 +8105,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8795,7 +8804,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ37">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>1.6</v>
@@ -8920,7 +8929,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9410,10 +9419,10 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ40">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>1.91</v>
@@ -9538,7 +9547,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9619,7 +9628,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9744,7 +9753,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9822,10 +9831,10 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR42">
         <v>0.6</v>
@@ -9950,7 +9959,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10028,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43">
         <v>1.27</v>
@@ -10156,7 +10165,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10237,7 +10246,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10362,7 +10371,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10980,7 +10989,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11392,7 +11401,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11598,7 +11607,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12088,10 +12097,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ53">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12297,7 +12306,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ54">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR54">
         <v>1.46</v>
@@ -12422,7 +12431,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12709,7 +12718,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12834,7 +12843,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13040,7 +13049,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13118,7 +13127,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58">
         <v>2.09</v>
@@ -13246,7 +13255,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13452,7 +13461,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13530,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ60">
         <v>0.73</v>
@@ -13658,7 +13667,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13864,7 +13873,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -14070,7 +14079,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14151,7 +14160,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ63">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR63">
         <v>1.81</v>
@@ -14276,7 +14285,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14482,7 +14491,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14688,7 +14697,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14766,7 +14775,7 @@
         <v>0.25</v>
       </c>
       <c r="AP66">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -15306,7 +15315,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15593,7 +15602,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ70">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR70">
         <v>2.49</v>
@@ -15718,7 +15727,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15796,10 +15805,10 @@
         <v>0.8</v>
       </c>
       <c r="AP71">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ71">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -15924,7 +15933,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16336,7 +16345,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16623,7 +16632,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR75">
         <v>1.22</v>
@@ -16748,7 +16757,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17032,7 +17041,7 @@
         <v>0.2</v>
       </c>
       <c r="AP77">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ77">
         <v>0.64</v>
@@ -17160,7 +17169,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17241,7 +17250,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR78">
         <v>1.57</v>
@@ -17366,7 +17375,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17444,7 +17453,7 @@
         <v>2.6</v>
       </c>
       <c r="AP79">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ79">
         <v>1.82</v>
@@ -17778,7 +17787,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17984,7 +17993,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18190,7 +18199,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18271,7 +18280,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ83">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR83">
         <v>1.12</v>
@@ -18396,7 +18405,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18602,7 +18611,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18680,7 +18689,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ85">
         <v>1.73</v>
@@ -19014,7 +19023,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19301,7 +19310,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR88">
         <v>1.41</v>
@@ -19426,7 +19435,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19710,7 +19719,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ90">
         <v>0.64</v>
@@ -19838,7 +19847,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -19919,7 +19928,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20122,7 +20131,7 @@
         <v>1.83</v>
       </c>
       <c r="AP92">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ92">
         <v>1.73</v>
@@ -20331,7 +20340,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ93">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -20456,7 +20465,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21361,7 +21370,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ98">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -21486,7 +21495,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21564,7 +21573,7 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ99">
         <v>3</v>
@@ -21692,7 +21701,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21898,7 +21907,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22104,7 +22113,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22182,7 +22191,7 @@
         <v>2.6</v>
       </c>
       <c r="AP102">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ102">
         <v>1.82</v>
@@ -22310,7 +22319,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22597,7 +22606,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.79</v>
@@ -22803,7 +22812,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR105">
         <v>1.53</v>
@@ -23134,7 +23143,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23546,7 +23555,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23624,7 +23633,7 @@
         <v>2</v>
       </c>
       <c r="AP109">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ109">
         <v>1.82</v>
@@ -23833,7 +23842,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ110">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR110">
         <v>1.53</v>
@@ -23958,7 +23967,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24036,10 +24045,10 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ111">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -24164,7 +24173,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24448,7 +24457,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ113">
         <v>0.64</v>
@@ -24988,7 +24997,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25194,7 +25203,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25400,7 +25409,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25478,7 +25487,7 @@
         <v>3</v>
       </c>
       <c r="AP118">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ118">
         <v>3</v>
@@ -25606,7 +25615,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25684,7 +25693,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ119">
         <v>1.27</v>
@@ -25812,7 +25821,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -25890,10 +25899,10 @@
         <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ120">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR120">
         <v>1.05</v>
@@ -26302,7 +26311,7 @@
         <v>2.14</v>
       </c>
       <c r="AP122">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
         <v>1.82</v>
@@ -26511,7 +26520,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR123">
         <v>1.46</v>
@@ -26636,7 +26645,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26842,7 +26851,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27048,7 +27057,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27460,7 +27469,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27541,7 +27550,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ128">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR128">
         <v>1.28</v>
@@ -27666,7 +27675,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27747,7 +27756,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ129">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR129">
         <v>1.62</v>
@@ -28078,7 +28087,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28696,7 +28705,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29108,7 +29117,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29186,7 +29195,7 @@
         <v>2</v>
       </c>
       <c r="AP136">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ136">
         <v>1.82</v>
@@ -29598,7 +29607,7 @@
         <v>1.43</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ138">
         <v>1.36</v>
@@ -29726,7 +29735,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29932,7 +29941,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30010,10 +30019,10 @@
         <v>0.88</v>
       </c>
       <c r="AP140">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ140">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR140">
         <v>1.53</v>
@@ -30138,7 +30147,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30219,7 +30228,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR141">
         <v>1.19</v>
@@ -30344,7 +30353,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30422,7 +30431,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ142">
         <v>1.27</v>
@@ -30550,7 +30559,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30628,7 +30637,7 @@
         <v>2.38</v>
       </c>
       <c r="AP143">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ143">
         <v>2.09</v>
@@ -31168,7 +31177,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31374,7 +31383,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31580,7 +31589,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31786,7 +31795,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32198,7 +32207,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32279,7 +32288,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ151">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR151">
         <v>1.68</v>
@@ -32404,7 +32413,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32482,7 +32491,7 @@
         <v>3</v>
       </c>
       <c r="AP152">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ152">
         <v>3</v>
@@ -32610,7 +32619,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32691,7 +32700,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ153">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR153">
         <v>1.01</v>
@@ -32897,7 +32906,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33022,7 +33031,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33306,7 +33315,7 @@
         <v>2.11</v>
       </c>
       <c r="AP156">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ156">
         <v>2.09</v>
@@ -33512,7 +33521,7 @@
         <v>0.44</v>
       </c>
       <c r="AP157">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AQ157">
         <v>0.64</v>
@@ -33640,7 +33649,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33846,7 +33855,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33924,10 +33933,10 @@
         <v>0.78</v>
       </c>
       <c r="AP159">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR159">
         <v>1.07</v>
@@ -34052,7 +34061,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34130,7 +34139,7 @@
         <v>1.38</v>
       </c>
       <c r="AP160">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ160">
         <v>1.36</v>
@@ -34258,7 +34267,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34876,7 +34885,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35082,7 +35091,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35494,7 +35503,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36112,7 +36121,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36411,31 +36420,31 @@
         <v>2.62</v>
       </c>
       <c r="AU171">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV171">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW171">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX171">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY171">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AZ171">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BA171">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB171">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC171">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD171">
         <v>0</v>
@@ -36887,6 +36896,830 @@
       </c>
       <c r="BP173">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7453848</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45697.41666666666</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>78</v>
+      </c>
+      <c r="H174" t="s">
+        <v>75</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174" t="s">
+        <v>87</v>
+      </c>
+      <c r="P174" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q174">
+        <v>3.4</v>
+      </c>
+      <c r="R174">
+        <v>2.1</v>
+      </c>
+      <c r="S174">
+        <v>3</v>
+      </c>
+      <c r="T174">
+        <v>1.4</v>
+      </c>
+      <c r="U174">
+        <v>2.75</v>
+      </c>
+      <c r="V174">
+        <v>3</v>
+      </c>
+      <c r="W174">
+        <v>1.36</v>
+      </c>
+      <c r="X174">
+        <v>7</v>
+      </c>
+      <c r="Y174">
+        <v>1.08</v>
+      </c>
+      <c r="Z174">
+        <v>4.5</v>
+      </c>
+      <c r="AA174">
+        <v>3.51</v>
+      </c>
+      <c r="AB174">
+        <v>1.78</v>
+      </c>
+      <c r="AC174">
+        <v>1.05</v>
+      </c>
+      <c r="AD174">
+        <v>8.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.29</v>
+      </c>
+      <c r="AF174">
+        <v>3.4</v>
+      </c>
+      <c r="AG174">
+        <v>1.98</v>
+      </c>
+      <c r="AH174">
+        <v>1.77</v>
+      </c>
+      <c r="AI174">
+        <v>1.73</v>
+      </c>
+      <c r="AJ174">
+        <v>2</v>
+      </c>
+      <c r="AK174">
+        <v>1.54</v>
+      </c>
+      <c r="AL174">
+        <v>1.29</v>
+      </c>
+      <c r="AM174">
+        <v>1.38</v>
+      </c>
+      <c r="AN174">
+        <v>0.7</v>
+      </c>
+      <c r="AO174">
+        <v>1.1</v>
+      </c>
+      <c r="AP174">
+        <v>0.64</v>
+      </c>
+      <c r="AQ174">
+        <v>1.27</v>
+      </c>
+      <c r="AR174">
+        <v>1.18</v>
+      </c>
+      <c r="AS174">
+        <v>1.32</v>
+      </c>
+      <c r="AT174">
+        <v>2.5</v>
+      </c>
+      <c r="AU174">
+        <v>4</v>
+      </c>
+      <c r="AV174">
+        <v>4</v>
+      </c>
+      <c r="AW174">
+        <v>2</v>
+      </c>
+      <c r="AX174">
+        <v>9</v>
+      </c>
+      <c r="AY174">
+        <v>6</v>
+      </c>
+      <c r="AZ174">
+        <v>15</v>
+      </c>
+      <c r="BA174">
+        <v>6</v>
+      </c>
+      <c r="BB174">
+        <v>4</v>
+      </c>
+      <c r="BC174">
+        <v>10</v>
+      </c>
+      <c r="BD174">
+        <v>2.05</v>
+      </c>
+      <c r="BE174">
+        <v>7.5</v>
+      </c>
+      <c r="BF174">
+        <v>2</v>
+      </c>
+      <c r="BG174">
+        <v>1.37</v>
+      </c>
+      <c r="BH174">
+        <v>2.66</v>
+      </c>
+      <c r="BI174">
+        <v>1.7</v>
+      </c>
+      <c r="BJ174">
+        <v>1.98</v>
+      </c>
+      <c r="BK174">
+        <v>2.15</v>
+      </c>
+      <c r="BL174">
+        <v>1.56</v>
+      </c>
+      <c r="BM174">
+        <v>2.92</v>
+      </c>
+      <c r="BN174">
+        <v>1.31</v>
+      </c>
+      <c r="BO174">
+        <v>3.9</v>
+      </c>
+      <c r="BP174">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7453852</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45697.5</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>82</v>
+      </c>
+      <c r="H175" t="s">
+        <v>71</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>87</v>
+      </c>
+      <c r="P175" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q175">
+        <v>2.38</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>4.5</v>
+      </c>
+      <c r="T175">
+        <v>1.4</v>
+      </c>
+      <c r="U175">
+        <v>2.75</v>
+      </c>
+      <c r="V175">
+        <v>3</v>
+      </c>
+      <c r="W175">
+        <v>1.36</v>
+      </c>
+      <c r="X175">
+        <v>7</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>1.85</v>
+      </c>
+      <c r="AA175">
+        <v>3.5</v>
+      </c>
+      <c r="AB175">
+        <v>4.1</v>
+      </c>
+      <c r="AC175">
+        <v>1.05</v>
+      </c>
+      <c r="AD175">
+        <v>8.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.3</v>
+      </c>
+      <c r="AF175">
+        <v>3.3</v>
+      </c>
+      <c r="AG175">
+        <v>1.98</v>
+      </c>
+      <c r="AH175">
+        <v>1.77</v>
+      </c>
+      <c r="AI175">
+        <v>1.83</v>
+      </c>
+      <c r="AJ175">
+        <v>1.83</v>
+      </c>
+      <c r="AK175">
+        <v>1.14</v>
+      </c>
+      <c r="AL175">
+        <v>1.22</v>
+      </c>
+      <c r="AM175">
+        <v>2.05</v>
+      </c>
+      <c r="AN175">
+        <v>1.3</v>
+      </c>
+      <c r="AO175">
+        <v>1</v>
+      </c>
+      <c r="AP175">
+        <v>1.18</v>
+      </c>
+      <c r="AQ175">
+        <v>1.18</v>
+      </c>
+      <c r="AR175">
+        <v>1.51</v>
+      </c>
+      <c r="AS175">
+        <v>1.03</v>
+      </c>
+      <c r="AT175">
+        <v>2.54</v>
+      </c>
+      <c r="AU175">
+        <v>11</v>
+      </c>
+      <c r="AV175">
+        <v>9</v>
+      </c>
+      <c r="AW175">
+        <v>5</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>16</v>
+      </c>
+      <c r="AZ175">
+        <v>15</v>
+      </c>
+      <c r="BA175">
+        <v>6</v>
+      </c>
+      <c r="BB175">
+        <v>4</v>
+      </c>
+      <c r="BC175">
+        <v>10</v>
+      </c>
+      <c r="BD175">
+        <v>1.51</v>
+      </c>
+      <c r="BE175">
+        <v>8.5</v>
+      </c>
+      <c r="BF175">
+        <v>3.16</v>
+      </c>
+      <c r="BG175">
+        <v>1.36</v>
+      </c>
+      <c r="BH175">
+        <v>2.7</v>
+      </c>
+      <c r="BI175">
+        <v>1.69</v>
+      </c>
+      <c r="BJ175">
+        <v>2</v>
+      </c>
+      <c r="BK175">
+        <v>2.14</v>
+      </c>
+      <c r="BL175">
+        <v>1.57</v>
+      </c>
+      <c r="BM175">
+        <v>2.88</v>
+      </c>
+      <c r="BN175">
+        <v>1.32</v>
+      </c>
+      <c r="BO175">
+        <v>3.88</v>
+      </c>
+      <c r="BP175">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7453855</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45697.58333333334</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>84</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>3</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>205</v>
+      </c>
+      <c r="P176" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q176">
+        <v>2.5</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>4.33</v>
+      </c>
+      <c r="T176">
+        <v>1.4</v>
+      </c>
+      <c r="U176">
+        <v>2.75</v>
+      </c>
+      <c r="V176">
+        <v>2.75</v>
+      </c>
+      <c r="W176">
+        <v>1.4</v>
+      </c>
+      <c r="X176">
+        <v>7</v>
+      </c>
+      <c r="Y176">
+        <v>1.08</v>
+      </c>
+      <c r="Z176">
+        <v>1.97</v>
+      </c>
+      <c r="AA176">
+        <v>3.41</v>
+      </c>
+      <c r="AB176">
+        <v>3.71</v>
+      </c>
+      <c r="AC176">
+        <v>1.05</v>
+      </c>
+      <c r="AD176">
+        <v>8.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.3</v>
+      </c>
+      <c r="AF176">
+        <v>3.3</v>
+      </c>
+      <c r="AG176">
+        <v>1.95</v>
+      </c>
+      <c r="AH176">
+        <v>1.77</v>
+      </c>
+      <c r="AI176">
+        <v>1.8</v>
+      </c>
+      <c r="AJ176">
+        <v>1.91</v>
+      </c>
+      <c r="AK176">
+        <v>1.18</v>
+      </c>
+      <c r="AL176">
+        <v>1.25</v>
+      </c>
+      <c r="AM176">
+        <v>1.9</v>
+      </c>
+      <c r="AN176">
+        <v>1.8</v>
+      </c>
+      <c r="AO176">
+        <v>0.8</v>
+      </c>
+      <c r="AP176">
+        <v>1.91</v>
+      </c>
+      <c r="AQ176">
+        <v>0.73</v>
+      </c>
+      <c r="AR176">
+        <v>1.74</v>
+      </c>
+      <c r="AS176">
+        <v>1.47</v>
+      </c>
+      <c r="AT176">
+        <v>3.21</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>4</v>
+      </c>
+      <c r="AW176">
+        <v>9</v>
+      </c>
+      <c r="AX176">
+        <v>4</v>
+      </c>
+      <c r="AY176">
+        <v>17</v>
+      </c>
+      <c r="AZ176">
+        <v>8</v>
+      </c>
+      <c r="BA176">
+        <v>5</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>8</v>
+      </c>
+      <c r="BD176">
+        <v>1.69</v>
+      </c>
+      <c r="BE176">
+        <v>8</v>
+      </c>
+      <c r="BF176">
+        <v>2.62</v>
+      </c>
+      <c r="BG176">
+        <v>1.3</v>
+      </c>
+      <c r="BH176">
+        <v>2.97</v>
+      </c>
+      <c r="BI176">
+        <v>1.56</v>
+      </c>
+      <c r="BJ176">
+        <v>2.16</v>
+      </c>
+      <c r="BK176">
+        <v>1.98</v>
+      </c>
+      <c r="BL176">
+        <v>1.7</v>
+      </c>
+      <c r="BM176">
+        <v>2.59</v>
+      </c>
+      <c r="BN176">
+        <v>1.39</v>
+      </c>
+      <c r="BO176">
+        <v>3.58</v>
+      </c>
+      <c r="BP176">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7453854</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F177">
+        <v>22</v>
+      </c>
+      <c r="G177" t="s">
+        <v>81</v>
+      </c>
+      <c r="H177" t="s">
+        <v>79</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177" t="s">
+        <v>87</v>
+      </c>
+      <c r="P177" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q177">
+        <v>3.1</v>
+      </c>
+      <c r="R177">
+        <v>2.05</v>
+      </c>
+      <c r="S177">
+        <v>3.4</v>
+      </c>
+      <c r="T177">
+        <v>1.44</v>
+      </c>
+      <c r="U177">
+        <v>2.63</v>
+      </c>
+      <c r="V177">
+        <v>3.25</v>
+      </c>
+      <c r="W177">
+        <v>1.33</v>
+      </c>
+      <c r="X177">
+        <v>7.5</v>
+      </c>
+      <c r="Y177">
+        <v>1.07</v>
+      </c>
+      <c r="Z177">
+        <v>2.75</v>
+      </c>
+      <c r="AA177">
+        <v>2.89</v>
+      </c>
+      <c r="AB177">
+        <v>2.78</v>
+      </c>
+      <c r="AC177">
+        <v>1.06</v>
+      </c>
+      <c r="AD177">
+        <v>8</v>
+      </c>
+      <c r="AE177">
+        <v>1.5</v>
+      </c>
+      <c r="AF177">
+        <v>2.4</v>
+      </c>
+      <c r="AG177">
+        <v>2.37</v>
+      </c>
+      <c r="AH177">
+        <v>1.48</v>
+      </c>
+      <c r="AI177">
+        <v>1.83</v>
+      </c>
+      <c r="AJ177">
+        <v>1.83</v>
+      </c>
+      <c r="AK177">
+        <v>1.39</v>
+      </c>
+      <c r="AL177">
+        <v>1.31</v>
+      </c>
+      <c r="AM177">
+        <v>1.5</v>
+      </c>
+      <c r="AN177">
+        <v>1.5</v>
+      </c>
+      <c r="AO177">
+        <v>1.3</v>
+      </c>
+      <c r="AP177">
+        <v>1.45</v>
+      </c>
+      <c r="AQ177">
+        <v>1.27</v>
+      </c>
+      <c r="AR177">
+        <v>1.08</v>
+      </c>
+      <c r="AS177">
+        <v>1.16</v>
+      </c>
+      <c r="AT177">
+        <v>2.24</v>
+      </c>
+      <c r="AU177">
+        <v>2</v>
+      </c>
+      <c r="AV177">
+        <v>3</v>
+      </c>
+      <c r="AW177">
+        <v>2</v>
+      </c>
+      <c r="AX177">
+        <v>1</v>
+      </c>
+      <c r="AY177">
+        <v>5</v>
+      </c>
+      <c r="AZ177">
+        <v>5</v>
+      </c>
+      <c r="BA177">
+        <v>1</v>
+      </c>
+      <c r="BB177">
+        <v>6</v>
+      </c>
+      <c r="BC177">
+        <v>7</v>
+      </c>
+      <c r="BD177">
+        <v>1.95</v>
+      </c>
+      <c r="BE177">
+        <v>7.5</v>
+      </c>
+      <c r="BF177">
+        <v>2.1</v>
+      </c>
+      <c r="BG177">
+        <v>1.4</v>
+      </c>
+      <c r="BH177">
+        <v>2.56</v>
+      </c>
+      <c r="BI177">
+        <v>1.8</v>
+      </c>
+      <c r="BJ177">
+        <v>2</v>
+      </c>
+      <c r="BK177">
+        <v>2.24</v>
+      </c>
+      <c r="BL177">
+        <v>1.52</v>
+      </c>
+      <c r="BM177">
+        <v>3.05</v>
+      </c>
+      <c r="BN177">
+        <v>1.28</v>
+      </c>
+      <c r="BO177">
+        <v>4.15</v>
+      </c>
+      <c r="BP177">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,12 @@
     <t>['66', '83', '90+6']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>['3', '16', '36', '76']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -722,9 +728,6 @@
   </si>
   <si>
     <t>['13', '18', '53', '59']</t>
-  </si>
-  <si>
-    <t>['18']</t>
   </si>
   <si>
     <t>['65', '83']</t>
@@ -896,6 +899,12 @@
   </si>
   <si>
     <t>['76', '80']</t>
+  </si>
+  <si>
+    <t>['75', '90+4']</t>
+  </si>
+  <si>
+    <t>['11', '31', '60', '65']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1522,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1797,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3">
         <v>2.09</v>
@@ -2131,7 +2140,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2212,7 +2221,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ5">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2543,7 +2552,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2624,7 +2633,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2749,7 +2758,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3161,7 +3170,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3367,7 +3376,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3573,7 +3582,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4397,7 +4406,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4475,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
         <v>0.73</v>
@@ -4684,7 +4693,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -5015,7 +5024,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5302,7 +5311,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ20">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5505,7 +5514,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ21">
         <v>1.27</v>
@@ -6045,7 +6054,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6663,7 +6672,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6869,7 +6878,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7359,7 +7368,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
         <v>2.09</v>
@@ -7487,7 +7496,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7693,7 +7702,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7980,7 +7989,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ33">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR33">
         <v>1.82</v>
@@ -8105,7 +8114,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8595,10 +8604,10 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR36">
         <v>1.22</v>
@@ -8929,7 +8938,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9547,7 +9556,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9753,7 +9762,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9959,7 +9968,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10165,7 +10174,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10371,7 +10380,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10449,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ45">
         <v>0.73</v>
@@ -10989,7 +10998,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11067,10 +11076,10 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ48">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR48">
         <v>1.07</v>
@@ -11276,7 +11285,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ49">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.36</v>
@@ -11401,7 +11410,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11607,7 +11616,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11891,7 +11900,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52">
         <v>1.73</v>
@@ -12431,7 +12440,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12843,7 +12852,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13049,7 +13058,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13255,7 +13264,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13461,7 +13470,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13667,7 +13676,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13745,7 +13754,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -13873,7 +13882,7 @@
         <v>133</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="Q62">
         <v>1.62</v>
@@ -14079,7 +14088,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14285,7 +14294,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14363,7 +14372,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
         <v>1.82</v>
@@ -14491,7 +14500,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14569,7 +14578,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65">
         <v>1.73</v>
@@ -14697,7 +14706,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14778,7 +14787,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -14984,7 +14993,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ67">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.33</v>
@@ -15315,7 +15324,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15393,7 +15402,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69">
         <v>3</v>
@@ -15727,7 +15736,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15933,7 +15942,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16345,7 +16354,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16757,7 +16766,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17044,7 +17053,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ77">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR77">
         <v>0.96</v>
@@ -17169,7 +17178,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17375,7 +17384,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17456,7 +17465,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ79">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR79">
         <v>1.64</v>
@@ -17787,7 +17796,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17993,7 +18002,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18071,7 +18080,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ82">
         <v>0.64</v>
@@ -18199,7 +18208,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18277,7 +18286,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83">
         <v>1.27</v>
@@ -18405,7 +18414,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18483,7 +18492,7 @@
         <v>3</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ84">
         <v>3</v>
@@ -18611,7 +18620,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19023,7 +19032,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19435,7 +19444,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19722,7 +19731,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19847,7 +19856,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20465,7 +20474,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20749,7 +20758,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ95">
         <v>0.64</v>
@@ -21161,7 +21170,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>1.27</v>
@@ -21495,7 +21504,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21701,7 +21710,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21782,7 +21791,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ100">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR100">
         <v>1.66</v>
@@ -21907,7 +21916,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -21985,7 +21994,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ101">
         <v>1.36</v>
@@ -22113,7 +22122,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22319,7 +22328,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23143,7 +23152,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23430,7 +23439,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR108">
         <v>0.6899999999999999</v>
@@ -23555,7 +23564,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23636,7 +23645,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ109">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR109">
         <v>1.11</v>
@@ -23967,7 +23976,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24173,7 +24182,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24251,7 +24260,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ112">
         <v>1.27</v>
@@ -24869,7 +24878,7 @@
         <v>0.14</v>
       </c>
       <c r="AP115">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ115">
         <v>0.09</v>
@@ -24997,7 +25006,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25075,7 +25084,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ116">
         <v>1.27</v>
@@ -25203,7 +25212,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25409,7 +25418,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25615,7 +25624,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25821,7 +25830,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26517,7 +26526,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ123">
         <v>1.18</v>
@@ -26645,7 +26654,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26851,7 +26860,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27057,7 +27066,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27138,7 +27147,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ126">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR126">
         <v>1.56</v>
@@ -27344,7 +27353,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ127">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27469,7 +27478,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27547,7 +27556,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ128">
         <v>1.27</v>
@@ -27675,7 +27684,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27959,7 +27968,7 @@
         <v>0.13</v>
       </c>
       <c r="AP130">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ130">
         <v>0.09</v>
@@ -28087,7 +28096,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28577,7 +28586,7 @@
         <v>0.88</v>
       </c>
       <c r="AP133">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ133">
         <v>0.73</v>
@@ -28705,7 +28714,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29117,7 +29126,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29735,7 +29744,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29941,7 +29950,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30147,7 +30156,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30225,7 +30234,7 @@
         <v>0.88</v>
       </c>
       <c r="AP141">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ141">
         <v>1.18</v>
@@ -30353,7 +30362,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30559,7 +30568,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31177,7 +31186,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31255,7 +31264,7 @@
         <v>0.78</v>
       </c>
       <c r="AP146">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ146">
         <v>0.73</v>
@@ -31383,7 +31392,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31464,7 +31473,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ147">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31589,7 +31598,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31795,7 +31804,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32082,7 +32091,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ150">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR150">
         <v>1.62</v>
@@ -32207,7 +32216,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32285,7 +32294,7 @@
         <v>0.78</v>
       </c>
       <c r="AP151">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ151">
         <v>0.73</v>
@@ -32413,7 +32422,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32619,7 +32628,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32903,7 +32912,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ154">
         <v>1.27</v>
@@ -33031,7 +33040,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33649,7 +33658,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33855,7 +33864,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34061,7 +34070,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34267,7 +34276,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34345,7 +34354,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ161">
         <v>1.36</v>
@@ -34551,7 +34560,7 @@
         <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ162">
         <v>1.73</v>
@@ -34885,7 +34894,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35091,7 +35100,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35169,10 +35178,10 @@
         <v>0.6</v>
       </c>
       <c r="AP165">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ165">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR165">
         <v>1.65</v>
@@ -35375,7 +35384,7 @@
         <v>0.1</v>
       </c>
       <c r="AP166">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ166">
         <v>0.09</v>
@@ -35503,7 +35512,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35996,7 +36005,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ169">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR169">
         <v>1.61</v>
@@ -36121,7 +36130,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36945,7 +36954,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37151,7 +37160,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37720,6 +37729,624 @@
       </c>
       <c r="BP177">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7453857</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45703.375</v>
+      </c>
+      <c r="F178">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>84</v>
+      </c>
+      <c r="H178" t="s">
+        <v>81</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>2</v>
+      </c>
+      <c r="N178">
+        <v>3</v>
+      </c>
+      <c r="O178" t="s">
+        <v>206</v>
+      </c>
+      <c r="P178" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q178">
+        <v>2.75</v>
+      </c>
+      <c r="R178">
+        <v>2.1</v>
+      </c>
+      <c r="S178">
+        <v>3.6</v>
+      </c>
+      <c r="T178">
+        <v>1.4</v>
+      </c>
+      <c r="U178">
+        <v>2.75</v>
+      </c>
+      <c r="V178">
+        <v>2.75</v>
+      </c>
+      <c r="W178">
+        <v>1.4</v>
+      </c>
+      <c r="X178">
+        <v>7</v>
+      </c>
+      <c r="Y178">
+        <v>1.08</v>
+      </c>
+      <c r="Z178">
+        <v>1.86</v>
+      </c>
+      <c r="AA178">
+        <v>3.45</v>
+      </c>
+      <c r="AB178">
+        <v>4.1</v>
+      </c>
+      <c r="AC178">
+        <v>1.02</v>
+      </c>
+      <c r="AD178">
+        <v>11</v>
+      </c>
+      <c r="AE178">
+        <v>1.29</v>
+      </c>
+      <c r="AF178">
+        <v>3.5</v>
+      </c>
+      <c r="AG178">
+        <v>2.05</v>
+      </c>
+      <c r="AH178">
+        <v>1.61</v>
+      </c>
+      <c r="AI178">
+        <v>1.73</v>
+      </c>
+      <c r="AJ178">
+        <v>2</v>
+      </c>
+      <c r="AK178">
+        <v>1.31</v>
+      </c>
+      <c r="AL178">
+        <v>1.31</v>
+      </c>
+      <c r="AM178">
+        <v>1.53</v>
+      </c>
+      <c r="AN178">
+        <v>1.36</v>
+      </c>
+      <c r="AO178">
+        <v>0.64</v>
+      </c>
+      <c r="AP178">
+        <v>1.25</v>
+      </c>
+      <c r="AQ178">
+        <v>0.83</v>
+      </c>
+      <c r="AR178">
+        <v>1.43</v>
+      </c>
+      <c r="AS178">
+        <v>1.38</v>
+      </c>
+      <c r="AT178">
+        <v>2.81</v>
+      </c>
+      <c r="AU178">
+        <v>6</v>
+      </c>
+      <c r="AV178">
+        <v>4</v>
+      </c>
+      <c r="AW178">
+        <v>14</v>
+      </c>
+      <c r="AX178">
+        <v>3</v>
+      </c>
+      <c r="AY178">
+        <v>21</v>
+      </c>
+      <c r="AZ178">
+        <v>7</v>
+      </c>
+      <c r="BA178">
+        <v>2</v>
+      </c>
+      <c r="BB178">
+        <v>5</v>
+      </c>
+      <c r="BC178">
+        <v>7</v>
+      </c>
+      <c r="BD178">
+        <v>1.64</v>
+      </c>
+      <c r="BE178">
+        <v>8</v>
+      </c>
+      <c r="BF178">
+        <v>2.77</v>
+      </c>
+      <c r="BG178">
+        <v>1.43</v>
+      </c>
+      <c r="BH178">
+        <v>2.63</v>
+      </c>
+      <c r="BI178">
+        <v>1.74</v>
+      </c>
+      <c r="BJ178">
+        <v>2.02</v>
+      </c>
+      <c r="BK178">
+        <v>2.22</v>
+      </c>
+      <c r="BL178">
+        <v>1.62</v>
+      </c>
+      <c r="BM178">
+        <v>2.85</v>
+      </c>
+      <c r="BN178">
+        <v>1.37</v>
+      </c>
+      <c r="BO178">
+        <v>3.9</v>
+      </c>
+      <c r="BP178">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7453859</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F179">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>83</v>
+      </c>
+      <c r="H179" t="s">
+        <v>82</v>
+      </c>
+      <c r="I179">
+        <v>3</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>3</v>
+      </c>
+      <c r="L179">
+        <v>4</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>5</v>
+      </c>
+      <c r="O179" t="s">
+        <v>207</v>
+      </c>
+      <c r="P179" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q179">
+        <v>2.2</v>
+      </c>
+      <c r="R179">
+        <v>2.25</v>
+      </c>
+      <c r="S179">
+        <v>4.75</v>
+      </c>
+      <c r="T179">
+        <v>1.36</v>
+      </c>
+      <c r="U179">
+        <v>3</v>
+      </c>
+      <c r="V179">
+        <v>2.63</v>
+      </c>
+      <c r="W179">
+        <v>1.44</v>
+      </c>
+      <c r="X179">
+        <v>6.5</v>
+      </c>
+      <c r="Y179">
+        <v>1.1</v>
+      </c>
+      <c r="Z179">
+        <v>1.7</v>
+      </c>
+      <c r="AA179">
+        <v>3.78</v>
+      </c>
+      <c r="AB179">
+        <v>4.6</v>
+      </c>
+      <c r="AC179">
+        <v>1.04</v>
+      </c>
+      <c r="AD179">
+        <v>9</v>
+      </c>
+      <c r="AE179">
+        <v>1.26</v>
+      </c>
+      <c r="AF179">
+        <v>3.6</v>
+      </c>
+      <c r="AG179">
+        <v>1.8</v>
+      </c>
+      <c r="AH179">
+        <v>1.94</v>
+      </c>
+      <c r="AI179">
+        <v>1.8</v>
+      </c>
+      <c r="AJ179">
+        <v>1.91</v>
+      </c>
+      <c r="AK179">
+        <v>1.17</v>
+      </c>
+      <c r="AL179">
+        <v>1.23</v>
+      </c>
+      <c r="AM179">
+        <v>2.07</v>
+      </c>
+      <c r="AN179">
+        <v>1.82</v>
+      </c>
+      <c r="AO179">
+        <v>1.82</v>
+      </c>
+      <c r="AP179">
+        <v>1.92</v>
+      </c>
+      <c r="AQ179">
+        <v>1.67</v>
+      </c>
+      <c r="AR179">
+        <v>1.67</v>
+      </c>
+      <c r="AS179">
+        <v>1.44</v>
+      </c>
+      <c r="AT179">
+        <v>3.11</v>
+      </c>
+      <c r="AU179">
+        <v>10</v>
+      </c>
+      <c r="AV179">
+        <v>5</v>
+      </c>
+      <c r="AW179">
+        <v>6</v>
+      </c>
+      <c r="AX179">
+        <v>4</v>
+      </c>
+      <c r="AY179">
+        <v>16</v>
+      </c>
+      <c r="AZ179">
+        <v>9</v>
+      </c>
+      <c r="BA179">
+        <v>6</v>
+      </c>
+      <c r="BB179">
+        <v>1</v>
+      </c>
+      <c r="BC179">
+        <v>7</v>
+      </c>
+      <c r="BD179">
+        <v>1.51</v>
+      </c>
+      <c r="BE179">
+        <v>8.5</v>
+      </c>
+      <c r="BF179">
+        <v>3.16</v>
+      </c>
+      <c r="BG179">
+        <v>1.39</v>
+      </c>
+      <c r="BH179">
+        <v>2.77</v>
+      </c>
+      <c r="BI179">
+        <v>1.68</v>
+      </c>
+      <c r="BJ179">
+        <v>2.12</v>
+      </c>
+      <c r="BK179">
+        <v>2.11</v>
+      </c>
+      <c r="BL179">
+        <v>1.68</v>
+      </c>
+      <c r="BM179">
+        <v>2.7</v>
+      </c>
+      <c r="BN179">
+        <v>1.41</v>
+      </c>
+      <c r="BO179">
+        <v>3.65</v>
+      </c>
+      <c r="BP179">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7453860</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F180">
+        <v>23</v>
+      </c>
+      <c r="G180" t="s">
+        <v>71</v>
+      </c>
+      <c r="H180" t="s">
+        <v>72</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180">
+        <v>2</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>4</v>
+      </c>
+      <c r="N180">
+        <v>4</v>
+      </c>
+      <c r="O180" t="s">
+        <v>87</v>
+      </c>
+      <c r="P180" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q180">
+        <v>13</v>
+      </c>
+      <c r="R180">
+        <v>2.75</v>
+      </c>
+      <c r="S180">
+        <v>1.5</v>
+      </c>
+      <c r="T180">
+        <v>1.29</v>
+      </c>
+      <c r="U180">
+        <v>3.5</v>
+      </c>
+      <c r="V180">
+        <v>2.25</v>
+      </c>
+      <c r="W180">
+        <v>1.57</v>
+      </c>
+      <c r="X180">
+        <v>5</v>
+      </c>
+      <c r="Y180">
+        <v>1.14</v>
+      </c>
+      <c r="Z180">
+        <v>15</v>
+      </c>
+      <c r="AA180">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AB180">
+        <v>1.12</v>
+      </c>
+      <c r="AC180">
+        <v>1.01</v>
+      </c>
+      <c r="AD180">
+        <v>17</v>
+      </c>
+      <c r="AE180">
+        <v>1.18</v>
+      </c>
+      <c r="AF180">
+        <v>4.5</v>
+      </c>
+      <c r="AG180">
+        <v>1.45</v>
+      </c>
+      <c r="AH180">
+        <v>2.56</v>
+      </c>
+      <c r="AI180">
+        <v>2.63</v>
+      </c>
+      <c r="AJ180">
+        <v>1.44</v>
+      </c>
+      <c r="AK180">
+        <v>6</v>
+      </c>
+      <c r="AL180">
+        <v>1.04</v>
+      </c>
+      <c r="AM180">
+        <v>1.01</v>
+      </c>
+      <c r="AN180">
+        <v>1.27</v>
+      </c>
+      <c r="AO180">
+        <v>3</v>
+      </c>
+      <c r="AP180">
+        <v>1.17</v>
+      </c>
+      <c r="AQ180">
+        <v>3</v>
+      </c>
+      <c r="AR180">
+        <v>1.34</v>
+      </c>
+      <c r="AS180">
+        <v>2.16</v>
+      </c>
+      <c r="AT180">
+        <v>3.5</v>
+      </c>
+      <c r="AU180">
+        <v>6</v>
+      </c>
+      <c r="AV180">
+        <v>10</v>
+      </c>
+      <c r="AW180">
+        <v>5</v>
+      </c>
+      <c r="AX180">
+        <v>13</v>
+      </c>
+      <c r="AY180">
+        <v>11</v>
+      </c>
+      <c r="AZ180">
+        <v>23</v>
+      </c>
+      <c r="BA180">
+        <v>2</v>
+      </c>
+      <c r="BB180">
+        <v>10</v>
+      </c>
+      <c r="BC180">
+        <v>12</v>
+      </c>
+      <c r="BD180">
+        <v>8.5</v>
+      </c>
+      <c r="BE180">
+        <v>13</v>
+      </c>
+      <c r="BF180">
+        <v>1.09</v>
+      </c>
+      <c r="BG180">
+        <v>1.43</v>
+      </c>
+      <c r="BH180">
+        <v>2.63</v>
+      </c>
+      <c r="BI180">
+        <v>1.74</v>
+      </c>
+      <c r="BJ180">
+        <v>2.02</v>
+      </c>
+      <c r="BK180">
+        <v>2.22</v>
+      </c>
+      <c r="BL180">
+        <v>1.62</v>
+      </c>
+      <c r="BM180">
+        <v>2.85</v>
+      </c>
+      <c r="BN180">
+        <v>1.37</v>
+      </c>
+      <c r="BO180">
+        <v>3.9</v>
+      </c>
+      <c r="BP180">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="299">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -904,7 +904,13 @@
     <t>['75', '90+4']</t>
   </si>
   <si>
-    <t>['11', '31', '60', '65']</t>
+    <t>['11', '31', '60', '64']</t>
+  </si>
+  <si>
+    <t>['6', '43', '51', '75']</t>
+  </si>
+  <si>
+    <t>['56', '74']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1600,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ2">
         <v>1.27</v>
@@ -2015,7 +2021,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ4">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3042,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
         <v>0.73</v>
@@ -3663,7 +3669,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ12">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
         <v>2.33</v>
@@ -3866,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>1.36</v>
@@ -4281,7 +4287,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ15">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4899,7 +4905,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ18">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5308,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
         <v>0.83</v>
@@ -5926,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23">
         <v>0.73</v>
@@ -6338,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
         <v>1.18</v>
@@ -6753,7 +6759,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ27">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -7986,7 +7992,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
         <v>1.67</v>
@@ -8195,7 +8201,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ34">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR34">
         <v>1.89</v>
@@ -8401,7 +8407,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ35">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -9016,7 +9022,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ38">
         <v>1.73</v>
@@ -9428,7 +9434,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ40">
         <v>1.27</v>
@@ -10667,7 +10673,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ46">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR46">
         <v>0.99</v>
@@ -10873,7 +10879,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR47">
         <v>1.89</v>
@@ -11488,10 +11494,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ50">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11694,7 +11700,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ51">
         <v>3</v>
@@ -13963,7 +13969,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ62">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -14166,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ63">
         <v>1.27</v>
@@ -14375,7 +14381,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR64">
         <v>1.12</v>
@@ -14784,7 +14790,7 @@
         <v>0.25</v>
       </c>
       <c r="AP66">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66">
         <v>0.83</v>
@@ -15196,10 +15202,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ68">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -17462,7 +17468,7 @@
         <v>2.6</v>
       </c>
       <c r="AP79">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ79">
         <v>1.67</v>
@@ -17668,7 +17674,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ80">
         <v>1.27</v>
@@ -17877,7 +17883,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ81">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR81">
         <v>1.32</v>
@@ -18083,7 +18089,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ82">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18904,10 +18910,10 @@
         <v>0.2</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ86">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -19522,7 +19528,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ89">
         <v>1.27</v>
@@ -20761,7 +20767,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ95">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR95">
         <v>1.17</v>
@@ -20964,10 +20970,10 @@
         <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ96">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -22200,10 +22206,10 @@
         <v>2.6</v>
       </c>
       <c r="AP102">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR102">
         <v>1.61</v>
@@ -22818,7 +22824,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ105">
         <v>1.18</v>
@@ -23230,7 +23236,7 @@
         <v>2.17</v>
       </c>
       <c r="AP107">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ107">
         <v>2.09</v>
@@ -24054,7 +24060,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ111">
         <v>1.27</v>
@@ -24469,7 +24475,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ113">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR113">
         <v>1.01</v>
@@ -24675,7 +24681,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ114">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24881,7 +24887,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ115">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -25702,7 +25708,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
         <v>1.27</v>
@@ -26117,7 +26123,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ121">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR121">
         <v>1.85</v>
@@ -26323,7 +26329,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR122">
         <v>1.45</v>
@@ -27762,7 +27768,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ129">
         <v>0.73</v>
@@ -27971,7 +27977,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ130">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28380,7 +28386,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ132">
         <v>0.73</v>
@@ -29001,7 +29007,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ135">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR135">
         <v>1.93</v>
@@ -29207,7 +29213,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR136">
         <v>1.2</v>
@@ -30440,7 +30446,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
         <v>1.27</v>
@@ -30855,7 +30861,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ144">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.18</v>
@@ -31061,7 +31067,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ145">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31882,7 +31888,7 @@
         <v>1.67</v>
       </c>
       <c r="AP149">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ149">
         <v>1.73</v>
@@ -32088,7 +32094,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ150">
         <v>0.83</v>
@@ -33324,7 +33330,7 @@
         <v>2.11</v>
       </c>
       <c r="AP156">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ156">
         <v>2.09</v>
@@ -33533,7 +33539,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ157">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR157">
         <v>1.13</v>
@@ -34769,7 +34775,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ163">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR163">
         <v>1.69</v>
@@ -34975,7 +34981,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ164">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR164">
         <v>1.67</v>
@@ -35387,7 +35393,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ166">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR166">
         <v>1.38</v>
@@ -35590,7 +35596,7 @@
         <v>3</v>
       </c>
       <c r="AP167">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
         <v>3</v>
@@ -36002,7 +36008,7 @@
         <v>2</v>
       </c>
       <c r="AP169">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ169">
         <v>1.67</v>
@@ -37444,7 +37450,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ176">
         <v>0.73</v>
@@ -38346,6 +38352,624 @@
         <v>3.9</v>
       </c>
       <c r="BP180">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7453861</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45704.375</v>
+      </c>
+      <c r="F181">
+        <v>23</v>
+      </c>
+      <c r="G181" t="s">
+        <v>70</v>
+      </c>
+      <c r="H181" t="s">
+        <v>73</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181" t="s">
+        <v>165</v>
+      </c>
+      <c r="P181" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q181">
+        <v>0</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+      <c r="S181">
+        <v>0</v>
+      </c>
+      <c r="T181">
+        <v>0</v>
+      </c>
+      <c r="U181">
+        <v>0</v>
+      </c>
+      <c r="V181">
+        <v>0</v>
+      </c>
+      <c r="W181">
+        <v>0</v>
+      </c>
+      <c r="X181">
+        <v>0</v>
+      </c>
+      <c r="Y181">
+        <v>0</v>
+      </c>
+      <c r="Z181">
+        <v>1.53</v>
+      </c>
+      <c r="AA181">
+        <v>3.55</v>
+      </c>
+      <c r="AB181">
+        <v>7.5</v>
+      </c>
+      <c r="AC181">
+        <v>0</v>
+      </c>
+      <c r="AD181">
+        <v>0</v>
+      </c>
+      <c r="AE181">
+        <v>0</v>
+      </c>
+      <c r="AF181">
+        <v>0</v>
+      </c>
+      <c r="AG181">
+        <v>1.87</v>
+      </c>
+      <c r="AH181">
+        <v>1.87</v>
+      </c>
+      <c r="AI181">
+        <v>0</v>
+      </c>
+      <c r="AJ181">
+        <v>0</v>
+      </c>
+      <c r="AK181">
+        <v>0</v>
+      </c>
+      <c r="AL181">
+        <v>0</v>
+      </c>
+      <c r="AM181">
+        <v>0</v>
+      </c>
+      <c r="AN181">
+        <v>1.82</v>
+      </c>
+      <c r="AO181">
+        <v>1.82</v>
+      </c>
+      <c r="AP181">
+        <v>1.92</v>
+      </c>
+      <c r="AQ181">
+        <v>1.67</v>
+      </c>
+      <c r="AR181">
+        <v>1.62</v>
+      </c>
+      <c r="AS181">
+        <v>0.72</v>
+      </c>
+      <c r="AT181">
+        <v>2.34</v>
+      </c>
+      <c r="AU181">
+        <v>-1</v>
+      </c>
+      <c r="AV181">
+        <v>-1</v>
+      </c>
+      <c r="AW181">
+        <v>-1</v>
+      </c>
+      <c r="AX181">
+        <v>-1</v>
+      </c>
+      <c r="AY181">
+        <v>-1</v>
+      </c>
+      <c r="AZ181">
+        <v>-1</v>
+      </c>
+      <c r="BA181">
+        <v>-1</v>
+      </c>
+      <c r="BB181">
+        <v>-1</v>
+      </c>
+      <c r="BC181">
+        <v>-1</v>
+      </c>
+      <c r="BD181">
+        <v>0</v>
+      </c>
+      <c r="BE181">
+        <v>0</v>
+      </c>
+      <c r="BF181">
+        <v>0</v>
+      </c>
+      <c r="BG181">
+        <v>0</v>
+      </c>
+      <c r="BH181">
+        <v>0</v>
+      </c>
+      <c r="BI181">
+        <v>0</v>
+      </c>
+      <c r="BJ181">
+        <v>0</v>
+      </c>
+      <c r="BK181">
+        <v>0</v>
+      </c>
+      <c r="BL181">
+        <v>0</v>
+      </c>
+      <c r="BM181">
+        <v>0</v>
+      </c>
+      <c r="BN181">
+        <v>0</v>
+      </c>
+      <c r="BO181">
+        <v>0</v>
+      </c>
+      <c r="BP181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7453856</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45704.41319444445</v>
+      </c>
+      <c r="F182">
+        <v>23</v>
+      </c>
+      <c r="G182" t="s">
+        <v>80</v>
+      </c>
+      <c r="H182" t="s">
+        <v>78</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>2</v>
+      </c>
+      <c r="K182">
+        <v>2</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>4</v>
+      </c>
+      <c r="N182">
+        <v>5</v>
+      </c>
+      <c r="O182" t="s">
+        <v>89</v>
+      </c>
+      <c r="P182" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q182">
+        <v>1.83</v>
+      </c>
+      <c r="R182">
+        <v>2.38</v>
+      </c>
+      <c r="S182">
+        <v>7.5</v>
+      </c>
+      <c r="T182">
+        <v>1.36</v>
+      </c>
+      <c r="U182">
+        <v>3</v>
+      </c>
+      <c r="V182">
+        <v>2.63</v>
+      </c>
+      <c r="W182">
+        <v>1.44</v>
+      </c>
+      <c r="X182">
+        <v>6.5</v>
+      </c>
+      <c r="Y182">
+        <v>1.1</v>
+      </c>
+      <c r="Z182">
+        <v>1.25</v>
+      </c>
+      <c r="AA182">
+        <v>5.5</v>
+      </c>
+      <c r="AB182">
+        <v>11</v>
+      </c>
+      <c r="AC182">
+        <v>1.01</v>
+      </c>
+      <c r="AD182">
+        <v>11</v>
+      </c>
+      <c r="AE182">
+        <v>1.24</v>
+      </c>
+      <c r="AF182">
+        <v>3.8</v>
+      </c>
+      <c r="AG182">
+        <v>1.83</v>
+      </c>
+      <c r="AH182">
+        <v>1.91</v>
+      </c>
+      <c r="AI182">
+        <v>2.1</v>
+      </c>
+      <c r="AJ182">
+        <v>1.67</v>
+      </c>
+      <c r="AK182">
+        <v>1.07</v>
+      </c>
+      <c r="AL182">
+        <v>1.14</v>
+      </c>
+      <c r="AM182">
+        <v>3.05</v>
+      </c>
+      <c r="AN182">
+        <v>1.91</v>
+      </c>
+      <c r="AO182">
+        <v>0.09</v>
+      </c>
+      <c r="AP182">
+        <v>1.75</v>
+      </c>
+      <c r="AQ182">
+        <v>0.33</v>
+      </c>
+      <c r="AR182">
+        <v>1.76</v>
+      </c>
+      <c r="AS182">
+        <v>1.06</v>
+      </c>
+      <c r="AT182">
+        <v>2.82</v>
+      </c>
+      <c r="AU182">
+        <v>3</v>
+      </c>
+      <c r="AV182">
+        <v>9</v>
+      </c>
+      <c r="AW182">
+        <v>11</v>
+      </c>
+      <c r="AX182">
+        <v>7</v>
+      </c>
+      <c r="AY182">
+        <v>14</v>
+      </c>
+      <c r="AZ182">
+        <v>16</v>
+      </c>
+      <c r="BA182">
+        <v>1</v>
+      </c>
+      <c r="BB182">
+        <v>5</v>
+      </c>
+      <c r="BC182">
+        <v>6</v>
+      </c>
+      <c r="BD182">
+        <v>1.11</v>
+      </c>
+      <c r="BE182">
+        <v>12</v>
+      </c>
+      <c r="BF182">
+        <v>7.5</v>
+      </c>
+      <c r="BG182">
+        <v>1.35</v>
+      </c>
+      <c r="BH182">
+        <v>2.74</v>
+      </c>
+      <c r="BI182">
+        <v>1.66</v>
+      </c>
+      <c r="BJ182">
+        <v>2.04</v>
+      </c>
+      <c r="BK182">
+        <v>2.07</v>
+      </c>
+      <c r="BL182">
+        <v>1.61</v>
+      </c>
+      <c r="BM182">
+        <v>2.74</v>
+      </c>
+      <c r="BN182">
+        <v>1.35</v>
+      </c>
+      <c r="BO182">
+        <v>3.72</v>
+      </c>
+      <c r="BP182">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7453862</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45704.54166666666</v>
+      </c>
+      <c r="F183">
+        <v>23</v>
+      </c>
+      <c r="G183" t="s">
+        <v>77</v>
+      </c>
+      <c r="H183" t="s">
+        <v>76</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>106</v>
+      </c>
+      <c r="P183" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q183">
+        <v>1.91</v>
+      </c>
+      <c r="R183">
+        <v>2.38</v>
+      </c>
+      <c r="S183">
+        <v>6.5</v>
+      </c>
+      <c r="T183">
+        <v>1.33</v>
+      </c>
+      <c r="U183">
+        <v>3.25</v>
+      </c>
+      <c r="V183">
+        <v>2.63</v>
+      </c>
+      <c r="W183">
+        <v>1.44</v>
+      </c>
+      <c r="X183">
+        <v>6</v>
+      </c>
+      <c r="Y183">
+        <v>1.11</v>
+      </c>
+      <c r="Z183">
+        <v>1.2</v>
+      </c>
+      <c r="AA183">
+        <v>6.2</v>
+      </c>
+      <c r="AB183">
+        <v>13</v>
+      </c>
+      <c r="AC183">
+        <v>1.01</v>
+      </c>
+      <c r="AD183">
+        <v>11</v>
+      </c>
+      <c r="AE183">
+        <v>1.18</v>
+      </c>
+      <c r="AF183">
+        <v>3.94</v>
+      </c>
+      <c r="AG183">
+        <v>1.47</v>
+      </c>
+      <c r="AH183">
+        <v>2.5</v>
+      </c>
+      <c r="AI183">
+        <v>2</v>
+      </c>
+      <c r="AJ183">
+        <v>1.73</v>
+      </c>
+      <c r="AK183">
+        <v>1.03</v>
+      </c>
+      <c r="AL183">
+        <v>1.13</v>
+      </c>
+      <c r="AM183">
+        <v>3.14</v>
+      </c>
+      <c r="AN183">
+        <v>1.18</v>
+      </c>
+      <c r="AO183">
+        <v>0.64</v>
+      </c>
+      <c r="AP183">
+        <v>1.08</v>
+      </c>
+      <c r="AQ183">
+        <v>0.83</v>
+      </c>
+      <c r="AR183">
+        <v>1.95</v>
+      </c>
+      <c r="AS183">
+        <v>1.04</v>
+      </c>
+      <c r="AT183">
+        <v>2.99</v>
+      </c>
+      <c r="AU183">
+        <v>7</v>
+      </c>
+      <c r="AV183">
+        <v>7</v>
+      </c>
+      <c r="AW183">
+        <v>10</v>
+      </c>
+      <c r="AX183">
+        <v>1</v>
+      </c>
+      <c r="AY183">
+        <v>17</v>
+      </c>
+      <c r="AZ183">
+        <v>8</v>
+      </c>
+      <c r="BA183">
+        <v>9</v>
+      </c>
+      <c r="BB183">
+        <v>4</v>
+      </c>
+      <c r="BC183">
+        <v>13</v>
+      </c>
+      <c r="BD183">
+        <v>1.19</v>
+      </c>
+      <c r="BE183">
+        <v>11</v>
+      </c>
+      <c r="BF183">
+        <v>6.09</v>
+      </c>
+      <c r="BG183">
+        <v>1.38</v>
+      </c>
+      <c r="BH183">
+        <v>2.62</v>
+      </c>
+      <c r="BI183">
+        <v>1.71</v>
+      </c>
+      <c r="BJ183">
+        <v>1.97</v>
+      </c>
+      <c r="BK183">
+        <v>2.15</v>
+      </c>
+      <c r="BL183">
+        <v>1.56</v>
+      </c>
+      <c r="BM183">
+        <v>2.88</v>
+      </c>
+      <c r="BN183">
+        <v>1.32</v>
+      </c>
+      <c r="BO183">
+        <v>3.9</v>
+      </c>
+      <c r="BP183">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -912,6 +912,9 @@
   <si>
     <t>['56', '74']</t>
   </si>
+  <si>
+    <t>['30']</t>
+  </si>
 </sst>
 </file>
 
@@ -1272,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2430,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
         <v>0.73</v>
@@ -2845,7 +2848,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ8">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3460,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ11">
         <v>1.18</v>
@@ -5726,10 +5729,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6965,7 +6968,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>2.33</v>
@@ -7786,7 +7789,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -8816,7 +8819,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>0.73</v>
@@ -9025,7 +9028,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>1.63</v>
@@ -9643,7 +9646,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -10670,7 +10673,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46">
         <v>0.83</v>
@@ -11288,7 +11291,7 @@
         <v>0.33</v>
       </c>
       <c r="AP49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -11909,7 +11912,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ52">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.32</v>
@@ -13966,7 +13969,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
         <v>0.33</v>
@@ -14175,7 +14178,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ63">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.81</v>
@@ -14587,7 +14590,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ65">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR65">
         <v>1.31</v>
@@ -14996,7 +14999,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ67">
         <v>1.67</v>
@@ -16026,7 +16029,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>1.36</v>
@@ -17265,7 +17268,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR78">
         <v>1.57</v>
@@ -17880,7 +17883,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ81">
         <v>1.67</v>
@@ -18295,7 +18298,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
         <v>1.12</v>
@@ -18707,7 +18710,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ85">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR85">
         <v>1.12</v>
@@ -19322,7 +19325,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ88">
         <v>1.18</v>
@@ -20149,7 +20152,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ92">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -21382,10 +21385,10 @@
         <v>0.6</v>
       </c>
       <c r="AP98">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ98">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -23033,7 +23036,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ106">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR106">
         <v>2.08</v>
@@ -23854,7 +23857,7 @@
         <v>1.29</v>
       </c>
       <c r="AP110">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ110">
         <v>1.27</v>
@@ -24063,7 +24066,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ111">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -25296,7 +25299,7 @@
         <v>1.8</v>
       </c>
       <c r="AP117">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ117">
         <v>1.36</v>
@@ -25917,7 +25920,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ120">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.05</v>
@@ -26738,7 +26741,7 @@
         <v>1.43</v>
       </c>
       <c r="AP124">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ124">
         <v>1.27</v>
@@ -26947,7 +26950,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ125">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27150,7 +27153,7 @@
         <v>0.38</v>
       </c>
       <c r="AP126">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ126">
         <v>0.83</v>
@@ -29828,7 +29831,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ139">
         <v>2.09</v>
@@ -30037,7 +30040,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ140">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR140">
         <v>1.53</v>
@@ -31064,7 +31067,7 @@
         <v>0.11</v>
       </c>
       <c r="AP145">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ145">
         <v>0.33</v>
@@ -31476,7 +31479,7 @@
         <v>1.89</v>
       </c>
       <c r="AP147">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147">
         <v>1.67</v>
@@ -31891,7 +31894,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ149">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR149">
         <v>2.02</v>
@@ -32715,7 +32718,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ153">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR153">
         <v>1.01</v>
@@ -34569,7 +34572,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ162">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR162">
         <v>1.35</v>
@@ -34772,7 +34775,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ163">
         <v>1.67</v>
@@ -35802,7 +35805,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ168">
         <v>0.73</v>
@@ -37041,7 +37044,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ174">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR174">
         <v>1.18</v>
@@ -38495,31 +38498,31 @@
         <v>2.34</v>
       </c>
       <c r="AU181">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV181">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW181">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AX181">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY181">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ181">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BA181">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB181">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC181">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD181">
         <v>0</v>
@@ -38971,6 +38974,418 @@
       </c>
       <c r="BP183">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7453863</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45705.45833333334</v>
+      </c>
+      <c r="F184">
+        <v>23</v>
+      </c>
+      <c r="G184" t="s">
+        <v>74</v>
+      </c>
+      <c r="H184" t="s">
+        <v>75</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>2</v>
+      </c>
+      <c r="O184" t="s">
+        <v>189</v>
+      </c>
+      <c r="P184" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q184">
+        <v>2.3</v>
+      </c>
+      <c r="R184">
+        <v>2.3</v>
+      </c>
+      <c r="S184">
+        <v>4.33</v>
+      </c>
+      <c r="T184">
+        <v>1.33</v>
+      </c>
+      <c r="U184">
+        <v>3.25</v>
+      </c>
+      <c r="V184">
+        <v>2.5</v>
+      </c>
+      <c r="W184">
+        <v>1.5</v>
+      </c>
+      <c r="X184">
+        <v>6</v>
+      </c>
+      <c r="Y184">
+        <v>1.11</v>
+      </c>
+      <c r="Z184">
+        <v>1.66</v>
+      </c>
+      <c r="AA184">
+        <v>3.59</v>
+      </c>
+      <c r="AB184">
+        <v>5.3</v>
+      </c>
+      <c r="AC184">
+        <v>1.06</v>
+      </c>
+      <c r="AD184">
+        <v>8</v>
+      </c>
+      <c r="AE184">
+        <v>1.31</v>
+      </c>
+      <c r="AF184">
+        <v>3.25</v>
+      </c>
+      <c r="AG184">
+        <v>1.94</v>
+      </c>
+      <c r="AH184">
+        <v>1.8</v>
+      </c>
+      <c r="AI184">
+        <v>1.67</v>
+      </c>
+      <c r="AJ184">
+        <v>2.1</v>
+      </c>
+      <c r="AK184">
+        <v>1.15</v>
+      </c>
+      <c r="AL184">
+        <v>1.24</v>
+      </c>
+      <c r="AM184">
+        <v>2.11</v>
+      </c>
+      <c r="AN184">
+        <v>1.55</v>
+      </c>
+      <c r="AO184">
+        <v>1.27</v>
+      </c>
+      <c r="AP184">
+        <v>1.5</v>
+      </c>
+      <c r="AQ184">
+        <v>1.25</v>
+      </c>
+      <c r="AR184">
+        <v>1.73</v>
+      </c>
+      <c r="AS184">
+        <v>1.34</v>
+      </c>
+      <c r="AT184">
+        <v>3.07</v>
+      </c>
+      <c r="AU184">
+        <v>3</v>
+      </c>
+      <c r="AV184">
+        <v>4</v>
+      </c>
+      <c r="AW184">
+        <v>8</v>
+      </c>
+      <c r="AX184">
+        <v>3</v>
+      </c>
+      <c r="AY184">
+        <v>11</v>
+      </c>
+      <c r="AZ184">
+        <v>7</v>
+      </c>
+      <c r="BA184">
+        <v>3</v>
+      </c>
+      <c r="BB184">
+        <v>6</v>
+      </c>
+      <c r="BC184">
+        <v>9</v>
+      </c>
+      <c r="BD184">
+        <v>1.37</v>
+      </c>
+      <c r="BE184">
+        <v>9</v>
+      </c>
+      <c r="BF184">
+        <v>3.83</v>
+      </c>
+      <c r="BG184">
+        <v>1.37</v>
+      </c>
+      <c r="BH184">
+        <v>2.66</v>
+      </c>
+      <c r="BI184">
+        <v>1.7</v>
+      </c>
+      <c r="BJ184">
+        <v>1.98</v>
+      </c>
+      <c r="BK184">
+        <v>2.15</v>
+      </c>
+      <c r="BL184">
+        <v>1.56</v>
+      </c>
+      <c r="BM184">
+        <v>2.92</v>
+      </c>
+      <c r="BN184">
+        <v>1.31</v>
+      </c>
+      <c r="BO184">
+        <v>3.9</v>
+      </c>
+      <c r="BP184">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7453858</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45705.54166666666</v>
+      </c>
+      <c r="F185">
+        <v>23</v>
+      </c>
+      <c r="G185" t="s">
+        <v>79</v>
+      </c>
+      <c r="H185" t="s">
+        <v>85</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>195</v>
+      </c>
+      <c r="P185" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q185">
+        <v>3.75</v>
+      </c>
+      <c r="R185">
+        <v>2.2</v>
+      </c>
+      <c r="S185">
+        <v>2.63</v>
+      </c>
+      <c r="T185">
+        <v>1.36</v>
+      </c>
+      <c r="U185">
+        <v>3</v>
+      </c>
+      <c r="V185">
+        <v>2.75</v>
+      </c>
+      <c r="W185">
+        <v>1.4</v>
+      </c>
+      <c r="X185">
+        <v>6.5</v>
+      </c>
+      <c r="Y185">
+        <v>1.1</v>
+      </c>
+      <c r="Z185">
+        <v>3.77</v>
+      </c>
+      <c r="AA185">
+        <v>3.04</v>
+      </c>
+      <c r="AB185">
+        <v>2.1</v>
+      </c>
+      <c r="AC185">
+        <v>1.09</v>
+      </c>
+      <c r="AD185">
+        <v>6.5</v>
+      </c>
+      <c r="AE185">
+        <v>1.43</v>
+      </c>
+      <c r="AF185">
+        <v>2.7</v>
+      </c>
+      <c r="AG185">
+        <v>2.3</v>
+      </c>
+      <c r="AH185">
+        <v>1.5</v>
+      </c>
+      <c r="AI185">
+        <v>1.73</v>
+      </c>
+      <c r="AJ185">
+        <v>2</v>
+      </c>
+      <c r="AK185">
+        <v>1.68</v>
+      </c>
+      <c r="AL185">
+        <v>1.33</v>
+      </c>
+      <c r="AM185">
+        <v>1.25</v>
+      </c>
+      <c r="AN185">
+        <v>1.18</v>
+      </c>
+      <c r="AO185">
+        <v>1.73</v>
+      </c>
+      <c r="AP185">
+        <v>1.17</v>
+      </c>
+      <c r="AQ185">
+        <v>1.67</v>
+      </c>
+      <c r="AR185">
+        <v>1.44</v>
+      </c>
+      <c r="AS185">
+        <v>1.69</v>
+      </c>
+      <c r="AT185">
+        <v>3.13</v>
+      </c>
+      <c r="AU185">
+        <v>6</v>
+      </c>
+      <c r="AV185">
+        <v>6</v>
+      </c>
+      <c r="AW185">
+        <v>9</v>
+      </c>
+      <c r="AX185">
+        <v>4</v>
+      </c>
+      <c r="AY185">
+        <v>15</v>
+      </c>
+      <c r="AZ185">
+        <v>10</v>
+      </c>
+      <c r="BA185">
+        <v>1</v>
+      </c>
+      <c r="BB185">
+        <v>1</v>
+      </c>
+      <c r="BC185">
+        <v>2</v>
+      </c>
+      <c r="BD185">
+        <v>2.55</v>
+      </c>
+      <c r="BE185">
+        <v>7.5</v>
+      </c>
+      <c r="BF185">
+        <v>1.69</v>
+      </c>
+      <c r="BG185">
+        <v>1.44</v>
+      </c>
+      <c r="BH185">
+        <v>2.43</v>
+      </c>
+      <c r="BI185">
+        <v>1.88</v>
+      </c>
+      <c r="BJ185">
+        <v>1.92</v>
+      </c>
+      <c r="BK185">
+        <v>2.33</v>
+      </c>
+      <c r="BL185">
+        <v>1.48</v>
+      </c>
+      <c r="BM185">
+        <v>3.2</v>
+      </c>
+      <c r="BN185">
+        <v>1.26</v>
+      </c>
+      <c r="BO185">
+        <v>4.35</v>
+      </c>
+      <c r="BP185">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,9 @@
     <t>['3', '16', '36', '76']</t>
   </si>
   <si>
+    <t>['30']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -913,7 +916,10 @@
     <t>['56', '74']</t>
   </si>
   <si>
-    <t>['30']</t>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1537,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2149,7 +2155,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2436,7 +2442,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2561,7 +2567,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2767,7 +2773,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2845,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8">
         <v>1.67</v>
@@ -3179,7 +3185,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3385,7 +3391,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3591,7 +3597,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4081,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14">
         <v>1.27</v>
@@ -4415,7 +4421,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5033,7 +5039,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5111,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -5938,7 +5944,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>1.76</v>
@@ -6063,7 +6069,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6553,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ26">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6681,7 +6687,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6887,7 +6893,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7505,7 +7511,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7711,7 +7717,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8123,7 +8129,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8407,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35">
         <v>0.33</v>
@@ -8947,7 +8953,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9565,7 +9571,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9643,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41">
         <v>1.25</v>
@@ -9771,7 +9777,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9977,7 +9983,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10058,7 +10064,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ43">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR43">
         <v>1.47</v>
@@ -10183,7 +10189,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10389,7 +10395,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10470,7 +10476,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ45">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -11007,7 +11013,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11419,7 +11425,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11625,7 +11631,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12115,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53">
         <v>0.73</v>
@@ -12449,7 +12455,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12530,7 +12536,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ55">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR55">
         <v>0</v>
@@ -12861,7 +12867,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13067,7 +13073,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13273,7 +13279,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13351,7 +13357,7 @@
         <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ59">
         <v>1.36</v>
@@ -13479,7 +13485,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13560,7 +13566,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ60">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR60">
         <v>0.73</v>
@@ -13685,7 +13691,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13766,7 +13772,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR61">
         <v>1.36</v>
@@ -14097,7 +14103,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14303,7 +14309,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14509,7 +14515,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14715,7 +14721,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15333,7 +15339,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15745,7 +15751,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15951,7 +15957,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16238,7 +16244,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ73">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR73">
         <v>1.97</v>
@@ -16363,7 +16369,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16444,7 +16450,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ74">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR74">
         <v>1.34</v>
@@ -16647,7 +16653,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ75">
         <v>1.18</v>
@@ -16775,7 +16781,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17187,7 +17193,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17393,7 +17399,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17805,7 +17811,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18011,7 +18017,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18217,7 +18223,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18423,7 +18429,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18629,7 +18635,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18707,7 +18713,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ85">
         <v>1.67</v>
@@ -19041,7 +19047,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19122,7 +19128,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ87">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR87">
         <v>2.4</v>
@@ -19453,7 +19459,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19534,7 +19540,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ89">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR89">
         <v>1.92</v>
@@ -19865,7 +19871,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -19943,7 +19949,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ91">
         <v>1.27</v>
@@ -20483,7 +20489,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21513,7 +21519,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21591,7 +21597,7 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ99">
         <v>3</v>
@@ -21719,7 +21725,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21925,7 +21931,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22131,7 +22137,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22337,7 +22343,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22415,10 +22421,10 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -23161,7 +23167,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23573,7 +23579,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23985,7 +23991,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24191,7 +24197,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24475,7 +24481,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ113">
         <v>0.83</v>
@@ -25015,7 +25021,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25096,7 +25102,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ116">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25221,7 +25227,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25427,7 +25433,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25633,7 +25639,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25839,7 +25845,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -25917,7 +25923,7 @@
         <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ120">
         <v>1.25</v>
@@ -26663,7 +26669,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26744,7 +26750,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ124">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR124">
         <v>1.33</v>
@@ -26869,7 +26875,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27075,7 +27081,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27359,7 +27365,7 @@
         <v>2.13</v>
       </c>
       <c r="AP127">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27487,7 +27493,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27693,7 +27699,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28105,7 +28111,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28392,7 +28398,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ132">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR132">
         <v>1.95</v>
@@ -28598,7 +28604,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ133">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28723,7 +28729,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29135,7 +29141,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29625,7 +29631,7 @@
         <v>1.43</v>
       </c>
       <c r="AP138">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ138">
         <v>1.36</v>
@@ -29753,7 +29759,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29959,7 +29965,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30165,7 +30171,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30371,7 +30377,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30452,7 +30458,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30577,7 +30583,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30655,7 +30661,7 @@
         <v>2.38</v>
       </c>
       <c r="AP143">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ143">
         <v>2.09</v>
@@ -30861,7 +30867,7 @@
         <v>2.11</v>
       </c>
       <c r="AP144">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ144">
         <v>1.67</v>
@@ -31195,7 +31201,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31276,7 +31282,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ146">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31401,7 +31407,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31607,7 +31613,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31813,7 +31819,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32225,7 +32231,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32431,7 +32437,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32637,7 +32643,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33049,7 +33055,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33130,7 +33136,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ155">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR155">
         <v>1.77</v>
@@ -33667,7 +33673,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33873,7 +33879,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33951,7 +33957,7 @@
         <v>0.78</v>
       </c>
       <c r="AP159">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ159">
         <v>1.18</v>
@@ -34079,7 +34085,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34285,7 +34291,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34903,7 +34909,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35109,7 +35115,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35521,7 +35527,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35808,7 +35814,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ168">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36139,7 +36145,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36217,7 +36223,7 @@
         <v>1.1</v>
       </c>
       <c r="AP170">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ170">
         <v>1.27</v>
@@ -36632,7 +36638,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ172">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR172">
         <v>2.01</v>
@@ -36963,7 +36969,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37169,7 +37175,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37659,7 +37665,7 @@
         <v>1.3</v>
       </c>
       <c r="AP177">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ177">
         <v>1.27</v>
@@ -37787,7 +37793,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38199,7 +38205,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38611,7 +38617,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38817,7 +38823,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39023,7 +39029,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39229,7 +39235,7 @@
         <v>195</v>
       </c>
       <c r="P185" t="s">
-        <v>299</v>
+        <v>208</v>
       </c>
       <c r="Q185">
         <v>3.75</v>
@@ -39386,6 +39392,418 @@
       </c>
       <c r="BP185">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7453871</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45709.45833333334</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>81</v>
+      </c>
+      <c r="H186" t="s">
+        <v>80</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>2</v>
+      </c>
+      <c r="O186" t="s">
+        <v>208</v>
+      </c>
+      <c r="P186" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q186">
+        <v>2.88</v>
+      </c>
+      <c r="R186">
+        <v>2.1</v>
+      </c>
+      <c r="S186">
+        <v>3.4</v>
+      </c>
+      <c r="T186">
+        <v>1.4</v>
+      </c>
+      <c r="U186">
+        <v>2.75</v>
+      </c>
+      <c r="V186">
+        <v>2.75</v>
+      </c>
+      <c r="W186">
+        <v>1.4</v>
+      </c>
+      <c r="X186">
+        <v>7</v>
+      </c>
+      <c r="Y186">
+        <v>1.08</v>
+      </c>
+      <c r="Z186">
+        <v>2.34</v>
+      </c>
+      <c r="AA186">
+        <v>3.32</v>
+      </c>
+      <c r="AB186">
+        <v>2.93</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>8.5</v>
+      </c>
+      <c r="AE186">
+        <v>1.28</v>
+      </c>
+      <c r="AF186">
+        <v>3.45</v>
+      </c>
+      <c r="AG186">
+        <v>1.94</v>
+      </c>
+      <c r="AH186">
+        <v>1.76</v>
+      </c>
+      <c r="AI186">
+        <v>1.73</v>
+      </c>
+      <c r="AJ186">
+        <v>2</v>
+      </c>
+      <c r="AK186">
+        <v>1.39</v>
+      </c>
+      <c r="AL186">
+        <v>1.29</v>
+      </c>
+      <c r="AM186">
+        <v>1.54</v>
+      </c>
+      <c r="AN186">
+        <v>1.45</v>
+      </c>
+      <c r="AO186">
+        <v>0.73</v>
+      </c>
+      <c r="AP186">
+        <v>1.42</v>
+      </c>
+      <c r="AQ186">
+        <v>0.75</v>
+      </c>
+      <c r="AR186">
+        <v>1.05</v>
+      </c>
+      <c r="AS186">
+        <v>1.43</v>
+      </c>
+      <c r="AT186">
+        <v>2.48</v>
+      </c>
+      <c r="AU186">
+        <v>4</v>
+      </c>
+      <c r="AV186">
+        <v>5</v>
+      </c>
+      <c r="AW186">
+        <v>10</v>
+      </c>
+      <c r="AX186">
+        <v>4</v>
+      </c>
+      <c r="AY186">
+        <v>17</v>
+      </c>
+      <c r="AZ186">
+        <v>11</v>
+      </c>
+      <c r="BA186">
+        <v>6</v>
+      </c>
+      <c r="BB186">
+        <v>5</v>
+      </c>
+      <c r="BC186">
+        <v>11</v>
+      </c>
+      <c r="BD186">
+        <v>2.05</v>
+      </c>
+      <c r="BE186">
+        <v>7.5</v>
+      </c>
+      <c r="BF186">
+        <v>2.05</v>
+      </c>
+      <c r="BG186">
+        <v>1.47</v>
+      </c>
+      <c r="BH186">
+        <v>2.5</v>
+      </c>
+      <c r="BI186">
+        <v>1.82</v>
+      </c>
+      <c r="BJ186">
+        <v>1.93</v>
+      </c>
+      <c r="BK186">
+        <v>2.34</v>
+      </c>
+      <c r="BL186">
+        <v>1.56</v>
+      </c>
+      <c r="BM186">
+        <v>3.02</v>
+      </c>
+      <c r="BN186">
+        <v>1.33</v>
+      </c>
+      <c r="BO186">
+        <v>4.2</v>
+      </c>
+      <c r="BP186">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7453866</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45709.5</v>
+      </c>
+      <c r="F187">
+        <v>24</v>
+      </c>
+      <c r="G187" t="s">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s">
+        <v>70</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
+        <v>87</v>
+      </c>
+      <c r="P187" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q187">
+        <v>4.75</v>
+      </c>
+      <c r="R187">
+        <v>2.25</v>
+      </c>
+      <c r="S187">
+        <v>2.25</v>
+      </c>
+      <c r="T187">
+        <v>1.36</v>
+      </c>
+      <c r="U187">
+        <v>3</v>
+      </c>
+      <c r="V187">
+        <v>2.63</v>
+      </c>
+      <c r="W187">
+        <v>1.44</v>
+      </c>
+      <c r="X187">
+        <v>6.5</v>
+      </c>
+      <c r="Y187">
+        <v>1.1</v>
+      </c>
+      <c r="Z187">
+        <v>3.84</v>
+      </c>
+      <c r="AA187">
+        <v>3.32</v>
+      </c>
+      <c r="AB187">
+        <v>1.97</v>
+      </c>
+      <c r="AC187">
+        <v>1.05</v>
+      </c>
+      <c r="AD187">
+        <v>8.5</v>
+      </c>
+      <c r="AE187">
+        <v>1.28</v>
+      </c>
+      <c r="AF187">
+        <v>3.45</v>
+      </c>
+      <c r="AG187">
+        <v>1.91</v>
+      </c>
+      <c r="AH187">
+        <v>1.73</v>
+      </c>
+      <c r="AI187">
+        <v>1.8</v>
+      </c>
+      <c r="AJ187">
+        <v>1.91</v>
+      </c>
+      <c r="AK187">
+        <v>2.02</v>
+      </c>
+      <c r="AL187">
+        <v>1.23</v>
+      </c>
+      <c r="AM187">
+        <v>1.19</v>
+      </c>
+      <c r="AN187">
+        <v>1.27</v>
+      </c>
+      <c r="AO187">
+        <v>1.27</v>
+      </c>
+      <c r="AP187">
+        <v>1.17</v>
+      </c>
+      <c r="AQ187">
+        <v>1.42</v>
+      </c>
+      <c r="AR187">
+        <v>1.22</v>
+      </c>
+      <c r="AS187">
+        <v>1.72</v>
+      </c>
+      <c r="AT187">
+        <v>2.94</v>
+      </c>
+      <c r="AU187">
+        <v>3</v>
+      </c>
+      <c r="AV187">
+        <v>8</v>
+      </c>
+      <c r="AW187">
+        <v>6</v>
+      </c>
+      <c r="AX187">
+        <v>8</v>
+      </c>
+      <c r="AY187">
+        <v>11</v>
+      </c>
+      <c r="AZ187">
+        <v>19</v>
+      </c>
+      <c r="BA187">
+        <v>5</v>
+      </c>
+      <c r="BB187">
+        <v>2</v>
+      </c>
+      <c r="BC187">
+        <v>7</v>
+      </c>
+      <c r="BD187">
+        <v>2.66</v>
+      </c>
+      <c r="BE187">
+        <v>7.5</v>
+      </c>
+      <c r="BF187">
+        <v>1.69</v>
+      </c>
+      <c r="BG187">
+        <v>1.55</v>
+      </c>
+      <c r="BH187">
+        <v>2.37</v>
+      </c>
+      <c r="BI187">
+        <v>1.92</v>
+      </c>
+      <c r="BJ187">
+        <v>1.82</v>
+      </c>
+      <c r="BK187">
+        <v>2.46</v>
+      </c>
+      <c r="BL187">
+        <v>1.48</v>
+      </c>
+      <c r="BM187">
+        <v>3.32</v>
+      </c>
+      <c r="BN187">
+        <v>1.26</v>
+      </c>
+      <c r="BO187">
+        <v>4.6</v>
+      </c>
+      <c r="BP187">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['30']</t>
   </si>
   <si>
+    <t>['46', '51', '62']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -920,6 +923,12 @@
   </si>
   <si>
     <t>['82']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['8', '59', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1537,7 +1546,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1824,7 +1833,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ3">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2027,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ4">
         <v>0.33</v>
@@ -2155,7 +2164,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2567,7 +2576,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2773,7 +2782,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3060,7 +3069,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3185,7 +3194,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3266,7 +3275,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ10">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3391,7 +3400,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3597,7 +3606,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3675,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ12">
         <v>1.67</v>
@@ -4421,7 +4430,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4502,7 +4511,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ16">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR16">
         <v>1.02</v>
@@ -5039,7 +5048,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6069,7 +6078,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6687,7 +6696,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6893,7 +6902,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -6971,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ28">
         <v>1.25</v>
@@ -7386,7 +7395,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7511,7 +7520,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7589,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ31">
         <v>1.36</v>
@@ -7717,7 +7726,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8129,7 +8138,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8828,7 +8837,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ37">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR37">
         <v>1.6</v>
@@ -8953,7 +8962,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9571,7 +9580,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9777,7 +9786,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9858,7 +9867,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ42">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR42">
         <v>0.6</v>
@@ -9983,7 +9992,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10189,7 +10198,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10267,7 +10276,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ44">
         <v>1.18</v>
@@ -10395,7 +10404,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11013,7 +11022,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11425,7 +11434,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11631,7 +11640,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12124,7 +12133,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ53">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12327,7 +12336,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ54">
         <v>1.27</v>
@@ -12455,7 +12464,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12739,7 +12748,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ56">
         <v>1.18</v>
@@ -12867,7 +12876,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13073,7 +13082,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13154,7 +13163,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ58">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13279,7 +13288,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13485,7 +13494,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13691,7 +13700,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14103,7 +14112,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14309,7 +14318,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14515,7 +14524,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14721,7 +14730,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15339,7 +15348,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15623,7 +15632,7 @@
         <v>1.2</v>
       </c>
       <c r="AP70">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ70">
         <v>1.27</v>
@@ -15751,7 +15760,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15832,7 +15841,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ71">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -15957,7 +15966,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16369,7 +16378,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16447,7 +16456,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -16781,7 +16790,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16862,7 +16871,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ76">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -17193,7 +17202,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17271,7 +17280,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ78">
         <v>1.25</v>
@@ -17399,7 +17408,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17811,7 +17820,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18017,7 +18026,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18223,7 +18232,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18429,7 +18438,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18635,7 +18644,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19047,7 +19056,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19125,7 +19134,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ87">
         <v>0.75</v>
@@ -19459,7 +19468,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19871,7 +19880,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20364,7 +20373,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ93">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -20489,7 +20498,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20570,7 +20579,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ94">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR94">
         <v>1.84</v>
@@ -21519,7 +21528,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21725,7 +21734,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21803,7 +21812,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ100">
         <v>1.67</v>
@@ -21931,7 +21940,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22137,7 +22146,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22343,7 +22352,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22630,7 +22639,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR104">
         <v>1.79</v>
@@ -23039,7 +23048,7 @@
         <v>1.71</v>
       </c>
       <c r="AP106">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ106">
         <v>1.67</v>
@@ -23167,7 +23176,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23248,7 +23257,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ107">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR107">
         <v>1.95</v>
@@ -23579,7 +23588,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23991,7 +24000,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24197,7 +24206,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24687,7 +24696,7 @@
         <v>2.33</v>
       </c>
       <c r="AP114">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ114">
         <v>1.67</v>
@@ -25021,7 +25030,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25227,7 +25236,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25433,7 +25442,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25639,7 +25648,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25845,7 +25854,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26129,7 +26138,7 @@
         <v>0.43</v>
       </c>
       <c r="AP121">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ121">
         <v>0.83</v>
@@ -26669,7 +26678,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26875,7 +26884,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27081,7 +27090,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27493,7 +27502,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27699,7 +27708,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27780,7 +27789,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ129">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR129">
         <v>1.62</v>
@@ -28111,7 +28120,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28729,7 +28738,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -28807,7 +28816,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ134">
         <v>1.36</v>
@@ -29013,7 +29022,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ135">
         <v>0.83</v>
@@ -29141,7 +29150,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29425,7 +29434,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ137">
         <v>1.27</v>
@@ -29759,7 +29768,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29840,7 +29849,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ139">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR139">
         <v>1.32</v>
@@ -29965,7 +29974,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30171,7 +30180,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30377,7 +30386,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30583,7 +30592,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30664,7 +30673,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ143">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR143">
         <v>1.05</v>
@@ -31201,7 +31210,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31407,7 +31416,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31613,7 +31622,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31819,7 +31828,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32231,7 +32240,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32312,7 +32321,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ151">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR151">
         <v>1.68</v>
@@ -32437,7 +32446,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32643,7 +32652,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33055,7 +33064,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33133,7 +33142,7 @@
         <v>1.56</v>
       </c>
       <c r="AP155">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ155">
         <v>1.42</v>
@@ -33342,7 +33351,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ156">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR156">
         <v>1.72</v>
@@ -33673,7 +33682,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33751,7 +33760,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -33879,7 +33888,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34085,7 +34094,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34291,7 +34300,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34909,7 +34918,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35115,7 +35124,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35527,7 +35536,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36145,7 +36154,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36635,7 +36644,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="AQ172">
         <v>1.42</v>
@@ -36841,10 +36850,10 @@
         <v>2.2</v>
       </c>
       <c r="AP173">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ173">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR173">
         <v>1.77</v>
@@ -36969,7 +36978,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37175,7 +37184,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37462,7 +37471,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ176">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37793,7 +37802,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38205,7 +38214,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38617,7 +38626,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38823,7 +38832,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39029,7 +39038,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39441,7 +39450,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39647,7 +39656,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39804,6 +39813,418 @@
       </c>
       <c r="BP187">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7453870</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45710.375</v>
+      </c>
+      <c r="F188">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>85</v>
+      </c>
+      <c r="H188" t="s">
+        <v>84</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>1</v>
+      </c>
+      <c r="O188" t="s">
+        <v>87</v>
+      </c>
+      <c r="P188" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q188">
+        <v>2</v>
+      </c>
+      <c r="R188">
+        <v>2.3</v>
+      </c>
+      <c r="S188">
+        <v>5.5</v>
+      </c>
+      <c r="T188">
+        <v>1.33</v>
+      </c>
+      <c r="U188">
+        <v>3.25</v>
+      </c>
+      <c r="V188">
+        <v>2.63</v>
+      </c>
+      <c r="W188">
+        <v>1.44</v>
+      </c>
+      <c r="X188">
+        <v>6</v>
+      </c>
+      <c r="Y188">
+        <v>1.11</v>
+      </c>
+      <c r="Z188">
+        <v>1.77</v>
+      </c>
+      <c r="AA188">
+        <v>3.23</v>
+      </c>
+      <c r="AB188">
+        <v>5.1</v>
+      </c>
+      <c r="AC188">
+        <v>1.04</v>
+      </c>
+      <c r="AD188">
+        <v>9.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.22</v>
+      </c>
+      <c r="AF188">
+        <v>3.95</v>
+      </c>
+      <c r="AG188">
+        <v>1.8</v>
+      </c>
+      <c r="AH188">
+        <v>1.94</v>
+      </c>
+      <c r="AI188">
+        <v>1.83</v>
+      </c>
+      <c r="AJ188">
+        <v>1.83</v>
+      </c>
+      <c r="AK188">
+        <v>1.11</v>
+      </c>
+      <c r="AL188">
+        <v>1.18</v>
+      </c>
+      <c r="AM188">
+        <v>2.5</v>
+      </c>
+      <c r="AN188">
+        <v>1.18</v>
+      </c>
+      <c r="AO188">
+        <v>0.73</v>
+      </c>
+      <c r="AP188">
+        <v>1.08</v>
+      </c>
+      <c r="AQ188">
+        <v>0.92</v>
+      </c>
+      <c r="AR188">
+        <v>1.79</v>
+      </c>
+      <c r="AS188">
+        <v>1.45</v>
+      </c>
+      <c r="AT188">
+        <v>3.24</v>
+      </c>
+      <c r="AU188">
+        <v>2</v>
+      </c>
+      <c r="AV188">
+        <v>8</v>
+      </c>
+      <c r="AW188">
+        <v>13</v>
+      </c>
+      <c r="AX188">
+        <v>6</v>
+      </c>
+      <c r="AY188">
+        <v>19</v>
+      </c>
+      <c r="AZ188">
+        <v>15</v>
+      </c>
+      <c r="BA188">
+        <v>5</v>
+      </c>
+      <c r="BB188">
+        <v>4</v>
+      </c>
+      <c r="BC188">
+        <v>9</v>
+      </c>
+      <c r="BD188">
+        <v>1.41</v>
+      </c>
+      <c r="BE188">
+        <v>9</v>
+      </c>
+      <c r="BF188">
+        <v>3.58</v>
+      </c>
+      <c r="BG188">
+        <v>1.39</v>
+      </c>
+      <c r="BH188">
+        <v>2.77</v>
+      </c>
+      <c r="BI188">
+        <v>1.68</v>
+      </c>
+      <c r="BJ188">
+        <v>2.12</v>
+      </c>
+      <c r="BK188">
+        <v>2.11</v>
+      </c>
+      <c r="BL188">
+        <v>1.68</v>
+      </c>
+      <c r="BM188">
+        <v>2.7</v>
+      </c>
+      <c r="BN188">
+        <v>1.41</v>
+      </c>
+      <c r="BO188">
+        <v>3.65</v>
+      </c>
+      <c r="BP188">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7453868</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>72</v>
+      </c>
+      <c r="H189" t="s">
+        <v>83</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>3</v>
+      </c>
+      <c r="M189">
+        <v>3</v>
+      </c>
+      <c r="N189">
+        <v>6</v>
+      </c>
+      <c r="O189" t="s">
+        <v>209</v>
+      </c>
+      <c r="P189" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q189">
+        <v>1.73</v>
+      </c>
+      <c r="R189">
+        <v>2.63</v>
+      </c>
+      <c r="S189">
+        <v>6.5</v>
+      </c>
+      <c r="T189">
+        <v>1.25</v>
+      </c>
+      <c r="U189">
+        <v>3.75</v>
+      </c>
+      <c r="V189">
+        <v>2.1</v>
+      </c>
+      <c r="W189">
+        <v>1.67</v>
+      </c>
+      <c r="X189">
+        <v>4.5</v>
+      </c>
+      <c r="Y189">
+        <v>1.17</v>
+      </c>
+      <c r="Z189">
+        <v>1.29</v>
+      </c>
+      <c r="AA189">
+        <v>5.7</v>
+      </c>
+      <c r="AB189">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC189">
+        <v>1.01</v>
+      </c>
+      <c r="AD189">
+        <v>17</v>
+      </c>
+      <c r="AE189">
+        <v>1.14</v>
+      </c>
+      <c r="AF189">
+        <v>5.2</v>
+      </c>
+      <c r="AG189">
+        <v>1.43</v>
+      </c>
+      <c r="AH189">
+        <v>2.62</v>
+      </c>
+      <c r="AI189">
+        <v>1.8</v>
+      </c>
+      <c r="AJ189">
+        <v>1.91</v>
+      </c>
+      <c r="AK189">
+        <v>1.07</v>
+      </c>
+      <c r="AL189">
+        <v>1.12</v>
+      </c>
+      <c r="AM189">
+        <v>3.2</v>
+      </c>
+      <c r="AN189">
+        <v>2.82</v>
+      </c>
+      <c r="AO189">
+        <v>2.09</v>
+      </c>
+      <c r="AP189">
+        <v>2.67</v>
+      </c>
+      <c r="AQ189">
+        <v>2</v>
+      </c>
+      <c r="AR189">
+        <v>2.16</v>
+      </c>
+      <c r="AS189">
+        <v>1.35</v>
+      </c>
+      <c r="AT189">
+        <v>3.51</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>15</v>
+      </c>
+      <c r="AX189">
+        <v>0</v>
+      </c>
+      <c r="AY189">
+        <v>21</v>
+      </c>
+      <c r="AZ189">
+        <v>4</v>
+      </c>
+      <c r="BA189">
+        <v>8</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>10</v>
+      </c>
+      <c r="BD189">
+        <v>1.19</v>
+      </c>
+      <c r="BE189">
+        <v>11</v>
+      </c>
+      <c r="BF189">
+        <v>5.67</v>
+      </c>
+      <c r="BG189">
+        <v>1.27</v>
+      </c>
+      <c r="BH189">
+        <v>3.27</v>
+      </c>
+      <c r="BI189">
+        <v>1.51</v>
+      </c>
+      <c r="BJ189">
+        <v>2.39</v>
+      </c>
+      <c r="BK189">
+        <v>1.85</v>
+      </c>
+      <c r="BL189">
+        <v>1.95</v>
+      </c>
+      <c r="BM189">
+        <v>2.36</v>
+      </c>
+      <c r="BN189">
+        <v>1.55</v>
+      </c>
+      <c r="BO189">
+        <v>3.1</v>
+      </c>
+      <c r="BP189">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1290,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ5">
         <v>1.67</v>
@@ -3272,7 +3272,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -3481,7 +3481,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ18">
         <v>0.33</v>
@@ -6159,7 +6159,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR24">
         <v>0.98</v>
@@ -6365,7 +6365,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR25">
         <v>1.68</v>
@@ -6774,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ27">
         <v>0.83</v>
@@ -7186,7 +7186,7 @@
         <v>1.5</v>
       </c>
       <c r="AP29">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -9246,10 +9246,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ39">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ42">
         <v>0.92</v>
@@ -10279,7 +10279,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ44">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -12542,7 +12542,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ55">
         <v>1.42</v>
@@ -12751,7 +12751,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ56">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12957,7 +12957,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ57">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR57">
         <v>1.94</v>
@@ -13572,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ60">
         <v>0.75</v>
@@ -16665,7 +16665,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ75">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
         <v>1.22</v>
@@ -16868,7 +16868,7 @@
         <v>1.75</v>
       </c>
       <c r="AP76">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ76">
         <v>2</v>
@@ -17074,7 +17074,7 @@
         <v>0.2</v>
       </c>
       <c r="AP77">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ77">
         <v>0.83</v>
@@ -17695,7 +17695,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ80">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -19343,7 +19343,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ88">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR88">
         <v>1.41</v>
@@ -20164,7 +20164,7 @@
         <v>1.83</v>
       </c>
       <c r="AP92">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ92">
         <v>1.67</v>
@@ -20370,7 +20370,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ93">
         <v>0.92</v>
@@ -21197,7 +21197,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR97">
         <v>1.33</v>
@@ -22845,7 +22845,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ105">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR105">
         <v>1.53</v>
@@ -23460,7 +23460,7 @@
         <v>0.29</v>
       </c>
       <c r="AP108">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ108">
         <v>0.83</v>
@@ -23666,7 +23666,7 @@
         <v>2</v>
       </c>
       <c r="AP109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ109">
         <v>1.67</v>
@@ -24287,7 +24287,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ112">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR112">
         <v>1.19</v>
@@ -25729,7 +25729,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR119">
         <v>1.78</v>
@@ -26553,7 +26553,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ123">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR123">
         <v>1.46</v>
@@ -28198,7 +28198,7 @@
         <v>3</v>
       </c>
       <c r="AP131">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ131">
         <v>3</v>
@@ -29228,7 +29228,7 @@
         <v>2</v>
       </c>
       <c r="AP136">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ136">
         <v>1.67</v>
@@ -29437,7 +29437,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ137">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR137">
         <v>1.8</v>
@@ -30261,7 +30261,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ141">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR141">
         <v>1.19</v>
@@ -32524,7 +32524,7 @@
         <v>3</v>
       </c>
       <c r="AP152">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ152">
         <v>3</v>
@@ -32730,7 +32730,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ153">
         <v>1.25</v>
@@ -33554,7 +33554,7 @@
         <v>0.44</v>
       </c>
       <c r="AP157">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ157">
         <v>0.83</v>
@@ -33763,7 +33763,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ158">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR158">
         <v>2</v>
@@ -33969,7 +33969,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ159">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR159">
         <v>1.07</v>
@@ -36235,7 +36235,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ170">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR170">
         <v>1.25</v>
@@ -36438,7 +36438,7 @@
         <v>1.5</v>
       </c>
       <c r="AP171">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ171">
         <v>1.36</v>
@@ -37056,7 +37056,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ174">
         <v>1.25</v>
@@ -37265,7 +37265,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ175">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR175">
         <v>1.51</v>
@@ -40225,6 +40225,418 @@
       </c>
       <c r="BP189">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7453867</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45711.54166666666</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>73</v>
+      </c>
+      <c r="H190" t="s">
+        <v>71</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
+        <v>96</v>
+      </c>
+      <c r="P190" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+      <c r="S190">
+        <v>0</v>
+      </c>
+      <c r="T190">
+        <v>0</v>
+      </c>
+      <c r="U190">
+        <v>0</v>
+      </c>
+      <c r="V190">
+        <v>0</v>
+      </c>
+      <c r="W190">
+        <v>0</v>
+      </c>
+      <c r="X190">
+        <v>0</v>
+      </c>
+      <c r="Y190">
+        <v>0</v>
+      </c>
+      <c r="Z190">
+        <v>2.11</v>
+      </c>
+      <c r="AA190">
+        <v>3.21</v>
+      </c>
+      <c r="AB190">
+        <v>3.5</v>
+      </c>
+      <c r="AC190">
+        <v>0</v>
+      </c>
+      <c r="AD190">
+        <v>0</v>
+      </c>
+      <c r="AE190">
+        <v>0</v>
+      </c>
+      <c r="AF190">
+        <v>0</v>
+      </c>
+      <c r="AG190">
+        <v>2.1</v>
+      </c>
+      <c r="AH190">
+        <v>1.6</v>
+      </c>
+      <c r="AI190">
+        <v>0</v>
+      </c>
+      <c r="AJ190">
+        <v>0</v>
+      </c>
+      <c r="AK190">
+        <v>0</v>
+      </c>
+      <c r="AL190">
+        <v>0</v>
+      </c>
+      <c r="AM190">
+        <v>0</v>
+      </c>
+      <c r="AN190">
+        <v>1.45</v>
+      </c>
+      <c r="AO190">
+        <v>1.18</v>
+      </c>
+      <c r="AP190">
+        <v>1.58</v>
+      </c>
+      <c r="AQ190">
+        <v>1.08</v>
+      </c>
+      <c r="AR190">
+        <v>1.16</v>
+      </c>
+      <c r="AS190">
+        <v>1.1</v>
+      </c>
+      <c r="AT190">
+        <v>2.26</v>
+      </c>
+      <c r="AU190">
+        <v>-1</v>
+      </c>
+      <c r="AV190">
+        <v>-1</v>
+      </c>
+      <c r="AW190">
+        <v>-1</v>
+      </c>
+      <c r="AX190">
+        <v>-1</v>
+      </c>
+      <c r="AY190">
+        <v>-1</v>
+      </c>
+      <c r="AZ190">
+        <v>-1</v>
+      </c>
+      <c r="BA190">
+        <v>-1</v>
+      </c>
+      <c r="BB190">
+        <v>-1</v>
+      </c>
+      <c r="BC190">
+        <v>-1</v>
+      </c>
+      <c r="BD190">
+        <v>0</v>
+      </c>
+      <c r="BE190">
+        <v>0</v>
+      </c>
+      <c r="BF190">
+        <v>0</v>
+      </c>
+      <c r="BG190">
+        <v>0</v>
+      </c>
+      <c r="BH190">
+        <v>0</v>
+      </c>
+      <c r="BI190">
+        <v>0</v>
+      </c>
+      <c r="BJ190">
+        <v>0</v>
+      </c>
+      <c r="BK190">
+        <v>0</v>
+      </c>
+      <c r="BL190">
+        <v>0</v>
+      </c>
+      <c r="BM190">
+        <v>0</v>
+      </c>
+      <c r="BN190">
+        <v>0</v>
+      </c>
+      <c r="BO190">
+        <v>0</v>
+      </c>
+      <c r="BP190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7453864</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45711.66666666666</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+      <c r="G191" t="s">
+        <v>78</v>
+      </c>
+      <c r="H191" t="s">
+        <v>74</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
+        <v>87</v>
+      </c>
+      <c r="P191" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q191">
+        <v>5.5</v>
+      </c>
+      <c r="R191">
+        <v>2.2</v>
+      </c>
+      <c r="S191">
+        <v>2.1</v>
+      </c>
+      <c r="T191">
+        <v>1.4</v>
+      </c>
+      <c r="U191">
+        <v>2.75</v>
+      </c>
+      <c r="V191">
+        <v>2.75</v>
+      </c>
+      <c r="W191">
+        <v>1.4</v>
+      </c>
+      <c r="X191">
+        <v>7</v>
+      </c>
+      <c r="Y191">
+        <v>1.08</v>
+      </c>
+      <c r="Z191">
+        <v>5.6</v>
+      </c>
+      <c r="AA191">
+        <v>3.96</v>
+      </c>
+      <c r="AB191">
+        <v>1.57</v>
+      </c>
+      <c r="AC191">
+        <v>1.05</v>
+      </c>
+      <c r="AD191">
+        <v>8.5</v>
+      </c>
+      <c r="AE191">
+        <v>1.27</v>
+      </c>
+      <c r="AF191">
+        <v>3.5</v>
+      </c>
+      <c r="AG191">
+        <v>1.85</v>
+      </c>
+      <c r="AH191">
+        <v>1.89</v>
+      </c>
+      <c r="AI191">
+        <v>1.91</v>
+      </c>
+      <c r="AJ191">
+        <v>1.8</v>
+      </c>
+      <c r="AK191">
+        <v>2.29</v>
+      </c>
+      <c r="AL191">
+        <v>1.21</v>
+      </c>
+      <c r="AM191">
+        <v>1.14</v>
+      </c>
+      <c r="AN191">
+        <v>0.64</v>
+      </c>
+      <c r="AO191">
+        <v>1.27</v>
+      </c>
+      <c r="AP191">
+        <v>0.58</v>
+      </c>
+      <c r="AQ191">
+        <v>1.42</v>
+      </c>
+      <c r="AR191">
+        <v>1.17</v>
+      </c>
+      <c r="AS191">
+        <v>1.39</v>
+      </c>
+      <c r="AT191">
+        <v>2.56</v>
+      </c>
+      <c r="AU191">
+        <v>4</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>5</v>
+      </c>
+      <c r="AX191">
+        <v>12</v>
+      </c>
+      <c r="AY191">
+        <v>9</v>
+      </c>
+      <c r="AZ191">
+        <v>21</v>
+      </c>
+      <c r="BA191">
+        <v>3</v>
+      </c>
+      <c r="BB191">
+        <v>5</v>
+      </c>
+      <c r="BC191">
+        <v>8</v>
+      </c>
+      <c r="BD191">
+        <v>3.33</v>
+      </c>
+      <c r="BE191">
+        <v>8.5</v>
+      </c>
+      <c r="BF191">
+        <v>1.45</v>
+      </c>
+      <c r="BG191">
+        <v>1.5</v>
+      </c>
+      <c r="BH191">
+        <v>2.41</v>
+      </c>
+      <c r="BI191">
+        <v>1.9</v>
+      </c>
+      <c r="BJ191">
+        <v>1.9</v>
+      </c>
+      <c r="BK191">
+        <v>2.42</v>
+      </c>
+      <c r="BL191">
+        <v>1.53</v>
+      </c>
+      <c r="BM191">
+        <v>3.25</v>
+      </c>
+      <c r="BN191">
+        <v>1.29</v>
+      </c>
+      <c r="BO191">
+        <v>4.4</v>
+      </c>
+      <c r="BP191">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t>['46', '51', '62']</t>
+  </si>
+  <si>
+    <t>['75', '77']</t>
   </si>
   <si>
     <t>['3', '15', '45+3']</t>
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1546,7 +1549,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2164,7 +2167,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2576,7 +2579,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2654,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7">
         <v>0.83</v>
@@ -2782,7 +2785,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3194,7 +3197,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3400,7 +3403,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3606,7 +3609,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3893,7 +3896,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4430,7 +4433,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4714,7 +4717,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
         <v>1.67</v>
@@ -5048,7 +5051,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6078,7 +6081,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6696,7 +6699,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6902,7 +6905,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7520,7 +7523,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7601,7 +7604,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ31">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7726,7 +7729,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8138,7 +8141,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8216,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ34">
         <v>1.67</v>
@@ -8962,7 +8965,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9580,7 +9583,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9786,7 +9789,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9992,7 +9995,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10198,7 +10201,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10404,7 +10407,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10894,7 +10897,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ47">
         <v>0.33</v>
@@ -11022,7 +11025,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11434,7 +11437,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11640,7 +11643,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12464,7 +12467,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12876,7 +12879,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -12954,7 +12957,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ57">
         <v>1.42</v>
@@ -13082,7 +13085,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13288,7 +13291,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13369,7 +13372,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13494,7 +13497,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13700,7 +13703,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14112,7 +14115,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14318,7 +14321,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14524,7 +14527,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14730,7 +14733,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15348,7 +15351,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15760,7 +15763,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15966,7 +15969,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16047,7 +16050,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.46</v>
@@ -16250,7 +16253,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ73">
         <v>1.42</v>
@@ -16378,7 +16381,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16790,7 +16793,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17202,7 +17205,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17408,7 +17411,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17820,7 +17823,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18026,7 +18029,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18232,7 +18235,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18438,7 +18441,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18644,7 +18647,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19056,7 +19059,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19468,7 +19471,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19880,7 +19883,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20498,7 +20501,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20576,7 +20579,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ94">
         <v>2</v>
@@ -21528,7 +21531,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21734,7 +21737,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21940,7 +21943,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22021,7 +22024,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ101">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22146,7 +22149,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22352,7 +22355,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22636,7 +22639,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>0.92</v>
@@ -23176,7 +23179,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23588,7 +23591,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24000,7 +24003,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24206,7 +24209,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25030,7 +25033,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25236,7 +25239,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25317,7 +25320,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ117">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25442,7 +25445,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25648,7 +25651,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25854,7 +25857,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26678,7 +26681,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26884,7 +26887,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -26962,7 +26965,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ125">
         <v>1.67</v>
@@ -27090,7 +27093,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27502,7 +27505,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27708,7 +27711,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28120,7 +28123,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28738,7 +28741,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -28819,7 +28822,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ134">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR134">
         <v>2.03</v>
@@ -29150,7 +29153,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29643,7 +29646,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ138">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR138">
         <v>1.06</v>
@@ -29768,7 +29771,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29974,7 +29977,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30180,7 +30183,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30386,7 +30389,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30592,7 +30595,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31210,7 +31213,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31416,7 +31419,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31622,7 +31625,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31700,7 +31703,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ148">
         <v>3</v>
@@ -31828,7 +31831,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32240,7 +32243,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32446,7 +32449,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32652,7 +32655,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33064,7 +33067,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33682,7 +33685,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33888,7 +33891,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34094,7 +34097,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34175,7 +34178,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ160">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR160">
         <v>1.53</v>
@@ -34300,7 +34303,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34381,7 +34384,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ161">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34918,7 +34921,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -34996,7 +34999,7 @@
         <v>0.4</v>
       </c>
       <c r="AP164">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ164">
         <v>0.83</v>
@@ -35124,7 +35127,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35536,7 +35539,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36154,7 +36157,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36441,7 +36444,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR171">
         <v>1.13</v>
@@ -36978,7 +36981,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37184,7 +37187,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37802,7 +37805,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38214,7 +38217,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38626,7 +38629,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38832,7 +38835,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39038,7 +39041,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39450,7 +39453,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39656,7 +39659,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39862,7 +39865,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40068,7 +40071,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40367,31 +40370,31 @@
         <v>2.26</v>
       </c>
       <c r="AU190">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV190">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW190">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX190">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY190">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AZ190">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA190">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB190">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC190">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD190">
         <v>0</v>
@@ -40637,6 +40640,212 @@
       </c>
       <c r="BP191">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7453865</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45712.52083333334</v>
+      </c>
+      <c r="F192">
+        <v>24</v>
+      </c>
+      <c r="G192" t="s">
+        <v>75</v>
+      </c>
+      <c r="H192" t="s">
+        <v>77</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>2</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>3</v>
+      </c>
+      <c r="O192" t="s">
+        <v>210</v>
+      </c>
+      <c r="P192" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q192">
+        <v>3.6</v>
+      </c>
+      <c r="R192">
+        <v>2.2</v>
+      </c>
+      <c r="S192">
+        <v>2.75</v>
+      </c>
+      <c r="T192">
+        <v>1.36</v>
+      </c>
+      <c r="U192">
+        <v>3</v>
+      </c>
+      <c r="V192">
+        <v>2.75</v>
+      </c>
+      <c r="W192">
+        <v>1.4</v>
+      </c>
+      <c r="X192">
+        <v>6.5</v>
+      </c>
+      <c r="Y192">
+        <v>1.1</v>
+      </c>
+      <c r="Z192">
+        <v>2.97</v>
+      </c>
+      <c r="AA192">
+        <v>3.58</v>
+      </c>
+      <c r="AB192">
+        <v>2.2</v>
+      </c>
+      <c r="AC192">
+        <v>1.02</v>
+      </c>
+      <c r="AD192">
+        <v>10</v>
+      </c>
+      <c r="AE192">
+        <v>1.25</v>
+      </c>
+      <c r="AF192">
+        <v>3.7</v>
+      </c>
+      <c r="AG192">
+        <v>1.77</v>
+      </c>
+      <c r="AH192">
+        <v>1.98</v>
+      </c>
+      <c r="AI192">
+        <v>1.73</v>
+      </c>
+      <c r="AJ192">
+        <v>2</v>
+      </c>
+      <c r="AK192">
+        <v>1.61</v>
+      </c>
+      <c r="AL192">
+        <v>1.29</v>
+      </c>
+      <c r="AM192">
+        <v>1.32</v>
+      </c>
+      <c r="AN192">
+        <v>1.27</v>
+      </c>
+      <c r="AO192">
+        <v>1.36</v>
+      </c>
+      <c r="AP192">
+        <v>1.42</v>
+      </c>
+      <c r="AQ192">
+        <v>1.25</v>
+      </c>
+      <c r="AR192">
+        <v>1.69</v>
+      </c>
+      <c r="AS192">
+        <v>1.54</v>
+      </c>
+      <c r="AT192">
+        <v>3.23</v>
+      </c>
+      <c r="AU192">
+        <v>8</v>
+      </c>
+      <c r="AV192">
+        <v>2</v>
+      </c>
+      <c r="AW192">
+        <v>4</v>
+      </c>
+      <c r="AX192">
+        <v>7</v>
+      </c>
+      <c r="AY192">
+        <v>14</v>
+      </c>
+      <c r="AZ192">
+        <v>11</v>
+      </c>
+      <c r="BA192">
+        <v>4</v>
+      </c>
+      <c r="BB192">
+        <v>6</v>
+      </c>
+      <c r="BC192">
+        <v>10</v>
+      </c>
+      <c r="BD192">
+        <v>2.34</v>
+      </c>
+      <c r="BE192">
+        <v>7.5</v>
+      </c>
+      <c r="BF192">
+        <v>1.82</v>
+      </c>
+      <c r="BG192">
+        <v>1.35</v>
+      </c>
+      <c r="BH192">
+        <v>2.74</v>
+      </c>
+      <c r="BI192">
+        <v>1.67</v>
+      </c>
+      <c r="BJ192">
+        <v>2.03</v>
+      </c>
+      <c r="BK192">
+        <v>2.1</v>
+      </c>
+      <c r="BL192">
+        <v>1.59</v>
+      </c>
+      <c r="BM192">
+        <v>2.83</v>
+      </c>
+      <c r="BN192">
+        <v>1.33</v>
+      </c>
+      <c r="BO192">
+        <v>3.75</v>
+      </c>
+      <c r="BP192">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="312">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,18 @@
     <t>['75', '77']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['36', '76']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -719,9 +731,6 @@
   </si>
   <si>
     <t>['85']</t>
-  </si>
-  <si>
-    <t>['11']</t>
   </si>
   <si>
     <t>['16', '68']</t>
@@ -932,6 +941,15 @@
   </si>
   <si>
     <t>['8', '59', '90+5']</t>
+  </si>
+  <si>
+    <t>['18', '45+3', '90+7']</t>
+  </si>
+  <si>
+    <t>['45+2', '61', '88', '90']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1567,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2042,7 +2060,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ4">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2167,7 +2185,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2248,7 +2266,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2579,7 +2597,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2785,7 +2803,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2866,7 +2884,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ8">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3197,7 +3215,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3403,7 +3421,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3481,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ11">
         <v>1.08</v>
@@ -3609,7 +3627,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3690,7 +3708,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR12">
         <v>2.33</v>
@@ -3893,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ13">
         <v>1.25</v>
@@ -4099,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ14">
         <v>1.42</v>
@@ -4433,7 +4451,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4720,7 +4738,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -4926,7 +4944,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ18">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5051,7 +5069,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5541,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1.27</v>
@@ -5750,7 +5768,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6081,7 +6099,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6365,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ25">
         <v>1.08</v>
@@ -6571,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ26">
         <v>1.42</v>
@@ -6699,7 +6717,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6905,7 +6923,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7395,7 +7413,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30">
         <v>2</v>
@@ -7523,7 +7541,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7729,7 +7747,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8016,7 +8034,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR33">
         <v>1.82</v>
@@ -8141,7 +8159,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8222,7 +8240,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ34">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR34">
         <v>1.89</v>
@@ -8428,7 +8446,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ35">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -8837,7 +8855,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ37">
         <v>0.92</v>
@@ -8965,7 +8983,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9046,7 +9064,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR38">
         <v>1.63</v>
@@ -9455,7 +9473,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ40">
         <v>1.27</v>
@@ -9583,7 +9601,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9789,7 +9807,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9995,7 +10013,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10201,7 +10219,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10407,7 +10425,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10485,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ45">
         <v>0.75</v>
@@ -10900,7 +10918,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ47">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR47">
         <v>1.89</v>
@@ -11025,7 +11043,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11106,7 +11124,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ48">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR48">
         <v>1.07</v>
@@ -11309,7 +11327,7 @@
         <v>0.33</v>
       </c>
       <c r="AP49">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -11437,7 +11455,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11518,7 +11536,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ50">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11643,7 +11661,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11927,10 +11945,10 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR52">
         <v>1.32</v>
@@ -12133,7 +12151,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ53">
         <v>0.92</v>
@@ -12467,7 +12485,7 @@
         <v>128</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -12879,7 +12897,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13085,7 +13103,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13291,7 +13309,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13497,7 +13515,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13703,7 +13721,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13781,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ61">
         <v>1.42</v>
@@ -13990,7 +14008,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -14115,7 +14133,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14321,7 +14339,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14402,7 +14420,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR64">
         <v>1.12</v>
@@ -14527,7 +14545,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14605,10 +14623,10 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ65">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR65">
         <v>1.31</v>
@@ -14733,7 +14751,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14811,7 +14829,7 @@
         <v>0.25</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ66">
         <v>0.83</v>
@@ -15017,10 +15035,10 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR67">
         <v>1.33</v>
@@ -15351,7 +15369,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15429,7 +15447,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>3</v>
@@ -15763,7 +15781,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15969,7 +15987,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16381,7 +16399,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16793,7 +16811,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17205,7 +17223,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17411,7 +17429,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17489,10 +17507,10 @@
         <v>2.6</v>
       </c>
       <c r="AP79">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ79">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR79">
         <v>1.64</v>
@@ -17823,7 +17841,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17901,10 +17919,10 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR81">
         <v>1.32</v>
@@ -18029,7 +18047,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18107,7 +18125,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18235,7 +18253,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18441,7 +18459,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18519,7 +18537,7 @@
         <v>3</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ84">
         <v>3</v>
@@ -18647,7 +18665,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18725,10 +18743,10 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR85">
         <v>1.12</v>
@@ -18934,7 +18952,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ86">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -19059,7 +19077,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19471,7 +19489,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19883,7 +19901,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20170,7 +20188,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20501,7 +20519,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20785,7 +20803,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ95">
         <v>0.83</v>
@@ -20994,7 +21012,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ96">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21197,7 +21215,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.42</v>
@@ -21403,7 +21421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP98">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ98">
         <v>1.25</v>
@@ -21531,7 +21549,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21609,7 +21627,7 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ99">
         <v>3</v>
@@ -21737,7 +21755,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21818,7 +21836,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ100">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR100">
         <v>1.66</v>
@@ -21943,7 +21961,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22149,7 +22167,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22227,10 +22245,10 @@
         <v>2.6</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ102">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR102">
         <v>1.61</v>
@@ -22355,7 +22373,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23054,7 +23072,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ106">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR106">
         <v>2.08</v>
@@ -23179,7 +23197,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23591,7 +23609,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23672,7 +23690,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ109">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR109">
         <v>1.11</v>
@@ -24003,7 +24021,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24081,7 +24099,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ111">
         <v>1.25</v>
@@ -24209,7 +24227,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24287,7 +24305,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ112">
         <v>1.42</v>
@@ -24493,7 +24511,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ113">
         <v>0.83</v>
@@ -24702,7 +24720,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ114">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24908,7 +24926,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ115">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -25033,7 +25051,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25111,7 +25129,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
         <v>1.42</v>
@@ -25239,7 +25257,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25317,7 +25335,7 @@
         <v>1.8</v>
       </c>
       <c r="AP117">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ117">
         <v>1.25</v>
@@ -25445,7 +25463,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25651,7 +25669,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25729,7 +25747,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ119">
         <v>1.42</v>
@@ -25857,7 +25875,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -25935,7 +25953,7 @@
         <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ120">
         <v>1.25</v>
@@ -26350,7 +26368,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR122">
         <v>1.45</v>
@@ -26553,7 +26571,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>1.08</v>
@@ -26681,7 +26699,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26759,7 +26777,7 @@
         <v>1.43</v>
       </c>
       <c r="AP124">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ124">
         <v>1.42</v>
@@ -26887,7 +26905,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -26968,7 +26986,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27093,7 +27111,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27380,7 +27398,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27505,7 +27523,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27711,7 +27729,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27995,10 +28013,10 @@
         <v>0.13</v>
       </c>
       <c r="AP130">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ130">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28123,7 +28141,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28613,7 +28631,7 @@
         <v>0.88</v>
       </c>
       <c r="AP133">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ133">
         <v>0.75</v>
@@ -28741,7 +28759,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29153,7 +29171,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29234,7 +29252,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ136">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR136">
         <v>1.2</v>
@@ -29643,7 +29661,7 @@
         <v>1.43</v>
       </c>
       <c r="AP138">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ138">
         <v>1.25</v>
@@ -29771,7 +29789,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29849,7 +29867,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ139">
         <v>2</v>
@@ -29977,7 +29995,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30183,7 +30201,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30261,7 +30279,7 @@
         <v>0.88</v>
       </c>
       <c r="AP141">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ141">
         <v>1.08</v>
@@ -30389,7 +30407,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30467,7 +30485,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ142">
         <v>1.42</v>
@@ -30595,7 +30613,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30673,7 +30691,7 @@
         <v>2.38</v>
       </c>
       <c r="AP143">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ143">
         <v>2</v>
@@ -30882,7 +30900,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR144">
         <v>1.18</v>
@@ -31085,10 +31103,10 @@
         <v>0.11</v>
       </c>
       <c r="AP145">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ145">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31213,7 +31231,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31419,7 +31437,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31500,7 +31518,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ147">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31625,7 +31643,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31831,7 +31849,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -31912,7 +31930,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ149">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR149">
         <v>2.02</v>
@@ -32243,7 +32261,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32321,7 +32339,7 @@
         <v>0.78</v>
       </c>
       <c r="AP151">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>0.92</v>
@@ -32449,7 +32467,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32655,7 +32673,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32939,7 +32957,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ154">
         <v>1.27</v>
@@ -33067,7 +33085,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33351,7 +33369,7 @@
         <v>2.11</v>
       </c>
       <c r="AP156">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ156">
         <v>2</v>
@@ -33685,7 +33703,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33891,7 +33909,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -33969,7 +33987,7 @@
         <v>0.78</v>
       </c>
       <c r="AP159">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ159">
         <v>1.08</v>
@@ -34097,7 +34115,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34303,7 +34321,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34381,7 +34399,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ161">
         <v>1.25</v>
@@ -34590,7 +34608,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ162">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR162">
         <v>1.35</v>
@@ -34796,7 +34814,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ163">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR163">
         <v>1.69</v>
@@ -34921,7 +34939,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35127,7 +35145,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35205,7 +35223,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
         <v>0.83</v>
@@ -35411,10 +35429,10 @@
         <v>0.1</v>
       </c>
       <c r="AP166">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ166">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR166">
         <v>1.38</v>
@@ -35539,7 +35557,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35823,7 +35841,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ168">
         <v>0.75</v>
@@ -36032,7 +36050,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ169">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR169">
         <v>1.61</v>
@@ -36157,7 +36175,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36981,7 +36999,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37187,7 +37205,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37471,7 +37489,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ176">
         <v>0.92</v>
@@ -37677,7 +37695,7 @@
         <v>1.3</v>
       </c>
       <c r="AP177">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ177">
         <v>1.27</v>
@@ -37805,7 +37823,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37883,7 +37901,7 @@
         <v>0.64</v>
       </c>
       <c r="AP178">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ178">
         <v>0.83</v>
@@ -38089,10 +38107,10 @@
         <v>1.82</v>
       </c>
       <c r="AP179">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR179">
         <v>1.67</v>
@@ -38217,7 +38235,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38504,7 +38522,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ181">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -38629,7 +38647,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38707,10 +38725,10 @@
         <v>0.09</v>
       </c>
       <c r="AP182">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ182">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AR182">
         <v>1.76</v>
@@ -38835,7 +38853,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39041,7 +39059,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39325,10 +39343,10 @@
         <v>1.73</v>
       </c>
       <c r="AP185">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ185">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39453,7 +39471,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39531,7 +39549,7 @@
         <v>0.73</v>
       </c>
       <c r="AP186">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ186">
         <v>0.75</v>
@@ -39659,7 +39677,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39865,7 +39883,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40071,7 +40089,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40689,7 +40707,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -40846,6 +40864,1036 @@
       </c>
       <c r="BP192">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7453872</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45714.375</v>
+      </c>
+      <c r="F193">
+        <v>25</v>
+      </c>
+      <c r="G193" t="s">
+        <v>81</v>
+      </c>
+      <c r="H193" t="s">
+        <v>78</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>211</v>
+      </c>
+      <c r="P193" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q193">
+        <v>2.03</v>
+      </c>
+      <c r="R193">
+        <v>2.25</v>
+      </c>
+      <c r="S193">
+        <v>6.2</v>
+      </c>
+      <c r="T193">
+        <v>1.38</v>
+      </c>
+      <c r="U193">
+        <v>2.8</v>
+      </c>
+      <c r="V193">
+        <v>2.7</v>
+      </c>
+      <c r="W193">
+        <v>1.41</v>
+      </c>
+      <c r="X193">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>1.1</v>
+      </c>
+      <c r="Z193">
+        <v>1.58</v>
+      </c>
+      <c r="AA193">
+        <v>3.78</v>
+      </c>
+      <c r="AB193">
+        <v>5.8</v>
+      </c>
+      <c r="AC193">
+        <v>1.05</v>
+      </c>
+      <c r="AD193">
+        <v>8.5</v>
+      </c>
+      <c r="AE193">
+        <v>1.31</v>
+      </c>
+      <c r="AF193">
+        <v>3.25</v>
+      </c>
+      <c r="AG193">
+        <v>2.05</v>
+      </c>
+      <c r="AH193">
+        <v>1.65</v>
+      </c>
+      <c r="AI193">
+        <v>2.01</v>
+      </c>
+      <c r="AJ193">
+        <v>1.71</v>
+      </c>
+      <c r="AK193">
+        <v>1.12</v>
+      </c>
+      <c r="AL193">
+        <v>1.21</v>
+      </c>
+      <c r="AM193">
+        <v>2.31</v>
+      </c>
+      <c r="AN193">
+        <v>1.42</v>
+      </c>
+      <c r="AO193">
+        <v>0.33</v>
+      </c>
+      <c r="AP193">
+        <v>1.54</v>
+      </c>
+      <c r="AQ193">
+        <v>0.31</v>
+      </c>
+      <c r="AR193">
+        <v>1.1</v>
+      </c>
+      <c r="AS193">
+        <v>1.16</v>
+      </c>
+      <c r="AT193">
+        <v>2.26</v>
+      </c>
+      <c r="AU193">
+        <v>8</v>
+      </c>
+      <c r="AV193">
+        <v>3</v>
+      </c>
+      <c r="AW193">
+        <v>10</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>23</v>
+      </c>
+      <c r="AZ193">
+        <v>9</v>
+      </c>
+      <c r="BA193">
+        <v>3</v>
+      </c>
+      <c r="BB193">
+        <v>2</v>
+      </c>
+      <c r="BC193">
+        <v>5</v>
+      </c>
+      <c r="BD193">
+        <v>1.37</v>
+      </c>
+      <c r="BE193">
+        <v>8.5</v>
+      </c>
+      <c r="BF193">
+        <v>3.85</v>
+      </c>
+      <c r="BG193">
+        <v>1.6</v>
+      </c>
+      <c r="BH193">
+        <v>2.25</v>
+      </c>
+      <c r="BI193">
+        <v>2.02</v>
+      </c>
+      <c r="BJ193">
+        <v>1.74</v>
+      </c>
+      <c r="BK193">
+        <v>2.6</v>
+      </c>
+      <c r="BL193">
+        <v>1.43</v>
+      </c>
+      <c r="BM193">
+        <v>3.55</v>
+      </c>
+      <c r="BN193">
+        <v>1.23</v>
+      </c>
+      <c r="BO193">
+        <v>4.95</v>
+      </c>
+      <c r="BP193">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7453875</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45714.5</v>
+      </c>
+      <c r="F194">
+        <v>25</v>
+      </c>
+      <c r="G194" t="s">
+        <v>79</v>
+      </c>
+      <c r="H194" t="s">
+        <v>72</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>2</v>
+      </c>
+      <c r="K194">
+        <v>3</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="M194">
+        <v>3</v>
+      </c>
+      <c r="N194">
+        <v>4</v>
+      </c>
+      <c r="O194" t="s">
+        <v>212</v>
+      </c>
+      <c r="P194" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q194">
+        <v>9.4</v>
+      </c>
+      <c r="R194">
+        <v>3.05</v>
+      </c>
+      <c r="S194">
+        <v>1.5</v>
+      </c>
+      <c r="T194">
+        <v>1.2</v>
+      </c>
+      <c r="U194">
+        <v>4</v>
+      </c>
+      <c r="V194">
+        <v>1.94</v>
+      </c>
+      <c r="W194">
+        <v>1.78</v>
+      </c>
+      <c r="X194">
+        <v>4</v>
+      </c>
+      <c r="Y194">
+        <v>1.22</v>
+      </c>
+      <c r="Z194">
+        <v>10</v>
+      </c>
+      <c r="AA194">
+        <v>6.3</v>
+      </c>
+      <c r="AB194">
+        <v>1.23</v>
+      </c>
+      <c r="AC194">
+        <v>1.03</v>
+      </c>
+      <c r="AD194">
+        <v>17</v>
+      </c>
+      <c r="AE194">
+        <v>1.12</v>
+      </c>
+      <c r="AF194">
+        <v>5.6</v>
+      </c>
+      <c r="AG194">
+        <v>1.43</v>
+      </c>
+      <c r="AH194">
+        <v>2.55</v>
+      </c>
+      <c r="AI194">
+        <v>1.87</v>
+      </c>
+      <c r="AJ194">
+        <v>1.82</v>
+      </c>
+      <c r="AK194">
+        <v>3.6</v>
+      </c>
+      <c r="AL194">
+        <v>1.12</v>
+      </c>
+      <c r="AM194">
+        <v>1.04</v>
+      </c>
+      <c r="AN194">
+        <v>1.17</v>
+      </c>
+      <c r="AO194">
+        <v>3</v>
+      </c>
+      <c r="AP194">
+        <v>1.08</v>
+      </c>
+      <c r="AQ194">
+        <v>3</v>
+      </c>
+      <c r="AR194">
+        <v>1.48</v>
+      </c>
+      <c r="AS194">
+        <v>2.22</v>
+      </c>
+      <c r="AT194">
+        <v>3.7</v>
+      </c>
+      <c r="AU194">
+        <v>5</v>
+      </c>
+      <c r="AV194">
+        <v>8</v>
+      </c>
+      <c r="AW194">
+        <v>3</v>
+      </c>
+      <c r="AX194">
+        <v>5</v>
+      </c>
+      <c r="AY194">
+        <v>8</v>
+      </c>
+      <c r="AZ194">
+        <v>14</v>
+      </c>
+      <c r="BA194">
+        <v>4</v>
+      </c>
+      <c r="BB194">
+        <v>5</v>
+      </c>
+      <c r="BC194">
+        <v>9</v>
+      </c>
+      <c r="BD194">
+        <v>4.46</v>
+      </c>
+      <c r="BE194">
+        <v>9</v>
+      </c>
+      <c r="BF194">
+        <v>1.3</v>
+      </c>
+      <c r="BG194">
+        <v>1.5</v>
+      </c>
+      <c r="BH194">
+        <v>2.41</v>
+      </c>
+      <c r="BI194">
+        <v>1.95</v>
+      </c>
+      <c r="BJ194">
+        <v>1.85</v>
+      </c>
+      <c r="BK194">
+        <v>2.42</v>
+      </c>
+      <c r="BL194">
+        <v>1.53</v>
+      </c>
+      <c r="BM194">
+        <v>3.25</v>
+      </c>
+      <c r="BN194">
+        <v>1.29</v>
+      </c>
+      <c r="BO194">
+        <v>4.4</v>
+      </c>
+      <c r="BP194">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7453876</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45714.58680555555</v>
+      </c>
+      <c r="F195">
+        <v>25</v>
+      </c>
+      <c r="G195" t="s">
+        <v>83</v>
+      </c>
+      <c r="H195" t="s">
+        <v>73</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>2</v>
+      </c>
+      <c r="O195" t="s">
+        <v>213</v>
+      </c>
+      <c r="P195" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q195">
+        <v>0</v>
+      </c>
+      <c r="R195">
+        <v>0</v>
+      </c>
+      <c r="S195">
+        <v>0</v>
+      </c>
+      <c r="T195">
+        <v>0</v>
+      </c>
+      <c r="U195">
+        <v>0</v>
+      </c>
+      <c r="V195">
+        <v>0</v>
+      </c>
+      <c r="W195">
+        <v>0</v>
+      </c>
+      <c r="X195">
+        <v>0</v>
+      </c>
+      <c r="Y195">
+        <v>0</v>
+      </c>
+      <c r="Z195">
+        <v>1.44</v>
+      </c>
+      <c r="AA195">
+        <v>4.4</v>
+      </c>
+      <c r="AB195">
+        <v>6.8</v>
+      </c>
+      <c r="AC195">
+        <v>0</v>
+      </c>
+      <c r="AD195">
+        <v>0</v>
+      </c>
+      <c r="AE195">
+        <v>0</v>
+      </c>
+      <c r="AF195">
+        <v>0</v>
+      </c>
+      <c r="AG195">
+        <v>1.85</v>
+      </c>
+      <c r="AH195">
+        <v>1.89</v>
+      </c>
+      <c r="AI195">
+        <v>0</v>
+      </c>
+      <c r="AJ195">
+        <v>0</v>
+      </c>
+      <c r="AK195">
+        <v>0</v>
+      </c>
+      <c r="AL195">
+        <v>0</v>
+      </c>
+      <c r="AM195">
+        <v>0</v>
+      </c>
+      <c r="AN195">
+        <v>1.92</v>
+      </c>
+      <c r="AO195">
+        <v>1.67</v>
+      </c>
+      <c r="AP195">
+        <v>2</v>
+      </c>
+      <c r="AQ195">
+        <v>1.54</v>
+      </c>
+      <c r="AR195">
+        <v>1.71</v>
+      </c>
+      <c r="AS195">
+        <v>0.7</v>
+      </c>
+      <c r="AT195">
+        <v>2.41</v>
+      </c>
+      <c r="AU195">
+        <v>-1</v>
+      </c>
+      <c r="AV195">
+        <v>-1</v>
+      </c>
+      <c r="AW195">
+        <v>-1</v>
+      </c>
+      <c r="AX195">
+        <v>-1</v>
+      </c>
+      <c r="AY195">
+        <v>-1</v>
+      </c>
+      <c r="AZ195">
+        <v>-1</v>
+      </c>
+      <c r="BA195">
+        <v>-1</v>
+      </c>
+      <c r="BB195">
+        <v>-1</v>
+      </c>
+      <c r="BC195">
+        <v>-1</v>
+      </c>
+      <c r="BD195">
+        <v>0</v>
+      </c>
+      <c r="BE195">
+        <v>0</v>
+      </c>
+      <c r="BF195">
+        <v>0</v>
+      </c>
+      <c r="BG195">
+        <v>0</v>
+      </c>
+      <c r="BH195">
+        <v>0</v>
+      </c>
+      <c r="BI195">
+        <v>0</v>
+      </c>
+      <c r="BJ195">
+        <v>0</v>
+      </c>
+      <c r="BK195">
+        <v>0</v>
+      </c>
+      <c r="BL195">
+        <v>0</v>
+      </c>
+      <c r="BM195">
+        <v>0</v>
+      </c>
+      <c r="BN195">
+        <v>0</v>
+      </c>
+      <c r="BO195">
+        <v>0</v>
+      </c>
+      <c r="BP195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7453873</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45714.60416666666</v>
+      </c>
+      <c r="F196">
+        <v>25</v>
+      </c>
+      <c r="G196" t="s">
+        <v>80</v>
+      </c>
+      <c r="H196" t="s">
+        <v>85</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>4</v>
+      </c>
+      <c r="N196">
+        <v>5</v>
+      </c>
+      <c r="O196" t="s">
+        <v>214</v>
+      </c>
+      <c r="P196" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q196">
+        <v>3.85</v>
+      </c>
+      <c r="R196">
+        <v>2.12</v>
+      </c>
+      <c r="S196">
+        <v>2.7</v>
+      </c>
+      <c r="T196">
+        <v>1.42</v>
+      </c>
+      <c r="U196">
+        <v>2.7</v>
+      </c>
+      <c r="V196">
+        <v>2.75</v>
+      </c>
+      <c r="W196">
+        <v>1.4</v>
+      </c>
+      <c r="X196">
+        <v>7.5</v>
+      </c>
+      <c r="Y196">
+        <v>1.08</v>
+      </c>
+      <c r="Z196">
+        <v>3.37</v>
+      </c>
+      <c r="AA196">
+        <v>3.17</v>
+      </c>
+      <c r="AB196">
+        <v>2.19</v>
+      </c>
+      <c r="AC196">
+        <v>1.06</v>
+      </c>
+      <c r="AD196">
+        <v>8</v>
+      </c>
+      <c r="AE196">
+        <v>1.31</v>
+      </c>
+      <c r="AF196">
+        <v>3.3</v>
+      </c>
+      <c r="AG196">
+        <v>1.94</v>
+      </c>
+      <c r="AH196">
+        <v>1.77</v>
+      </c>
+      <c r="AI196">
+        <v>1.74</v>
+      </c>
+      <c r="AJ196">
+        <v>1.97</v>
+      </c>
+      <c r="AK196">
+        <v>1.64</v>
+      </c>
+      <c r="AL196">
+        <v>1.3</v>
+      </c>
+      <c r="AM196">
+        <v>1.3</v>
+      </c>
+      <c r="AN196">
+        <v>1.75</v>
+      </c>
+      <c r="AO196">
+        <v>1.67</v>
+      </c>
+      <c r="AP196">
+        <v>1.62</v>
+      </c>
+      <c r="AQ196">
+        <v>1.77</v>
+      </c>
+      <c r="AR196">
+        <v>1.72</v>
+      </c>
+      <c r="AS196">
+        <v>1.67</v>
+      </c>
+      <c r="AT196">
+        <v>3.39</v>
+      </c>
+      <c r="AU196">
+        <v>2</v>
+      </c>
+      <c r="AV196">
+        <v>11</v>
+      </c>
+      <c r="AW196">
+        <v>4</v>
+      </c>
+      <c r="AX196">
+        <v>9</v>
+      </c>
+      <c r="AY196">
+        <v>8</v>
+      </c>
+      <c r="AZ196">
+        <v>22</v>
+      </c>
+      <c r="BA196">
+        <v>2</v>
+      </c>
+      <c r="BB196">
+        <v>7</v>
+      </c>
+      <c r="BC196">
+        <v>9</v>
+      </c>
+      <c r="BD196">
+        <v>2.28</v>
+      </c>
+      <c r="BE196">
+        <v>8</v>
+      </c>
+      <c r="BF196">
+        <v>1.85</v>
+      </c>
+      <c r="BG196">
+        <v>1.36</v>
+      </c>
+      <c r="BH196">
+        <v>2.92</v>
+      </c>
+      <c r="BI196">
+        <v>1.62</v>
+      </c>
+      <c r="BJ196">
+        <v>2.22</v>
+      </c>
+      <c r="BK196">
+        <v>2.02</v>
+      </c>
+      <c r="BL196">
+        <v>1.74</v>
+      </c>
+      <c r="BM196">
+        <v>2.57</v>
+      </c>
+      <c r="BN196">
+        <v>1.45</v>
+      </c>
+      <c r="BO196">
+        <v>3.42</v>
+      </c>
+      <c r="BP196">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7453874</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45714.64583333334</v>
+      </c>
+      <c r="F197">
+        <v>25</v>
+      </c>
+      <c r="G197" t="s">
+        <v>84</v>
+      </c>
+      <c r="H197" t="s">
+        <v>82</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>2</v>
+      </c>
+      <c r="O197" t="s">
+        <v>173</v>
+      </c>
+      <c r="P197" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q197">
+        <v>3.25</v>
+      </c>
+      <c r="R197">
+        <v>2.11</v>
+      </c>
+      <c r="S197">
+        <v>3.1</v>
+      </c>
+      <c r="T197">
+        <v>1.42</v>
+      </c>
+      <c r="U197">
+        <v>2.7</v>
+      </c>
+      <c r="V197">
+        <v>2.75</v>
+      </c>
+      <c r="W197">
+        <v>1.4</v>
+      </c>
+      <c r="X197">
+        <v>7.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.08</v>
+      </c>
+      <c r="Z197">
+        <v>2.65</v>
+      </c>
+      <c r="AA197">
+        <v>3.17</v>
+      </c>
+      <c r="AB197">
+        <v>2.65</v>
+      </c>
+      <c r="AC197">
+        <v>1.06</v>
+      </c>
+      <c r="AD197">
+        <v>8</v>
+      </c>
+      <c r="AE197">
+        <v>1.3</v>
+      </c>
+      <c r="AF197">
+        <v>3.3</v>
+      </c>
+      <c r="AG197">
+        <v>1.98</v>
+      </c>
+      <c r="AH197">
+        <v>1.77</v>
+      </c>
+      <c r="AI197">
+        <v>1.71</v>
+      </c>
+      <c r="AJ197">
+        <v>2.01</v>
+      </c>
+      <c r="AK197">
+        <v>1.46</v>
+      </c>
+      <c r="AL197">
+        <v>1.31</v>
+      </c>
+      <c r="AM197">
+        <v>1.42</v>
+      </c>
+      <c r="AN197">
+        <v>1.25</v>
+      </c>
+      <c r="AO197">
+        <v>1.67</v>
+      </c>
+      <c r="AP197">
+        <v>1.23</v>
+      </c>
+      <c r="AQ197">
+        <v>1.62</v>
+      </c>
+      <c r="AR197">
+        <v>1.49</v>
+      </c>
+      <c r="AS197">
+        <v>1.41</v>
+      </c>
+      <c r="AT197">
+        <v>2.9</v>
+      </c>
+      <c r="AU197">
+        <v>4</v>
+      </c>
+      <c r="AV197">
+        <v>10</v>
+      </c>
+      <c r="AW197">
+        <v>4</v>
+      </c>
+      <c r="AX197">
+        <v>1</v>
+      </c>
+      <c r="AY197">
+        <v>10</v>
+      </c>
+      <c r="AZ197">
+        <v>11</v>
+      </c>
+      <c r="BA197">
+        <v>5</v>
+      </c>
+      <c r="BB197">
+        <v>6</v>
+      </c>
+      <c r="BC197">
+        <v>11</v>
+      </c>
+      <c r="BD197">
+        <v>1.64</v>
+      </c>
+      <c r="BE197">
+        <v>8</v>
+      </c>
+      <c r="BF197">
+        <v>2.77</v>
+      </c>
+      <c r="BG197">
+        <v>1.43</v>
+      </c>
+      <c r="BH197">
+        <v>2.63</v>
+      </c>
+      <c r="BI197">
+        <v>1.74</v>
+      </c>
+      <c r="BJ197">
+        <v>2.02</v>
+      </c>
+      <c r="BK197">
+        <v>2.22</v>
+      </c>
+      <c r="BL197">
+        <v>1.62</v>
+      </c>
+      <c r="BM197">
+        <v>2.85</v>
+      </c>
+      <c r="BN197">
+        <v>1.37</v>
+      </c>
+      <c r="BO197">
+        <v>3.9</v>
+      </c>
+      <c r="BP197">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -659,6 +659,12 @@
   </si>
   <si>
     <t>['20']</t>
+  </si>
+  <si>
+    <t>['56', '80']</t>
+  </si>
+  <si>
+    <t>['31', '54']</t>
   </si>
   <si>
     <t>['3', '15', '45+3']</t>
@@ -1311,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1567,7 +1573,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1645,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.27</v>
@@ -1851,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ3">
         <v>2</v>
@@ -2185,7 +2191,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2597,7 +2603,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2803,7 +2809,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3087,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9">
         <v>0.92</v>
@@ -3215,7 +3221,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3421,7 +3427,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3627,7 +3633,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4120,7 +4126,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ14">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4326,7 +4332,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ15">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4451,7 +4457,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4529,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ16">
         <v>0.92</v>
@@ -5069,7 +5075,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5353,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ20">
         <v>0.83</v>
@@ -5971,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -6099,7 +6105,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6180,7 +6186,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR24">
         <v>0.98</v>
@@ -6717,7 +6723,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6798,7 +6804,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ27">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6923,7 +6929,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7004,7 +7010,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR28">
         <v>2.33</v>
@@ -7541,7 +7547,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7747,7 +7753,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8031,7 +8037,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ33">
         <v>1.62</v>
@@ -8159,7 +8165,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8649,7 +8655,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ36">
         <v>0.83</v>
@@ -8983,7 +8989,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9061,7 +9067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>1.77</v>
@@ -9270,7 +9276,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9601,7 +9607,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9682,7 +9688,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ41">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9807,7 +9813,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10013,7 +10019,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10219,7 +10225,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10425,7 +10431,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10712,7 +10718,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ46">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR46">
         <v>0.99</v>
@@ -11043,7 +11049,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11121,7 +11127,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ48">
         <v>1.62</v>
@@ -11455,7 +11461,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11533,7 +11539,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ50">
         <v>1.54</v>
@@ -11661,7 +11667,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11739,7 +11745,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>3</v>
@@ -12897,7 +12903,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -12978,7 +12984,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ57">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR57">
         <v>1.94</v>
@@ -13103,7 +13109,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13309,7 +13315,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13515,7 +13521,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13721,7 +13727,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14133,7 +14139,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14211,10 +14217,10 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR63">
         <v>1.81</v>
@@ -14339,7 +14345,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14417,7 +14423,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ64">
         <v>1.54</v>
@@ -14545,7 +14551,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14751,7 +14757,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15241,10 +15247,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -15369,7 +15375,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15781,7 +15787,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15987,7 +15993,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16399,7 +16405,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16811,7 +16817,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17223,7 +17229,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17304,7 +17310,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ78">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR78">
         <v>1.57</v>
@@ -17429,7 +17435,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17713,10 +17719,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -17841,7 +17847,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18047,7 +18053,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18128,7 +18134,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18253,7 +18259,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18331,10 +18337,10 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR83">
         <v>1.12</v>
@@ -18459,7 +18465,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18665,7 +18671,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18949,7 +18955,7 @@
         <v>0.2</v>
       </c>
       <c r="AP86">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ86">
         <v>0.31</v>
@@ -19077,7 +19083,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19489,7 +19495,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19567,7 +19573,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ89">
         <v>1.42</v>
@@ -19901,7 +19907,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20519,7 +20525,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20806,7 +20812,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR95">
         <v>1.17</v>
@@ -21009,7 +21015,7 @@
         <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>0.31</v>
@@ -21218,7 +21224,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR97">
         <v>1.33</v>
@@ -21424,7 +21430,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -21549,7 +21555,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21755,7 +21761,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21961,7 +21967,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22039,7 +22045,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ101">
         <v>1.25</v>
@@ -22167,7 +22173,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22373,7 +22379,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22863,7 +22869,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.08</v>
@@ -23197,7 +23203,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23275,7 +23281,7 @@
         <v>2.17</v>
       </c>
       <c r="AP107">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ107">
         <v>2</v>
@@ -23609,7 +23615,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24021,7 +24027,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24102,7 +24108,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ111">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -24227,7 +24233,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24308,7 +24314,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ112">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR112">
         <v>1.19</v>
@@ -24514,7 +24520,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ113">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR113">
         <v>1.01</v>
@@ -24923,7 +24929,7 @@
         <v>0.14</v>
       </c>
       <c r="AP115">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ115">
         <v>0.31</v>
@@ -25051,7 +25057,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25257,7 +25263,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25463,7 +25469,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25669,7 +25675,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25750,7 +25756,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ119">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR119">
         <v>1.78</v>
@@ -25875,7 +25881,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -25956,7 +25962,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR120">
         <v>1.05</v>
@@ -26162,7 +26168,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ121">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR121">
         <v>1.85</v>
@@ -26699,7 +26705,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26905,7 +26911,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27111,7 +27117,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27523,7 +27529,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27601,7 +27607,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ128">
         <v>1.27</v>
@@ -27729,7 +27735,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27807,7 +27813,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>0.92</v>
@@ -28141,7 +28147,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28425,7 +28431,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ132">
         <v>0.75</v>
@@ -28759,7 +28765,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29046,7 +29052,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ135">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR135">
         <v>1.93</v>
@@ -29171,7 +29177,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29458,7 +29464,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ137">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR137">
         <v>1.8</v>
@@ -29789,7 +29795,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29995,7 +30001,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30076,7 +30082,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ140">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR140">
         <v>1.53</v>
@@ -30201,7 +30207,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30407,7 +30413,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30613,7 +30619,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31231,7 +31237,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31309,7 +31315,7 @@
         <v>0.78</v>
       </c>
       <c r="AP146">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ146">
         <v>0.75</v>
@@ -31437,7 +31443,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31643,7 +31649,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31849,7 +31855,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -31927,7 +31933,7 @@
         <v>1.67</v>
       </c>
       <c r="AP149">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ149">
         <v>1.77</v>
@@ -32133,7 +32139,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ150">
         <v>0.83</v>
@@ -32261,7 +32267,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32467,7 +32473,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32673,7 +32679,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32754,7 +32760,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ153">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR153">
         <v>1.01</v>
@@ -33085,7 +33091,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33578,7 +33584,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ157">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR157">
         <v>1.13</v>
@@ -33703,7 +33709,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33784,7 +33790,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ158">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR158">
         <v>2</v>
@@ -33909,7 +33915,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34115,7 +34121,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34321,7 +34327,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34605,7 +34611,7 @@
         <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ162">
         <v>1.77</v>
@@ -34939,7 +34945,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35020,7 +35026,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ164">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR164">
         <v>1.67</v>
@@ -35145,7 +35151,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35557,7 +35563,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35635,7 +35641,7 @@
         <v>3</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ167">
         <v>3</v>
@@ -36047,7 +36053,7 @@
         <v>2</v>
       </c>
       <c r="AP169">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
         <v>1.62</v>
@@ -36175,7 +36181,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36256,7 +36262,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ170">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR170">
         <v>1.25</v>
@@ -36999,7 +37005,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37080,7 +37086,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ174">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR174">
         <v>1.18</v>
@@ -37205,7 +37211,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37823,7 +37829,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38235,7 +38241,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38313,7 +38319,7 @@
         <v>3</v>
       </c>
       <c r="AP180">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ180">
         <v>3</v>
@@ -38519,7 +38525,7 @@
         <v>1.82</v>
       </c>
       <c r="AP181">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.54</v>
@@ -38647,7 +38653,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38853,7 +38859,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -38931,10 +38937,10 @@
         <v>0.64</v>
       </c>
       <c r="AP183">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ183">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR183">
         <v>1.95</v>
@@ -39059,7 +39065,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39140,7 +39146,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ184">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR184">
         <v>1.73</v>
@@ -39471,7 +39477,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39677,7 +39683,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39883,7 +39889,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40089,7 +40095,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40582,7 +40588,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ191">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR191">
         <v>1.17</v>
@@ -40707,7 +40713,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -41119,7 +41125,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41531,7 +41537,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41737,7 +41743,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -41894,6 +41900,624 @@
       </c>
       <c r="BP197">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7453877</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45715.54166666666</v>
+      </c>
+      <c r="F198">
+        <v>25</v>
+      </c>
+      <c r="G198" t="s">
+        <v>71</v>
+      </c>
+      <c r="H198" t="s">
+        <v>76</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>192</v>
+      </c>
+      <c r="P198" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q198">
+        <v>2.4</v>
+      </c>
+      <c r="R198">
+        <v>2.05</v>
+      </c>
+      <c r="S198">
+        <v>4.75</v>
+      </c>
+      <c r="T198">
+        <v>1.44</v>
+      </c>
+      <c r="U198">
+        <v>2.63</v>
+      </c>
+      <c r="V198">
+        <v>3.25</v>
+      </c>
+      <c r="W198">
+        <v>1.33</v>
+      </c>
+      <c r="X198">
+        <v>7.5</v>
+      </c>
+      <c r="Y198">
+        <v>1.07</v>
+      </c>
+      <c r="Z198">
+        <v>1.8</v>
+      </c>
+      <c r="AA198">
+        <v>3.4</v>
+      </c>
+      <c r="AB198">
+        <v>4.2</v>
+      </c>
+      <c r="AC198">
+        <v>1.06</v>
+      </c>
+      <c r="AD198">
+        <v>8</v>
+      </c>
+      <c r="AE198">
+        <v>1.36</v>
+      </c>
+      <c r="AF198">
+        <v>3</v>
+      </c>
+      <c r="AG198">
+        <v>2</v>
+      </c>
+      <c r="AH198">
+        <v>1.65</v>
+      </c>
+      <c r="AI198">
+        <v>2</v>
+      </c>
+      <c r="AJ198">
+        <v>1.73</v>
+      </c>
+      <c r="AK198">
+        <v>1.19</v>
+      </c>
+      <c r="AL198">
+        <v>1.26</v>
+      </c>
+      <c r="AM198">
+        <v>1.85</v>
+      </c>
+      <c r="AN198">
+        <v>1.17</v>
+      </c>
+      <c r="AO198">
+        <v>0.83</v>
+      </c>
+      <c r="AP198">
+        <v>1.15</v>
+      </c>
+      <c r="AQ198">
+        <v>0.85</v>
+      </c>
+      <c r="AR198">
+        <v>1.34</v>
+      </c>
+      <c r="AS198">
+        <v>1.07</v>
+      </c>
+      <c r="AT198">
+        <v>2.41</v>
+      </c>
+      <c r="AU198">
+        <v>7</v>
+      </c>
+      <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>11</v>
+      </c>
+      <c r="AX198">
+        <v>7</v>
+      </c>
+      <c r="AY198">
+        <v>22</v>
+      </c>
+      <c r="AZ198">
+        <v>13</v>
+      </c>
+      <c r="BA198">
+        <v>5</v>
+      </c>
+      <c r="BB198">
+        <v>1</v>
+      </c>
+      <c r="BC198">
+        <v>6</v>
+      </c>
+      <c r="BD198">
+        <v>1.91</v>
+      </c>
+      <c r="BE198">
+        <v>7.5</v>
+      </c>
+      <c r="BF198">
+        <v>2.2</v>
+      </c>
+      <c r="BG198">
+        <v>1.59</v>
+      </c>
+      <c r="BH198">
+        <v>2.15</v>
+      </c>
+      <c r="BI198">
+        <v>2.03</v>
+      </c>
+      <c r="BJ198">
+        <v>1.7</v>
+      </c>
+      <c r="BK198">
+        <v>2.55</v>
+      </c>
+      <c r="BL198">
+        <v>1.42</v>
+      </c>
+      <c r="BM198">
+        <v>3.5</v>
+      </c>
+      <c r="BN198">
+        <v>1.24</v>
+      </c>
+      <c r="BO198">
+        <v>4.9</v>
+      </c>
+      <c r="BP198">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7453878</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45715.60416666666</v>
+      </c>
+      <c r="F199">
+        <v>25</v>
+      </c>
+      <c r="G199" t="s">
+        <v>70</v>
+      </c>
+      <c r="H199" t="s">
+        <v>75</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>2</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>215</v>
+      </c>
+      <c r="P199" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q199">
+        <v>2.1</v>
+      </c>
+      <c r="R199">
+        <v>2.3</v>
+      </c>
+      <c r="S199">
+        <v>5</v>
+      </c>
+      <c r="T199">
+        <v>1.33</v>
+      </c>
+      <c r="U199">
+        <v>3.25</v>
+      </c>
+      <c r="V199">
+        <v>2.5</v>
+      </c>
+      <c r="W199">
+        <v>1.5</v>
+      </c>
+      <c r="X199">
+        <v>5.5</v>
+      </c>
+      <c r="Y199">
+        <v>1.13</v>
+      </c>
+      <c r="Z199">
+        <v>1.81</v>
+      </c>
+      <c r="AA199">
+        <v>3.59</v>
+      </c>
+      <c r="AB199">
+        <v>4.2</v>
+      </c>
+      <c r="AC199">
+        <v>1.04</v>
+      </c>
+      <c r="AD199">
+        <v>9</v>
+      </c>
+      <c r="AE199">
+        <v>1.21</v>
+      </c>
+      <c r="AF199">
+        <v>4.1</v>
+      </c>
+      <c r="AG199">
+        <v>1.92</v>
+      </c>
+      <c r="AH199">
+        <v>1.82</v>
+      </c>
+      <c r="AI199">
+        <v>1.73</v>
+      </c>
+      <c r="AJ199">
+        <v>2</v>
+      </c>
+      <c r="AK199">
+        <v>1.16</v>
+      </c>
+      <c r="AL199">
+        <v>1.21</v>
+      </c>
+      <c r="AM199">
+        <v>2.2</v>
+      </c>
+      <c r="AN199">
+        <v>1.92</v>
+      </c>
+      <c r="AO199">
+        <v>1.25</v>
+      </c>
+      <c r="AP199">
+        <v>2</v>
+      </c>
+      <c r="AQ199">
+        <v>1.15</v>
+      </c>
+      <c r="AR199">
+        <v>1.64</v>
+      </c>
+      <c r="AS199">
+        <v>1.32</v>
+      </c>
+      <c r="AT199">
+        <v>2.96</v>
+      </c>
+      <c r="AU199">
+        <v>5</v>
+      </c>
+      <c r="AV199">
+        <v>2</v>
+      </c>
+      <c r="AW199">
+        <v>5</v>
+      </c>
+      <c r="AX199">
+        <v>4</v>
+      </c>
+      <c r="AY199">
+        <v>12</v>
+      </c>
+      <c r="AZ199">
+        <v>6</v>
+      </c>
+      <c r="BA199">
+        <v>6</v>
+      </c>
+      <c r="BB199">
+        <v>3</v>
+      </c>
+      <c r="BC199">
+        <v>9</v>
+      </c>
+      <c r="BD199">
+        <v>1.41</v>
+      </c>
+      <c r="BE199">
+        <v>9</v>
+      </c>
+      <c r="BF199">
+        <v>3.58</v>
+      </c>
+      <c r="BG199">
+        <v>1.32</v>
+      </c>
+      <c r="BH199">
+        <v>3</v>
+      </c>
+      <c r="BI199">
+        <v>1.55</v>
+      </c>
+      <c r="BJ199">
+        <v>2.23</v>
+      </c>
+      <c r="BK199">
+        <v>2</v>
+      </c>
+      <c r="BL199">
+        <v>1.8</v>
+      </c>
+      <c r="BM199">
+        <v>2.4</v>
+      </c>
+      <c r="BN199">
+        <v>1.48</v>
+      </c>
+      <c r="BO199">
+        <v>3.2</v>
+      </c>
+      <c r="BP199">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7453879</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45715.625</v>
+      </c>
+      <c r="F200">
+        <v>25</v>
+      </c>
+      <c r="G200" t="s">
+        <v>77</v>
+      </c>
+      <c r="H200" t="s">
+        <v>74</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>2</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>3</v>
+      </c>
+      <c r="O200" t="s">
+        <v>216</v>
+      </c>
+      <c r="P200" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q200">
+        <v>3.1</v>
+      </c>
+      <c r="R200">
+        <v>2.05</v>
+      </c>
+      <c r="S200">
+        <v>3.25</v>
+      </c>
+      <c r="T200">
+        <v>1.44</v>
+      </c>
+      <c r="U200">
+        <v>2.63</v>
+      </c>
+      <c r="V200">
+        <v>3</v>
+      </c>
+      <c r="W200">
+        <v>1.36</v>
+      </c>
+      <c r="X200">
+        <v>7</v>
+      </c>
+      <c r="Y200">
+        <v>1.08</v>
+      </c>
+      <c r="Z200">
+        <v>2.09</v>
+      </c>
+      <c r="AA200">
+        <v>3.39</v>
+      </c>
+      <c r="AB200">
+        <v>3.39</v>
+      </c>
+      <c r="AC200">
+        <v>1.05</v>
+      </c>
+      <c r="AD200">
+        <v>8.5</v>
+      </c>
+      <c r="AE200">
+        <v>1.31</v>
+      </c>
+      <c r="AF200">
+        <v>3.25</v>
+      </c>
+      <c r="AG200">
+        <v>1.89</v>
+      </c>
+      <c r="AH200">
+        <v>1.85</v>
+      </c>
+      <c r="AI200">
+        <v>1.8</v>
+      </c>
+      <c r="AJ200">
+        <v>1.91</v>
+      </c>
+      <c r="AK200">
+        <v>1.46</v>
+      </c>
+      <c r="AL200">
+        <v>1.28</v>
+      </c>
+      <c r="AM200">
+        <v>1.47</v>
+      </c>
+      <c r="AN200">
+        <v>1.08</v>
+      </c>
+      <c r="AO200">
+        <v>1.42</v>
+      </c>
+      <c r="AP200">
+        <v>1.23</v>
+      </c>
+      <c r="AQ200">
+        <v>1.31</v>
+      </c>
+      <c r="AR200">
+        <v>1.97</v>
+      </c>
+      <c r="AS200">
+        <v>1.42</v>
+      </c>
+      <c r="AT200">
+        <v>3.39</v>
+      </c>
+      <c r="AU200">
+        <v>6</v>
+      </c>
+      <c r="AV200">
+        <v>2</v>
+      </c>
+      <c r="AW200">
+        <v>12</v>
+      </c>
+      <c r="AX200">
+        <v>4</v>
+      </c>
+      <c r="AY200">
+        <v>23</v>
+      </c>
+      <c r="AZ200">
+        <v>6</v>
+      </c>
+      <c r="BA200">
+        <v>8</v>
+      </c>
+      <c r="BB200">
+        <v>2</v>
+      </c>
+      <c r="BC200">
+        <v>10</v>
+      </c>
+      <c r="BD200">
+        <v>1.75</v>
+      </c>
+      <c r="BE200">
+        <v>7.5</v>
+      </c>
+      <c r="BF200">
+        <v>2.45</v>
+      </c>
+      <c r="BG200">
+        <v>1.53</v>
+      </c>
+      <c r="BH200">
+        <v>2.27</v>
+      </c>
+      <c r="BI200">
+        <v>2</v>
+      </c>
+      <c r="BJ200">
+        <v>1.8</v>
+      </c>
+      <c r="BK200">
+        <v>2.43</v>
+      </c>
+      <c r="BL200">
+        <v>1.47</v>
+      </c>
+      <c r="BM200">
+        <v>3.2</v>
+      </c>
+      <c r="BN200">
+        <v>1.27</v>
+      </c>
+      <c r="BO200">
+        <v>4.5</v>
+      </c>
+      <c r="BP200">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -42466,7 +42466,7 @@
         <v>4</v>
       </c>
       <c r="AY200">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ200">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -41424,31 +41424,31 @@
         <v>2.41</v>
       </c>
       <c r="AU195">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AV195">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW195">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AX195">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY195">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="AZ195">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA195">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB195">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC195">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD195">
         <v>0</v>
@@ -41854,13 +41854,13 @@
         <v>11</v>
       </c>
       <c r="BA197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB197">
         <v>6</v>
       </c>
       <c r="BC197">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD197">
         <v>1.64</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -667,6 +667,9 @@
     <t>['31', '54']</t>
   </si>
   <si>
+    <t>['28', '79']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -956,6 +959,9 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['32', '36', '64', '82']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1579,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1860,7 +1866,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2191,7 +2197,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2478,7 +2484,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2603,7 +2609,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2809,7 +2815,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2887,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ8">
         <v>1.77</v>
@@ -3221,7 +3227,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3302,7 +3308,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3427,7 +3433,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3633,7 +3639,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4329,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>0.85</v>
@@ -4457,7 +4463,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5075,7 +5081,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5153,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -5980,7 +5986,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR23">
         <v>1.76</v>
@@ -6105,7 +6111,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6183,7 +6189,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1.31</v>
@@ -6723,7 +6729,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6929,7 +6935,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7422,7 +7428,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ30">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7547,7 +7553,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7753,7 +7759,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8165,7 +8171,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8449,7 +8455,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ35">
         <v>0.31</v>
@@ -8989,7 +8995,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9607,7 +9613,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9685,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41">
         <v>1.15</v>
@@ -9813,7 +9819,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10019,7 +10025,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10097,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
         <v>1.42</v>
@@ -10225,7 +10231,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10431,7 +10437,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10512,7 +10518,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ45">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -11049,7 +11055,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11461,7 +11467,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11667,7 +11673,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12903,7 +12909,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13109,7 +13115,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13187,10 +13193,10 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13315,7 +13321,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13393,7 +13399,7 @@
         <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -13521,7 +13527,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13602,7 +13608,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ60">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR60">
         <v>0.73</v>
@@ -13727,7 +13733,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14139,7 +14145,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14345,7 +14351,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14551,7 +14557,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14757,7 +14763,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15375,7 +15381,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15787,7 +15793,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15865,7 +15871,7 @@
         <v>0.8</v>
       </c>
       <c r="AP71">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
         <v>0.92</v>
@@ -15993,7 +15999,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16405,7 +16411,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16486,7 +16492,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ74">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR74">
         <v>1.34</v>
@@ -16689,7 +16695,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ75">
         <v>1.08</v>
@@ -16817,7 +16823,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16898,7 +16904,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -17229,7 +17235,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17435,7 +17441,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17847,7 +17853,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18053,7 +18059,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18259,7 +18265,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18465,7 +18471,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18671,7 +18677,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19083,7 +19089,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19164,7 +19170,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ87">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR87">
         <v>2.4</v>
@@ -19495,7 +19501,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19779,7 +19785,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ90">
         <v>0.83</v>
@@ -19907,7 +19913,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -19985,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ91">
         <v>1.27</v>
@@ -20525,7 +20531,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20606,7 +20612,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ94">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR94">
         <v>1.84</v>
@@ -21555,7 +21561,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21761,7 +21767,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21967,7 +21973,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22173,7 +22179,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22379,7 +22385,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22457,10 +22463,10 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -23203,7 +23209,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23284,7 +23290,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ107">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR107">
         <v>1.95</v>
@@ -23615,7 +23621,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24027,7 +24033,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24233,7 +24239,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25057,7 +25063,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25263,7 +25269,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25469,7 +25475,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25547,7 +25553,7 @@
         <v>3</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ118">
         <v>3</v>
@@ -25675,7 +25681,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25881,7 +25887,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26371,7 +26377,7 @@
         <v>2.14</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122">
         <v>1.54</v>
@@ -26705,7 +26711,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26911,7 +26917,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27117,7 +27123,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27401,7 +27407,7 @@
         <v>2.13</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ127">
         <v>1.62</v>
@@ -27529,7 +27535,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27735,7 +27741,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28147,7 +28153,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28434,7 +28440,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ132">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR132">
         <v>1.95</v>
@@ -28640,7 +28646,7 @@
         <v>2</v>
       </c>
       <c r="AQ133">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28765,7 +28771,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -29177,7 +29183,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29795,7 +29801,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29876,7 +29882,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ139">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR139">
         <v>1.32</v>
@@ -30001,7 +30007,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30079,7 +30085,7 @@
         <v>0.88</v>
       </c>
       <c r="AP140">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ140">
         <v>1.15</v>
@@ -30207,7 +30213,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30413,7 +30419,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30619,7 +30625,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30700,7 +30706,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR143">
         <v>1.05</v>
@@ -30903,7 +30909,7 @@
         <v>2.11</v>
       </c>
       <c r="AP144">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ144">
         <v>1.54</v>
@@ -31237,7 +31243,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31318,7 +31324,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ146">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31443,7 +31449,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31649,7 +31655,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31855,7 +31861,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32267,7 +32273,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32473,7 +32479,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32679,7 +32685,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33091,7 +33097,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33378,7 +33384,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ156">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR156">
         <v>1.72</v>
@@ -33709,7 +33715,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33915,7 +33921,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34121,7 +34127,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34199,7 +34205,7 @@
         <v>1.38</v>
       </c>
       <c r="AP160">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ160">
         <v>1.25</v>
@@ -34327,7 +34333,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34945,7 +34951,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35151,7 +35157,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35563,7 +35569,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35850,7 +35856,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ168">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36181,7 +36187,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36259,7 +36265,7 @@
         <v>1.1</v>
       </c>
       <c r="AP170">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ170">
         <v>1.31</v>
@@ -36880,7 +36886,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ173">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR173">
         <v>1.77</v>
@@ -37005,7 +37011,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37211,7 +37217,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37289,7 +37295,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ175">
         <v>1.08</v>
@@ -37829,7 +37835,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38241,7 +38247,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38653,7 +38659,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38859,7 +38865,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39065,7 +39071,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39477,7 +39483,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39558,7 +39564,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ186">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR186">
         <v>1.05</v>
@@ -39683,7 +39689,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39761,7 +39767,7 @@
         <v>1.27</v>
       </c>
       <c r="AP187">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ187">
         <v>1.42</v>
@@ -39889,7 +39895,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40095,7 +40101,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40176,7 +40182,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ189">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR189">
         <v>2.16</v>
@@ -40713,7 +40719,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -41125,7 +41131,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41537,7 +41543,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41743,7 +41749,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42518,6 +42524,418 @@
       </c>
       <c r="BP200">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7453886</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45718.375</v>
+      </c>
+      <c r="F201">
+        <v>26</v>
+      </c>
+      <c r="G201" t="s">
+        <v>82</v>
+      </c>
+      <c r="H201" t="s">
+        <v>80</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>2</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>2</v>
+      </c>
+      <c r="O201" t="s">
+        <v>217</v>
+      </c>
+      <c r="P201" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q201">
+        <v>2.6</v>
+      </c>
+      <c r="R201">
+        <v>2.1</v>
+      </c>
+      <c r="S201">
+        <v>3.9</v>
+      </c>
+      <c r="T201">
+        <v>1.38</v>
+      </c>
+      <c r="U201">
+        <v>2.8</v>
+      </c>
+      <c r="V201">
+        <v>2.65</v>
+      </c>
+      <c r="W201">
+        <v>1.42</v>
+      </c>
+      <c r="X201">
+        <v>6.5</v>
+      </c>
+      <c r="Y201">
+        <v>1.1</v>
+      </c>
+      <c r="Z201">
+        <v>2.11</v>
+      </c>
+      <c r="AA201">
+        <v>3.28</v>
+      </c>
+      <c r="AB201">
+        <v>3.41</v>
+      </c>
+      <c r="AC201">
+        <v>1.05</v>
+      </c>
+      <c r="AD201">
+        <v>8.5</v>
+      </c>
+      <c r="AE201">
+        <v>1.28</v>
+      </c>
+      <c r="AF201">
+        <v>3.4</v>
+      </c>
+      <c r="AG201">
+        <v>1.85</v>
+      </c>
+      <c r="AH201">
+        <v>1.89</v>
+      </c>
+      <c r="AI201">
+        <v>1.67</v>
+      </c>
+      <c r="AJ201">
+        <v>2</v>
+      </c>
+      <c r="AK201">
+        <v>1.3</v>
+      </c>
+      <c r="AL201">
+        <v>1.25</v>
+      </c>
+      <c r="AM201">
+        <v>1.7</v>
+      </c>
+      <c r="AN201">
+        <v>1.18</v>
+      </c>
+      <c r="AO201">
+        <v>0.75</v>
+      </c>
+      <c r="AP201">
+        <v>1.33</v>
+      </c>
+      <c r="AQ201">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR201">
+        <v>1.57</v>
+      </c>
+      <c r="AS201">
+        <v>1.42</v>
+      </c>
+      <c r="AT201">
+        <v>2.99</v>
+      </c>
+      <c r="AU201">
+        <v>9</v>
+      </c>
+      <c r="AV201">
+        <v>3</v>
+      </c>
+      <c r="AW201">
+        <v>10</v>
+      </c>
+      <c r="AX201">
+        <v>10</v>
+      </c>
+      <c r="AY201">
+        <v>19</v>
+      </c>
+      <c r="AZ201">
+        <v>13</v>
+      </c>
+      <c r="BA201">
+        <v>6</v>
+      </c>
+      <c r="BB201">
+        <v>5</v>
+      </c>
+      <c r="BC201">
+        <v>11</v>
+      </c>
+      <c r="BD201">
+        <v>0</v>
+      </c>
+      <c r="BE201">
+        <v>0</v>
+      </c>
+      <c r="BF201">
+        <v>0</v>
+      </c>
+      <c r="BG201">
+        <v>0</v>
+      </c>
+      <c r="BH201">
+        <v>0</v>
+      </c>
+      <c r="BI201">
+        <v>0</v>
+      </c>
+      <c r="BJ201">
+        <v>0</v>
+      </c>
+      <c r="BK201">
+        <v>0</v>
+      </c>
+      <c r="BL201">
+        <v>0</v>
+      </c>
+      <c r="BM201">
+        <v>0</v>
+      </c>
+      <c r="BN201">
+        <v>0</v>
+      </c>
+      <c r="BO201">
+        <v>0</v>
+      </c>
+      <c r="BP201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7453883</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F202">
+        <v>26</v>
+      </c>
+      <c r="G202" t="s">
+        <v>76</v>
+      </c>
+      <c r="H202" t="s">
+        <v>83</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>2</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>4</v>
+      </c>
+      <c r="N202">
+        <v>5</v>
+      </c>
+      <c r="O202" t="s">
+        <v>119</v>
+      </c>
+      <c r="P202" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q202">
+        <v>7</v>
+      </c>
+      <c r="R202">
+        <v>2.3</v>
+      </c>
+      <c r="S202">
+        <v>1.85</v>
+      </c>
+      <c r="T202">
+        <v>1.35</v>
+      </c>
+      <c r="U202">
+        <v>2.95</v>
+      </c>
+      <c r="V202">
+        <v>2.6</v>
+      </c>
+      <c r="W202">
+        <v>1.44</v>
+      </c>
+      <c r="X202">
+        <v>6.5</v>
+      </c>
+      <c r="Y202">
+        <v>1.11</v>
+      </c>
+      <c r="Z202">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA202">
+        <v>3.59</v>
+      </c>
+      <c r="AB202">
+        <v>1.5</v>
+      </c>
+      <c r="AC202">
+        <v>1.05</v>
+      </c>
+      <c r="AD202">
+        <v>8.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.28</v>
+      </c>
+      <c r="AF202">
+        <v>3.4</v>
+      </c>
+      <c r="AG202">
+        <v>1.83</v>
+      </c>
+      <c r="AH202">
+        <v>1.91</v>
+      </c>
+      <c r="AI202">
+        <v>1.93</v>
+      </c>
+      <c r="AJ202">
+        <v>1.73</v>
+      </c>
+      <c r="AK202">
+        <v>2.6</v>
+      </c>
+      <c r="AL202">
+        <v>1.2</v>
+      </c>
+      <c r="AM202">
+        <v>1.05</v>
+      </c>
+      <c r="AN202">
+        <v>1.17</v>
+      </c>
+      <c r="AO202">
+        <v>2</v>
+      </c>
+      <c r="AP202">
+        <v>1.08</v>
+      </c>
+      <c r="AQ202">
+        <v>2.08</v>
+      </c>
+      <c r="AR202">
+        <v>1.22</v>
+      </c>
+      <c r="AS202">
+        <v>1.29</v>
+      </c>
+      <c r="AT202">
+        <v>2.51</v>
+      </c>
+      <c r="AU202">
+        <v>5</v>
+      </c>
+      <c r="AV202">
+        <v>6</v>
+      </c>
+      <c r="AW202">
+        <v>6</v>
+      </c>
+      <c r="AX202">
+        <v>6</v>
+      </c>
+      <c r="AY202">
+        <v>12</v>
+      </c>
+      <c r="AZ202">
+        <v>12</v>
+      </c>
+      <c r="BA202">
+        <v>3</v>
+      </c>
+      <c r="BB202">
+        <v>1</v>
+      </c>
+      <c r="BC202">
+        <v>4</v>
+      </c>
+      <c r="BD202">
+        <v>0</v>
+      </c>
+      <c r="BE202">
+        <v>0</v>
+      </c>
+      <c r="BF202">
+        <v>0</v>
+      </c>
+      <c r="BG202">
+        <v>0</v>
+      </c>
+      <c r="BH202">
+        <v>0</v>
+      </c>
+      <c r="BI202">
+        <v>0</v>
+      </c>
+      <c r="BJ202">
+        <v>0</v>
+      </c>
+      <c r="BK202">
+        <v>0</v>
+      </c>
+      <c r="BL202">
+        <v>0</v>
+      </c>
+      <c r="BM202">
+        <v>0</v>
+      </c>
+      <c r="BN202">
+        <v>0</v>
+      </c>
+      <c r="BO202">
+        <v>0</v>
+      </c>
+      <c r="BP202">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,12 @@
     <t>['28', '79']</t>
   </si>
   <si>
+    <t>['20', '46', '70', '81']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -862,9 +868,6 @@
     <t>['14', '47']</t>
   </si>
   <si>
-    <t>['80']</t>
-  </si>
-  <si>
     <t>['24', '67']</t>
   </si>
   <si>
@@ -962,6 +965,9 @@
   </si>
   <si>
     <t>['32', '36', '64', '82']</t>
+  </si>
+  <si>
+    <t>['37', '48', '57']</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1579,7 +1585,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2069,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ4">
         <v>0.31</v>
@@ -2197,7 +2203,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2609,7 +2615,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2690,7 +2696,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2815,7 +2821,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3102,7 +3108,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3227,7 +3233,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3433,7 +3439,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3639,7 +3645,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3717,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ12">
         <v>1.54</v>
@@ -4463,7 +4469,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4544,7 +4550,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ16">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR16">
         <v>1.02</v>
@@ -5081,7 +5087,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5368,7 +5374,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ20">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -6111,7 +6117,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6729,7 +6735,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6935,7 +6941,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7013,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ28">
         <v>1.15</v>
@@ -7553,7 +7559,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7631,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>1.25</v>
@@ -7759,7 +7765,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8171,7 +8177,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8664,7 +8670,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ36">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.22</v>
@@ -8870,7 +8876,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ37">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR37">
         <v>1.6</v>
@@ -8995,7 +9001,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9613,7 +9619,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9819,7 +9825,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9900,7 +9906,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ42">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR42">
         <v>0.6</v>
@@ -10025,7 +10031,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10231,7 +10237,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10309,7 +10315,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>1.08</v>
@@ -10437,7 +10443,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11055,7 +11061,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11342,7 +11348,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.36</v>
@@ -11467,7 +11473,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11673,7 +11679,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12166,7 +12172,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ53">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12369,7 +12375,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
         <v>1.27</v>
@@ -12781,7 +12787,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ56">
         <v>1.08</v>
@@ -12909,7 +12915,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13115,7 +13121,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13321,7 +13327,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13527,7 +13533,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13733,7 +13739,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14145,7 +14151,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14351,7 +14357,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14557,7 +14563,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14763,7 +14769,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14844,7 +14850,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ66">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15381,7 +15387,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15665,7 +15671,7 @@
         <v>1.2</v>
       </c>
       <c r="AP70">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ70">
         <v>1.27</v>
@@ -15793,7 +15799,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15874,7 +15880,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -15999,7 +16005,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16411,7 +16417,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16489,7 +16495,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
         <v>0.6899999999999999</v>
@@ -16823,7 +16829,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17110,7 +17116,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ77">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>0.96</v>
@@ -17235,7 +17241,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17313,7 +17319,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>1.15</v>
@@ -17441,7 +17447,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17853,7 +17859,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18059,7 +18065,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18265,7 +18271,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18471,7 +18477,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18677,7 +18683,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19089,7 +19095,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19167,7 +19173,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ87">
         <v>0.6899999999999999</v>
@@ -19501,7 +19507,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19788,7 +19794,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ90">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19913,7 +19919,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20406,7 +20412,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ93">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -20531,7 +20537,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21561,7 +21567,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21767,7 +21773,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21845,7 +21851,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>1.62</v>
@@ -21973,7 +21979,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22179,7 +22185,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22385,7 +22391,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22672,7 +22678,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR104">
         <v>1.79</v>
@@ -23081,7 +23087,7 @@
         <v>1.71</v>
       </c>
       <c r="AP106">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ106">
         <v>1.77</v>
@@ -23209,7 +23215,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23496,7 +23502,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ108">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>0.6899999999999999</v>
@@ -23621,7 +23627,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24033,7 +24039,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24239,7 +24245,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24729,7 +24735,7 @@
         <v>2.33</v>
       </c>
       <c r="AP114">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>1.54</v>
@@ -25063,7 +25069,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25269,7 +25275,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25475,7 +25481,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25681,7 +25687,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25887,7 +25893,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26171,7 +26177,7 @@
         <v>0.43</v>
       </c>
       <c r="AP121">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ121">
         <v>0.85</v>
@@ -26711,7 +26717,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26917,7 +26923,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27123,7 +27129,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27204,7 +27210,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ126">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR126">
         <v>1.56</v>
@@ -27535,7 +27541,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27741,7 +27747,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27822,7 +27828,7 @@
         <v>2</v>
       </c>
       <c r="AQ129">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR129">
         <v>1.62</v>
@@ -28153,7 +28159,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28771,7 +28777,7 @@
         <v>180</v>
       </c>
       <c r="P134" t="s">
-        <v>282</v>
+        <v>219</v>
       </c>
       <c r="Q134">
         <v>1.62</v>
@@ -28849,7 +28855,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ134">
         <v>1.25</v>
@@ -29055,7 +29061,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ135">
         <v>0.85</v>
@@ -29183,7 +29189,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29467,7 +29473,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
         <v>1.31</v>
@@ -29801,7 +29807,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30007,7 +30013,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30213,7 +30219,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30419,7 +30425,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30625,7 +30631,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31243,7 +31249,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31449,7 +31455,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31655,7 +31661,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31861,7 +31867,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32148,7 +32154,7 @@
         <v>2</v>
       </c>
       <c r="AQ150">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.62</v>
@@ -32273,7 +32279,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32354,7 +32360,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR151">
         <v>1.68</v>
@@ -32479,7 +32485,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32685,7 +32691,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33097,7 +33103,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33175,7 +33181,7 @@
         <v>1.56</v>
       </c>
       <c r="AP155">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
         <v>1.42</v>
@@ -33715,7 +33721,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33793,7 +33799,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ158">
         <v>1.31</v>
@@ -33921,7 +33927,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34127,7 +34133,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34333,7 +34339,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34951,7 +34957,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35157,7 +35163,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35238,7 +35244,7 @@
         <v>2</v>
       </c>
       <c r="AQ165">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>1.65</v>
@@ -35569,7 +35575,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36187,7 +36193,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36677,7 +36683,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ172">
         <v>1.42</v>
@@ -36883,7 +36889,7 @@
         <v>2.2</v>
       </c>
       <c r="AP173">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>2.08</v>
@@ -37011,7 +37017,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37217,7 +37223,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37504,7 +37510,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ176">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37835,7 +37841,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37916,7 +37922,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ178">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38247,7 +38253,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38659,7 +38665,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38865,7 +38871,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39071,7 +39077,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39483,7 +39489,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39689,7 +39695,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39895,7 +39901,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -39973,10 +39979,10 @@
         <v>0.73</v>
       </c>
       <c r="AP188">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ188">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR188">
         <v>1.79</v>
@@ -40101,7 +40107,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40179,7 +40185,7 @@
         <v>2.09</v>
       </c>
       <c r="AP189">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ189">
         <v>2.08</v>
@@ -40719,7 +40725,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -41131,7 +41137,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41543,7 +41549,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41749,7 +41755,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42779,7 +42785,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -42936,6 +42942,418 @@
       </c>
       <c r="BP202">
         <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7453885</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F203">
+        <v>26</v>
+      </c>
+      <c r="G203" t="s">
+        <v>72</v>
+      </c>
+      <c r="H203" t="s">
+        <v>84</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>4</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>4</v>
+      </c>
+      <c r="O203" t="s">
+        <v>218</v>
+      </c>
+      <c r="P203" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q203">
+        <v>1.24</v>
+      </c>
+      <c r="R203">
+        <v>4.15</v>
+      </c>
+      <c r="S203">
+        <v>17</v>
+      </c>
+      <c r="T203">
+        <v>1.11</v>
+      </c>
+      <c r="U203">
+        <v>5.4</v>
+      </c>
+      <c r="V203">
+        <v>1.68</v>
+      </c>
+      <c r="W203">
+        <v>2.11</v>
+      </c>
+      <c r="X203">
+        <v>2.98</v>
+      </c>
+      <c r="Y203">
+        <v>1.33</v>
+      </c>
+      <c r="Z203">
+        <v>1.04</v>
+      </c>
+      <c r="AA203">
+        <v>13</v>
+      </c>
+      <c r="AB203">
+        <v>36</v>
+      </c>
+      <c r="AC203">
+        <v>1</v>
+      </c>
+      <c r="AD203">
+        <v>24</v>
+      </c>
+      <c r="AE203">
+        <v>1.03</v>
+      </c>
+      <c r="AF203">
+        <v>12</v>
+      </c>
+      <c r="AG203">
+        <v>1.13</v>
+      </c>
+      <c r="AH203">
+        <v>5.25</v>
+      </c>
+      <c r="AI203">
+        <v>2.42</v>
+      </c>
+      <c r="AJ203">
+        <v>1.53</v>
+      </c>
+      <c r="AK203">
+        <v>1</v>
+      </c>
+      <c r="AL203">
+        <v>1.01</v>
+      </c>
+      <c r="AM203">
+        <v>9.9</v>
+      </c>
+      <c r="AN203">
+        <v>2.67</v>
+      </c>
+      <c r="AO203">
+        <v>0.92</v>
+      </c>
+      <c r="AP203">
+        <v>2.69</v>
+      </c>
+      <c r="AQ203">
+        <v>0.85</v>
+      </c>
+      <c r="AR203">
+        <v>2.16</v>
+      </c>
+      <c r="AS203">
+        <v>1.49</v>
+      </c>
+      <c r="AT203">
+        <v>3.65</v>
+      </c>
+      <c r="AU203">
+        <v>12</v>
+      </c>
+      <c r="AV203">
+        <v>2</v>
+      </c>
+      <c r="AW203">
+        <v>4</v>
+      </c>
+      <c r="AX203">
+        <v>3</v>
+      </c>
+      <c r="AY203">
+        <v>18</v>
+      </c>
+      <c r="AZ203">
+        <v>6</v>
+      </c>
+      <c r="BA203">
+        <v>12</v>
+      </c>
+      <c r="BB203">
+        <v>1</v>
+      </c>
+      <c r="BC203">
+        <v>13</v>
+      </c>
+      <c r="BD203">
+        <v>0</v>
+      </c>
+      <c r="BE203">
+        <v>0</v>
+      </c>
+      <c r="BF203">
+        <v>0</v>
+      </c>
+      <c r="BG203">
+        <v>0</v>
+      </c>
+      <c r="BH203">
+        <v>0</v>
+      </c>
+      <c r="BI203">
+        <v>0</v>
+      </c>
+      <c r="BJ203">
+        <v>0</v>
+      </c>
+      <c r="BK203">
+        <v>0</v>
+      </c>
+      <c r="BL203">
+        <v>0</v>
+      </c>
+      <c r="BM203">
+        <v>0</v>
+      </c>
+      <c r="BN203">
+        <v>0</v>
+      </c>
+      <c r="BO203">
+        <v>0</v>
+      </c>
+      <c r="BP203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7453887</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45718.54166666666</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="s">
+        <v>85</v>
+      </c>
+      <c r="H204" t="s">
+        <v>81</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>3</v>
+      </c>
+      <c r="N204">
+        <v>4</v>
+      </c>
+      <c r="O204" t="s">
+        <v>219</v>
+      </c>
+      <c r="P204" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q204">
+        <v>1.85</v>
+      </c>
+      <c r="R204">
+        <v>2.3</v>
+      </c>
+      <c r="S204">
+        <v>7</v>
+      </c>
+      <c r="T204">
+        <v>1.35</v>
+      </c>
+      <c r="U204">
+        <v>2.95</v>
+      </c>
+      <c r="V204">
+        <v>2.6</v>
+      </c>
+      <c r="W204">
+        <v>1.44</v>
+      </c>
+      <c r="X204">
+        <v>6.5</v>
+      </c>
+      <c r="Y204">
+        <v>1.11</v>
+      </c>
+      <c r="Z204">
+        <v>1.54</v>
+      </c>
+      <c r="AA204">
+        <v>4</v>
+      </c>
+      <c r="AB204">
+        <v>5.8</v>
+      </c>
+      <c r="AC204">
+        <v>1.05</v>
+      </c>
+      <c r="AD204">
+        <v>8.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.28</v>
+      </c>
+      <c r="AF204">
+        <v>3.45</v>
+      </c>
+      <c r="AG204">
+        <v>1.87</v>
+      </c>
+      <c r="AH204">
+        <v>1.87</v>
+      </c>
+      <c r="AI204">
+        <v>1.93</v>
+      </c>
+      <c r="AJ204">
+        <v>1.73</v>
+      </c>
+      <c r="AK204">
+        <v>1.05</v>
+      </c>
+      <c r="AL204">
+        <v>1.2</v>
+      </c>
+      <c r="AM204">
+        <v>2.6</v>
+      </c>
+      <c r="AN204">
+        <v>1.08</v>
+      </c>
+      <c r="AO204">
+        <v>0.83</v>
+      </c>
+      <c r="AP204">
+        <v>1</v>
+      </c>
+      <c r="AQ204">
+        <v>1</v>
+      </c>
+      <c r="AR204">
+        <v>1.77</v>
+      </c>
+      <c r="AS204">
+        <v>1.36</v>
+      </c>
+      <c r="AT204">
+        <v>3.13</v>
+      </c>
+      <c r="AU204">
+        <v>5</v>
+      </c>
+      <c r="AV204">
+        <v>6</v>
+      </c>
+      <c r="AW204">
+        <v>6</v>
+      </c>
+      <c r="AX204">
+        <v>6</v>
+      </c>
+      <c r="AY204">
+        <v>11</v>
+      </c>
+      <c r="AZ204">
+        <v>12</v>
+      </c>
+      <c r="BA204">
+        <v>4</v>
+      </c>
+      <c r="BB204">
+        <v>2</v>
+      </c>
+      <c r="BC204">
+        <v>6</v>
+      </c>
+      <c r="BD204">
+        <v>1.41</v>
+      </c>
+      <c r="BE204">
+        <v>8.5</v>
+      </c>
+      <c r="BF204">
+        <v>3.68</v>
+      </c>
+      <c r="BG204">
+        <v>1.4</v>
+      </c>
+      <c r="BH204">
+        <v>2.75</v>
+      </c>
+      <c r="BI204">
+        <v>1.76</v>
+      </c>
+      <c r="BJ204">
+        <v>2</v>
+      </c>
+      <c r="BK204">
+        <v>2.2</v>
+      </c>
+      <c r="BL204">
+        <v>1.62</v>
+      </c>
+      <c r="BM204">
+        <v>3</v>
+      </c>
+      <c r="BN204">
+        <v>1.36</v>
+      </c>
+      <c r="BO204">
+        <v>4</v>
+      </c>
+      <c r="BP204">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,9 @@
     <t>['80']</t>
   </si>
   <si>
+    <t>['7', '44', '75', '85']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1329,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1588,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2203,7 +2206,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2615,7 +2618,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2821,7 +2824,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3233,7 +3236,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3311,7 +3314,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ10">
         <v>2.08</v>
@@ -3439,7 +3442,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3645,7 +3648,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3932,7 +3935,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ13">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4469,7 +4472,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5087,7 +5090,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6117,7 +6120,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6735,7 +6738,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6941,7 +6944,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7225,7 +7228,7 @@
         <v>1.5</v>
       </c>
       <c r="AP29">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -7559,7 +7562,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7640,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7765,7 +7768,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8177,7 +8180,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -9001,7 +9004,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9619,7 +9622,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9825,7 +9828,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9903,7 +9906,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ42">
         <v>0.85</v>
@@ -10031,7 +10034,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10237,7 +10240,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10443,7 +10446,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11061,7 +11064,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11473,7 +11476,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11679,7 +11682,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12915,7 +12918,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13121,7 +13124,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13327,7 +13330,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13408,7 +13411,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13533,7 +13536,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13611,7 +13614,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ60">
         <v>0.6899999999999999</v>
@@ -13739,7 +13742,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14151,7 +14154,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14357,7 +14360,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14563,7 +14566,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14769,7 +14772,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15387,7 +15390,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15799,7 +15802,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16005,7 +16008,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16086,7 +16089,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>1.46</v>
@@ -16417,7 +16420,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16829,7 +16832,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17113,7 +17116,7 @@
         <v>0.2</v>
       </c>
       <c r="AP77">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17241,7 +17244,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17447,7 +17450,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17859,7 +17862,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18065,7 +18068,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18271,7 +18274,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18477,7 +18480,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18683,7 +18686,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19095,7 +19098,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19507,7 +19510,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19919,7 +19922,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20203,7 +20206,7 @@
         <v>1.83</v>
       </c>
       <c r="AP92">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ92">
         <v>1.77</v>
@@ -20537,7 +20540,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21567,7 +21570,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21773,7 +21776,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21979,7 +21982,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22060,7 +22063,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ101">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22185,7 +22188,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22391,7 +22394,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23215,7 +23218,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23627,7 +23630,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23705,7 +23708,7 @@
         <v>2</v>
       </c>
       <c r="AP109">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ109">
         <v>1.62</v>
@@ -24039,7 +24042,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24245,7 +24248,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25069,7 +25072,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25275,7 +25278,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25356,7 +25359,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ117">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25481,7 +25484,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25687,7 +25690,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25893,7 +25896,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26717,7 +26720,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26923,7 +26926,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27129,7 +27132,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27541,7 +27544,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27747,7 +27750,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28159,7 +28162,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28858,7 +28861,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ134">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR134">
         <v>2.03</v>
@@ -29189,7 +29192,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29267,7 +29270,7 @@
         <v>2</v>
       </c>
       <c r="AP136">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ136">
         <v>1.54</v>
@@ -29682,7 +29685,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ138">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR138">
         <v>1.06</v>
@@ -29807,7 +29810,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30013,7 +30016,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30219,7 +30222,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30425,7 +30428,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30631,7 +30634,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31249,7 +31252,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31455,7 +31458,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31661,7 +31664,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31867,7 +31870,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32279,7 +32282,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32485,7 +32488,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32563,7 +32566,7 @@
         <v>3</v>
       </c>
       <c r="AP152">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ152">
         <v>3</v>
@@ -32691,7 +32694,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33103,7 +33106,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33593,7 +33596,7 @@
         <v>0.44</v>
       </c>
       <c r="AP157">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ157">
         <v>0.85</v>
@@ -33721,7 +33724,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33927,7 +33930,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34133,7 +34136,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34214,7 +34217,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR160">
         <v>1.53</v>
@@ -34339,7 +34342,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34420,7 +34423,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ161">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34957,7 +34960,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35163,7 +35166,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35575,7 +35578,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36193,7 +36196,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36480,7 +36483,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
         <v>1.13</v>
@@ -37017,7 +37020,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37095,7 +37098,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ174">
         <v>1.15</v>
@@ -37223,7 +37226,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37841,7 +37844,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38253,7 +38256,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38665,7 +38668,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38871,7 +38874,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39077,7 +39080,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39489,7 +39492,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39695,7 +39698,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39901,7 +39904,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40107,7 +40110,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40597,7 +40600,7 @@
         <v>1.27</v>
       </c>
       <c r="AP191">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AQ191">
         <v>1.31</v>
@@ -40725,7 +40728,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -40806,7 +40809,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ192">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR192">
         <v>1.69</v>
@@ -41137,7 +41140,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41549,7 +41552,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41755,7 +41758,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42785,7 +42788,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43197,7 +43200,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43354,6 +43357,212 @@
       </c>
       <c r="BP204">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7453880</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45719.41666666666</v>
+      </c>
+      <c r="F205">
+        <v>26</v>
+      </c>
+      <c r="G205" t="s">
+        <v>78</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205">
+        <v>2</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>4</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>5</v>
+      </c>
+      <c r="O205" t="s">
+        <v>220</v>
+      </c>
+      <c r="P205" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q205">
+        <v>5.5</v>
+      </c>
+      <c r="R205">
+        <v>2.3</v>
+      </c>
+      <c r="S205">
+        <v>2.05</v>
+      </c>
+      <c r="T205">
+        <v>1.36</v>
+      </c>
+      <c r="U205">
+        <v>3</v>
+      </c>
+      <c r="V205">
+        <v>2.63</v>
+      </c>
+      <c r="W205">
+        <v>1.44</v>
+      </c>
+      <c r="X205">
+        <v>6</v>
+      </c>
+      <c r="Y205">
+        <v>1.11</v>
+      </c>
+      <c r="Z205">
+        <v>7.7</v>
+      </c>
+      <c r="AA205">
+        <v>3.52</v>
+      </c>
+      <c r="AB205">
+        <v>1.52</v>
+      </c>
+      <c r="AC205">
+        <v>1.04</v>
+      </c>
+      <c r="AD205">
+        <v>9</v>
+      </c>
+      <c r="AE205">
+        <v>1.25</v>
+      </c>
+      <c r="AF205">
+        <v>3.8</v>
+      </c>
+      <c r="AG205">
+        <v>1.7</v>
+      </c>
+      <c r="AH205">
+        <v>1.95</v>
+      </c>
+      <c r="AI205">
+        <v>1.83</v>
+      </c>
+      <c r="AJ205">
+        <v>1.83</v>
+      </c>
+      <c r="AK205">
+        <v>2.45</v>
+      </c>
+      <c r="AL205">
+        <v>1.17</v>
+      </c>
+      <c r="AM205">
+        <v>1.1</v>
+      </c>
+      <c r="AN205">
+        <v>0.58</v>
+      </c>
+      <c r="AO205">
+        <v>1.25</v>
+      </c>
+      <c r="AP205">
+        <v>0.77</v>
+      </c>
+      <c r="AQ205">
+        <v>1.15</v>
+      </c>
+      <c r="AR205">
+        <v>1.17</v>
+      </c>
+      <c r="AS205">
+        <v>1.5</v>
+      </c>
+      <c r="AT205">
+        <v>2.67</v>
+      </c>
+      <c r="AU205">
+        <v>8</v>
+      </c>
+      <c r="AV205">
+        <v>7</v>
+      </c>
+      <c r="AW205">
+        <v>7</v>
+      </c>
+      <c r="AX205">
+        <v>11</v>
+      </c>
+      <c r="AY205">
+        <v>17</v>
+      </c>
+      <c r="AZ205">
+        <v>24</v>
+      </c>
+      <c r="BA205">
+        <v>3</v>
+      </c>
+      <c r="BB205">
+        <v>9</v>
+      </c>
+      <c r="BC205">
+        <v>12</v>
+      </c>
+      <c r="BD205">
+        <v>3.59</v>
+      </c>
+      <c r="BE205">
+        <v>8.5</v>
+      </c>
+      <c r="BF205">
+        <v>1.41</v>
+      </c>
+      <c r="BG205">
+        <v>1.43</v>
+      </c>
+      <c r="BH205">
+        <v>2.63</v>
+      </c>
+      <c r="BI205">
+        <v>1.74</v>
+      </c>
+      <c r="BJ205">
+        <v>2.02</v>
+      </c>
+      <c r="BK205">
+        <v>2.22</v>
+      </c>
+      <c r="BL205">
+        <v>1.62</v>
+      </c>
+      <c r="BM205">
+        <v>2.85</v>
+      </c>
+      <c r="BN205">
+        <v>1.37</v>
+      </c>
+      <c r="BO205">
+        <v>3.9</v>
+      </c>
+      <c r="BP205">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,12 @@
     <t>['7', '44', '75', '85']</t>
   </si>
   <si>
+    <t>['23', '45']</t>
+  </si>
+  <si>
+    <t>['65']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -698,9 +704,6 @@
   </si>
   <si>
     <t>['19', '37']</t>
-  </si>
-  <si>
-    <t>['65']</t>
   </si>
   <si>
     <t>['53', '63', '68', '83']</t>
@@ -971,6 +974,9 @@
   </si>
   <si>
     <t>['37', '48', '57']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1588,7 +1594,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1669,7 +1675,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2206,7 +2212,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2284,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5">
         <v>1.62</v>
@@ -2490,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6">
         <v>0.6899999999999999</v>
@@ -2618,7 +2624,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2696,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2824,7 +2830,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3236,7 +3242,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3442,7 +3448,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3523,7 +3529,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3648,7 +3654,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4472,7 +4478,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4756,7 +4762,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ17">
         <v>1.62</v>
@@ -4962,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ18">
         <v>0.31</v>
@@ -5090,7 +5096,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5583,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5786,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22">
         <v>1.77</v>
@@ -6120,7 +6126,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6407,7 +6413,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ25">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.68</v>
@@ -6613,7 +6619,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ26">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6738,7 +6744,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6816,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27">
         <v>0.85</v>
@@ -6944,7 +6950,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7231,7 +7237,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR29">
         <v>0.53</v>
@@ -7562,7 +7568,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7768,7 +7774,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7846,7 +7852,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -8180,7 +8186,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8258,7 +8264,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ34">
         <v>1.54</v>
@@ -9004,7 +9010,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9288,7 +9294,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ39">
         <v>1.31</v>
@@ -9497,7 +9503,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR40">
         <v>1.91</v>
@@ -9622,7 +9628,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9828,7 +9834,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10034,7 +10040,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10115,7 +10121,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.47</v>
@@ -10240,7 +10246,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10321,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10446,7 +10452,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10730,7 +10736,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ46">
         <v>0.85</v>
@@ -10936,7 +10942,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47">
         <v>0.31</v>
@@ -11064,7 +11070,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11476,7 +11482,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11682,7 +11688,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12381,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>1.46</v>
@@ -12584,10 +12590,10 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR55">
         <v>0</v>
@@ -12793,7 +12799,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ56">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12918,7 +12924,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -12996,7 +13002,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ57">
         <v>1.31</v>
@@ -13124,7 +13130,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13330,7 +13336,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13536,7 +13542,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13742,7 +13748,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13823,7 +13829,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ61">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR61">
         <v>1.36</v>
@@ -14026,7 +14032,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62">
         <v>0.31</v>
@@ -14154,7 +14160,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14360,7 +14366,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14566,7 +14572,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14772,7 +14778,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15390,7 +15396,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15677,7 +15683,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ70">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR70">
         <v>2.49</v>
@@ -15802,7 +15808,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16008,7 +16014,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16086,7 +16092,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16292,10 +16298,10 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ73">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR73">
         <v>1.97</v>
@@ -16420,7 +16426,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16707,7 +16713,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ75">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.22</v>
@@ -16832,7 +16838,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16910,7 +16916,7 @@
         <v>1.75</v>
       </c>
       <c r="AP76">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ76">
         <v>2.08</v>
@@ -17244,7 +17250,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17450,7 +17456,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17862,7 +17868,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18068,7 +18074,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18274,7 +18280,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18480,7 +18486,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18686,7 +18692,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19098,7 +19104,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19382,10 +19388,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ88">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.41</v>
@@ -19510,7 +19516,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19591,7 +19597,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ89">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR89">
         <v>1.92</v>
@@ -19922,7 +19928,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20003,7 +20009,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ91">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20412,7 +20418,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ93">
         <v>0.85</v>
@@ -20540,7 +20546,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20618,7 +20624,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ94">
         <v>2.08</v>
@@ -21570,7 +21576,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21776,7 +21782,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21982,7 +21988,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22188,7 +22194,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22394,7 +22400,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22678,7 +22684,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ104">
         <v>0.85</v>
@@ -22887,7 +22893,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.53</v>
@@ -23218,7 +23224,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23502,7 +23508,7 @@
         <v>0.29</v>
       </c>
       <c r="AP108">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23630,7 +23636,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23914,10 +23920,10 @@
         <v>1.29</v>
       </c>
       <c r="AP110">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ110">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR110">
         <v>1.53</v>
@@ -24042,7 +24048,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24248,7 +24254,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25072,7 +25078,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25153,7 +25159,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25278,7 +25284,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25484,7 +25490,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25690,7 +25696,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25896,7 +25902,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26595,7 +26601,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.46</v>
@@ -26720,7 +26726,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26801,7 +26807,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ124">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR124">
         <v>1.33</v>
@@ -26926,7 +26932,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27004,7 +27010,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ125">
         <v>1.77</v>
@@ -27132,7 +27138,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27210,7 +27216,7 @@
         <v>0.38</v>
       </c>
       <c r="AP126">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27544,7 +27550,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27625,7 +27631,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ128">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR128">
         <v>1.28</v>
@@ -27750,7 +27756,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28162,7 +28168,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28240,7 +28246,7 @@
         <v>3</v>
       </c>
       <c r="AP131">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ131">
         <v>3</v>
@@ -29192,7 +29198,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29810,7 +29816,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30016,7 +30022,7 @@
         <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="Q140">
         <v>2.4</v>
@@ -30222,7 +30228,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30303,7 +30309,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ141">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.19</v>
@@ -30428,7 +30434,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30509,7 +30515,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ142">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30634,7 +30640,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31252,7 +31258,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31458,7 +31464,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31536,7 +31542,7 @@
         <v>1.89</v>
       </c>
       <c r="AP147">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ147">
         <v>1.62</v>
@@ -31664,7 +31670,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31742,7 +31748,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ148">
         <v>3</v>
@@ -31870,7 +31876,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32282,7 +32288,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32488,7 +32494,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32694,7 +32700,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32772,7 +32778,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ153">
         <v>1.15</v>
@@ -32981,7 +32987,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ154">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33106,7 +33112,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33187,7 +33193,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR155">
         <v>1.77</v>
@@ -33724,7 +33730,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33930,7 +33936,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34011,7 +34017,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ159">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.07</v>
@@ -34136,7 +34142,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34342,7 +34348,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34832,7 +34838,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ163">
         <v>1.54</v>
@@ -34960,7 +34966,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35038,7 +35044,7 @@
         <v>0.4</v>
       </c>
       <c r="AP164">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ164">
         <v>0.85</v>
@@ -35166,7 +35172,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35578,7 +35584,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36196,7 +36202,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36480,7 +36486,7 @@
         <v>1.5</v>
       </c>
       <c r="AP171">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ171">
         <v>1.15</v>
@@ -36689,7 +36695,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ172">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR172">
         <v>2.01</v>
@@ -37020,7 +37026,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37226,7 +37232,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37307,7 +37313,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ175">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR175">
         <v>1.51</v>
@@ -37719,7 +37725,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ177">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR177">
         <v>1.08</v>
@@ -37844,7 +37850,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38256,7 +38262,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38668,7 +38674,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38874,7 +38880,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39080,7 +39086,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39158,7 +39164,7 @@
         <v>1.27</v>
       </c>
       <c r="AP184">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ184">
         <v>1.15</v>
@@ -39492,7 +39498,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39698,7 +39704,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39779,7 +39785,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ187">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR187">
         <v>1.22</v>
@@ -39904,7 +39910,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40110,7 +40116,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40394,10 +40400,10 @@
         <v>1.18</v>
       </c>
       <c r="AP190">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ190">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -40728,7 +40734,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -40806,7 +40812,7 @@
         <v>1.36</v>
       </c>
       <c r="AP192">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192">
         <v>1.15</v>
@@ -41140,7 +41146,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41552,7 +41558,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41758,7 +41764,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42788,7 +42794,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43200,7 +43206,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43406,7 +43412,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43563,6 +43569,624 @@
       </c>
       <c r="BP205">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7453882</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45719.52083333334</v>
+      </c>
+      <c r="F206">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s">
+        <v>75</v>
+      </c>
+      <c r="H206" t="s">
+        <v>71</v>
+      </c>
+      <c r="I206">
+        <v>2</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>2</v>
+      </c>
+      <c r="O206" t="s">
+        <v>221</v>
+      </c>
+      <c r="P206" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q206">
+        <v>2.75</v>
+      </c>
+      <c r="R206">
+        <v>2.05</v>
+      </c>
+      <c r="S206">
+        <v>3.75</v>
+      </c>
+      <c r="T206">
+        <v>1.44</v>
+      </c>
+      <c r="U206">
+        <v>2.63</v>
+      </c>
+      <c r="V206">
+        <v>3.25</v>
+      </c>
+      <c r="W206">
+        <v>1.33</v>
+      </c>
+      <c r="X206">
+        <v>7.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.07</v>
+      </c>
+      <c r="Z206">
+        <v>2.07</v>
+      </c>
+      <c r="AA206">
+        <v>3</v>
+      </c>
+      <c r="AB206">
+        <v>3.94</v>
+      </c>
+      <c r="AC206">
+        <v>1.06</v>
+      </c>
+      <c r="AD206">
+        <v>8</v>
+      </c>
+      <c r="AE206">
+        <v>1.33</v>
+      </c>
+      <c r="AF206">
+        <v>3.2</v>
+      </c>
+      <c r="AG206">
+        <v>1.95</v>
+      </c>
+      <c r="AH206">
+        <v>1.79</v>
+      </c>
+      <c r="AI206">
+        <v>1.83</v>
+      </c>
+      <c r="AJ206">
+        <v>1.83</v>
+      </c>
+      <c r="AK206">
+        <v>1.22</v>
+      </c>
+      <c r="AL206">
+        <v>1.25</v>
+      </c>
+      <c r="AM206">
+        <v>1.85</v>
+      </c>
+      <c r="AN206">
+        <v>1.42</v>
+      </c>
+      <c r="AO206">
+        <v>1.08</v>
+      </c>
+      <c r="AP206">
+        <v>1.54</v>
+      </c>
+      <c r="AQ206">
+        <v>1</v>
+      </c>
+      <c r="AR206">
+        <v>1.7</v>
+      </c>
+      <c r="AS206">
+        <v>1.13</v>
+      </c>
+      <c r="AT206">
+        <v>2.83</v>
+      </c>
+      <c r="AU206">
+        <v>6</v>
+      </c>
+      <c r="AV206">
+        <v>3</v>
+      </c>
+      <c r="AW206">
+        <v>3</v>
+      </c>
+      <c r="AX206">
+        <v>6</v>
+      </c>
+      <c r="AY206">
+        <v>11</v>
+      </c>
+      <c r="AZ206">
+        <v>12</v>
+      </c>
+      <c r="BA206">
+        <v>5</v>
+      </c>
+      <c r="BB206">
+        <v>4</v>
+      </c>
+      <c r="BC206">
+        <v>9</v>
+      </c>
+      <c r="BD206">
+        <v>1.51</v>
+      </c>
+      <c r="BE206">
+        <v>8.5</v>
+      </c>
+      <c r="BF206">
+        <v>3.16</v>
+      </c>
+      <c r="BG206">
+        <v>1.39</v>
+      </c>
+      <c r="BH206">
+        <v>2.77</v>
+      </c>
+      <c r="BI206">
+        <v>1.68</v>
+      </c>
+      <c r="BJ206">
+        <v>2.12</v>
+      </c>
+      <c r="BK206">
+        <v>2.11</v>
+      </c>
+      <c r="BL206">
+        <v>1.68</v>
+      </c>
+      <c r="BM206">
+        <v>2.7</v>
+      </c>
+      <c r="BN206">
+        <v>1.41</v>
+      </c>
+      <c r="BO206">
+        <v>3.65</v>
+      </c>
+      <c r="BP206">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7453884</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45719.60416666666</v>
+      </c>
+      <c r="F207">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s">
+        <v>73</v>
+      </c>
+      <c r="H207" t="s">
+        <v>79</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>2</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>152</v>
+      </c>
+      <c r="P207" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q207">
+        <v>0</v>
+      </c>
+      <c r="R207">
+        <v>0</v>
+      </c>
+      <c r="S207">
+        <v>0</v>
+      </c>
+      <c r="T207">
+        <v>0</v>
+      </c>
+      <c r="U207">
+        <v>0</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="W207">
+        <v>0</v>
+      </c>
+      <c r="X207">
+        <v>0</v>
+      </c>
+      <c r="Y207">
+        <v>0</v>
+      </c>
+      <c r="Z207">
+        <v>2.03</v>
+      </c>
+      <c r="AA207">
+        <v>3.27</v>
+      </c>
+      <c r="AB207">
+        <v>3.68</v>
+      </c>
+      <c r="AC207">
+        <v>0</v>
+      </c>
+      <c r="AD207">
+        <v>0</v>
+      </c>
+      <c r="AE207">
+        <v>0</v>
+      </c>
+      <c r="AF207">
+        <v>0</v>
+      </c>
+      <c r="AG207">
+        <v>1.94</v>
+      </c>
+      <c r="AH207">
+        <v>1.8</v>
+      </c>
+      <c r="AI207">
+        <v>0</v>
+      </c>
+      <c r="AJ207">
+        <v>0</v>
+      </c>
+      <c r="AK207">
+        <v>0</v>
+      </c>
+      <c r="AL207">
+        <v>0</v>
+      </c>
+      <c r="AM207">
+        <v>0</v>
+      </c>
+      <c r="AN207">
+        <v>1.58</v>
+      </c>
+      <c r="AO207">
+        <v>1.27</v>
+      </c>
+      <c r="AP207">
+        <v>1.54</v>
+      </c>
+      <c r="AQ207">
+        <v>1.25</v>
+      </c>
+      <c r="AR207">
+        <v>1.13</v>
+      </c>
+      <c r="AS207">
+        <v>1.14</v>
+      </c>
+      <c r="AT207">
+        <v>2.27</v>
+      </c>
+      <c r="AU207">
+        <v>-1</v>
+      </c>
+      <c r="AV207">
+        <v>-1</v>
+      </c>
+      <c r="AW207">
+        <v>-1</v>
+      </c>
+      <c r="AX207">
+        <v>-1</v>
+      </c>
+      <c r="AY207">
+        <v>-1</v>
+      </c>
+      <c r="AZ207">
+        <v>-1</v>
+      </c>
+      <c r="BA207">
+        <v>-1</v>
+      </c>
+      <c r="BB207">
+        <v>-1</v>
+      </c>
+      <c r="BC207">
+        <v>-1</v>
+      </c>
+      <c r="BD207">
+        <v>0</v>
+      </c>
+      <c r="BE207">
+        <v>0</v>
+      </c>
+      <c r="BF207">
+        <v>0</v>
+      </c>
+      <c r="BG207">
+        <v>0</v>
+      </c>
+      <c r="BH207">
+        <v>0</v>
+      </c>
+      <c r="BI207">
+        <v>0</v>
+      </c>
+      <c r="BJ207">
+        <v>0</v>
+      </c>
+      <c r="BK207">
+        <v>0</v>
+      </c>
+      <c r="BL207">
+        <v>0</v>
+      </c>
+      <c r="BM207">
+        <v>0</v>
+      </c>
+      <c r="BN207">
+        <v>0</v>
+      </c>
+      <c r="BO207">
+        <v>0</v>
+      </c>
+      <c r="BP207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7453881</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s">
+        <v>74</v>
+      </c>
+      <c r="H208" t="s">
+        <v>70</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208" t="s">
+        <v>222</v>
+      </c>
+      <c r="P208" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q208">
+        <v>2.6</v>
+      </c>
+      <c r="R208">
+        <v>2.2</v>
+      </c>
+      <c r="S208">
+        <v>3.75</v>
+      </c>
+      <c r="T208">
+        <v>1.36</v>
+      </c>
+      <c r="U208">
+        <v>3</v>
+      </c>
+      <c r="V208">
+        <v>2.63</v>
+      </c>
+      <c r="W208">
+        <v>1.44</v>
+      </c>
+      <c r="X208">
+        <v>6.5</v>
+      </c>
+      <c r="Y208">
+        <v>1.1</v>
+      </c>
+      <c r="Z208">
+        <v>2.15</v>
+      </c>
+      <c r="AA208">
+        <v>3.25</v>
+      </c>
+      <c r="AB208">
+        <v>3.36</v>
+      </c>
+      <c r="AC208">
+        <v>1.05</v>
+      </c>
+      <c r="AD208">
+        <v>8.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.25</v>
+      </c>
+      <c r="AF208">
+        <v>3.6</v>
+      </c>
+      <c r="AG208">
+        <v>1.87</v>
+      </c>
+      <c r="AH208">
+        <v>1.87</v>
+      </c>
+      <c r="AI208">
+        <v>1.67</v>
+      </c>
+      <c r="AJ208">
+        <v>2.1</v>
+      </c>
+      <c r="AK208">
+        <v>1.3</v>
+      </c>
+      <c r="AL208">
+        <v>1.25</v>
+      </c>
+      <c r="AM208">
+        <v>1.7</v>
+      </c>
+      <c r="AN208">
+        <v>1.5</v>
+      </c>
+      <c r="AO208">
+        <v>1.42</v>
+      </c>
+      <c r="AP208">
+        <v>1.46</v>
+      </c>
+      <c r="AQ208">
+        <v>1.38</v>
+      </c>
+      <c r="AR208">
+        <v>1.69</v>
+      </c>
+      <c r="AS208">
+        <v>1.75</v>
+      </c>
+      <c r="AT208">
+        <v>3.44</v>
+      </c>
+      <c r="AU208">
+        <v>5</v>
+      </c>
+      <c r="AV208">
+        <v>5</v>
+      </c>
+      <c r="AW208">
+        <v>2</v>
+      </c>
+      <c r="AX208">
+        <v>8</v>
+      </c>
+      <c r="AY208">
+        <v>8</v>
+      </c>
+      <c r="AZ208">
+        <v>16</v>
+      </c>
+      <c r="BA208">
+        <v>1</v>
+      </c>
+      <c r="BB208">
+        <v>6</v>
+      </c>
+      <c r="BC208">
+        <v>7</v>
+      </c>
+      <c r="BD208">
+        <v>1.69</v>
+      </c>
+      <c r="BE208">
+        <v>7.5</v>
+      </c>
+      <c r="BF208">
+        <v>2.55</v>
+      </c>
+      <c r="BG208">
+        <v>1.5</v>
+      </c>
+      <c r="BH208">
+        <v>2.41</v>
+      </c>
+      <c r="BI208">
+        <v>1.92</v>
+      </c>
+      <c r="BJ208">
+        <v>1.88</v>
+      </c>
+      <c r="BK208">
+        <v>2.42</v>
+      </c>
+      <c r="BL208">
+        <v>1.53</v>
+      </c>
+      <c r="BM208">
+        <v>3.25</v>
+      </c>
+      <c r="BN208">
+        <v>1.29</v>
+      </c>
+      <c r="BO208">
+        <v>4.4</v>
+      </c>
+      <c r="BP208">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -42699,13 +42699,13 @@
         <v>13</v>
       </c>
       <c r="BA201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB201">
         <v>5</v>
       </c>
       <c r="BC201">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD201">
         <v>0</v>
@@ -43111,13 +43111,13 @@
         <v>6</v>
       </c>
       <c r="BA203">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BB203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC203">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BD203">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -43917,31 +43917,31 @@
         <v>2.27</v>
       </c>
       <c r="AU207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX207">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY207">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ207">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BA207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB207">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC207">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD207">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2293,7 +2293,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ5">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ14">
         <v>1.31</v>
@@ -4765,7 +4765,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ17">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ26">
         <v>1.38</v>
@@ -8061,7 +8061,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ33">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR33">
         <v>1.82</v>
@@ -11151,7 +11151,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ48">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR48">
         <v>1.07</v>
@@ -12178,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ53">
         <v>0.85</v>
@@ -15065,7 +15065,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ67">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR67">
         <v>1.33</v>
@@ -17537,7 +17537,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ79">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR79">
         <v>1.64</v>
@@ -18770,7 +18770,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ85">
         <v>1.77</v>
@@ -21654,7 +21654,7 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ99">
         <v>3</v>
@@ -21863,7 +21863,7 @@
         <v>1</v>
       </c>
       <c r="AQ100">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR100">
         <v>1.66</v>
@@ -23717,7 +23717,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ109">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR109">
         <v>1.11</v>
@@ -24538,7 +24538,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ113">
         <v>0.85</v>
@@ -25980,7 +25980,7 @@
         <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
         <v>1.15</v>
@@ -27425,7 +27425,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ127">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -29688,7 +29688,7 @@
         <v>1.43</v>
       </c>
       <c r="AP138">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ138">
         <v>1.15</v>
@@ -30718,7 +30718,7 @@
         <v>2.38</v>
       </c>
       <c r="AP143">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ143">
         <v>2.08</v>
@@ -31545,7 +31545,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ147">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -34014,7 +34014,7 @@
         <v>0.78</v>
       </c>
       <c r="AP159">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -36077,7 +36077,7 @@
         <v>2</v>
       </c>
       <c r="AQ169">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR169">
         <v>1.61</v>
@@ -37722,7 +37722,7 @@
         <v>1.3</v>
       </c>
       <c r="AP177">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ177">
         <v>1.25</v>
@@ -38137,7 +38137,7 @@
         <v>2</v>
       </c>
       <c r="AQ179">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR179">
         <v>1.67</v>
@@ -39576,7 +39576,7 @@
         <v>0.73</v>
       </c>
       <c r="AP186">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ186">
         <v>0.6899999999999999</v>
@@ -41018,7 +41018,7 @@
         <v>0.33</v>
       </c>
       <c r="AP193">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ193">
         <v>0.31</v>
@@ -41845,7 +41845,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ197">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR197">
         <v>1.49</v>
@@ -44187,6 +44187,212 @@
       </c>
       <c r="BP208">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7453889</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F209">
+        <v>27</v>
+      </c>
+      <c r="G209" t="s">
+        <v>81</v>
+      </c>
+      <c r="H209" t="s">
+        <v>82</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>1</v>
+      </c>
+      <c r="O209" t="s">
+        <v>87</v>
+      </c>
+      <c r="P209" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q209">
+        <v>3.2</v>
+      </c>
+      <c r="R209">
+        <v>2</v>
+      </c>
+      <c r="S209">
+        <v>3.25</v>
+      </c>
+      <c r="T209">
+        <v>1.44</v>
+      </c>
+      <c r="U209">
+        <v>2.63</v>
+      </c>
+      <c r="V209">
+        <v>3.25</v>
+      </c>
+      <c r="W209">
+        <v>1.33</v>
+      </c>
+      <c r="X209">
+        <v>7.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.07</v>
+      </c>
+      <c r="Z209">
+        <v>2.55</v>
+      </c>
+      <c r="AA209">
+        <v>3.28</v>
+      </c>
+      <c r="AB209">
+        <v>2.68</v>
+      </c>
+      <c r="AC209">
+        <v>1.06</v>
+      </c>
+      <c r="AD209">
+        <v>8</v>
+      </c>
+      <c r="AE209">
+        <v>1.36</v>
+      </c>
+      <c r="AF209">
+        <v>3</v>
+      </c>
+      <c r="AG209">
+        <v>2.05</v>
+      </c>
+      <c r="AH209">
+        <v>1.61</v>
+      </c>
+      <c r="AI209">
+        <v>1.83</v>
+      </c>
+      <c r="AJ209">
+        <v>1.83</v>
+      </c>
+      <c r="AK209">
+        <v>1.45</v>
+      </c>
+      <c r="AL209">
+        <v>1.28</v>
+      </c>
+      <c r="AM209">
+        <v>1.48</v>
+      </c>
+      <c r="AN209">
+        <v>1.54</v>
+      </c>
+      <c r="AO209">
+        <v>1.62</v>
+      </c>
+      <c r="AP209">
+        <v>1.43</v>
+      </c>
+      <c r="AQ209">
+        <v>1.71</v>
+      </c>
+      <c r="AR209">
+        <v>1.19</v>
+      </c>
+      <c r="AS209">
+        <v>1.45</v>
+      </c>
+      <c r="AT209">
+        <v>2.64</v>
+      </c>
+      <c r="AU209">
+        <v>-1</v>
+      </c>
+      <c r="AV209">
+        <v>-1</v>
+      </c>
+      <c r="AW209">
+        <v>-1</v>
+      </c>
+      <c r="AX209">
+        <v>-1</v>
+      </c>
+      <c r="AY209">
+        <v>-1</v>
+      </c>
+      <c r="AZ209">
+        <v>-1</v>
+      </c>
+      <c r="BA209">
+        <v>-1</v>
+      </c>
+      <c r="BB209">
+        <v>-1</v>
+      </c>
+      <c r="BC209">
+        <v>-1</v>
+      </c>
+      <c r="BD209">
+        <v>1.95</v>
+      </c>
+      <c r="BE209">
+        <v>7.5</v>
+      </c>
+      <c r="BF209">
+        <v>2.1</v>
+      </c>
+      <c r="BG209">
+        <v>1.55</v>
+      </c>
+      <c r="BH209">
+        <v>2.37</v>
+      </c>
+      <c r="BI209">
+        <v>1.92</v>
+      </c>
+      <c r="BJ209">
+        <v>1.82</v>
+      </c>
+      <c r="BK209">
+        <v>2.46</v>
+      </c>
+      <c r="BL209">
+        <v>1.48</v>
+      </c>
+      <c r="BM209">
+        <v>3.32</v>
+      </c>
+      <c r="BN209">
+        <v>1.26</v>
+      </c>
+      <c r="BO209">
+        <v>4.6</v>
+      </c>
+      <c r="BP209">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,18 @@
     <t>['65']</t>
   </si>
   <si>
+    <t>['5', '29']</t>
+  </si>
+  <si>
+    <t>['21', '54', '90']</t>
+  </si>
+  <si>
+    <t>['5', '30', '71']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -977,6 +989,15 @@
   </si>
   <si>
     <t>['27']</t>
+  </si>
+  <si>
+    <t>['10', '23', '71']</t>
+  </si>
+  <si>
+    <t>['68', '83']</t>
+  </si>
+  <si>
+    <t>['9', '55', '73']</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1594,7 +1615,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1672,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ2">
         <v>1.25</v>
@@ -1878,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
         <v>2.08</v>
@@ -2212,7 +2233,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2624,7 +2645,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2830,7 +2851,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3242,7 +3263,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3448,7 +3469,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3526,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3654,7 +3675,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3938,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4147,7 +4168,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ14">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4353,7 +4374,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4556,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16">
         <v>0.85</v>
@@ -5096,7 +5117,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5586,7 +5607,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ21">
         <v>1.25</v>
@@ -5998,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23">
         <v>0.6899999999999999</v>
@@ -6126,7 +6147,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6207,7 +6228,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>0.98</v>
@@ -6410,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6744,7 +6765,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6825,7 +6846,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ27">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -6950,7 +6971,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7031,7 +7052,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ28">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR28">
         <v>2.33</v>
@@ -7568,7 +7589,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7649,7 +7670,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7774,7 +7795,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8186,7 +8207,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8676,7 +8697,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8882,7 +8903,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ37">
         <v>0.85</v>
@@ -9010,7 +9031,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9088,7 +9109,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38">
         <v>1.77</v>
@@ -9297,7 +9318,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ39">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9500,7 +9521,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40">
         <v>1.25</v>
@@ -9628,7 +9649,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9709,7 +9730,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.05</v>
@@ -9834,7 +9855,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10040,7 +10061,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10246,7 +10267,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10452,7 +10473,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10739,7 +10760,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ46">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR46">
         <v>0.99</v>
@@ -11070,7 +11091,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11148,7 +11169,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ48">
         <v>1.71</v>
@@ -11354,7 +11375,7 @@
         <v>0.33</v>
       </c>
       <c r="AP49">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11482,7 +11503,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11688,7 +11709,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11766,7 +11787,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
         <v>3</v>
@@ -11972,7 +11993,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ52">
         <v>1.77</v>
@@ -12924,7 +12945,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13005,7 +13026,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ57">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR57">
         <v>1.94</v>
@@ -13130,7 +13151,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13336,7 +13357,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13417,7 +13438,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13542,7 +13563,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13748,7 +13769,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14160,7 +14181,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14241,7 +14262,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ63">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR63">
         <v>1.81</v>
@@ -14366,7 +14387,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14444,7 +14465,7 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ64">
         <v>1.54</v>
@@ -14572,7 +14593,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14778,7 +14799,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14856,7 +14877,7 @@
         <v>0.25</v>
       </c>
       <c r="AP66">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -15062,7 +15083,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ67">
         <v>1.71</v>
@@ -15268,10 +15289,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -15396,7 +15417,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15474,7 +15495,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ69">
         <v>3</v>
@@ -15808,7 +15829,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16014,7 +16035,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16095,7 +16116,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR72">
         <v>1.46</v>
@@ -16426,7 +16447,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16838,7 +16859,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17250,7 +17271,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17331,7 +17352,7 @@
         <v>1</v>
       </c>
       <c r="AQ78">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR78">
         <v>1.57</v>
@@ -17456,7 +17477,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17534,7 +17555,7 @@
         <v>2.6</v>
       </c>
       <c r="AP79">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
         <v>1.71</v>
@@ -17740,10 +17761,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ80">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -17868,7 +17889,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17946,7 +17967,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ81">
         <v>1.54</v>
@@ -18074,7 +18095,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18152,10 +18173,10 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ82">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18280,7 +18301,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18358,10 +18379,10 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ83">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR83">
         <v>1.12</v>
@@ -18486,7 +18507,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18692,7 +18713,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19104,7 +19125,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19516,7 +19537,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19928,7 +19949,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20546,7 +20567,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20833,7 +20854,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ95">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR95">
         <v>1.17</v>
@@ -21036,7 +21057,7 @@
         <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ96">
         <v>0.31</v>
@@ -21242,10 +21263,10 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ97">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR97">
         <v>1.33</v>
@@ -21448,10 +21469,10 @@
         <v>0.6</v>
       </c>
       <c r="AP98">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR98">
         <v>1.32</v>
@@ -21576,7 +21597,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21782,7 +21803,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21988,7 +22009,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22066,10 +22087,10 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ101">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22194,7 +22215,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22272,7 +22293,7 @@
         <v>2.6</v>
       </c>
       <c r="AP102">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>1.54</v>
@@ -22400,7 +22421,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22890,7 +22911,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ105">
         <v>1</v>
@@ -23224,7 +23245,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23636,7 +23657,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24048,7 +24069,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24126,10 +24147,10 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -24254,7 +24275,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24335,7 +24356,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ112">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR112">
         <v>1.19</v>
@@ -24541,7 +24562,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ113">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR113">
         <v>1.01</v>
@@ -24950,7 +24971,7 @@
         <v>0.14</v>
       </c>
       <c r="AP115">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115">
         <v>0.31</v>
@@ -25078,7 +25099,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25156,7 +25177,7 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ116">
         <v>1.38</v>
@@ -25284,7 +25305,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25362,10 +25383,10 @@
         <v>1.8</v>
       </c>
       <c r="AP117">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ117">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25490,7 +25511,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25696,7 +25717,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25774,10 +25795,10 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR119">
         <v>1.78</v>
@@ -25902,7 +25923,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -25983,7 +26004,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ120">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR120">
         <v>1.05</v>
@@ -26189,7 +26210,7 @@
         <v>1</v>
       </c>
       <c r="AQ121">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR121">
         <v>1.85</v>
@@ -26598,7 +26619,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26726,7 +26747,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26804,7 +26825,7 @@
         <v>1.43</v>
       </c>
       <c r="AP124">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ124">
         <v>1.38</v>
@@ -26932,7 +26953,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27138,7 +27159,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27550,7 +27571,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27628,7 +27649,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ128">
         <v>1.25</v>
@@ -27756,7 +27777,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27834,7 +27855,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ129">
         <v>0.85</v>
@@ -28040,7 +28061,7 @@
         <v>0.13</v>
       </c>
       <c r="AP130">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ130">
         <v>0.31</v>
@@ -28168,7 +28189,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28658,7 +28679,7 @@
         <v>0.88</v>
       </c>
       <c r="AP133">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ133">
         <v>0.6899999999999999</v>
@@ -28867,7 +28888,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ134">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR134">
         <v>2.03</v>
@@ -29073,7 +29094,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ135">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR135">
         <v>1.93</v>
@@ -29198,7 +29219,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29485,7 +29506,7 @@
         <v>1</v>
       </c>
       <c r="AQ137">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR137">
         <v>1.8</v>
@@ -29691,7 +29712,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ138">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR138">
         <v>1.06</v>
@@ -29816,7 +29837,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29894,7 +29915,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ139">
         <v>2.08</v>
@@ -30103,7 +30124,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ140">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR140">
         <v>1.53</v>
@@ -30228,7 +30249,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30434,7 +30455,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30512,7 +30533,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ142">
         <v>1.38</v>
@@ -30640,7 +30661,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31130,7 +31151,7 @@
         <v>0.11</v>
       </c>
       <c r="AP145">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ145">
         <v>0.31</v>
@@ -31258,7 +31279,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31336,7 +31357,7 @@
         <v>0.78</v>
       </c>
       <c r="AP146">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ146">
         <v>0.6899999999999999</v>
@@ -31464,7 +31485,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31670,7 +31691,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31876,7 +31897,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32160,7 +32181,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32288,7 +32309,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32366,7 +32387,7 @@
         <v>0.78</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ151">
         <v>0.85</v>
@@ -32494,7 +32515,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32700,7 +32721,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32781,7 +32802,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ153">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR153">
         <v>1.01</v>
@@ -33112,7 +33133,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33396,7 +33417,7 @@
         <v>2.11</v>
       </c>
       <c r="AP156">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156">
         <v>2.08</v>
@@ -33605,7 +33626,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ157">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR157">
         <v>1.13</v>
@@ -33730,7 +33751,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33811,7 +33832,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ158">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR158">
         <v>2</v>
@@ -33936,7 +33957,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34142,7 +34163,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34223,7 +34244,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR160">
         <v>1.53</v>
@@ -34348,7 +34369,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34429,7 +34450,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ161">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34632,7 +34653,7 @@
         <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ162">
         <v>1.77</v>
@@ -34966,7 +34987,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35047,7 +35068,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ164">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR164">
         <v>1.67</v>
@@ -35172,7 +35193,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35250,7 +35271,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35584,7 +35605,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35868,7 +35889,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ168">
         <v>0.6899999999999999</v>
@@ -36074,7 +36095,7 @@
         <v>2</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ169">
         <v>1.71</v>
@@ -36202,7 +36223,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36283,7 +36304,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ170">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR170">
         <v>1.25</v>
@@ -36489,7 +36510,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR171">
         <v>1.13</v>
@@ -37026,7 +37047,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37107,7 +37128,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ174">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR174">
         <v>1.18</v>
@@ -37232,7 +37253,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37516,7 +37537,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>0.85</v>
@@ -37850,7 +37871,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38134,7 +38155,7 @@
         <v>1.82</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ179">
         <v>1.71</v>
@@ -38262,7 +38283,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38340,7 +38361,7 @@
         <v>3</v>
       </c>
       <c r="AP180">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ180">
         <v>3</v>
@@ -38546,7 +38567,7 @@
         <v>1.82</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ181">
         <v>1.54</v>
@@ -38674,7 +38695,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38752,7 +38773,7 @@
         <v>0.09</v>
       </c>
       <c r="AP182">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ182">
         <v>0.31</v>
@@ -38880,7 +38901,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -38961,7 +38982,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ183">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR183">
         <v>1.95</v>
@@ -39086,7 +39107,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39167,7 +39188,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ184">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR184">
         <v>1.73</v>
@@ -39370,7 +39391,7 @@
         <v>1.73</v>
       </c>
       <c r="AP185">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ185">
         <v>1.77</v>
@@ -39498,7 +39519,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39704,7 +39725,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39910,7 +39931,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40116,7 +40137,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40609,7 +40630,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ191">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR191">
         <v>1.17</v>
@@ -40734,7 +40755,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -40815,7 +40836,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ192">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR192">
         <v>1.69</v>
@@ -41146,7 +41167,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41224,7 +41245,7 @@
         <v>3</v>
       </c>
       <c r="AP194">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ194">
         <v>3</v>
@@ -41430,7 +41451,7 @@
         <v>1.67</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195">
         <v>1.54</v>
@@ -41558,7 +41579,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41636,7 +41657,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196">
         <v>1.77</v>
@@ -41764,7 +41785,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42048,10 +42069,10 @@
         <v>0.83</v>
       </c>
       <c r="AP198">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ198">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR198">
         <v>1.34</v>
@@ -42254,10 +42275,10 @@
         <v>1.25</v>
       </c>
       <c r="AP199">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ199">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR199">
         <v>1.64</v>
@@ -42463,7 +42484,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ200">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR200">
         <v>1.97</v>
@@ -42794,7 +42815,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43206,7 +43227,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43412,7 +43433,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43493,7 +43514,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ205">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR205">
         <v>1.17</v>
@@ -43824,7 +43845,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44329,31 +44350,31 @@
         <v>2.64</v>
       </c>
       <c r="AU209">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV209">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW209">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX209">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY209">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AZ209">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA209">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB209">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC209">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD209">
         <v>1.95</v>
@@ -44393,6 +44414,1036 @@
       </c>
       <c r="BP209">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7453893</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45724.375</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="s">
+        <v>71</v>
+      </c>
+      <c r="H210" t="s">
+        <v>74</v>
+      </c>
+      <c r="I210">
+        <v>2</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>2</v>
+      </c>
+      <c r="L210">
+        <v>2</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>3</v>
+      </c>
+      <c r="O210" t="s">
+        <v>223</v>
+      </c>
+      <c r="P210" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q210">
+        <v>3.75</v>
+      </c>
+      <c r="R210">
+        <v>2.05</v>
+      </c>
+      <c r="S210">
+        <v>2.75</v>
+      </c>
+      <c r="T210">
+        <v>1.44</v>
+      </c>
+      <c r="U210">
+        <v>2.63</v>
+      </c>
+      <c r="V210">
+        <v>3.25</v>
+      </c>
+      <c r="W210">
+        <v>1.33</v>
+      </c>
+      <c r="X210">
+        <v>7.5</v>
+      </c>
+      <c r="Y210">
+        <v>1.07</v>
+      </c>
+      <c r="Z210">
+        <v>3.41</v>
+      </c>
+      <c r="AA210">
+        <v>3.2</v>
+      </c>
+      <c r="AB210">
+        <v>2.15</v>
+      </c>
+      <c r="AC210">
+        <v>1.06</v>
+      </c>
+      <c r="AD210">
+        <v>8</v>
+      </c>
+      <c r="AE210">
+        <v>1.36</v>
+      </c>
+      <c r="AF210">
+        <v>3</v>
+      </c>
+      <c r="AG210">
+        <v>2.05</v>
+      </c>
+      <c r="AH210">
+        <v>1.61</v>
+      </c>
+      <c r="AI210">
+        <v>1.83</v>
+      </c>
+      <c r="AJ210">
+        <v>1.83</v>
+      </c>
+      <c r="AK210">
+        <v>1.7</v>
+      </c>
+      <c r="AL210">
+        <v>1.28</v>
+      </c>
+      <c r="AM210">
+        <v>1.28</v>
+      </c>
+      <c r="AN210">
+        <v>1.15</v>
+      </c>
+      <c r="AO210">
+        <v>1.31</v>
+      </c>
+      <c r="AP210">
+        <v>1.29</v>
+      </c>
+      <c r="AQ210">
+        <v>1.21</v>
+      </c>
+      <c r="AR210">
+        <v>1.42</v>
+      </c>
+      <c r="AS210">
+        <v>1.37</v>
+      </c>
+      <c r="AT210">
+        <v>2.79</v>
+      </c>
+      <c r="AU210">
+        <v>5</v>
+      </c>
+      <c r="AV210">
+        <v>10</v>
+      </c>
+      <c r="AW210">
+        <v>1</v>
+      </c>
+      <c r="AX210">
+        <v>3</v>
+      </c>
+      <c r="AY210">
+        <v>7</v>
+      </c>
+      <c r="AZ210">
+        <v>13</v>
+      </c>
+      <c r="BA210">
+        <v>4</v>
+      </c>
+      <c r="BB210">
+        <v>7</v>
+      </c>
+      <c r="BC210">
+        <v>11</v>
+      </c>
+      <c r="BD210">
+        <v>2.53</v>
+      </c>
+      <c r="BE210">
+        <v>7.5</v>
+      </c>
+      <c r="BF210">
+        <v>1.75</v>
+      </c>
+      <c r="BG210">
+        <v>1.66</v>
+      </c>
+      <c r="BH210">
+        <v>2.14</v>
+      </c>
+      <c r="BI210">
+        <v>2.11</v>
+      </c>
+      <c r="BJ210">
+        <v>1.68</v>
+      </c>
+      <c r="BK210">
+        <v>2.75</v>
+      </c>
+      <c r="BL210">
+        <v>1.4</v>
+      </c>
+      <c r="BM210">
+        <v>3.78</v>
+      </c>
+      <c r="BN210">
+        <v>1.21</v>
+      </c>
+      <c r="BO210">
+        <v>5.35</v>
+      </c>
+      <c r="BP210">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7453890</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F211">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>80</v>
+      </c>
+      <c r="H211" t="s">
+        <v>72</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211">
+        <v>2</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>3</v>
+      </c>
+      <c r="N211">
+        <v>3</v>
+      </c>
+      <c r="O211" t="s">
+        <v>87</v>
+      </c>
+      <c r="P211" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q211">
+        <v>9.5</v>
+      </c>
+      <c r="R211">
+        <v>3</v>
+      </c>
+      <c r="S211">
+        <v>1.5</v>
+      </c>
+      <c r="T211">
+        <v>1.2</v>
+      </c>
+      <c r="U211">
+        <v>4.33</v>
+      </c>
+      <c r="V211">
+        <v>1.91</v>
+      </c>
+      <c r="W211">
+        <v>1.8</v>
+      </c>
+      <c r="X211">
+        <v>4</v>
+      </c>
+      <c r="Y211">
+        <v>1.22</v>
+      </c>
+      <c r="Z211">
+        <v>11</v>
+      </c>
+      <c r="AA211">
+        <v>7.3</v>
+      </c>
+      <c r="AB211">
+        <v>1.18</v>
+      </c>
+      <c r="AC211">
+        <v>1.01</v>
+      </c>
+      <c r="AD211">
+        <v>18</v>
+      </c>
+      <c r="AE211">
+        <v>1.08</v>
+      </c>
+      <c r="AF211">
+        <v>7</v>
+      </c>
+      <c r="AG211">
+        <v>1.37</v>
+      </c>
+      <c r="AH211">
+        <v>2.85</v>
+      </c>
+      <c r="AI211">
+        <v>1.91</v>
+      </c>
+      <c r="AJ211">
+        <v>1.8</v>
+      </c>
+      <c r="AK211">
+        <v>5.35</v>
+      </c>
+      <c r="AL211">
+        <v>1.04</v>
+      </c>
+      <c r="AM211">
+        <v>1.01</v>
+      </c>
+      <c r="AN211">
+        <v>1.62</v>
+      </c>
+      <c r="AO211">
+        <v>3</v>
+      </c>
+      <c r="AP211">
+        <v>1.5</v>
+      </c>
+      <c r="AQ211">
+        <v>3</v>
+      </c>
+      <c r="AR211">
+        <v>1.64</v>
+      </c>
+      <c r="AS211">
+        <v>2.21</v>
+      </c>
+      <c r="AT211">
+        <v>3.85</v>
+      </c>
+      <c r="AU211">
+        <v>3</v>
+      </c>
+      <c r="AV211">
+        <v>8</v>
+      </c>
+      <c r="AW211">
+        <v>7</v>
+      </c>
+      <c r="AX211">
+        <v>10</v>
+      </c>
+      <c r="AY211">
+        <v>11</v>
+      </c>
+      <c r="AZ211">
+        <v>18</v>
+      </c>
+      <c r="BA211">
+        <v>4</v>
+      </c>
+      <c r="BB211">
+        <v>8</v>
+      </c>
+      <c r="BC211">
+        <v>12</v>
+      </c>
+      <c r="BD211">
+        <v>6.5</v>
+      </c>
+      <c r="BE211">
+        <v>11</v>
+      </c>
+      <c r="BF211">
+        <v>1.14</v>
+      </c>
+      <c r="BG211">
+        <v>1.26</v>
+      </c>
+      <c r="BH211">
+        <v>3.38</v>
+      </c>
+      <c r="BI211">
+        <v>1.48</v>
+      </c>
+      <c r="BJ211">
+        <v>2.45</v>
+      </c>
+      <c r="BK211">
+        <v>1.82</v>
+      </c>
+      <c r="BL211">
+        <v>1.93</v>
+      </c>
+      <c r="BM211">
+        <v>2.3</v>
+      </c>
+      <c r="BN211">
+        <v>1.57</v>
+      </c>
+      <c r="BO211">
+        <v>2.93</v>
+      </c>
+      <c r="BP211">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7453891</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45724.58333333334</v>
+      </c>
+      <c r="F212">
+        <v>27</v>
+      </c>
+      <c r="G212" t="s">
+        <v>79</v>
+      </c>
+      <c r="H212" t="s">
+        <v>76</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>3</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>3</v>
+      </c>
+      <c r="O212" t="s">
+        <v>224</v>
+      </c>
+      <c r="P212" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q212">
+        <v>2.5</v>
+      </c>
+      <c r="R212">
+        <v>2.05</v>
+      </c>
+      <c r="S212">
+        <v>4.5</v>
+      </c>
+      <c r="T212">
+        <v>1.44</v>
+      </c>
+      <c r="U212">
+        <v>2.63</v>
+      </c>
+      <c r="V212">
+        <v>3.25</v>
+      </c>
+      <c r="W212">
+        <v>1.33</v>
+      </c>
+      <c r="X212">
+        <v>8</v>
+      </c>
+      <c r="Y212">
+        <v>1.06</v>
+      </c>
+      <c r="Z212">
+        <v>1.83</v>
+      </c>
+      <c r="AA212">
+        <v>3.5</v>
+      </c>
+      <c r="AB212">
+        <v>3.8</v>
+      </c>
+      <c r="AC212">
+        <v>1</v>
+      </c>
+      <c r="AD212">
+        <v>9</v>
+      </c>
+      <c r="AE212">
+        <v>1.26</v>
+      </c>
+      <c r="AF212">
+        <v>3.22</v>
+      </c>
+      <c r="AG212">
+        <v>2.15</v>
+      </c>
+      <c r="AH212">
+        <v>1.67</v>
+      </c>
+      <c r="AI212">
+        <v>2</v>
+      </c>
+      <c r="AJ212">
+        <v>1.73</v>
+      </c>
+      <c r="AK212">
+        <v>1.15</v>
+      </c>
+      <c r="AL212">
+        <v>1.24</v>
+      </c>
+      <c r="AM212">
+        <v>2.25</v>
+      </c>
+      <c r="AN212">
+        <v>1.08</v>
+      </c>
+      <c r="AO212">
+        <v>0.85</v>
+      </c>
+      <c r="AP212">
+        <v>1.21</v>
+      </c>
+      <c r="AQ212">
+        <v>0.79</v>
+      </c>
+      <c r="AR212">
+        <v>1.45</v>
+      </c>
+      <c r="AS212">
+        <v>1.12</v>
+      </c>
+      <c r="AT212">
+        <v>2.57</v>
+      </c>
+      <c r="AU212">
+        <v>6</v>
+      </c>
+      <c r="AV212">
+        <v>2</v>
+      </c>
+      <c r="AW212">
+        <v>2</v>
+      </c>
+      <c r="AX212">
+        <v>8</v>
+      </c>
+      <c r="AY212">
+        <v>10</v>
+      </c>
+      <c r="AZ212">
+        <v>13</v>
+      </c>
+      <c r="BA212">
+        <v>3</v>
+      </c>
+      <c r="BB212">
+        <v>6</v>
+      </c>
+      <c r="BC212">
+        <v>9</v>
+      </c>
+      <c r="BD212">
+        <v>1.64</v>
+      </c>
+      <c r="BE212">
+        <v>7.5</v>
+      </c>
+      <c r="BF212">
+        <v>2.78</v>
+      </c>
+      <c r="BG212">
+        <v>1.74</v>
+      </c>
+      <c r="BH212">
+        <v>2.02</v>
+      </c>
+      <c r="BI212">
+        <v>2.25</v>
+      </c>
+      <c r="BJ212">
+        <v>1.6</v>
+      </c>
+      <c r="BK212">
+        <v>2.95</v>
+      </c>
+      <c r="BL212">
+        <v>1.35</v>
+      </c>
+      <c r="BM212">
+        <v>4.15</v>
+      </c>
+      <c r="BN212">
+        <v>1.17</v>
+      </c>
+      <c r="BO212">
+        <v>5.85</v>
+      </c>
+      <c r="BP212">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7453892</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45724.58680555555</v>
+      </c>
+      <c r="F213">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>83</v>
+      </c>
+      <c r="H213" t="s">
+        <v>75</v>
+      </c>
+      <c r="I213">
+        <v>2</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>2</v>
+      </c>
+      <c r="L213">
+        <v>3</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>5</v>
+      </c>
+      <c r="O213" t="s">
+        <v>225</v>
+      </c>
+      <c r="P213" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q213">
+        <v>1.8</v>
+      </c>
+      <c r="R213">
+        <v>2.5</v>
+      </c>
+      <c r="S213">
+        <v>6</v>
+      </c>
+      <c r="T213">
+        <v>1.25</v>
+      </c>
+      <c r="U213">
+        <v>3.75</v>
+      </c>
+      <c r="V213">
+        <v>2.25</v>
+      </c>
+      <c r="W213">
+        <v>1.57</v>
+      </c>
+      <c r="X213">
+        <v>4.5</v>
+      </c>
+      <c r="Y213">
+        <v>1.17</v>
+      </c>
+      <c r="Z213">
+        <v>1.41</v>
+      </c>
+      <c r="AA213">
+        <v>4.8</v>
+      </c>
+      <c r="AB213">
+        <v>6.5</v>
+      </c>
+      <c r="AC213">
+        <v>1.01</v>
+      </c>
+      <c r="AD213">
+        <v>17</v>
+      </c>
+      <c r="AE213">
+        <v>1.15</v>
+      </c>
+      <c r="AF213">
+        <v>5</v>
+      </c>
+      <c r="AG213">
+        <v>1.53</v>
+      </c>
+      <c r="AH213">
+        <v>2.34</v>
+      </c>
+      <c r="AI213">
+        <v>1.8</v>
+      </c>
+      <c r="AJ213">
+        <v>1.91</v>
+      </c>
+      <c r="AK213">
+        <v>1.03</v>
+      </c>
+      <c r="AL213">
+        <v>1.12</v>
+      </c>
+      <c r="AM213">
+        <v>3.2</v>
+      </c>
+      <c r="AN213">
+        <v>2</v>
+      </c>
+      <c r="AO213">
+        <v>1.15</v>
+      </c>
+      <c r="AP213">
+        <v>2.07</v>
+      </c>
+      <c r="AQ213">
+        <v>1.07</v>
+      </c>
+      <c r="AR213">
+        <v>1.85</v>
+      </c>
+      <c r="AS213">
+        <v>1.29</v>
+      </c>
+      <c r="AT213">
+        <v>3.14</v>
+      </c>
+      <c r="AU213">
+        <v>7</v>
+      </c>
+      <c r="AV213">
+        <v>6</v>
+      </c>
+      <c r="AW213">
+        <v>3</v>
+      </c>
+      <c r="AX213">
+        <v>4</v>
+      </c>
+      <c r="AY213">
+        <v>12</v>
+      </c>
+      <c r="AZ213">
+        <v>11</v>
+      </c>
+      <c r="BA213">
+        <v>1</v>
+      </c>
+      <c r="BB213">
+        <v>3</v>
+      </c>
+      <c r="BC213">
+        <v>4</v>
+      </c>
+      <c r="BD213">
+        <v>1.26</v>
+      </c>
+      <c r="BE213">
+        <v>10</v>
+      </c>
+      <c r="BF213">
+        <v>4.64</v>
+      </c>
+      <c r="BG213">
+        <v>1.28</v>
+      </c>
+      <c r="BH213">
+        <v>3.25</v>
+      </c>
+      <c r="BI213">
+        <v>1.52</v>
+      </c>
+      <c r="BJ213">
+        <v>2.37</v>
+      </c>
+      <c r="BK213">
+        <v>1.87</v>
+      </c>
+      <c r="BL213">
+        <v>1.87</v>
+      </c>
+      <c r="BM213">
+        <v>2.38</v>
+      </c>
+      <c r="BN213">
+        <v>1.54</v>
+      </c>
+      <c r="BO213">
+        <v>3.12</v>
+      </c>
+      <c r="BP213">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7453894</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45724.625</v>
+      </c>
+      <c r="F214">
+        <v>27</v>
+      </c>
+      <c r="G214" t="s">
+        <v>70</v>
+      </c>
+      <c r="H214" t="s">
+        <v>77</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>3</v>
+      </c>
+      <c r="N214">
+        <v>4</v>
+      </c>
+      <c r="O214" t="s">
+        <v>226</v>
+      </c>
+      <c r="P214" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q214">
+        <v>2.63</v>
+      </c>
+      <c r="R214">
+        <v>2.2</v>
+      </c>
+      <c r="S214">
+        <v>3.75</v>
+      </c>
+      <c r="T214">
+        <v>1.36</v>
+      </c>
+      <c r="U214">
+        <v>3</v>
+      </c>
+      <c r="V214">
+        <v>2.63</v>
+      </c>
+      <c r="W214">
+        <v>1.44</v>
+      </c>
+      <c r="X214">
+        <v>6.5</v>
+      </c>
+      <c r="Y214">
+        <v>1.1</v>
+      </c>
+      <c r="Z214">
+        <v>2.12</v>
+      </c>
+      <c r="AA214">
+        <v>3.57</v>
+      </c>
+      <c r="AB214">
+        <v>3.15</v>
+      </c>
+      <c r="AC214">
+        <v>1.05</v>
+      </c>
+      <c r="AD214">
+        <v>8.5</v>
+      </c>
+      <c r="AE214">
+        <v>1.25</v>
+      </c>
+      <c r="AF214">
+        <v>3.65</v>
+      </c>
+      <c r="AG214">
+        <v>1.61</v>
+      </c>
+      <c r="AH214">
+        <v>2.1</v>
+      </c>
+      <c r="AI214">
+        <v>1.67</v>
+      </c>
+      <c r="AJ214">
+        <v>2.1</v>
+      </c>
+      <c r="AK214">
+        <v>1.35</v>
+      </c>
+      <c r="AL214">
+        <v>1.25</v>
+      </c>
+      <c r="AM214">
+        <v>1.65</v>
+      </c>
+      <c r="AN214">
+        <v>2</v>
+      </c>
+      <c r="AO214">
+        <v>1.15</v>
+      </c>
+      <c r="AP214">
+        <v>1.86</v>
+      </c>
+      <c r="AQ214">
+        <v>1.29</v>
+      </c>
+      <c r="AR214">
+        <v>1.63</v>
+      </c>
+      <c r="AS214">
+        <v>1.54</v>
+      </c>
+      <c r="AT214">
+        <v>3.17</v>
+      </c>
+      <c r="AU214">
+        <v>3</v>
+      </c>
+      <c r="AV214">
+        <v>10</v>
+      </c>
+      <c r="AW214">
+        <v>5</v>
+      </c>
+      <c r="AX214">
+        <v>4</v>
+      </c>
+      <c r="AY214">
+        <v>8</v>
+      </c>
+      <c r="AZ214">
+        <v>15</v>
+      </c>
+      <c r="BA214">
+        <v>5</v>
+      </c>
+      <c r="BB214">
+        <v>4</v>
+      </c>
+      <c r="BC214">
+        <v>9</v>
+      </c>
+      <c r="BD214">
+        <v>2</v>
+      </c>
+      <c r="BE214">
+        <v>7.5</v>
+      </c>
+      <c r="BF214">
+        <v>2.1</v>
+      </c>
+      <c r="BG214">
+        <v>1.39</v>
+      </c>
+      <c r="BH214">
+        <v>2.77</v>
+      </c>
+      <c r="BI214">
+        <v>1.68</v>
+      </c>
+      <c r="BJ214">
+        <v>2.11</v>
+      </c>
+      <c r="BK214">
+        <v>2.11</v>
+      </c>
+      <c r="BL214">
+        <v>1.68</v>
+      </c>
+      <c r="BM214">
+        <v>2.7</v>
+      </c>
+      <c r="BN214">
+        <v>1.41</v>
+      </c>
+      <c r="BO214">
+        <v>3.65</v>
+      </c>
+      <c r="BP214">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,16 +685,22 @@
     <t>['65']</t>
   </si>
   <si>
-    <t>['5', '29']</t>
+    <t>['21', '54', '90']</t>
   </si>
   <si>
-    <t>['21', '54', '90']</t>
+    <t>['5', '29']</t>
   </si>
   <si>
     <t>['5', '30', '71']</t>
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['12', '42', '77']</t>
+  </si>
+  <si>
+    <t>['73']</t>
   </si>
   <si>
     <t>['3', '15', '45+3']</t>
@@ -1359,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1615,7 +1621,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2108,7 +2114,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ4">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2233,7 +2239,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2645,7 +2651,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2851,7 +2857,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3263,7 +3269,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3469,7 +3475,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3675,7 +3681,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3756,7 +3762,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ12">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR12">
         <v>2.33</v>
@@ -4992,7 +4998,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ18">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5117,7 +5123,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6147,7 +6153,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6765,7 +6771,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6971,7 +6977,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -7461,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30">
         <v>2.08</v>
@@ -7589,7 +7595,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7667,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31">
         <v>1.29</v>
@@ -7795,7 +7801,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8207,7 +8213,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8288,7 +8294,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ34">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR34">
         <v>1.89</v>
@@ -8494,7 +8500,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ35">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -9031,7 +9037,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9649,7 +9655,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9855,7 +9861,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10061,7 +10067,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10267,7 +10273,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10345,7 +10351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10473,7 +10479,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10551,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
         <v>0.6899999999999999</v>
@@ -10966,7 +10972,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ47">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR47">
         <v>1.89</v>
@@ -11091,7 +11097,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11503,7 +11509,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11584,7 +11590,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ50">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11709,7 +11715,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12405,7 +12411,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ54">
         <v>1.25</v>
@@ -12945,7 +12951,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13151,7 +13157,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13357,7 +13363,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13563,7 +13569,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13769,7 +13775,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13847,7 +13853,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61">
         <v>1.38</v>
@@ -14056,7 +14062,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -14181,7 +14187,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14387,7 +14393,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14468,7 +14474,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ64">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR64">
         <v>1.12</v>
@@ -14593,7 +14599,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14671,7 +14677,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ65">
         <v>1.77</v>
@@ -14799,7 +14805,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15417,7 +15423,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15829,7 +15835,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16035,7 +16041,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16447,7 +16453,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16525,7 +16531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ74">
         <v>0.6899999999999999</v>
@@ -16859,7 +16865,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17271,7 +17277,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17349,7 +17355,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ78">
         <v>1.07</v>
@@ -17477,7 +17483,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17889,7 +17895,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -17970,7 +17976,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ81">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR81">
         <v>1.32</v>
@@ -18095,7 +18101,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18301,7 +18307,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18507,7 +18513,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18585,7 +18591,7 @@
         <v>3</v>
       </c>
       <c r="AP84">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>3</v>
@@ -18713,7 +18719,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19000,7 +19006,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ86">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -19125,7 +19131,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19537,7 +19543,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19949,7 +19955,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20567,7 +20573,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20851,7 +20857,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95">
         <v>0.79</v>
@@ -21060,7 +21066,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21597,7 +21603,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21803,7 +21809,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21881,7 +21887,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ100">
         <v>1.71</v>
@@ -22009,7 +22015,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22215,7 +22221,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22296,7 +22302,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR102">
         <v>1.61</v>
@@ -22421,7 +22427,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23245,7 +23251,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23657,7 +23663,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24069,7 +24075,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24275,7 +24281,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24353,7 +24359,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ112">
         <v>1.21</v>
@@ -24765,10 +24771,10 @@
         <v>2.33</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ114">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24974,7 +24980,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ115">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -25099,7 +25105,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25305,7 +25311,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25511,7 +25517,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25717,7 +25723,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25923,7 +25929,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26207,7 +26213,7 @@
         <v>0.43</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ121">
         <v>0.79</v>
@@ -26416,7 +26422,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ122">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR122">
         <v>1.45</v>
@@ -26747,7 +26753,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26953,7 +26959,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27159,7 +27165,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27571,7 +27577,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27777,7 +27783,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28064,7 +28070,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ130">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28189,7 +28195,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -29219,7 +29225,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29300,7 +29306,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ136">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR136">
         <v>1.2</v>
@@ -29503,7 +29509,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ137">
         <v>1.21</v>
@@ -29837,7 +29843,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30249,7 +30255,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30327,7 +30333,7 @@
         <v>0.88</v>
       </c>
       <c r="AP141">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -30455,7 +30461,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30661,7 +30667,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30948,7 +30954,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ144">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR144">
         <v>1.18</v>
@@ -31154,7 +31160,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ145">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31279,7 +31285,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31485,7 +31491,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31691,7 +31697,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31897,7 +31903,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32309,7 +32315,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32515,7 +32521,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32721,7 +32727,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33005,7 +33011,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ154">
         <v>1.25</v>
@@ -33133,7 +33139,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33211,7 +33217,7 @@
         <v>1.56</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ155">
         <v>1.38</v>
@@ -33751,7 +33757,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33957,7 +33963,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34163,7 +34169,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34369,7 +34375,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34447,7 +34453,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ161">
         <v>1.29</v>
@@ -34862,7 +34868,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ163">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR163">
         <v>1.69</v>
@@ -34987,7 +34993,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35193,7 +35199,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35477,10 +35483,10 @@
         <v>0.1</v>
       </c>
       <c r="AP166">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ166">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR166">
         <v>1.38</v>
@@ -35605,7 +35611,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36223,7 +36229,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36919,7 +36925,7 @@
         <v>2.2</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ173">
         <v>2.08</v>
@@ -37047,7 +37053,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37253,7 +37259,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37871,7 +37877,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37949,7 +37955,7 @@
         <v>0.64</v>
       </c>
       <c r="AP178">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38283,7 +38289,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38570,7 +38576,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ181">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -38695,7 +38701,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38776,7 +38782,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ182">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR182">
         <v>1.76</v>
@@ -38901,7 +38907,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39107,7 +39113,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39519,7 +39525,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39725,7 +39731,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39931,7 +39937,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40009,7 +40015,7 @@
         <v>0.73</v>
       </c>
       <c r="AP188">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
         <v>0.85</v>
@@ -40137,7 +40143,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40755,7 +40761,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -41042,7 +41048,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ193">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR193">
         <v>1.1</v>
@@ -41167,7 +41173,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41454,7 +41460,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ195">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR195">
         <v>1.71</v>
@@ -41579,7 +41585,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41785,7 +41791,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -41863,7 +41869,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ197">
         <v>1.71</v>
@@ -42815,7 +42821,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43227,7 +43233,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43305,7 +43311,7 @@
         <v>0.83</v>
       </c>
       <c r="AP204">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
         <v>1</v>
@@ -43433,7 +43439,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43845,7 +43851,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44421,7 +44427,7 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>7453893</v>
+        <v>7453891</v>
       </c>
       <c r="C210" t="s">
         <v>68</v>
@@ -44430,31 +44436,31 @@
         <v>69</v>
       </c>
       <c r="E210" s="2">
-        <v>45724.375</v>
+        <v>45723.66666666666</v>
       </c>
       <c r="F210">
         <v>27</v>
       </c>
       <c r="G210" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H210" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J210">
         <v>0</v>
       </c>
       <c r="K210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L210">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N210">
         <v>3</v>
@@ -44463,16 +44469,16 @@
         <v>223</v>
       </c>
       <c r="P210" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="Q210">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="R210">
         <v>2.05</v>
       </c>
       <c r="S210">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="T210">
         <v>1.44</v>
@@ -44487,139 +44493,139 @@
         <v>1.33</v>
       </c>
       <c r="X210">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y210">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z210">
-        <v>3.41</v>
+        <v>1.83</v>
       </c>
       <c r="AA210">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB210">
+        <v>3.8</v>
+      </c>
+      <c r="AC210">
+        <v>1</v>
+      </c>
+      <c r="AD210">
+        <v>9</v>
+      </c>
+      <c r="AE210">
+        <v>1.26</v>
+      </c>
+      <c r="AF210">
+        <v>3.22</v>
+      </c>
+      <c r="AG210">
         <v>2.15</v>
       </c>
-      <c r="AC210">
-        <v>1.06</v>
-      </c>
-      <c r="AD210">
+      <c r="AH210">
+        <v>1.67</v>
+      </c>
+      <c r="AI210">
+        <v>2</v>
+      </c>
+      <c r="AJ210">
+        <v>1.73</v>
+      </c>
+      <c r="AK210">
+        <v>1.15</v>
+      </c>
+      <c r="AL210">
+        <v>1.24</v>
+      </c>
+      <c r="AM210">
+        <v>2.25</v>
+      </c>
+      <c r="AN210">
+        <v>1.08</v>
+      </c>
+      <c r="AO210">
+        <v>0.85</v>
+      </c>
+      <c r="AP210">
+        <v>1.21</v>
+      </c>
+      <c r="AQ210">
+        <v>0.79</v>
+      </c>
+      <c r="AR210">
+        <v>1.45</v>
+      </c>
+      <c r="AS210">
+        <v>1.12</v>
+      </c>
+      <c r="AT210">
+        <v>2.57</v>
+      </c>
+      <c r="AU210">
+        <v>6</v>
+      </c>
+      <c r="AV210">
+        <v>2</v>
+      </c>
+      <c r="AW210">
+        <v>2</v>
+      </c>
+      <c r="AX210">
         <v>8</v>
       </c>
-      <c r="AE210">
-        <v>1.36</v>
-      </c>
-      <c r="AF210">
-        <v>3</v>
-      </c>
-      <c r="AG210">
-        <v>2.05</v>
-      </c>
-      <c r="AH210">
-        <v>1.61</v>
-      </c>
-      <c r="AI210">
-        <v>1.83</v>
-      </c>
-      <c r="AJ210">
-        <v>1.83</v>
-      </c>
-      <c r="AK210">
-        <v>1.7</v>
-      </c>
-      <c r="AL210">
-        <v>1.28</v>
-      </c>
-      <c r="AM210">
-        <v>1.28</v>
-      </c>
-      <c r="AN210">
-        <v>1.15</v>
-      </c>
-      <c r="AO210">
-        <v>1.31</v>
-      </c>
-      <c r="AP210">
-        <v>1.29</v>
-      </c>
-      <c r="AQ210">
-        <v>1.21</v>
-      </c>
-      <c r="AR210">
-        <v>1.42</v>
-      </c>
-      <c r="AS210">
-        <v>1.37</v>
-      </c>
-      <c r="AT210">
-        <v>2.79</v>
-      </c>
-      <c r="AU210">
-        <v>5</v>
-      </c>
-      <c r="AV210">
+      <c r="AY210">
         <v>10</v>
-      </c>
-      <c r="AW210">
-        <v>1</v>
-      </c>
-      <c r="AX210">
-        <v>3</v>
-      </c>
-      <c r="AY210">
-        <v>7</v>
       </c>
       <c r="AZ210">
         <v>13</v>
       </c>
       <c r="BA210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB210">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC210">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD210">
-        <v>2.53</v>
+        <v>1.64</v>
       </c>
       <c r="BE210">
         <v>7.5</v>
       </c>
       <c r="BF210">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="BG210">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BH210">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="BI210">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BJ210">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BK210">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="BL210">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BM210">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="BN210">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BO210">
-        <v>5.35</v>
+        <v>5.85</v>
       </c>
       <c r="BP210">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="211" spans="1:68">
@@ -44627,7 +44633,7 @@
         <v>210</v>
       </c>
       <c r="B211">
-        <v>7453890</v>
+        <v>7453893</v>
       </c>
       <c r="C211" t="s">
         <v>68</v>
@@ -44636,196 +44642,196 @@
         <v>69</v>
       </c>
       <c r="E211" s="2">
-        <v>45724.5</v>
+        <v>45724.375</v>
       </c>
       <c r="F211">
         <v>27</v>
       </c>
       <c r="G211" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H211" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J211">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K211">
         <v>2</v>
       </c>
       <c r="L211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N211">
         <v>3</v>
       </c>
       <c r="O211" t="s">
-        <v>87</v>
+        <v>224</v>
       </c>
       <c r="P211" t="s">
-        <v>325</v>
+        <v>183</v>
       </c>
       <c r="Q211">
-        <v>9.5</v>
+        <v>3.75</v>
       </c>
       <c r="R211">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="S211">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="T211">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="U211">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="V211">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="W211">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="X211">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="Y211">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z211">
-        <v>11</v>
+        <v>3.41</v>
       </c>
       <c r="AA211">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB211">
-        <v>1.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC211">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AD211">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AE211">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF211">
+        <v>3</v>
+      </c>
+      <c r="AG211">
+        <v>2.05</v>
+      </c>
+      <c r="AH211">
+        <v>1.61</v>
+      </c>
+      <c r="AI211">
+        <v>1.83</v>
+      </c>
+      <c r="AJ211">
+        <v>1.83</v>
+      </c>
+      <c r="AK211">
+        <v>1.7</v>
+      </c>
+      <c r="AL211">
+        <v>1.28</v>
+      </c>
+      <c r="AM211">
+        <v>1.28</v>
+      </c>
+      <c r="AN211">
+        <v>1.15</v>
+      </c>
+      <c r="AO211">
+        <v>1.31</v>
+      </c>
+      <c r="AP211">
+        <v>1.29</v>
+      </c>
+      <c r="AQ211">
+        <v>1.21</v>
+      </c>
+      <c r="AR211">
+        <v>1.42</v>
+      </c>
+      <c r="AS211">
+        <v>1.37</v>
+      </c>
+      <c r="AT211">
+        <v>2.79</v>
+      </c>
+      <c r="AU211">
+        <v>5</v>
+      </c>
+      <c r="AV211">
+        <v>10</v>
+      </c>
+      <c r="AW211">
+        <v>1</v>
+      </c>
+      <c r="AX211">
+        <v>3</v>
+      </c>
+      <c r="AY211">
         <v>7</v>
       </c>
-      <c r="AG211">
-        <v>1.37</v>
-      </c>
-      <c r="AH211">
-        <v>2.85</v>
-      </c>
-      <c r="AI211">
-        <v>1.91</v>
-      </c>
-      <c r="AJ211">
-        <v>1.8</v>
-      </c>
-      <c r="AK211">
-        <v>5.35</v>
-      </c>
-      <c r="AL211">
-        <v>1.04</v>
-      </c>
-      <c r="AM211">
-        <v>1.01</v>
-      </c>
-      <c r="AN211">
-        <v>1.62</v>
-      </c>
-      <c r="AO211">
-        <v>3</v>
-      </c>
-      <c r="AP211">
-        <v>1.5</v>
-      </c>
-      <c r="AQ211">
-        <v>3</v>
-      </c>
-      <c r="AR211">
-        <v>1.64</v>
-      </c>
-      <c r="AS211">
-        <v>2.21</v>
-      </c>
-      <c r="AT211">
-        <v>3.85</v>
-      </c>
-      <c r="AU211">
-        <v>3</v>
-      </c>
-      <c r="AV211">
-        <v>8</v>
-      </c>
-      <c r="AW211">
-        <v>7</v>
-      </c>
-      <c r="AX211">
-        <v>10</v>
-      </c>
-      <c r="AY211">
-        <v>11</v>
-      </c>
       <c r="AZ211">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA211">
         <v>4</v>
       </c>
       <c r="BB211">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC211">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD211">
-        <v>6.5</v>
+        <v>2.53</v>
       </c>
       <c r="BE211">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="BF211">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="BG211">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="BH211">
-        <v>3.38</v>
+        <v>2.14</v>
       </c>
       <c r="BI211">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="BJ211">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="BK211">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="BL211">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="BM211">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="BN211">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="BO211">
-        <v>2.93</v>
+        <v>5.35</v>
       </c>
       <c r="BP211">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="212" spans="1:68">
@@ -44833,7 +44839,7 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>7453891</v>
+        <v>7453890</v>
       </c>
       <c r="C212" t="s">
         <v>68</v>
@@ -44842,196 +44848,196 @@
         <v>69</v>
       </c>
       <c r="E212" s="2">
-        <v>45724.58333333334</v>
+        <v>45724.5</v>
       </c>
       <c r="F212">
         <v>27</v>
       </c>
       <c r="G212" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H212" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J212">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L212">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M212">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N212">
         <v>3</v>
       </c>
       <c r="O212" t="s">
-        <v>224</v>
+        <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>87</v>
+        <v>327</v>
       </c>
       <c r="Q212">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="R212">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="S212">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="T212">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="U212">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="V212">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="W212">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="X212">
+        <v>4</v>
+      </c>
+      <c r="Y212">
+        <v>1.22</v>
+      </c>
+      <c r="Z212">
+        <v>11</v>
+      </c>
+      <c r="AA212">
+        <v>7.3</v>
+      </c>
+      <c r="AB212">
+        <v>1.18</v>
+      </c>
+      <c r="AC212">
+        <v>1.01</v>
+      </c>
+      <c r="AD212">
+        <v>18</v>
+      </c>
+      <c r="AE212">
+        <v>1.08</v>
+      </c>
+      <c r="AF212">
+        <v>7</v>
+      </c>
+      <c r="AG212">
+        <v>1.37</v>
+      </c>
+      <c r="AH212">
+        <v>2.85</v>
+      </c>
+      <c r="AI212">
+        <v>1.91</v>
+      </c>
+      <c r="AJ212">
+        <v>1.8</v>
+      </c>
+      <c r="AK212">
+        <v>5.35</v>
+      </c>
+      <c r="AL212">
+        <v>1.04</v>
+      </c>
+      <c r="AM212">
+        <v>1.01</v>
+      </c>
+      <c r="AN212">
+        <v>1.62</v>
+      </c>
+      <c r="AO212">
+        <v>3</v>
+      </c>
+      <c r="AP212">
+        <v>1.5</v>
+      </c>
+      <c r="AQ212">
+        <v>3</v>
+      </c>
+      <c r="AR212">
+        <v>1.64</v>
+      </c>
+      <c r="AS212">
+        <v>2.21</v>
+      </c>
+      <c r="AT212">
+        <v>3.85</v>
+      </c>
+      <c r="AU212">
+        <v>3</v>
+      </c>
+      <c r="AV212">
         <v>8</v>
       </c>
-      <c r="Y212">
-        <v>1.06</v>
-      </c>
-      <c r="Z212">
-        <v>1.83</v>
-      </c>
-      <c r="AA212">
-        <v>3.5</v>
-      </c>
-      <c r="AB212">
-        <v>3.8</v>
-      </c>
-      <c r="AC212">
-        <v>1</v>
-      </c>
-      <c r="AD212">
-        <v>9</v>
-      </c>
-      <c r="AE212">
+      <c r="AW212">
+        <v>7</v>
+      </c>
+      <c r="AX212">
+        <v>10</v>
+      </c>
+      <c r="AY212">
+        <v>11</v>
+      </c>
+      <c r="AZ212">
+        <v>18</v>
+      </c>
+      <c r="BA212">
+        <v>4</v>
+      </c>
+      <c r="BB212">
+        <v>8</v>
+      </c>
+      <c r="BC212">
+        <v>12</v>
+      </c>
+      <c r="BD212">
+        <v>6.5</v>
+      </c>
+      <c r="BE212">
+        <v>11</v>
+      </c>
+      <c r="BF212">
+        <v>1.14</v>
+      </c>
+      <c r="BG212">
         <v>1.26</v>
       </c>
-      <c r="AF212">
-        <v>3.22</v>
-      </c>
-      <c r="AG212">
-        <v>2.15</v>
-      </c>
-      <c r="AH212">
-        <v>1.67</v>
-      </c>
-      <c r="AI212">
-        <v>2</v>
-      </c>
-      <c r="AJ212">
-        <v>1.73</v>
-      </c>
-      <c r="AK212">
-        <v>1.15</v>
-      </c>
-      <c r="AL212">
-        <v>1.24</v>
-      </c>
-      <c r="AM212">
-        <v>2.25</v>
-      </c>
-      <c r="AN212">
-        <v>1.08</v>
-      </c>
-      <c r="AO212">
-        <v>0.85</v>
-      </c>
-      <c r="AP212">
-        <v>1.21</v>
-      </c>
-      <c r="AQ212">
-        <v>0.79</v>
-      </c>
-      <c r="AR212">
-        <v>1.45</v>
-      </c>
-      <c r="AS212">
-        <v>1.12</v>
-      </c>
-      <c r="AT212">
-        <v>2.57</v>
-      </c>
-      <c r="AU212">
-        <v>6</v>
-      </c>
-      <c r="AV212">
-        <v>2</v>
-      </c>
-      <c r="AW212">
-        <v>2</v>
-      </c>
-      <c r="AX212">
-        <v>8</v>
-      </c>
-      <c r="AY212">
-        <v>10</v>
-      </c>
-      <c r="AZ212">
-        <v>13</v>
-      </c>
-      <c r="BA212">
-        <v>3</v>
-      </c>
-      <c r="BB212">
-        <v>6</v>
-      </c>
-      <c r="BC212">
-        <v>9</v>
-      </c>
-      <c r="BD212">
-        <v>1.64</v>
-      </c>
-      <c r="BE212">
-        <v>7.5</v>
-      </c>
-      <c r="BF212">
-        <v>2.78</v>
-      </c>
-      <c r="BG212">
-        <v>1.74</v>
-      </c>
       <c r="BH212">
-        <v>2.02</v>
+        <v>3.38</v>
       </c>
       <c r="BI212">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="BJ212">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="BK212">
-        <v>2.95</v>
+        <v>1.82</v>
       </c>
       <c r="BL212">
+        <v>1.93</v>
+      </c>
+      <c r="BM212">
+        <v>2.3</v>
+      </c>
+      <c r="BN212">
+        <v>1.57</v>
+      </c>
+      <c r="BO212">
+        <v>2.93</v>
+      </c>
+      <c r="BP212">
         <v>1.35</v>
-      </c>
-      <c r="BM212">
-        <v>4.15</v>
-      </c>
-      <c r="BN212">
-        <v>1.17</v>
-      </c>
-      <c r="BO212">
-        <v>5.85</v>
-      </c>
-      <c r="BP212">
-        <v>1.08</v>
       </c>
     </row>
     <row r="213" spans="1:68">
@@ -45081,7 +45087,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45287,7 +45293,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45444,6 +45450,418 @@
       </c>
       <c r="BP214">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7454216</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F215">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>84</v>
+      </c>
+      <c r="H215" t="s">
+        <v>73</v>
+      </c>
+      <c r="I215">
+        <v>2</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+      <c r="L215">
+        <v>3</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>3</v>
+      </c>
+      <c r="O215" t="s">
+        <v>227</v>
+      </c>
+      <c r="P215" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q215">
+        <v>0</v>
+      </c>
+      <c r="R215">
+        <v>0</v>
+      </c>
+      <c r="S215">
+        <v>0</v>
+      </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="U215">
+        <v>0</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="W215">
+        <v>0</v>
+      </c>
+      <c r="X215">
+        <v>0</v>
+      </c>
+      <c r="Y215">
+        <v>0</v>
+      </c>
+      <c r="Z215">
+        <v>1.57</v>
+      </c>
+      <c r="AA215">
+        <v>4.1</v>
+      </c>
+      <c r="AB215">
+        <v>5.3</v>
+      </c>
+      <c r="AC215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>0</v>
+      </c>
+      <c r="AE215">
+        <v>0</v>
+      </c>
+      <c r="AF215">
+        <v>0</v>
+      </c>
+      <c r="AG215">
+        <v>1.85</v>
+      </c>
+      <c r="AH215">
+        <v>1.89</v>
+      </c>
+      <c r="AI215">
+        <v>0</v>
+      </c>
+      <c r="AJ215">
+        <v>0</v>
+      </c>
+      <c r="AK215">
+        <v>0</v>
+      </c>
+      <c r="AL215">
+        <v>0</v>
+      </c>
+      <c r="AM215">
+        <v>0</v>
+      </c>
+      <c r="AN215">
+        <v>1.23</v>
+      </c>
+      <c r="AO215">
+        <v>1.54</v>
+      </c>
+      <c r="AP215">
+        <v>1.36</v>
+      </c>
+      <c r="AQ215">
+        <v>1.43</v>
+      </c>
+      <c r="AR215">
+        <v>1.47</v>
+      </c>
+      <c r="AS215">
+        <v>0.66</v>
+      </c>
+      <c r="AT215">
+        <v>2.13</v>
+      </c>
+      <c r="AU215">
+        <v>-1</v>
+      </c>
+      <c r="AV215">
+        <v>-1</v>
+      </c>
+      <c r="AW215">
+        <v>-1</v>
+      </c>
+      <c r="AX215">
+        <v>-1</v>
+      </c>
+      <c r="AY215">
+        <v>-1</v>
+      </c>
+      <c r="AZ215">
+        <v>-1</v>
+      </c>
+      <c r="BA215">
+        <v>-1</v>
+      </c>
+      <c r="BB215">
+        <v>-1</v>
+      </c>
+      <c r="BC215">
+        <v>-1</v>
+      </c>
+      <c r="BD215">
+        <v>0</v>
+      </c>
+      <c r="BE215">
+        <v>0</v>
+      </c>
+      <c r="BF215">
+        <v>0</v>
+      </c>
+      <c r="BG215">
+        <v>0</v>
+      </c>
+      <c r="BH215">
+        <v>0</v>
+      </c>
+      <c r="BI215">
+        <v>0</v>
+      </c>
+      <c r="BJ215">
+        <v>0</v>
+      </c>
+      <c r="BK215">
+        <v>0</v>
+      </c>
+      <c r="BL215">
+        <v>0</v>
+      </c>
+      <c r="BM215">
+        <v>0</v>
+      </c>
+      <c r="BN215">
+        <v>0</v>
+      </c>
+      <c r="BO215">
+        <v>0</v>
+      </c>
+      <c r="BP215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7453888</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45725.54166666666</v>
+      </c>
+      <c r="F216">
+        <v>27</v>
+      </c>
+      <c r="G216" t="s">
+        <v>85</v>
+      </c>
+      <c r="H216" t="s">
+        <v>78</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
+        <v>228</v>
+      </c>
+      <c r="P216" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q216">
+        <v>1.8</v>
+      </c>
+      <c r="R216">
+        <v>2.4</v>
+      </c>
+      <c r="S216">
+        <v>7</v>
+      </c>
+      <c r="T216">
+        <v>1.3</v>
+      </c>
+      <c r="U216">
+        <v>3.4</v>
+      </c>
+      <c r="V216">
+        <v>2.5</v>
+      </c>
+      <c r="W216">
+        <v>1.5</v>
+      </c>
+      <c r="X216">
+        <v>5.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.13</v>
+      </c>
+      <c r="Z216">
+        <v>1.14</v>
+      </c>
+      <c r="AA216">
+        <v>7.4</v>
+      </c>
+      <c r="AB216">
+        <v>17</v>
+      </c>
+      <c r="AC216">
+        <v>1.03</v>
+      </c>
+      <c r="AD216">
+        <v>10</v>
+      </c>
+      <c r="AE216">
+        <v>1.2</v>
+      </c>
+      <c r="AF216">
+        <v>4.2</v>
+      </c>
+      <c r="AG216">
+        <v>1.42</v>
+      </c>
+      <c r="AH216">
+        <v>2.65</v>
+      </c>
+      <c r="AI216">
+        <v>2</v>
+      </c>
+      <c r="AJ216">
+        <v>1.73</v>
+      </c>
+      <c r="AK216">
+        <v>1.03</v>
+      </c>
+      <c r="AL216">
+        <v>1.13</v>
+      </c>
+      <c r="AM216">
+        <v>3.1</v>
+      </c>
+      <c r="AN216">
+        <v>1</v>
+      </c>
+      <c r="AO216">
+        <v>0.31</v>
+      </c>
+      <c r="AP216">
+        <v>1.14</v>
+      </c>
+      <c r="AQ216">
+        <v>0.29</v>
+      </c>
+      <c r="AR216">
+        <v>1.76</v>
+      </c>
+      <c r="AS216">
+        <v>1.14</v>
+      </c>
+      <c r="AT216">
+        <v>2.9</v>
+      </c>
+      <c r="AU216">
+        <v>3</v>
+      </c>
+      <c r="AV216">
+        <v>6</v>
+      </c>
+      <c r="AW216">
+        <v>9</v>
+      </c>
+      <c r="AX216">
+        <v>6</v>
+      </c>
+      <c r="AY216">
+        <v>16</v>
+      </c>
+      <c r="AZ216">
+        <v>15</v>
+      </c>
+      <c r="BA216">
+        <v>4</v>
+      </c>
+      <c r="BB216">
+        <v>5</v>
+      </c>
+      <c r="BC216">
+        <v>9</v>
+      </c>
+      <c r="BD216">
+        <v>1.1</v>
+      </c>
+      <c r="BE216">
+        <v>13</v>
+      </c>
+      <c r="BF216">
+        <v>8</v>
+      </c>
+      <c r="BG216">
+        <v>1.44</v>
+      </c>
+      <c r="BH216">
+        <v>2.6</v>
+      </c>
+      <c r="BI216">
+        <v>1.81</v>
+      </c>
+      <c r="BJ216">
+        <v>1.91</v>
+      </c>
+      <c r="BK216">
+        <v>2.4</v>
+      </c>
+      <c r="BL216">
+        <v>1.52</v>
+      </c>
+      <c r="BM216">
+        <v>0</v>
+      </c>
+      <c r="BN216">
+        <v>0</v>
+      </c>
+      <c r="BO216">
+        <v>0</v>
+      </c>
+      <c r="BP216">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -45592,31 +45592,31 @@
         <v>2.13</v>
       </c>
       <c r="AU215">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV215">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW215">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX215">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY215">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ215">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA215">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB215">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC215">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD215">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="331">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1005,6 +1005,9 @@
   <si>
     <t>['9', '55', '73']</t>
   </si>
+  <si>
+    <t>['15', '53']</t>
+  </si>
 </sst>
 </file>
 
@@ -1365,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1702,7 +1705,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ2">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -4377,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15">
         <v>0.79</v>
@@ -5616,7 +5619,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ21">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6231,7 +6234,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -7264,7 +7267,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
         <v>0.53</v>
@@ -9530,7 +9533,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR40">
         <v>1.91</v>
@@ -10145,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ43">
         <v>1.38</v>
@@ -12414,7 +12417,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR54">
         <v>1.46</v>
@@ -13235,7 +13238,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ58">
         <v>2.08</v>
@@ -15710,7 +15713,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ70">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR70">
         <v>2.49</v>
@@ -15913,7 +15916,7 @@
         <v>0.8</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ71">
         <v>0.85</v>
@@ -19827,7 +19830,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20036,7 +20039,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -23950,7 +23953,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ110">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR110">
         <v>1.53</v>
@@ -25595,7 +25598,7 @@
         <v>3</v>
       </c>
       <c r="AP118">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ118">
         <v>3</v>
@@ -26419,7 +26422,7 @@
         <v>2.14</v>
       </c>
       <c r="AP122">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ122">
         <v>1.43</v>
@@ -27658,7 +27661,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ128">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR128">
         <v>1.28</v>
@@ -30127,7 +30130,7 @@
         <v>0.88</v>
       </c>
       <c r="AP140">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -33014,7 +33017,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -34247,7 +34250,7 @@
         <v>1.38</v>
       </c>
       <c r="AP160">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ160">
         <v>1.29</v>
@@ -37337,7 +37340,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37752,7 +37755,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ177">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR177">
         <v>1.08</v>
@@ -42693,7 +42696,7 @@
         <v>0.75</v>
       </c>
       <c r="AP201">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ201">
         <v>0.6899999999999999</v>
@@ -43932,7 +43935,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ207">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR207">
         <v>1.13</v>
@@ -45862,6 +45865,212 @@
       </c>
       <c r="BP216">
         <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7453869</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45728.41666666666</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>82</v>
+      </c>
+      <c r="H217" t="s">
+        <v>79</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="K217">
+        <v>2</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>3</v>
+      </c>
+      <c r="O217" t="s">
+        <v>189</v>
+      </c>
+      <c r="P217" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q217">
+        <v>3</v>
+      </c>
+      <c r="R217">
+        <v>2.05</v>
+      </c>
+      <c r="S217">
+        <v>3.4</v>
+      </c>
+      <c r="T217">
+        <v>1.44</v>
+      </c>
+      <c r="U217">
+        <v>2.63</v>
+      </c>
+      <c r="V217">
+        <v>3</v>
+      </c>
+      <c r="W217">
+        <v>1.36</v>
+      </c>
+      <c r="X217">
+        <v>7</v>
+      </c>
+      <c r="Y217">
+        <v>1.08</v>
+      </c>
+      <c r="Z217">
+        <v>2.26</v>
+      </c>
+      <c r="AA217">
+        <v>3.15</v>
+      </c>
+      <c r="AB217">
+        <v>3.23</v>
+      </c>
+      <c r="AC217">
+        <v>1.05</v>
+      </c>
+      <c r="AD217">
+        <v>8.5</v>
+      </c>
+      <c r="AE217">
+        <v>1.31</v>
+      </c>
+      <c r="AF217">
+        <v>3.25</v>
+      </c>
+      <c r="AG217">
+        <v>1.94</v>
+      </c>
+      <c r="AH217">
+        <v>1.8</v>
+      </c>
+      <c r="AI217">
+        <v>1.8</v>
+      </c>
+      <c r="AJ217">
+        <v>1.91</v>
+      </c>
+      <c r="AK217">
+        <v>1.39</v>
+      </c>
+      <c r="AL217">
+        <v>1.29</v>
+      </c>
+      <c r="AM217">
+        <v>1.52</v>
+      </c>
+      <c r="AN217">
+        <v>1.33</v>
+      </c>
+      <c r="AO217">
+        <v>1.25</v>
+      </c>
+      <c r="AP217">
+        <v>1.23</v>
+      </c>
+      <c r="AQ217">
+        <v>1.38</v>
+      </c>
+      <c r="AR217">
+        <v>1.61</v>
+      </c>
+      <c r="AS217">
+        <v>1.21</v>
+      </c>
+      <c r="AT217">
+        <v>2.82</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>13</v>
+      </c>
+      <c r="AX217">
+        <v>4</v>
+      </c>
+      <c r="AY217">
+        <v>23</v>
+      </c>
+      <c r="AZ217">
+        <v>8</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>4</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>1.85</v>
+      </c>
+      <c r="BE217">
+        <v>7.5</v>
+      </c>
+      <c r="BF217">
+        <v>2.33</v>
+      </c>
+      <c r="BG217">
+        <v>1.43</v>
+      </c>
+      <c r="BH217">
+        <v>2.63</v>
+      </c>
+      <c r="BI217">
+        <v>1.74</v>
+      </c>
+      <c r="BJ217">
+        <v>2.02</v>
+      </c>
+      <c r="BK217">
+        <v>2.22</v>
+      </c>
+      <c r="BL217">
+        <v>1.62</v>
+      </c>
+      <c r="BM217">
+        <v>2.85</v>
+      </c>
+      <c r="BN217">
+        <v>1.37</v>
+      </c>
+      <c r="BO217">
+        <v>3.9</v>
+      </c>
+      <c r="BP217">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="332">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,9 @@
     <t>['73']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -731,9 +734,6 @@
   </si>
   <si>
     <t>['4', '55']</t>
-  </si>
-  <si>
-    <t>['51']</t>
   </si>
   <si>
     <t>['36', '45', '90+6']</t>
@@ -1007,6 +1007,9 @@
   </si>
   <si>
     <t>['15', '53']</t>
+  </si>
+  <si>
+    <t>['60', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1624,7 +1627,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2242,7 +2245,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2654,7 +2657,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2860,7 +2863,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2938,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.77</v>
@@ -3147,7 +3150,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ9">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3272,7 +3275,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3478,7 +3481,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3684,7 +3687,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4589,7 +4592,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ16">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.02</v>
@@ -5126,7 +5129,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5204,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -6156,7 +6159,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6774,7 +6777,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6980,7 +6983,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="Q28">
         <v>1.44</v>
@@ -8500,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>0.29</v>
@@ -8915,7 +8918,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ37">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.6</v>
@@ -9736,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -9945,7 +9948,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ42">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>0.6</v>
@@ -12211,7 +12214,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ53">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -13444,7 +13447,7 @@
         <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>1.29</v>
@@ -15919,7 +15922,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ71">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -16740,7 +16743,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -20036,7 +20039,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ91">
         <v>1.38</v>
@@ -20451,7 +20454,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ93">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -22508,7 +22511,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ103">
         <v>0.6899999999999999</v>
@@ -22717,7 +22720,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ104">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.79</v>
@@ -27452,7 +27455,7 @@
         <v>2.13</v>
       </c>
       <c r="AP127">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>1.71</v>
@@ -27580,7 +27583,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27867,7 +27870,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ129">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.62</v>
@@ -30954,7 +30957,7 @@
         <v>2.11</v>
       </c>
       <c r="AP144">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
         <v>1.43</v>
@@ -32399,7 +32402,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ151">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR151">
         <v>1.68</v>
@@ -36310,7 +36313,7 @@
         <v>1.1</v>
       </c>
       <c r="AP170">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
         <v>1.21</v>
@@ -37549,7 +37552,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -39812,7 +39815,7 @@
         <v>1.27</v>
       </c>
       <c r="AP187">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ187">
         <v>1.38</v>
@@ -40021,7 +40024,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ188">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.79</v>
@@ -40764,7 +40767,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="Q192">
         <v>3.6</v>
@@ -42902,7 +42905,7 @@
         <v>2</v>
       </c>
       <c r="AP202">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ202">
         <v>2.08</v>
@@ -43111,7 +43114,7 @@
         <v>2.69</v>
       </c>
       <c r="AQ203">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR203">
         <v>2.16</v>
@@ -46071,6 +46074,212 @@
       </c>
       <c r="BP217">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7453899</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45731.41666666666</v>
+      </c>
+      <c r="F218">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s">
+        <v>84</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>2</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>229</v>
+      </c>
+      <c r="P218" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q218">
+        <v>6</v>
+      </c>
+      <c r="R218">
+        <v>2.1</v>
+      </c>
+      <c r="S218">
+        <v>2.1</v>
+      </c>
+      <c r="T218">
+        <v>1.44</v>
+      </c>
+      <c r="U218">
+        <v>2.63</v>
+      </c>
+      <c r="V218">
+        <v>3</v>
+      </c>
+      <c r="W218">
+        <v>1.36</v>
+      </c>
+      <c r="X218">
+        <v>7.5</v>
+      </c>
+      <c r="Y218">
+        <v>1.07</v>
+      </c>
+      <c r="Z218">
+        <v>7.5</v>
+      </c>
+      <c r="AA218">
+        <v>4</v>
+      </c>
+      <c r="AB218">
+        <v>1.48</v>
+      </c>
+      <c r="AC218">
+        <v>1.05</v>
+      </c>
+      <c r="AD218">
+        <v>8.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.33</v>
+      </c>
+      <c r="AF218">
+        <v>3.1</v>
+      </c>
+      <c r="AG218">
+        <v>2.08</v>
+      </c>
+      <c r="AH218">
+        <v>1.73</v>
+      </c>
+      <c r="AI218">
+        <v>2.25</v>
+      </c>
+      <c r="AJ218">
+        <v>1.57</v>
+      </c>
+      <c r="AK218">
+        <v>2.3</v>
+      </c>
+      <c r="AL218">
+        <v>1.2</v>
+      </c>
+      <c r="AM218">
+        <v>1.13</v>
+      </c>
+      <c r="AN218">
+        <v>1.08</v>
+      </c>
+      <c r="AO218">
+        <v>0.85</v>
+      </c>
+      <c r="AP218">
+        <v>1</v>
+      </c>
+      <c r="AQ218">
+        <v>1</v>
+      </c>
+      <c r="AR218">
+        <v>1.23</v>
+      </c>
+      <c r="AS218">
+        <v>1.43</v>
+      </c>
+      <c r="AT218">
+        <v>2.66</v>
+      </c>
+      <c r="AU218">
+        <v>3</v>
+      </c>
+      <c r="AV218">
+        <v>5</v>
+      </c>
+      <c r="AW218">
+        <v>0</v>
+      </c>
+      <c r="AX218">
+        <v>16</v>
+      </c>
+      <c r="AY218">
+        <v>3</v>
+      </c>
+      <c r="AZ218">
+        <v>21</v>
+      </c>
+      <c r="BA218">
+        <v>0</v>
+      </c>
+      <c r="BB218">
+        <v>15</v>
+      </c>
+      <c r="BC218">
+        <v>15</v>
+      </c>
+      <c r="BD218">
+        <v>2.05</v>
+      </c>
+      <c r="BE218">
+        <v>6.1</v>
+      </c>
+      <c r="BF218">
+        <v>2.24</v>
+      </c>
+      <c r="BG218">
+        <v>1.49</v>
+      </c>
+      <c r="BH218">
+        <v>2.43</v>
+      </c>
+      <c r="BI218">
+        <v>1.86</v>
+      </c>
+      <c r="BJ218">
+        <v>1.88</v>
+      </c>
+      <c r="BK218">
+        <v>2.4</v>
+      </c>
+      <c r="BL218">
+        <v>1.53</v>
+      </c>
+      <c r="BM218">
+        <v>3.2</v>
+      </c>
+      <c r="BN218">
+        <v>1.3</v>
+      </c>
+      <c r="BO218">
+        <v>4.35</v>
+      </c>
+      <c r="BP218">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,15 @@
     <t>['51']</t>
   </si>
   <si>
+    <t>['20', '36', '56', '60']</t>
+  </si>
+  <si>
+    <t>['60', '90+17']</t>
+  </si>
+  <si>
+    <t>['4', '34', '48']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1371,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1636,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2117,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ4">
         <v>0.29</v>
@@ -2245,7 +2254,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2657,7 +2666,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2738,7 +2747,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2863,7 +2872,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2944,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="AQ8">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3147,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3275,7 +3284,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3481,7 +3490,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3562,7 +3571,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3687,7 +3696,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3765,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ12">
         <v>1.43</v>
@@ -4383,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15">
         <v>0.79</v>
@@ -5129,7 +5138,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5413,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -5828,7 +5837,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ22">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6159,7 +6168,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6237,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -6446,7 +6455,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR25">
         <v>1.68</v>
@@ -6777,7 +6786,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7061,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ28">
         <v>1.07</v>
@@ -7601,7 +7610,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7807,7 +7816,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8091,7 +8100,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ33">
         <v>1.71</v>
@@ -8219,7 +8228,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8712,7 +8721,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR36">
         <v>1.22</v>
@@ -9043,7 +9052,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9124,7 +9133,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ38">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR38">
         <v>1.63</v>
@@ -9661,7 +9670,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9867,7 +9876,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10073,7 +10082,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10151,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ43">
         <v>1.38</v>
@@ -10279,7 +10288,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10360,7 +10369,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR44">
         <v>1.19</v>
@@ -10485,7 +10494,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11103,7 +11112,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11390,7 +11399,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR49">
         <v>1.36</v>
@@ -11515,7 +11524,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11593,7 +11602,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ50">
         <v>1.43</v>
@@ -11721,7 +11730,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12008,7 +12017,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ52">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR52">
         <v>1.32</v>
@@ -12829,10 +12838,10 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR56">
         <v>2.35</v>
@@ -12957,7 +12966,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13163,7 +13172,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13241,7 +13250,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ58">
         <v>2.08</v>
@@ -13369,7 +13378,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13575,7 +13584,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13781,7 +13790,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14193,7 +14202,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14271,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ63">
         <v>1.07</v>
@@ -14399,7 +14408,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14605,7 +14614,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14686,7 +14695,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ65">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR65">
         <v>1.31</v>
@@ -14811,7 +14820,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14892,7 +14901,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15429,7 +15438,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15713,7 +15722,7 @@
         <v>1.2</v>
       </c>
       <c r="AP70">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ70">
         <v>1.38</v>
@@ -15841,7 +15850,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15919,7 +15928,7 @@
         <v>0.8</v>
       </c>
       <c r="AP71">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -16047,7 +16056,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16459,7 +16468,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16746,7 +16755,7 @@
         <v>1</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR75">
         <v>1.22</v>
@@ -16871,7 +16880,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17158,7 +17167,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR77">
         <v>0.96</v>
@@ -17283,7 +17292,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17489,7 +17498,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17901,7 +17910,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18107,7 +18116,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18313,7 +18322,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18519,7 +18528,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18725,7 +18734,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18806,7 +18815,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ85">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR85">
         <v>1.12</v>
@@ -19009,7 +19018,7 @@
         <v>0.2</v>
       </c>
       <c r="AP86">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ86">
         <v>0.29</v>
@@ -19137,7 +19146,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19215,7 +19224,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ87">
         <v>0.6899999999999999</v>
@@ -19424,7 +19433,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR88">
         <v>1.41</v>
@@ -19549,7 +19558,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19627,7 +19636,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ89">
         <v>1.38</v>
@@ -19833,10 +19842,10 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19961,7 +19970,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20248,7 +20257,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ92">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20579,7 +20588,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21609,7 +21618,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21815,7 +21824,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -22021,7 +22030,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22227,7 +22236,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22433,7 +22442,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22926,7 +22935,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR105">
         <v>1.53</v>
@@ -23129,10 +23138,10 @@
         <v>1.71</v>
       </c>
       <c r="AP106">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ106">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR106">
         <v>2.08</v>
@@ -23257,7 +23266,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23335,7 +23344,7 @@
         <v>2.17</v>
       </c>
       <c r="AP107">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
         <v>2.08</v>
@@ -23544,7 +23553,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR108">
         <v>0.6899999999999999</v>
@@ -23669,7 +23678,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24081,7 +24090,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24287,7 +24296,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25111,7 +25120,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25317,7 +25326,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25523,7 +25532,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25601,7 +25610,7 @@
         <v>3</v>
       </c>
       <c r="AP118">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ118">
         <v>3</v>
@@ -25729,7 +25738,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25935,7 +25944,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26425,7 +26434,7 @@
         <v>2.14</v>
       </c>
       <c r="AP122">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ122">
         <v>1.43</v>
@@ -26634,7 +26643,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR123">
         <v>1.46</v>
@@ -26759,7 +26768,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26965,7 +26974,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27046,7 +27055,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ125">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27171,7 +27180,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27252,7 +27261,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR126">
         <v>1.56</v>
@@ -27583,7 +27592,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27789,7 +27798,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28201,7 +28210,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28485,7 +28494,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ132">
         <v>0.6899999999999999</v>
@@ -28897,7 +28906,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ134">
         <v>1.29</v>
@@ -29103,7 +29112,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ135">
         <v>0.79</v>
@@ -29231,7 +29240,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29849,7 +29858,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30133,7 +30142,7 @@
         <v>0.88</v>
       </c>
       <c r="AP140">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30261,7 +30270,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30342,7 +30351,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR141">
         <v>1.19</v>
@@ -30467,7 +30476,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30673,7 +30682,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31291,7 +31300,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31497,7 +31506,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31703,7 +31712,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31909,7 +31918,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -31987,10 +31996,10 @@
         <v>1.67</v>
       </c>
       <c r="AP149">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR149">
         <v>2.02</v>
@@ -32196,7 +32205,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ150">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR150">
         <v>1.62</v>
@@ -32321,7 +32330,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32527,7 +32536,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32733,7 +32742,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33145,7 +33154,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33763,7 +33772,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33841,7 +33850,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ158">
         <v>1.21</v>
@@ -33969,7 +33978,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34050,7 +34059,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159">
         <v>1.07</v>
@@ -34175,7 +34184,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34253,7 +34262,7 @@
         <v>1.38</v>
       </c>
       <c r="AP160">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
         <v>1.29</v>
@@ -34381,7 +34390,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34668,7 +34677,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ162">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR162">
         <v>1.35</v>
@@ -34999,7 +35008,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35205,7 +35214,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35286,7 +35295,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR165">
         <v>1.65</v>
@@ -35617,7 +35626,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35695,7 +35704,7 @@
         <v>3</v>
       </c>
       <c r="AP167">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ167">
         <v>3</v>
@@ -36235,7 +36244,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36725,7 +36734,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ172">
         <v>1.38</v>
@@ -37059,7 +37068,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37265,7 +37274,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37343,10 +37352,10 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR175">
         <v>1.51</v>
@@ -37883,7 +37892,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -37964,7 +37973,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38295,7 +38304,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38707,7 +38716,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38913,7 +38922,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -38991,7 +39000,7 @@
         <v>0.64</v>
       </c>
       <c r="AP183">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183">
         <v>0.79</v>
@@ -39119,7 +39128,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39406,7 +39415,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ185">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39531,7 +39540,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39737,7 +39746,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39943,7 +39952,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40149,7 +40158,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40227,7 +40236,7 @@
         <v>2.09</v>
       </c>
       <c r="AP189">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ189">
         <v>2.08</v>
@@ -40436,7 +40445,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -41179,7 +41188,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41591,7 +41600,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41672,7 +41681,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR196">
         <v>1.72</v>
@@ -41797,7 +41806,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42493,7 +42502,7 @@
         <v>1.42</v>
       </c>
       <c r="AP200">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200">
         <v>1.21</v>
@@ -42699,7 +42708,7 @@
         <v>0.75</v>
       </c>
       <c r="AP201">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ201">
         <v>0.6899999999999999</v>
@@ -42827,7 +42836,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43111,7 +43120,7 @@
         <v>0.92</v>
       </c>
       <c r="AP203">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -43239,7 +43248,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43320,7 +43329,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR204">
         <v>1.77</v>
@@ -43445,7 +43454,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43732,7 +43741,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR206">
         <v>1.7</v>
@@ -43857,7 +43866,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44887,7 +44896,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45093,7 +45102,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45299,7 +45308,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45917,7 +45926,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -45995,7 +46004,7 @@
         <v>1.25</v>
       </c>
       <c r="AP217">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ217">
         <v>1.38</v>
@@ -46123,7 +46132,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q218">
         <v>6</v>
@@ -46280,6 +46289,624 @@
       </c>
       <c r="BP218">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7453896</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45732.375</v>
+      </c>
+      <c r="F219">
+        <v>28</v>
+      </c>
+      <c r="G219" t="s">
+        <v>77</v>
+      </c>
+      <c r="H219" t="s">
+        <v>71</v>
+      </c>
+      <c r="I219">
+        <v>2</v>
+      </c>
+      <c r="J219">
+        <v>2</v>
+      </c>
+      <c r="K219">
+        <v>4</v>
+      </c>
+      <c r="L219">
+        <v>4</v>
+      </c>
+      <c r="M219">
+        <v>2</v>
+      </c>
+      <c r="N219">
+        <v>6</v>
+      </c>
+      <c r="O219" t="s">
+        <v>230</v>
+      </c>
+      <c r="P219" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q219">
+        <v>2.1</v>
+      </c>
+      <c r="R219">
+        <v>2.25</v>
+      </c>
+      <c r="S219">
+        <v>5.5</v>
+      </c>
+      <c r="T219">
+        <v>1.36</v>
+      </c>
+      <c r="U219">
+        <v>3</v>
+      </c>
+      <c r="V219">
+        <v>2.63</v>
+      </c>
+      <c r="W219">
+        <v>1.44</v>
+      </c>
+      <c r="X219">
+        <v>6.5</v>
+      </c>
+      <c r="Y219">
+        <v>1.1</v>
+      </c>
+      <c r="Z219">
+        <v>1.57</v>
+      </c>
+      <c r="AA219">
+        <v>4.2</v>
+      </c>
+      <c r="AB219">
+        <v>5.1</v>
+      </c>
+      <c r="AC219">
+        <v>1.04</v>
+      </c>
+      <c r="AD219">
+        <v>9</v>
+      </c>
+      <c r="AE219">
+        <v>1.25</v>
+      </c>
+      <c r="AF219">
+        <v>3.8</v>
+      </c>
+      <c r="AG219">
+        <v>1.7</v>
+      </c>
+      <c r="AH219">
+        <v>1.95</v>
+      </c>
+      <c r="AI219">
+        <v>1.83</v>
+      </c>
+      <c r="AJ219">
+        <v>1.83</v>
+      </c>
+      <c r="AK219">
+        <v>1.11</v>
+      </c>
+      <c r="AL219">
+        <v>1.18</v>
+      </c>
+      <c r="AM219">
+        <v>2.38</v>
+      </c>
+      <c r="AN219">
+        <v>1.23</v>
+      </c>
+      <c r="AO219">
+        <v>1</v>
+      </c>
+      <c r="AP219">
+        <v>1.36</v>
+      </c>
+      <c r="AQ219">
+        <v>0.93</v>
+      </c>
+      <c r="AR219">
+        <v>1.95</v>
+      </c>
+      <c r="AS219">
+        <v>1.14</v>
+      </c>
+      <c r="AT219">
+        <v>3.09</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>5</v>
+      </c>
+      <c r="AW219">
+        <v>2</v>
+      </c>
+      <c r="AX219">
+        <v>8</v>
+      </c>
+      <c r="AY219">
+        <v>7</v>
+      </c>
+      <c r="AZ219">
+        <v>13</v>
+      </c>
+      <c r="BA219">
+        <v>4</v>
+      </c>
+      <c r="BB219">
+        <v>4</v>
+      </c>
+      <c r="BC219">
+        <v>8</v>
+      </c>
+      <c r="BD219">
+        <v>1.21</v>
+      </c>
+      <c r="BE219">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF219">
+        <v>6.68</v>
+      </c>
+      <c r="BG219">
+        <v>1.42</v>
+      </c>
+      <c r="BH219">
+        <v>2.65</v>
+      </c>
+      <c r="BI219">
+        <v>1.74</v>
+      </c>
+      <c r="BJ219">
+        <v>2.03</v>
+      </c>
+      <c r="BK219">
+        <v>2.2</v>
+      </c>
+      <c r="BL219">
+        <v>1.62</v>
+      </c>
+      <c r="BM219">
+        <v>2.83</v>
+      </c>
+      <c r="BN219">
+        <v>1.37</v>
+      </c>
+      <c r="BO219">
+        <v>3.88</v>
+      </c>
+      <c r="BP219">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7453901</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45732.5</v>
+      </c>
+      <c r="F220">
+        <v>28</v>
+      </c>
+      <c r="G220" t="s">
+        <v>72</v>
+      </c>
+      <c r="H220" t="s">
+        <v>81</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>3</v>
+      </c>
+      <c r="O220" t="s">
+        <v>231</v>
+      </c>
+      <c r="P220" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q220">
+        <v>1.36</v>
+      </c>
+      <c r="R220">
+        <v>3.25</v>
+      </c>
+      <c r="S220">
+        <v>13</v>
+      </c>
+      <c r="T220">
+        <v>1.2</v>
+      </c>
+      <c r="U220">
+        <v>4.33</v>
+      </c>
+      <c r="V220">
+        <v>1.83</v>
+      </c>
+      <c r="W220">
+        <v>1.83</v>
+      </c>
+      <c r="X220">
+        <v>3.75</v>
+      </c>
+      <c r="Y220">
+        <v>1.25</v>
+      </c>
+      <c r="Z220">
+        <v>1.07</v>
+      </c>
+      <c r="AA220">
+        <v>12</v>
+      </c>
+      <c r="AB220">
+        <v>19</v>
+      </c>
+      <c r="AC220">
+        <v>1.01</v>
+      </c>
+      <c r="AD220">
+        <v>26</v>
+      </c>
+      <c r="AE220">
+        <v>1.08</v>
+      </c>
+      <c r="AF220">
+        <v>7</v>
+      </c>
+      <c r="AG220">
+        <v>1.3</v>
+      </c>
+      <c r="AH220">
+        <v>3.21</v>
+      </c>
+      <c r="AI220">
+        <v>2.38</v>
+      </c>
+      <c r="AJ220">
+        <v>1.53</v>
+      </c>
+      <c r="AK220">
+        <v>1.01</v>
+      </c>
+      <c r="AL220">
+        <v>1.01</v>
+      </c>
+      <c r="AM220">
+        <v>7</v>
+      </c>
+      <c r="AN220">
+        <v>2.69</v>
+      </c>
+      <c r="AO220">
+        <v>1</v>
+      </c>
+      <c r="AP220">
+        <v>2.71</v>
+      </c>
+      <c r="AQ220">
+        <v>0.93</v>
+      </c>
+      <c r="AR220">
+        <v>2.2</v>
+      </c>
+      <c r="AS220">
+        <v>1.37</v>
+      </c>
+      <c r="AT220">
+        <v>3.57</v>
+      </c>
+      <c r="AU220">
+        <v>6</v>
+      </c>
+      <c r="AV220">
+        <v>5</v>
+      </c>
+      <c r="AW220">
+        <v>13</v>
+      </c>
+      <c r="AX220">
+        <v>2</v>
+      </c>
+      <c r="AY220">
+        <v>23</v>
+      </c>
+      <c r="AZ220">
+        <v>8</v>
+      </c>
+      <c r="BA220">
+        <v>11</v>
+      </c>
+      <c r="BB220">
+        <v>1</v>
+      </c>
+      <c r="BC220">
+        <v>12</v>
+      </c>
+      <c r="BD220">
+        <v>1.13</v>
+      </c>
+      <c r="BE220">
+        <v>11</v>
+      </c>
+      <c r="BF220">
+        <v>8.1</v>
+      </c>
+      <c r="BG220">
+        <v>1.25</v>
+      </c>
+      <c r="BH220">
+        <v>3.42</v>
+      </c>
+      <c r="BI220">
+        <v>1.48</v>
+      </c>
+      <c r="BJ220">
+        <v>2.48</v>
+      </c>
+      <c r="BK220">
+        <v>1.8</v>
+      </c>
+      <c r="BL220">
+        <v>1.94</v>
+      </c>
+      <c r="BM220">
+        <v>2.28</v>
+      </c>
+      <c r="BN220">
+        <v>1.59</v>
+      </c>
+      <c r="BO220">
+        <v>2.9</v>
+      </c>
+      <c r="BP220">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7453902</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>82</v>
+      </c>
+      <c r="H221" t="s">
+        <v>85</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>3</v>
+      </c>
+      <c r="L221">
+        <v>3</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>4</v>
+      </c>
+      <c r="O221" t="s">
+        <v>232</v>
+      </c>
+      <c r="P221" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q221">
+        <v>4.5</v>
+      </c>
+      <c r="R221">
+        <v>2.05</v>
+      </c>
+      <c r="S221">
+        <v>2.4</v>
+      </c>
+      <c r="T221">
+        <v>1.44</v>
+      </c>
+      <c r="U221">
+        <v>2.63</v>
+      </c>
+      <c r="V221">
+        <v>3.25</v>
+      </c>
+      <c r="W221">
+        <v>1.33</v>
+      </c>
+      <c r="X221">
+        <v>7.5</v>
+      </c>
+      <c r="Y221">
+        <v>1.07</v>
+      </c>
+      <c r="Z221">
+        <v>3.91</v>
+      </c>
+      <c r="AA221">
+        <v>3.59</v>
+      </c>
+      <c r="AB221">
+        <v>1.87</v>
+      </c>
+      <c r="AC221">
+        <v>1.06</v>
+      </c>
+      <c r="AD221">
+        <v>8</v>
+      </c>
+      <c r="AE221">
+        <v>1.35</v>
+      </c>
+      <c r="AF221">
+        <v>3</v>
+      </c>
+      <c r="AG221">
+        <v>2</v>
+      </c>
+      <c r="AH221">
+        <v>1.75</v>
+      </c>
+      <c r="AI221">
+        <v>1.91</v>
+      </c>
+      <c r="AJ221">
+        <v>1.8</v>
+      </c>
+      <c r="AK221">
+        <v>1.85</v>
+      </c>
+      <c r="AL221">
+        <v>1.25</v>
+      </c>
+      <c r="AM221">
+        <v>1.22</v>
+      </c>
+      <c r="AN221">
+        <v>1.23</v>
+      </c>
+      <c r="AO221">
+        <v>1.77</v>
+      </c>
+      <c r="AP221">
+        <v>1.36</v>
+      </c>
+      <c r="AQ221">
+        <v>1.64</v>
+      </c>
+      <c r="AR221">
+        <v>1.65</v>
+      </c>
+      <c r="AS221">
+        <v>1.75</v>
+      </c>
+      <c r="AT221">
+        <v>3.4</v>
+      </c>
+      <c r="AU221">
+        <v>6</v>
+      </c>
+      <c r="AV221">
+        <v>5</v>
+      </c>
+      <c r="AW221">
+        <v>1</v>
+      </c>
+      <c r="AX221">
+        <v>7</v>
+      </c>
+      <c r="AY221">
+        <v>7</v>
+      </c>
+      <c r="AZ221">
+        <v>12</v>
+      </c>
+      <c r="BA221">
+        <v>4</v>
+      </c>
+      <c r="BB221">
+        <v>8</v>
+      </c>
+      <c r="BC221">
+        <v>12</v>
+      </c>
+      <c r="BD221">
+        <v>2.24</v>
+      </c>
+      <c r="BE221">
+        <v>6.1</v>
+      </c>
+      <c r="BF221">
+        <v>2.05</v>
+      </c>
+      <c r="BG221">
+        <v>1.39</v>
+      </c>
+      <c r="BH221">
+        <v>2.75</v>
+      </c>
+      <c r="BI221">
+        <v>1.69</v>
+      </c>
+      <c r="BJ221">
+        <v>2.1</v>
+      </c>
+      <c r="BK221">
+        <v>2.13</v>
+      </c>
+      <c r="BL221">
+        <v>1.67</v>
+      </c>
+      <c r="BM221">
+        <v>2.72</v>
+      </c>
+      <c r="BN221">
+        <v>1.4</v>
+      </c>
+      <c r="BO221">
+        <v>3.68</v>
+      </c>
+      <c r="BP221">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1380,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1923,7 +1923,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>1.71</v>
@@ -2538,10 +2538,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>0.29</v>
@@ -5834,7 +5834,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22">
         <v>1.64</v>
@@ -6043,7 +6043,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR23">
         <v>1.76</v>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>0.79</v>
@@ -7485,7 +7485,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ30">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7894,7 +7894,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -9336,7 +9336,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1.21</v>
@@ -10575,7 +10575,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -10778,7 +10778,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ46">
         <v>0.79</v>
@@ -12632,7 +12632,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55">
         <v>1.38</v>
@@ -13253,7 +13253,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ58">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13665,7 +13665,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ60">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR60">
         <v>0.73</v>
@@ -14074,7 +14074,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ62">
         <v>0.29</v>
@@ -16134,7 +16134,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
         <v>1.29</v>
@@ -16549,7 +16549,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ74">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR74">
         <v>1.34</v>
@@ -16958,10 +16958,10 @@
         <v>1.75</v>
       </c>
       <c r="AP76">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -19227,7 +19227,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ87">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR87">
         <v>2.4</v>
@@ -19430,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
         <v>0.93</v>
@@ -20460,7 +20460,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20669,7 +20669,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ94">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR94">
         <v>1.84</v>
@@ -22523,7 +22523,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -23347,7 +23347,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ107">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR107">
         <v>1.95</v>
@@ -23550,7 +23550,7 @@
         <v>0.29</v>
       </c>
       <c r="AP108">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ108">
         <v>0.93</v>
@@ -23962,7 +23962,7 @@
         <v>1.29</v>
       </c>
       <c r="AP110">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ110">
         <v>1.38</v>
@@ -27258,7 +27258,7 @@
         <v>0.38</v>
       </c>
       <c r="AP126">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126">
         <v>0.93</v>
@@ -28288,7 +28288,7 @@
         <v>3</v>
       </c>
       <c r="AP131">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
         <v>3</v>
@@ -28497,7 +28497,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ132">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR132">
         <v>1.95</v>
@@ -28703,7 +28703,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ133">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -29939,7 +29939,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ139">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR139">
         <v>1.32</v>
@@ -30763,7 +30763,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ143">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR143">
         <v>1.05</v>
@@ -31381,7 +31381,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ146">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31584,7 +31584,7 @@
         <v>1.89</v>
       </c>
       <c r="AP147">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ147">
         <v>1.71</v>
@@ -32820,7 +32820,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
         <v>1.07</v>
@@ -33441,7 +33441,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ156">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR156">
         <v>1.72</v>
@@ -34880,7 +34880,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ163">
         <v>1.43</v>
@@ -35913,7 +35913,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36528,7 +36528,7 @@
         <v>1.5</v>
       </c>
       <c r="AP171">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ171">
         <v>1.29</v>
@@ -36943,7 +36943,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ173">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR173">
         <v>1.77</v>
@@ -39206,7 +39206,7 @@
         <v>1.27</v>
       </c>
       <c r="AP184">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ184">
         <v>1.07</v>
@@ -39621,7 +39621,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ186">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR186">
         <v>1.05</v>
@@ -40239,7 +40239,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ189">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR189">
         <v>2.16</v>
@@ -40442,7 +40442,7 @@
         <v>1.18</v>
       </c>
       <c r="AP190">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ190">
         <v>0.93</v>
@@ -42711,7 +42711,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ201">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR201">
         <v>1.57</v>
@@ -42917,7 +42917,7 @@
         <v>1</v>
       </c>
       <c r="AQ202">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR202">
         <v>1.22</v>
@@ -43944,7 +43944,7 @@
         <v>1.27</v>
       </c>
       <c r="AP207">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ207">
         <v>1.38</v>
@@ -44150,7 +44150,7 @@
         <v>1.42</v>
       </c>
       <c r="AP208">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ208">
         <v>1.38</v>
@@ -46907,6 +46907,418 @@
       </c>
       <c r="BP221">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7453897</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45732.58680555555</v>
+      </c>
+      <c r="F222">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>74</v>
+      </c>
+      <c r="H222" t="s">
+        <v>83</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>1</v>
+      </c>
+      <c r="O222" t="s">
+        <v>87</v>
+      </c>
+      <c r="P222" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q222">
+        <v>3.5</v>
+      </c>
+      <c r="R222">
+        <v>2.2</v>
+      </c>
+      <c r="S222">
+        <v>2.75</v>
+      </c>
+      <c r="T222">
+        <v>1.36</v>
+      </c>
+      <c r="U222">
+        <v>3</v>
+      </c>
+      <c r="V222">
+        <v>2.63</v>
+      </c>
+      <c r="W222">
+        <v>1.44</v>
+      </c>
+      <c r="X222">
+        <v>6.5</v>
+      </c>
+      <c r="Y222">
+        <v>1.1</v>
+      </c>
+      <c r="Z222">
+        <v>3.17</v>
+      </c>
+      <c r="AA222">
+        <v>3.41</v>
+      </c>
+      <c r="AB222">
+        <v>2.17</v>
+      </c>
+      <c r="AC222">
+        <v>1.05</v>
+      </c>
+      <c r="AD222">
+        <v>8.5</v>
+      </c>
+      <c r="AE222">
+        <v>1.25</v>
+      </c>
+      <c r="AF222">
+        <v>3.7</v>
+      </c>
+      <c r="AG222">
+        <v>1.77</v>
+      </c>
+      <c r="AH222">
+        <v>1.98</v>
+      </c>
+      <c r="AI222">
+        <v>1.62</v>
+      </c>
+      <c r="AJ222">
+        <v>2.2</v>
+      </c>
+      <c r="AK222">
+        <v>1.65</v>
+      </c>
+      <c r="AL222">
+        <v>1.25</v>
+      </c>
+      <c r="AM222">
+        <v>1.33</v>
+      </c>
+      <c r="AN222">
+        <v>1.46</v>
+      </c>
+      <c r="AO222">
+        <v>2.08</v>
+      </c>
+      <c r="AP222">
+        <v>1.36</v>
+      </c>
+      <c r="AQ222">
+        <v>2.14</v>
+      </c>
+      <c r="AR222">
+        <v>1.65</v>
+      </c>
+      <c r="AS222">
+        <v>1.31</v>
+      </c>
+      <c r="AT222">
+        <v>2.96</v>
+      </c>
+      <c r="AU222">
+        <v>4</v>
+      </c>
+      <c r="AV222">
+        <v>2</v>
+      </c>
+      <c r="AW222">
+        <v>9</v>
+      </c>
+      <c r="AX222">
+        <v>4</v>
+      </c>
+      <c r="AY222">
+        <v>13</v>
+      </c>
+      <c r="AZ222">
+        <v>6</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>1</v>
+      </c>
+      <c r="BC222">
+        <v>4</v>
+      </c>
+      <c r="BD222">
+        <v>2.05</v>
+      </c>
+      <c r="BE222">
+        <v>6.1</v>
+      </c>
+      <c r="BF222">
+        <v>2.24</v>
+      </c>
+      <c r="BG222">
+        <v>1.46</v>
+      </c>
+      <c r="BH222">
+        <v>2.53</v>
+      </c>
+      <c r="BI222">
+        <v>1.8</v>
+      </c>
+      <c r="BJ222">
+        <v>1.95</v>
+      </c>
+      <c r="BK222">
+        <v>2.3</v>
+      </c>
+      <c r="BL222">
+        <v>1.57</v>
+      </c>
+      <c r="BM222">
+        <v>2.98</v>
+      </c>
+      <c r="BN222">
+        <v>1.34</v>
+      </c>
+      <c r="BO222">
+        <v>4.1</v>
+      </c>
+      <c r="BP222">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7453900</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45732.66666666666</v>
+      </c>
+      <c r="F223">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>73</v>
+      </c>
+      <c r="H223" t="s">
+        <v>80</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>2</v>
+      </c>
+      <c r="O223" t="s">
+        <v>176</v>
+      </c>
+      <c r="P223" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q223">
+        <v>0</v>
+      </c>
+      <c r="R223">
+        <v>0</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>0</v>
+      </c>
+      <c r="U223">
+        <v>0</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
+      </c>
+      <c r="W223">
+        <v>0</v>
+      </c>
+      <c r="X223">
+        <v>0</v>
+      </c>
+      <c r="Y223">
+        <v>0</v>
+      </c>
+      <c r="Z223">
+        <v>2.79</v>
+      </c>
+      <c r="AA223">
+        <v>3.5</v>
+      </c>
+      <c r="AB223">
+        <v>2.35</v>
+      </c>
+      <c r="AC223">
+        <v>0</v>
+      </c>
+      <c r="AD223">
+        <v>0</v>
+      </c>
+      <c r="AE223">
+        <v>0</v>
+      </c>
+      <c r="AF223">
+        <v>0</v>
+      </c>
+      <c r="AG223">
+        <v>1.85</v>
+      </c>
+      <c r="AH223">
+        <v>1.89</v>
+      </c>
+      <c r="AI223">
+        <v>0</v>
+      </c>
+      <c r="AJ223">
+        <v>0</v>
+      </c>
+      <c r="AK223">
+        <v>0</v>
+      </c>
+      <c r="AL223">
+        <v>0</v>
+      </c>
+      <c r="AM223">
+        <v>0</v>
+      </c>
+      <c r="AN223">
+        <v>1.54</v>
+      </c>
+      <c r="AO223">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP223">
+        <v>1.5</v>
+      </c>
+      <c r="AQ223">
+        <v>0.71</v>
+      </c>
+      <c r="AR223">
+        <v>1.16</v>
+      </c>
+      <c r="AS223">
+        <v>1.41</v>
+      </c>
+      <c r="AT223">
+        <v>2.57</v>
+      </c>
+      <c r="AU223">
+        <v>-1</v>
+      </c>
+      <c r="AV223">
+        <v>-1</v>
+      </c>
+      <c r="AW223">
+        <v>-1</v>
+      </c>
+      <c r="AX223">
+        <v>-1</v>
+      </c>
+      <c r="AY223">
+        <v>-1</v>
+      </c>
+      <c r="AZ223">
+        <v>-1</v>
+      </c>
+      <c r="BA223">
+        <v>-1</v>
+      </c>
+      <c r="BB223">
+        <v>-1</v>
+      </c>
+      <c r="BC223">
+        <v>-1</v>
+      </c>
+      <c r="BD223">
+        <v>0</v>
+      </c>
+      <c r="BE223">
+        <v>0</v>
+      </c>
+      <c r="BF223">
+        <v>0</v>
+      </c>
+      <c r="BG223">
+        <v>0</v>
+      </c>
+      <c r="BH223">
+        <v>0</v>
+      </c>
+      <c r="BI223">
+        <v>0</v>
+      </c>
+      <c r="BJ223">
+        <v>0</v>
+      </c>
+      <c r="BK223">
+        <v>0</v>
+      </c>
+      <c r="BL223">
+        <v>0</v>
+      </c>
+      <c r="BM223">
+        <v>0</v>
+      </c>
+      <c r="BN223">
+        <v>0</v>
+      </c>
+      <c r="BO223">
+        <v>0</v>
+      </c>
+      <c r="BP223">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="337">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,9 @@
     <t>['4', '34', '48']</t>
   </si>
   <si>
+    <t>['39', '68', '88']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1019,6 +1022,9 @@
   </si>
   <si>
     <t>['60', '90+4']</t>
+  </si>
+  <si>
+    <t>['76']</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1636,7 +1642,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1717,7 +1723,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ2">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2254,7 +2260,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2666,7 +2672,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2744,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
         <v>0.93</v>
@@ -2872,7 +2878,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3284,7 +3290,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3490,7 +3496,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3696,7 +3702,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4804,7 +4810,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ17">
         <v>1.71</v>
@@ -5138,7 +5144,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5631,7 +5637,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6168,7 +6174,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6786,7 +6792,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7279,7 +7285,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR29">
         <v>0.53</v>
@@ -7610,7 +7616,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7816,7 +7822,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8228,7 +8234,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8306,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ34">
         <v>1.43</v>
@@ -9052,7 +9058,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9545,7 +9551,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
         <v>1.91</v>
@@ -9670,7 +9676,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9876,7 +9882,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10082,7 +10088,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10288,7 +10294,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10494,7 +10500,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10984,7 +10990,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ47">
         <v>0.29</v>
@@ -11112,7 +11118,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11524,7 +11530,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11730,7 +11736,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12429,7 +12435,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR54">
         <v>1.46</v>
@@ -12966,7 +12972,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13044,7 +13050,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ57">
         <v>1.21</v>
@@ -13172,7 +13178,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13378,7 +13384,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13584,7 +13590,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13790,7 +13796,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14202,7 +14208,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14408,7 +14414,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14614,7 +14620,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14820,7 +14826,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15438,7 +15444,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15725,7 +15731,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ70">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR70">
         <v>2.49</v>
@@ -15850,7 +15856,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16056,7 +16062,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16340,7 +16346,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ73">
         <v>1.38</v>
@@ -16468,7 +16474,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16880,7 +16886,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17292,7 +17298,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17498,7 +17504,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17910,7 +17916,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18116,7 +18122,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18322,7 +18328,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18528,7 +18534,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18734,7 +18740,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19146,7 +19152,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19558,7 +19564,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19970,7 +19976,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20051,7 +20057,7 @@
         <v>1</v>
       </c>
       <c r="AQ91">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20588,7 +20594,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20666,7 +20672,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ94">
         <v>2.14</v>
@@ -21618,7 +21624,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21824,7 +21830,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -22030,7 +22036,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22236,7 +22242,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22442,7 +22448,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22726,7 +22732,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -23266,7 +23272,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23678,7 +23684,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23965,7 +23971,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
         <v>1.53</v>
@@ -24090,7 +24096,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24296,7 +24302,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25120,7 +25126,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25326,7 +25332,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25532,7 +25538,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25738,7 +25744,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25944,7 +25950,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26768,7 +26774,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26974,7 +26980,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27052,7 +27058,7 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ125">
         <v>1.64</v>
@@ -27180,7 +27186,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27592,7 +27598,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27673,7 +27679,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ128">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR128">
         <v>1.28</v>
@@ -27798,7 +27804,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28210,7 +28216,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -29240,7 +29246,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29858,7 +29864,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30270,7 +30276,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30476,7 +30482,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30682,7 +30688,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31300,7 +31306,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31506,7 +31512,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31712,7 +31718,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31790,7 +31796,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ148">
         <v>3</v>
@@ -31918,7 +31924,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32330,7 +32336,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32536,7 +32542,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32742,7 +32748,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33029,7 +33035,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33154,7 +33160,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33772,7 +33778,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33978,7 +33984,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34184,7 +34190,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34390,7 +34396,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -35008,7 +35014,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35086,7 +35092,7 @@
         <v>0.4</v>
       </c>
       <c r="AP164">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ164">
         <v>0.79</v>
@@ -35214,7 +35220,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35626,7 +35632,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36244,7 +36250,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -37068,7 +37074,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37274,7 +37280,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37767,7 +37773,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ177">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR177">
         <v>1.08</v>
@@ -37892,7 +37898,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38304,7 +38310,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38716,7 +38722,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38922,7 +38928,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39128,7 +39134,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39540,7 +39546,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39746,7 +39752,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39952,7 +39958,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40158,7 +40164,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40854,7 +40860,7 @@
         <v>1.36</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ192">
         <v>1.29</v>
@@ -41188,7 +41194,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41600,7 +41606,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41806,7 +41812,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42836,7 +42842,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43248,7 +43254,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43454,7 +43460,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43738,7 +43744,7 @@
         <v>1.08</v>
       </c>
       <c r="AP206">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ206">
         <v>0.93</v>
@@ -43866,7 +43872,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -43947,7 +43953,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR207">
         <v>1.13</v>
@@ -44896,7 +44902,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45102,7 +45108,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45308,7 +45314,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45926,7 +45932,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46007,7 +46013,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ217">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46132,7 +46138,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q218">
         <v>6</v>
@@ -46338,7 +46344,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q219">
         <v>2.1</v>
@@ -46750,7 +46756,7 @@
         <v>232</v>
       </c>
       <c r="P221" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q221">
         <v>4.5</v>
@@ -46956,7 +46962,7 @@
         <v>87</v>
       </c>
       <c r="P222" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q222">
         <v>3.5</v>
@@ -47255,31 +47261,31 @@
         <v>2.57</v>
       </c>
       <c r="AU223">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV223">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW223">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AX223">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AY223">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AZ223">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BA223">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB223">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC223">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD223">
         <v>0</v>
@@ -47319,6 +47325,212 @@
       </c>
       <c r="BP223">
         <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7453898</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45733.625</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>75</v>
+      </c>
+      <c r="H224" t="s">
+        <v>79</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>3</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>4</v>
+      </c>
+      <c r="O224" t="s">
+        <v>233</v>
+      </c>
+      <c r="P224" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q224">
+        <v>2.6</v>
+      </c>
+      <c r="R224">
+        <v>2.05</v>
+      </c>
+      <c r="S224">
+        <v>4.33</v>
+      </c>
+      <c r="T224">
+        <v>1.44</v>
+      </c>
+      <c r="U224">
+        <v>2.63</v>
+      </c>
+      <c r="V224">
+        <v>3.25</v>
+      </c>
+      <c r="W224">
+        <v>1.33</v>
+      </c>
+      <c r="X224">
+        <v>7.5</v>
+      </c>
+      <c r="Y224">
+        <v>1.07</v>
+      </c>
+      <c r="Z224">
+        <v>1.97</v>
+      </c>
+      <c r="AA224">
+        <v>3.5</v>
+      </c>
+      <c r="AB224">
+        <v>3.62</v>
+      </c>
+      <c r="AC224">
+        <v>1.06</v>
+      </c>
+      <c r="AD224">
+        <v>8</v>
+      </c>
+      <c r="AE224">
+        <v>1.36</v>
+      </c>
+      <c r="AF224">
+        <v>2.95</v>
+      </c>
+      <c r="AG224">
+        <v>1.91</v>
+      </c>
+      <c r="AH224">
+        <v>1.83</v>
+      </c>
+      <c r="AI224">
+        <v>1.83</v>
+      </c>
+      <c r="AJ224">
+        <v>1.83</v>
+      </c>
+      <c r="AK224">
+        <v>1.28</v>
+      </c>
+      <c r="AL224">
+        <v>1.25</v>
+      </c>
+      <c r="AM224">
+        <v>1.73</v>
+      </c>
+      <c r="AN224">
+        <v>1.54</v>
+      </c>
+      <c r="AO224">
+        <v>1.38</v>
+      </c>
+      <c r="AP224">
+        <v>1.64</v>
+      </c>
+      <c r="AQ224">
+        <v>1.29</v>
+      </c>
+      <c r="AR224">
+        <v>1.67</v>
+      </c>
+      <c r="AS224">
+        <v>1.19</v>
+      </c>
+      <c r="AT224">
+        <v>2.86</v>
+      </c>
+      <c r="AU224">
+        <v>10</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>12</v>
+      </c>
+      <c r="AX224">
+        <v>5</v>
+      </c>
+      <c r="AY224">
+        <v>26</v>
+      </c>
+      <c r="AZ224">
+        <v>10</v>
+      </c>
+      <c r="BA224">
+        <v>9</v>
+      </c>
+      <c r="BB224">
+        <v>4</v>
+      </c>
+      <c r="BC224">
+        <v>13</v>
+      </c>
+      <c r="BD224">
+        <v>1.59</v>
+      </c>
+      <c r="BE224">
+        <v>6.4</v>
+      </c>
+      <c r="BF224">
+        <v>3.12</v>
+      </c>
+      <c r="BG224">
+        <v>1.35</v>
+      </c>
+      <c r="BH224">
+        <v>2.74</v>
+      </c>
+      <c r="BI224">
+        <v>1.67</v>
+      </c>
+      <c r="BJ224">
+        <v>2.03</v>
+      </c>
+      <c r="BK224">
+        <v>2.1</v>
+      </c>
+      <c r="BL224">
+        <v>1.59</v>
+      </c>
+      <c r="BM224">
+        <v>2.83</v>
+      </c>
+      <c r="BN224">
+        <v>1.33</v>
+      </c>
+      <c r="BO224">
+        <v>3.75</v>
+      </c>
+      <c r="BP224">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1392,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -7494,7 +7494,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30">
         <v>2.14</v>
@@ -10584,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
         <v>0.71</v>
@@ -13880,7 +13880,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
         <v>1.36</v>
@@ -14704,7 +14704,7 @@
         <v>1.25</v>
       </c>
       <c r="AP65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65">
         <v>1.64</v>
@@ -18618,7 +18618,7 @@
         <v>3</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ84">
         <v>3</v>
@@ -20884,7 +20884,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95">
         <v>0.79</v>
@@ -24386,7 +24386,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ112">
         <v>1.21</v>
@@ -30360,7 +30360,7 @@
         <v>0.88</v>
       </c>
       <c r="AP141">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ141">
         <v>0.93</v>
@@ -33038,7 +33038,7 @@
         <v>1.33</v>
       </c>
       <c r="AP154">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ154">
         <v>1.29</v>
@@ -34480,7 +34480,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ161">
         <v>1.29</v>
@@ -35510,7 +35510,7 @@
         <v>0.1</v>
       </c>
       <c r="AP166">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ166">
         <v>0.29</v>
@@ -37982,7 +37982,7 @@
         <v>0.64</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
@@ -41896,7 +41896,7 @@
         <v>1.67</v>
       </c>
       <c r="AP197">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ197">
         <v>1.71</v>
@@ -45604,7 +45604,7 @@
         <v>1.54</v>
       </c>
       <c r="AP215">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ215">
         <v>1.43</v>
@@ -46237,31 +46237,31 @@
         <v>2.96</v>
       </c>
       <c r="AU218">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV218">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW218">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AX218">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AY218">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AZ218">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="BA218">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB218">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC218">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD218">
         <v>3.66</v>
@@ -47743,6 +47743,212 @@
       </c>
       <c r="BP225">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7453907</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F226">
+        <v>29</v>
+      </c>
+      <c r="G226" t="s">
+        <v>84</v>
+      </c>
+      <c r="H226" t="s">
+        <v>75</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226" t="s">
+        <v>87</v>
+      </c>
+      <c r="P226" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q226">
+        <v>2.75</v>
+      </c>
+      <c r="R226">
+        <v>2.25</v>
+      </c>
+      <c r="S226">
+        <v>3.25</v>
+      </c>
+      <c r="T226">
+        <v>1.33</v>
+      </c>
+      <c r="U226">
+        <v>3.25</v>
+      </c>
+      <c r="V226">
+        <v>2.5</v>
+      </c>
+      <c r="W226">
+        <v>1.5</v>
+      </c>
+      <c r="X226">
+        <v>5.5</v>
+      </c>
+      <c r="Y226">
+        <v>1.13</v>
+      </c>
+      <c r="Z226">
+        <v>2.3</v>
+      </c>
+      <c r="AA226">
+        <v>3.5</v>
+      </c>
+      <c r="AB226">
+        <v>2.87</v>
+      </c>
+      <c r="AC226">
+        <v>1.01</v>
+      </c>
+      <c r="AD226">
+        <v>11</v>
+      </c>
+      <c r="AE226">
+        <v>1.16</v>
+      </c>
+      <c r="AF226">
+        <v>4.15</v>
+      </c>
+      <c r="AG226">
+        <v>1.83</v>
+      </c>
+      <c r="AH226">
+        <v>1.91</v>
+      </c>
+      <c r="AI226">
+        <v>1.57</v>
+      </c>
+      <c r="AJ226">
+        <v>2.25</v>
+      </c>
+      <c r="AK226">
+        <v>1.39</v>
+      </c>
+      <c r="AL226">
+        <v>1.24</v>
+      </c>
+      <c r="AM226">
+        <v>1.55</v>
+      </c>
+      <c r="AN226">
+        <v>1.36</v>
+      </c>
+      <c r="AO226">
+        <v>1.07</v>
+      </c>
+      <c r="AP226">
+        <v>1.33</v>
+      </c>
+      <c r="AQ226">
+        <v>1.07</v>
+      </c>
+      <c r="AR226">
+        <v>1.51</v>
+      </c>
+      <c r="AS226">
+        <v>1.3</v>
+      </c>
+      <c r="AT226">
+        <v>2.81</v>
+      </c>
+      <c r="AU226">
+        <v>6</v>
+      </c>
+      <c r="AV226">
+        <v>3</v>
+      </c>
+      <c r="AW226">
+        <v>6</v>
+      </c>
+      <c r="AX226">
+        <v>4</v>
+      </c>
+      <c r="AY226">
+        <v>15</v>
+      </c>
+      <c r="AZ226">
+        <v>9</v>
+      </c>
+      <c r="BA226">
+        <v>3</v>
+      </c>
+      <c r="BB226">
+        <v>4</v>
+      </c>
+      <c r="BC226">
+        <v>7</v>
+      </c>
+      <c r="BD226">
+        <v>1.75</v>
+      </c>
+      <c r="BE226">
+        <v>8</v>
+      </c>
+      <c r="BF226">
+        <v>2.52</v>
+      </c>
+      <c r="BG226">
+        <v>1.39</v>
+      </c>
+      <c r="BH226">
+        <v>2.77</v>
+      </c>
+      <c r="BI226">
+        <v>1.68</v>
+      </c>
+      <c r="BJ226">
+        <v>2.11</v>
+      </c>
+      <c r="BK226">
+        <v>2.11</v>
+      </c>
+      <c r="BL226">
+        <v>1.68</v>
+      </c>
+      <c r="BM226">
+        <v>2.7</v>
+      </c>
+      <c r="BN226">
+        <v>1.41</v>
+      </c>
+      <c r="BO226">
+        <v>3.65</v>
+      </c>
+      <c r="BP226">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,15 @@
     <t>['39', '68', '88']</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['20', '37', '69']</t>
+  </si>
+  <si>
+    <t>['62', '65', '90']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1031,6 +1040,12 @@
   </si>
   <si>
     <t>['76']</t>
+  </si>
+  <si>
+    <t>['7', '17']</t>
+  </si>
+  <si>
+    <t>['40', '49', '51', '77', '81']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1663,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1932,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3">
         <v>2.14</v>
@@ -2141,7 +2156,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ4">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2266,7 +2281,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2678,7 +2693,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2884,7 +2899,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3296,7 +3311,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3502,7 +3517,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3708,7 +3723,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3789,7 +3804,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>2.33</v>
@@ -3992,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4198,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>1.21</v>
@@ -4404,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ15">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4610,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5025,7 +5040,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5150,7 +5165,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5640,7 +5655,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
         <v>1.29</v>
@@ -6180,7 +6195,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6258,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -6464,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25">
         <v>0.93</v>
@@ -6670,10 +6685,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR26">
         <v>0.95</v>
@@ -6798,7 +6813,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6879,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
         <v>0</v>
@@ -7622,7 +7637,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7700,10 +7715,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ31">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7828,7 +7843,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8240,7 +8255,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8321,7 +8336,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR34">
         <v>1.89</v>
@@ -8527,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -8730,7 +8745,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ36">
         <v>0.93</v>
@@ -9064,7 +9079,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9554,7 +9569,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
         <v>1.29</v>
@@ -9682,7 +9697,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9888,7 +9903,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10094,7 +10109,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10172,10 +10187,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ43">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR43">
         <v>1.47</v>
@@ -10300,7 +10315,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10378,7 +10393,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ44">
         <v>0.93</v>
@@ -10506,7 +10521,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10793,7 +10808,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ46">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR46">
         <v>0.99</v>
@@ -10999,7 +11014,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ47">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR47">
         <v>1.89</v>
@@ -11124,7 +11139,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11202,7 +11217,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ48">
         <v>1.71</v>
@@ -11536,7 +11551,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11617,7 +11632,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ50">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11742,7 +11757,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12026,7 +12041,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>1.64</v>
@@ -12232,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12438,7 +12453,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ54">
         <v>1.29</v>
@@ -12647,7 +12662,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ55">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>0</v>
@@ -12978,7 +12993,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13184,7 +13199,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13262,7 +13277,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ58">
         <v>2.14</v>
@@ -13390,7 +13405,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13471,7 +13486,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>1.22</v>
@@ -13596,7 +13611,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13802,7 +13817,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -13883,7 +13898,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.36</v>
@@ -14089,7 +14104,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ62">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR62">
         <v>1.13</v>
@@ -14214,7 +14229,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14420,7 +14435,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14498,10 +14513,10 @@
         <v>2.33</v>
       </c>
       <c r="AP64">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ64">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR64">
         <v>1.12</v>
@@ -14626,7 +14641,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14832,7 +14847,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14910,7 +14925,7 @@
         <v>0.25</v>
       </c>
       <c r="AP66">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ66">
         <v>0.93</v>
@@ -15325,7 +15340,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR68">
         <v>1.54</v>
@@ -15450,7 +15465,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15528,7 +15543,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>3</v>
@@ -15862,7 +15877,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15940,7 +15955,7 @@
         <v>0.8</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -16068,7 +16083,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16149,7 +16164,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.46</v>
@@ -16355,7 +16370,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ73">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR73">
         <v>1.97</v>
@@ -16480,7 +16495,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16558,7 +16573,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ74">
         <v>0.71</v>
@@ -16892,7 +16907,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17304,7 +17319,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17382,7 +17397,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ78">
         <v>1.07</v>
@@ -17510,7 +17525,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17588,7 +17603,7 @@
         <v>2.6</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ79">
         <v>1.71</v>
@@ -17922,7 +17937,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18003,7 +18018,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ81">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR81">
         <v>1.32</v>
@@ -18128,7 +18143,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18206,10 +18221,10 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18334,7 +18349,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18412,7 +18427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ83">
         <v>1.07</v>
@@ -18540,7 +18555,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18746,7 +18761,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18824,7 +18839,7 @@
         <v>1.6</v>
       </c>
       <c r="AP85">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85">
         <v>1.64</v>
@@ -19033,7 +19048,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ86">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR86">
         <v>1.93</v>
@@ -19158,7 +19173,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19570,7 +19585,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19651,7 +19666,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR89">
         <v>1.92</v>
@@ -19854,7 +19869,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ90">
         <v>0.93</v>
@@ -19982,7 +19997,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20600,7 +20615,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20887,7 +20902,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ95">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR95">
         <v>1.17</v>
@@ -21093,7 +21108,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ96">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21296,7 +21311,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.21</v>
@@ -21630,7 +21645,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21708,7 +21723,7 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ99">
         <v>3</v>
@@ -21836,7 +21851,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21914,7 +21929,7 @@
         <v>2.33</v>
       </c>
       <c r="AP100">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ100">
         <v>1.71</v>
@@ -22042,7 +22057,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22120,10 +22135,10 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ101">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR101">
         <v>1.12</v>
@@ -22248,7 +22263,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22326,10 +22341,10 @@
         <v>2.6</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR102">
         <v>1.61</v>
@@ -22454,7 +22469,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -23278,7 +23293,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23690,7 +23705,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24102,7 +24117,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24180,7 +24195,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111">
         <v>1.07</v>
@@ -24308,7 +24323,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -24592,10 +24607,10 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ113">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR113">
         <v>1.01</v>
@@ -24798,10 +24813,10 @@
         <v>2.33</v>
       </c>
       <c r="AP114">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ114">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -25004,10 +25019,10 @@
         <v>0.14</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR115">
         <v>1.12</v>
@@ -25132,7 +25147,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25210,10 +25225,10 @@
         <v>1.5</v>
       </c>
       <c r="AP116">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25338,7 +25353,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25419,7 +25434,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ117">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
         <v>1.31</v>
@@ -25544,7 +25559,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25622,7 +25637,7 @@
         <v>3</v>
       </c>
       <c r="AP118">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ118">
         <v>3</v>
@@ -25750,7 +25765,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25828,7 +25843,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ119">
         <v>1.21</v>
@@ -25956,7 +25971,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26034,7 +26049,7 @@
         <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ120">
         <v>1.07</v>
@@ -26240,10 +26255,10 @@
         <v>0.43</v>
       </c>
       <c r="AP121">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ121">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR121">
         <v>1.85</v>
@@ -26446,10 +26461,10 @@
         <v>2.14</v>
       </c>
       <c r="AP122">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ122">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR122">
         <v>1.45</v>
@@ -26652,7 +26667,7 @@
         <v>0.86</v>
       </c>
       <c r="AP123">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>0.93</v>
@@ -26780,7 +26795,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -26861,7 +26876,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ124">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR124">
         <v>1.33</v>
@@ -26986,7 +27001,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27192,7 +27207,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27604,7 +27619,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27682,7 +27697,7 @@
         <v>1.13</v>
       </c>
       <c r="AP128">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ128">
         <v>1.29</v>
@@ -27810,7 +27825,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28094,10 +28109,10 @@
         <v>0.13</v>
       </c>
       <c r="AP130">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ130">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28222,7 +28237,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28712,7 +28727,7 @@
         <v>0.88</v>
       </c>
       <c r="AP133">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ133">
         <v>0.71</v>
@@ -28921,7 +28936,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ134">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR134">
         <v>2.03</v>
@@ -29127,7 +29142,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ135">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.93</v>
@@ -29252,7 +29267,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29333,7 +29348,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ136">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR136">
         <v>1.2</v>
@@ -29536,7 +29551,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
         <v>1.21</v>
@@ -29742,10 +29757,10 @@
         <v>1.43</v>
       </c>
       <c r="AP138">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ138">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR138">
         <v>1.06</v>
@@ -29870,7 +29885,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30154,7 +30169,7 @@
         <v>0.88</v>
       </c>
       <c r="AP140">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30282,7 +30297,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30488,7 +30503,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30566,10 +30581,10 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ142">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30694,7 +30709,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30772,7 +30787,7 @@
         <v>2.38</v>
       </c>
       <c r="AP143">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ143">
         <v>2.14</v>
@@ -30981,7 +30996,7 @@
         <v>1</v>
       </c>
       <c r="AQ144">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR144">
         <v>1.18</v>
@@ -31187,7 +31202,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ145">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR145">
         <v>1.37</v>
@@ -31312,7 +31327,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31390,7 +31405,7 @@
         <v>0.78</v>
       </c>
       <c r="AP146">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ146">
         <v>0.71</v>
@@ -31518,7 +31533,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31724,7 +31739,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31930,7 +31945,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32342,7 +32357,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32420,7 +32435,7 @@
         <v>0.78</v>
       </c>
       <c r="AP151">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32548,7 +32563,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32754,7 +32769,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33166,7 +33181,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33244,10 +33259,10 @@
         <v>1.56</v>
       </c>
       <c r="AP155">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ155">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR155">
         <v>1.77</v>
@@ -33450,7 +33465,7 @@
         <v>2.11</v>
       </c>
       <c r="AP156">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ156">
         <v>2.14</v>
@@ -33659,7 +33674,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ157">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR157">
         <v>1.13</v>
@@ -33784,7 +33799,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33990,7 +34005,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34068,7 +34083,7 @@
         <v>0.78</v>
       </c>
       <c r="AP159">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ159">
         <v>0.93</v>
@@ -34196,7 +34211,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34274,10 +34289,10 @@
         <v>1.38</v>
       </c>
       <c r="AP160">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ160">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR160">
         <v>1.53</v>
@@ -34402,7 +34417,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34483,7 +34498,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ161">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR161">
         <v>1.42</v>
@@ -34686,7 +34701,7 @@
         <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ162">
         <v>1.64</v>
@@ -34895,7 +34910,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ163">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR163">
         <v>1.69</v>
@@ -35020,7 +35035,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35101,7 +35116,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ164">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR164">
         <v>1.67</v>
@@ -35226,7 +35241,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35304,7 +35319,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ165">
         <v>0.93</v>
@@ -35513,7 +35528,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ166">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR166">
         <v>1.38</v>
@@ -35638,7 +35653,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36256,7 +36271,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36543,7 +36558,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ171">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR171">
         <v>1.13</v>
@@ -36749,7 +36764,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ172">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR172">
         <v>2.01</v>
@@ -36952,7 +36967,7 @@
         <v>2.2</v>
       </c>
       <c r="AP173">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ173">
         <v>2.14</v>
@@ -37080,7 +37095,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37286,7 +37301,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37364,7 +37379,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ175">
         <v>0.93</v>
@@ -37570,7 +37585,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37776,7 +37791,7 @@
         <v>1.3</v>
       </c>
       <c r="AP177">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ177">
         <v>1.29</v>
@@ -37904,7 +37919,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38188,7 +38203,7 @@
         <v>1.82</v>
       </c>
       <c r="AP179">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
         <v>1.71</v>
@@ -38316,7 +38331,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38394,7 +38409,7 @@
         <v>3</v>
       </c>
       <c r="AP180">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ180">
         <v>3</v>
@@ -38603,7 +38618,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ181">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -38728,7 +38743,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38806,10 +38821,10 @@
         <v>0.09</v>
       </c>
       <c r="AP182">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ182">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR182">
         <v>1.76</v>
@@ -38934,7 +38949,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39015,7 +39030,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ183">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR183">
         <v>1.95</v>
@@ -39140,7 +39155,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39552,7 +39567,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39630,7 +39645,7 @@
         <v>0.73</v>
       </c>
       <c r="AP186">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ186">
         <v>0.71</v>
@@ -39758,7 +39773,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39839,7 +39854,7 @@
         <v>1</v>
       </c>
       <c r="AQ187">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR187">
         <v>1.22</v>
@@ -39964,7 +39979,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40042,7 +40057,7 @@
         <v>0.73</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ188">
         <v>1</v>
@@ -40170,7 +40185,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40869,7 +40884,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ192">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR192">
         <v>1.69</v>
@@ -41072,10 +41087,10 @@
         <v>0.33</v>
       </c>
       <c r="AP193">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ193">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR193">
         <v>1.1</v>
@@ -41200,7 +41215,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41484,10 +41499,10 @@
         <v>1.67</v>
       </c>
       <c r="AP195">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ195">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR195">
         <v>1.71</v>
@@ -41612,7 +41627,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41690,7 +41705,7 @@
         <v>1.67</v>
       </c>
       <c r="AP196">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ196">
         <v>1.64</v>
@@ -41818,7 +41833,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42102,10 +42117,10 @@
         <v>0.83</v>
       </c>
       <c r="AP198">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ198">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR198">
         <v>1.34</v>
@@ -42720,7 +42735,7 @@
         <v>0.75</v>
       </c>
       <c r="AP201">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ201">
         <v>0.71</v>
@@ -42848,7 +42863,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43260,7 +43275,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43338,7 +43353,7 @@
         <v>0.83</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ204">
         <v>0.93</v>
@@ -43466,7 +43481,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43547,7 +43562,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ205">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR205">
         <v>1.17</v>
@@ -43878,7 +43893,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44165,7 +44180,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ208">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR208">
         <v>1.69</v>
@@ -44368,7 +44383,7 @@
         <v>1.62</v>
       </c>
       <c r="AP209">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ209">
         <v>1.71</v>
@@ -44577,7 +44592,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ210">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
         <v>1.45</v>
@@ -44780,7 +44795,7 @@
         <v>1.31</v>
       </c>
       <c r="AP211">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ211">
         <v>1.21</v>
@@ -44908,7 +44923,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -44986,7 +45001,7 @@
         <v>3</v>
       </c>
       <c r="AP212">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ212">
         <v>3</v>
@@ -45114,7 +45129,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45192,7 +45207,7 @@
         <v>1.15</v>
       </c>
       <c r="AP213">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ213">
         <v>1.07</v>
@@ -45320,7 +45335,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45401,7 +45416,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ214">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR214">
         <v>1.63</v>
@@ -45607,7 +45622,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ215">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR215">
         <v>1.47</v>
@@ -45810,10 +45825,10 @@
         <v>0.31</v>
       </c>
       <c r="AP216">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ216">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR216">
         <v>1.76</v>
@@ -45938,7 +45953,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46016,7 +46031,7 @@
         <v>1.25</v>
       </c>
       <c r="AP217">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ217">
         <v>1.29</v>
@@ -46144,7 +46159,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46225,7 +46240,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ218">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR218">
         <v>1.22</v>
@@ -46350,7 +46365,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q219">
         <v>6</v>
@@ -46556,7 +46571,7 @@
         <v>231</v>
       </c>
       <c r="P220" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46968,7 +46983,7 @@
         <v>233</v>
       </c>
       <c r="P222" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q222">
         <v>4.5</v>
@@ -47046,7 +47061,7 @@
         <v>1.77</v>
       </c>
       <c r="AP222">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ222">
         <v>1.64</v>
@@ -47174,7 +47189,7 @@
         <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q223">
         <v>3.5</v>
@@ -47586,7 +47601,7 @@
         <v>234</v>
       </c>
       <c r="P225" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q225">
         <v>2.6</v>
@@ -47949,6 +47964,1242 @@
       </c>
       <c r="BP226">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7453906</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F227">
+        <v>29</v>
+      </c>
+      <c r="G227" t="s">
+        <v>80</v>
+      </c>
+      <c r="H227" t="s">
+        <v>76</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>2</v>
+      </c>
+      <c r="K227">
+        <v>3</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>2</v>
+      </c>
+      <c r="N227">
+        <v>3</v>
+      </c>
+      <c r="O227" t="s">
+        <v>235</v>
+      </c>
+      <c r="P227" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q227">
+        <v>2.6</v>
+      </c>
+      <c r="R227">
+        <v>2.25</v>
+      </c>
+      <c r="S227">
+        <v>3.6</v>
+      </c>
+      <c r="T227">
+        <v>1.33</v>
+      </c>
+      <c r="U227">
+        <v>3.25</v>
+      </c>
+      <c r="V227">
+        <v>2.63</v>
+      </c>
+      <c r="W227">
+        <v>1.44</v>
+      </c>
+      <c r="X227">
+        <v>6</v>
+      </c>
+      <c r="Y227">
+        <v>1.11</v>
+      </c>
+      <c r="Z227">
+        <v>1.5</v>
+      </c>
+      <c r="AA227">
+        <v>4.3</v>
+      </c>
+      <c r="AB227">
+        <v>5.9</v>
+      </c>
+      <c r="AC227">
+        <v>1.01</v>
+      </c>
+      <c r="AD227">
+        <v>11</v>
+      </c>
+      <c r="AE227">
+        <v>1.18</v>
+      </c>
+      <c r="AF227">
+        <v>3.88</v>
+      </c>
+      <c r="AG227">
+        <v>1.7</v>
+      </c>
+      <c r="AH227">
+        <v>2.1</v>
+      </c>
+      <c r="AI227">
+        <v>1.62</v>
+      </c>
+      <c r="AJ227">
+        <v>2.2</v>
+      </c>
+      <c r="AK227">
+        <v>1.28</v>
+      </c>
+      <c r="AL227">
+        <v>1.24</v>
+      </c>
+      <c r="AM227">
+        <v>1.7</v>
+      </c>
+      <c r="AN227">
+        <v>1.5</v>
+      </c>
+      <c r="AO227">
+        <v>0.79</v>
+      </c>
+      <c r="AP227">
+        <v>1.4</v>
+      </c>
+      <c r="AQ227">
+        <v>0.93</v>
+      </c>
+      <c r="AR227">
+        <v>1.6</v>
+      </c>
+      <c r="AS227">
+        <v>1.12</v>
+      </c>
+      <c r="AT227">
+        <v>2.72</v>
+      </c>
+      <c r="AU227">
+        <v>7</v>
+      </c>
+      <c r="AV227">
+        <v>14</v>
+      </c>
+      <c r="AW227">
+        <v>5</v>
+      </c>
+      <c r="AX227">
+        <v>2</v>
+      </c>
+      <c r="AY227">
+        <v>13</v>
+      </c>
+      <c r="AZ227">
+        <v>16</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
+        <v>2</v>
+      </c>
+      <c r="BC227">
+        <v>7</v>
+      </c>
+      <c r="BD227">
+        <v>1.91</v>
+      </c>
+      <c r="BE227">
+        <v>7.5</v>
+      </c>
+      <c r="BF227">
+        <v>2.2</v>
+      </c>
+      <c r="BG227">
+        <v>1.47</v>
+      </c>
+      <c r="BH227">
+        <v>2.5</v>
+      </c>
+      <c r="BI227">
+        <v>1.82</v>
+      </c>
+      <c r="BJ227">
+        <v>1.98</v>
+      </c>
+      <c r="BK227">
+        <v>2.34</v>
+      </c>
+      <c r="BL227">
+        <v>1.56</v>
+      </c>
+      <c r="BM227">
+        <v>3.02</v>
+      </c>
+      <c r="BN227">
+        <v>1.33</v>
+      </c>
+      <c r="BO227">
+        <v>4.2</v>
+      </c>
+      <c r="BP227">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7453909</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45745.52083333334</v>
+      </c>
+      <c r="F228">
+        <v>29</v>
+      </c>
+      <c r="G228" t="s">
+        <v>83</v>
+      </c>
+      <c r="H228" t="s">
+        <v>77</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228" t="s">
+        <v>87</v>
+      </c>
+      <c r="P228" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q228">
+        <v>1.95</v>
+      </c>
+      <c r="R228">
+        <v>2.4</v>
+      </c>
+      <c r="S228">
+        <v>5.5</v>
+      </c>
+      <c r="T228">
+        <v>1.3</v>
+      </c>
+      <c r="U228">
+        <v>3.4</v>
+      </c>
+      <c r="V228">
+        <v>2.38</v>
+      </c>
+      <c r="W228">
+        <v>1.53</v>
+      </c>
+      <c r="X228">
+        <v>5</v>
+      </c>
+      <c r="Y228">
+        <v>1.14</v>
+      </c>
+      <c r="Z228">
+        <v>1.84</v>
+      </c>
+      <c r="AA228">
+        <v>3.76</v>
+      </c>
+      <c r="AB228">
+        <v>3.82</v>
+      </c>
+      <c r="AC228">
+        <v>1.01</v>
+      </c>
+      <c r="AD228">
+        <v>13</v>
+      </c>
+      <c r="AE228">
+        <v>1.15</v>
+      </c>
+      <c r="AF228">
+        <v>4.25</v>
+      </c>
+      <c r="AG228">
+        <v>1.68</v>
+      </c>
+      <c r="AH228">
+        <v>2.06</v>
+      </c>
+      <c r="AI228">
+        <v>1.73</v>
+      </c>
+      <c r="AJ228">
+        <v>2</v>
+      </c>
+      <c r="AK228">
+        <v>1.08</v>
+      </c>
+      <c r="AL228">
+        <v>1.15</v>
+      </c>
+      <c r="AM228">
+        <v>2.64</v>
+      </c>
+      <c r="AN228">
+        <v>2.07</v>
+      </c>
+      <c r="AO228">
+        <v>1.29</v>
+      </c>
+      <c r="AP228">
+        <v>2</v>
+      </c>
+      <c r="AQ228">
+        <v>1.27</v>
+      </c>
+      <c r="AR228">
+        <v>1.81</v>
+      </c>
+      <c r="AS228">
+        <v>1.57</v>
+      </c>
+      <c r="AT228">
+        <v>3.38</v>
+      </c>
+      <c r="AU228">
+        <v>4</v>
+      </c>
+      <c r="AV228">
+        <v>3</v>
+      </c>
+      <c r="AW228">
+        <v>8</v>
+      </c>
+      <c r="AX228">
+        <v>7</v>
+      </c>
+      <c r="AY228">
+        <v>13</v>
+      </c>
+      <c r="AZ228">
+        <v>12</v>
+      </c>
+      <c r="BA228">
+        <v>5</v>
+      </c>
+      <c r="BB228">
+        <v>6</v>
+      </c>
+      <c r="BC228">
+        <v>11</v>
+      </c>
+      <c r="BD228">
+        <v>1.64</v>
+      </c>
+      <c r="BE228">
+        <v>8</v>
+      </c>
+      <c r="BF228">
+        <v>2.77</v>
+      </c>
+      <c r="BG228">
+        <v>1.39</v>
+      </c>
+      <c r="BH228">
+        <v>2.77</v>
+      </c>
+      <c r="BI228">
+        <v>1.68</v>
+      </c>
+      <c r="BJ228">
+        <v>2.11</v>
+      </c>
+      <c r="BK228">
+        <v>2.11</v>
+      </c>
+      <c r="BL228">
+        <v>1.68</v>
+      </c>
+      <c r="BM228">
+        <v>2.7</v>
+      </c>
+      <c r="BN228">
+        <v>1.41</v>
+      </c>
+      <c r="BO228">
+        <v>3.65</v>
+      </c>
+      <c r="BP228">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7453904</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45745.625</v>
+      </c>
+      <c r="F229">
+        <v>29</v>
+      </c>
+      <c r="G229" t="s">
+        <v>85</v>
+      </c>
+      <c r="H229" t="s">
+        <v>72</v>
+      </c>
+      <c r="I229">
+        <v>2</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>3</v>
+      </c>
+      <c r="L229">
+        <v>3</v>
+      </c>
+      <c r="M229">
+        <v>5</v>
+      </c>
+      <c r="N229">
+        <v>8</v>
+      </c>
+      <c r="O229" t="s">
+        <v>236</v>
+      </c>
+      <c r="P229" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q229">
+        <v>8</v>
+      </c>
+      <c r="R229">
+        <v>2.6</v>
+      </c>
+      <c r="S229">
+        <v>1.67</v>
+      </c>
+      <c r="T229">
+        <v>1.29</v>
+      </c>
+      <c r="U229">
+        <v>3.5</v>
+      </c>
+      <c r="V229">
+        <v>2.25</v>
+      </c>
+      <c r="W229">
+        <v>1.57</v>
+      </c>
+      <c r="X229">
+        <v>4.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.17</v>
+      </c>
+      <c r="Z229">
+        <v>11</v>
+      </c>
+      <c r="AA229">
+        <v>5</v>
+      </c>
+      <c r="AB229">
+        <v>1.25</v>
+      </c>
+      <c r="AC229">
+        <v>1.01</v>
+      </c>
+      <c r="AD229">
+        <v>17</v>
+      </c>
+      <c r="AE229">
+        <v>1.13</v>
+      </c>
+      <c r="AF229">
+        <v>4.6</v>
+      </c>
+      <c r="AG229">
+        <v>1.53</v>
+      </c>
+      <c r="AH229">
+        <v>2.38</v>
+      </c>
+      <c r="AI229">
+        <v>2</v>
+      </c>
+      <c r="AJ229">
+        <v>1.73</v>
+      </c>
+      <c r="AK229">
+        <v>3.46</v>
+      </c>
+      <c r="AL229">
+        <v>1.13</v>
+      </c>
+      <c r="AM229">
+        <v>1</v>
+      </c>
+      <c r="AN229">
+        <v>1.14</v>
+      </c>
+      <c r="AO229">
+        <v>3</v>
+      </c>
+      <c r="AP229">
+        <v>1.07</v>
+      </c>
+      <c r="AQ229">
+        <v>3</v>
+      </c>
+      <c r="AR229">
+        <v>1.73</v>
+      </c>
+      <c r="AS229">
+        <v>2.2</v>
+      </c>
+      <c r="AT229">
+        <v>3.93</v>
+      </c>
+      <c r="AU229">
+        <v>6</v>
+      </c>
+      <c r="AV229">
+        <v>10</v>
+      </c>
+      <c r="AW229">
+        <v>3</v>
+      </c>
+      <c r="AX229">
+        <v>12</v>
+      </c>
+      <c r="AY229">
+        <v>9</v>
+      </c>
+      <c r="AZ229">
+        <v>27</v>
+      </c>
+      <c r="BA229">
+        <v>1</v>
+      </c>
+      <c r="BB229">
+        <v>6</v>
+      </c>
+      <c r="BC229">
+        <v>7</v>
+      </c>
+      <c r="BD229">
+        <v>6.16</v>
+      </c>
+      <c r="BE229">
+        <v>11</v>
+      </c>
+      <c r="BF229">
+        <v>1.18</v>
+      </c>
+      <c r="BG229">
+        <v>1.36</v>
+      </c>
+      <c r="BH229">
+        <v>2.92</v>
+      </c>
+      <c r="BI229">
+        <v>1.62</v>
+      </c>
+      <c r="BJ229">
+        <v>2.22</v>
+      </c>
+      <c r="BK229">
+        <v>2.02</v>
+      </c>
+      <c r="BL229">
+        <v>1.74</v>
+      </c>
+      <c r="BM229">
+        <v>2.57</v>
+      </c>
+      <c r="BN229">
+        <v>1.45</v>
+      </c>
+      <c r="BO229">
+        <v>3.42</v>
+      </c>
+      <c r="BP229">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7453910</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45745.66666666666</v>
+      </c>
+      <c r="F230">
+        <v>29</v>
+      </c>
+      <c r="G230" t="s">
+        <v>71</v>
+      </c>
+      <c r="H230" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>183</v>
+      </c>
+      <c r="P230" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q230">
+        <v>3.2</v>
+      </c>
+      <c r="R230">
+        <v>2.1</v>
+      </c>
+      <c r="S230">
+        <v>3.1</v>
+      </c>
+      <c r="T230">
+        <v>1.4</v>
+      </c>
+      <c r="U230">
+        <v>2.75</v>
+      </c>
+      <c r="V230">
+        <v>2.75</v>
+      </c>
+      <c r="W230">
+        <v>1.4</v>
+      </c>
+      <c r="X230">
+        <v>7</v>
+      </c>
+      <c r="Y230">
+        <v>1.08</v>
+      </c>
+      <c r="Z230">
+        <v>2.85</v>
+      </c>
+      <c r="AA230">
+        <v>3.21</v>
+      </c>
+      <c r="AB230">
+        <v>2.45</v>
+      </c>
+      <c r="AC230">
+        <v>1.01</v>
+      </c>
+      <c r="AD230">
+        <v>9</v>
+      </c>
+      <c r="AE230">
+        <v>1.24</v>
+      </c>
+      <c r="AF230">
+        <v>3.34</v>
+      </c>
+      <c r="AG230">
+        <v>1.98</v>
+      </c>
+      <c r="AH230">
+        <v>1.77</v>
+      </c>
+      <c r="AI230">
+        <v>1.73</v>
+      </c>
+      <c r="AJ230">
+        <v>2</v>
+      </c>
+      <c r="AK230">
+        <v>1.49</v>
+      </c>
+      <c r="AL230">
+        <v>1.26</v>
+      </c>
+      <c r="AM230">
+        <v>1.42</v>
+      </c>
+      <c r="AN230">
+        <v>1.29</v>
+      </c>
+      <c r="AO230">
+        <v>1.36</v>
+      </c>
+      <c r="AP230">
+        <v>1.4</v>
+      </c>
+      <c r="AQ230">
+        <v>1.27</v>
+      </c>
+      <c r="AR230">
+        <v>1.39</v>
+      </c>
+      <c r="AS230">
+        <v>1.77</v>
+      </c>
+      <c r="AT230">
+        <v>3.16</v>
+      </c>
+      <c r="AU230">
+        <v>3</v>
+      </c>
+      <c r="AV230">
+        <v>3</v>
+      </c>
+      <c r="AW230">
+        <v>9</v>
+      </c>
+      <c r="AX230">
+        <v>13</v>
+      </c>
+      <c r="AY230">
+        <v>12</v>
+      </c>
+      <c r="AZ230">
+        <v>22</v>
+      </c>
+      <c r="BA230">
+        <v>4</v>
+      </c>
+      <c r="BB230">
+        <v>2</v>
+      </c>
+      <c r="BC230">
+        <v>6</v>
+      </c>
+      <c r="BD230">
+        <v>2.2</v>
+      </c>
+      <c r="BE230">
+        <v>7.5</v>
+      </c>
+      <c r="BF230">
+        <v>1.91</v>
+      </c>
+      <c r="BG230">
+        <v>1.47</v>
+      </c>
+      <c r="BH230">
+        <v>2.5</v>
+      </c>
+      <c r="BI230">
+        <v>1.82</v>
+      </c>
+      <c r="BJ230">
+        <v>1.98</v>
+      </c>
+      <c r="BK230">
+        <v>2.34</v>
+      </c>
+      <c r="BL230">
+        <v>1.56</v>
+      </c>
+      <c r="BM230">
+        <v>3.02</v>
+      </c>
+      <c r="BN230">
+        <v>1.33</v>
+      </c>
+      <c r="BO230">
+        <v>4.2</v>
+      </c>
+      <c r="BP230">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7453903</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F231">
+        <v>29</v>
+      </c>
+      <c r="G231" t="s">
+        <v>82</v>
+      </c>
+      <c r="H231" t="s">
+        <v>78</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>3</v>
+      </c>
+      <c r="O231" t="s">
+        <v>237</v>
+      </c>
+      <c r="P231" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q231">
+        <v>1.8</v>
+      </c>
+      <c r="R231">
+        <v>2.5</v>
+      </c>
+      <c r="S231">
+        <v>7.5</v>
+      </c>
+      <c r="T231">
+        <v>1.3</v>
+      </c>
+      <c r="U231">
+        <v>3.4</v>
+      </c>
+      <c r="V231">
+        <v>2.5</v>
+      </c>
+      <c r="W231">
+        <v>1.5</v>
+      </c>
+      <c r="X231">
+        <v>5.5</v>
+      </c>
+      <c r="Y231">
+        <v>1.13</v>
+      </c>
+      <c r="Z231">
+        <v>1.27</v>
+      </c>
+      <c r="AA231">
+        <v>5.1</v>
+      </c>
+      <c r="AB231">
+        <v>9.5</v>
+      </c>
+      <c r="AC231">
+        <v>1.04</v>
+      </c>
+      <c r="AD231">
+        <v>9.5</v>
+      </c>
+      <c r="AE231">
+        <v>1.2</v>
+      </c>
+      <c r="AF231">
+        <v>4.2</v>
+      </c>
+      <c r="AG231">
+        <v>1.67</v>
+      </c>
+      <c r="AH231">
+        <v>2</v>
+      </c>
+      <c r="AI231">
+        <v>2</v>
+      </c>
+      <c r="AJ231">
+        <v>1.73</v>
+      </c>
+      <c r="AK231">
+        <v>1.01</v>
+      </c>
+      <c r="AL231">
+        <v>1.14</v>
+      </c>
+      <c r="AM231">
+        <v>3.22</v>
+      </c>
+      <c r="AN231">
+        <v>1.36</v>
+      </c>
+      <c r="AO231">
+        <v>0.29</v>
+      </c>
+      <c r="AP231">
+        <v>1.47</v>
+      </c>
+      <c r="AQ231">
+        <v>0.27</v>
+      </c>
+      <c r="AR231">
+        <v>1.62</v>
+      </c>
+      <c r="AS231">
+        <v>1.17</v>
+      </c>
+      <c r="AT231">
+        <v>2.79</v>
+      </c>
+      <c r="AU231">
+        <v>8</v>
+      </c>
+      <c r="AV231">
+        <v>5</v>
+      </c>
+      <c r="AW231">
+        <v>10</v>
+      </c>
+      <c r="AX231">
+        <v>4</v>
+      </c>
+      <c r="AY231">
+        <v>22</v>
+      </c>
+      <c r="AZ231">
+        <v>12</v>
+      </c>
+      <c r="BA231">
+        <v>7</v>
+      </c>
+      <c r="BB231">
+        <v>2</v>
+      </c>
+      <c r="BC231">
+        <v>9</v>
+      </c>
+      <c r="BD231">
+        <v>1.26</v>
+      </c>
+      <c r="BE231">
+        <v>10</v>
+      </c>
+      <c r="BF231">
+        <v>5.06</v>
+      </c>
+      <c r="BG231">
+        <v>1.4</v>
+      </c>
+      <c r="BH231">
+        <v>2.56</v>
+      </c>
+      <c r="BI231">
+        <v>1.8</v>
+      </c>
+      <c r="BJ231">
+        <v>2</v>
+      </c>
+      <c r="BK231">
+        <v>2.24</v>
+      </c>
+      <c r="BL231">
+        <v>1.52</v>
+      </c>
+      <c r="BM231">
+        <v>3.05</v>
+      </c>
+      <c r="BN231">
+        <v>1.28</v>
+      </c>
+      <c r="BO231">
+        <v>4.1</v>
+      </c>
+      <c r="BP231">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7453905</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45746.47916666666</v>
+      </c>
+      <c r="F232">
+        <v>29</v>
+      </c>
+      <c r="G232" t="s">
+        <v>81</v>
+      </c>
+      <c r="H232" t="s">
+        <v>73</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232" t="s">
+        <v>87</v>
+      </c>
+      <c r="P232" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q232">
+        <v>0</v>
+      </c>
+      <c r="R232">
+        <v>0</v>
+      </c>
+      <c r="S232">
+        <v>0</v>
+      </c>
+      <c r="T232">
+        <v>0</v>
+      </c>
+      <c r="U232">
+        <v>0</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
+      </c>
+      <c r="W232">
+        <v>0</v>
+      </c>
+      <c r="X232">
+        <v>0</v>
+      </c>
+      <c r="Y232">
+        <v>0</v>
+      </c>
+      <c r="Z232">
+        <v>1.71</v>
+      </c>
+      <c r="AA232">
+        <v>3.3</v>
+      </c>
+      <c r="AB232">
+        <v>4.7</v>
+      </c>
+      <c r="AC232">
+        <v>0</v>
+      </c>
+      <c r="AD232">
+        <v>0</v>
+      </c>
+      <c r="AE232">
+        <v>0</v>
+      </c>
+      <c r="AF232">
+        <v>0</v>
+      </c>
+      <c r="AG232">
+        <v>2.05</v>
+      </c>
+      <c r="AH232">
+        <v>1.61</v>
+      </c>
+      <c r="AI232">
+        <v>0</v>
+      </c>
+      <c r="AJ232">
+        <v>0</v>
+      </c>
+      <c r="AK232">
+        <v>0</v>
+      </c>
+      <c r="AL232">
+        <v>0</v>
+      </c>
+      <c r="AM232">
+        <v>0</v>
+      </c>
+      <c r="AN232">
+        <v>1.43</v>
+      </c>
+      <c r="AO232">
+        <v>1.43</v>
+      </c>
+      <c r="AP232">
+        <v>1.4</v>
+      </c>
+      <c r="AQ232">
+        <v>1.4</v>
+      </c>
+      <c r="AR232">
+        <v>1.19</v>
+      </c>
+      <c r="AS232">
+        <v>0.75</v>
+      </c>
+      <c r="AT232">
+        <v>1.94</v>
+      </c>
+      <c r="AU232">
+        <v>-1</v>
+      </c>
+      <c r="AV232">
+        <v>-1</v>
+      </c>
+      <c r="AW232">
+        <v>-1</v>
+      </c>
+      <c r="AX232">
+        <v>-1</v>
+      </c>
+      <c r="AY232">
+        <v>-1</v>
+      </c>
+      <c r="AZ232">
+        <v>-1</v>
+      </c>
+      <c r="BA232">
+        <v>-1</v>
+      </c>
+      <c r="BB232">
+        <v>-1</v>
+      </c>
+      <c r="BC232">
+        <v>-1</v>
+      </c>
+      <c r="BD232">
+        <v>0</v>
+      </c>
+      <c r="BE232">
+        <v>0</v>
+      </c>
+      <c r="BF232">
+        <v>0</v>
+      </c>
+      <c r="BG232">
+        <v>0</v>
+      </c>
+      <c r="BH232">
+        <v>0</v>
+      </c>
+      <c r="BI232">
+        <v>0</v>
+      </c>
+      <c r="BJ232">
+        <v>0</v>
+      </c>
+      <c r="BK232">
+        <v>0</v>
+      </c>
+      <c r="BL232">
+        <v>0</v>
+      </c>
+      <c r="BM232">
+        <v>0</v>
+      </c>
+      <c r="BN232">
+        <v>0</v>
+      </c>
+      <c r="BO232">
+        <v>0</v>
+      </c>
+      <c r="BP232">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="345">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1047,6 +1047,9 @@
   <si>
     <t>['40', '49', '51', '77', '81']</t>
   </si>
+  <si>
+    <t>['8', '90+3']</t>
+  </si>
 </sst>
 </file>
 
@@ -1407,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3595,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
         <v>0.93</v>
@@ -4216,7 +4219,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -6276,7 +6279,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>0.98</v>
@@ -8951,7 +8954,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -9366,7 +9369,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -11423,7 +11426,7 @@
         <v>0.33</v>
       </c>
       <c r="AP49">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49">
         <v>0.93</v>
@@ -13074,7 +13077,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
         <v>1.94</v>
@@ -15131,7 +15134,7 @@
         <v>2.5</v>
       </c>
       <c r="AP67">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ67">
         <v>1.71</v>
@@ -17812,7 +17815,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ80">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
         <v>1.56</v>
@@ -18015,7 +18018,7 @@
         <v>2.5</v>
       </c>
       <c r="AP81">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ81">
         <v>1.4</v>
@@ -21314,7 +21317,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR97">
         <v>1.33</v>
@@ -21517,7 +21520,7 @@
         <v>0.6</v>
       </c>
       <c r="AP98">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ98">
         <v>1.07</v>
@@ -24404,7 +24407,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ112">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR112">
         <v>1.19</v>
@@ -25431,7 +25434,7 @@
         <v>1.8</v>
       </c>
       <c r="AP117">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ117">
         <v>1.27</v>
@@ -25846,7 +25849,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ119">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR119">
         <v>1.78</v>
@@ -26873,7 +26876,7 @@
         <v>1.43</v>
       </c>
       <c r="AP124">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ124">
         <v>1.27</v>
@@ -29554,7 +29557,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.8</v>
@@ -29963,7 +29966,7 @@
         <v>2.29</v>
       </c>
       <c r="AP139">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ139">
         <v>2.14</v>
@@ -31199,7 +31202,7 @@
         <v>0.11</v>
       </c>
       <c r="AP145">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ145">
         <v>0.27</v>
@@ -33880,7 +33883,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ158">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR158">
         <v>2</v>
@@ -35937,7 +35940,7 @@
         <v>0.7</v>
       </c>
       <c r="AP168">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ168">
         <v>0.71</v>
@@ -36352,7 +36355,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR170">
         <v>1.25</v>
@@ -39439,7 +39442,7 @@
         <v>1.73</v>
       </c>
       <c r="AP185">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ185">
         <v>1.64</v>
@@ -40678,7 +40681,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ191">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR191">
         <v>1.17</v>
@@ -41293,7 +41296,7 @@
         <v>3</v>
       </c>
       <c r="AP194">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ194">
         <v>3</v>
@@ -42532,7 +42535,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ200">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR200">
         <v>1.97</v>
@@ -44589,7 +44592,7 @@
         <v>0.85</v>
       </c>
       <c r="AP210">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ210">
         <v>0.93</v>
@@ -44798,7 +44801,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ211">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR211">
         <v>1.42</v>
@@ -49200,6 +49203,212 @@
       </c>
       <c r="BP232">
         <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7453908</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45746.60416666666</v>
+      </c>
+      <c r="F233">
+        <v>29</v>
+      </c>
+      <c r="G233" t="s">
+        <v>79</v>
+      </c>
+      <c r="H233" t="s">
+        <v>74</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>2</v>
+      </c>
+      <c r="L233">
+        <v>1</v>
+      </c>
+      <c r="M233">
+        <v>2</v>
+      </c>
+      <c r="N233">
+        <v>3</v>
+      </c>
+      <c r="O233" t="s">
+        <v>182</v>
+      </c>
+      <c r="P233" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q233">
+        <v>2.75</v>
+      </c>
+      <c r="R233">
+        <v>2.05</v>
+      </c>
+      <c r="S233">
+        <v>4</v>
+      </c>
+      <c r="T233">
+        <v>1.44</v>
+      </c>
+      <c r="U233">
+        <v>2.63</v>
+      </c>
+      <c r="V233">
+        <v>3.25</v>
+      </c>
+      <c r="W233">
+        <v>1.33</v>
+      </c>
+      <c r="X233">
+        <v>7.5</v>
+      </c>
+      <c r="Y233">
+        <v>1.07</v>
+      </c>
+      <c r="Z233">
+        <v>2.3</v>
+      </c>
+      <c r="AA233">
+        <v>3.2</v>
+      </c>
+      <c r="AB233">
+        <v>2.9</v>
+      </c>
+      <c r="AC233">
+        <v>1.06</v>
+      </c>
+      <c r="AD233">
+        <v>8</v>
+      </c>
+      <c r="AE233">
+        <v>1.36</v>
+      </c>
+      <c r="AF233">
+        <v>3</v>
+      </c>
+      <c r="AG233">
+        <v>2.39</v>
+      </c>
+      <c r="AH233">
+        <v>1.51</v>
+      </c>
+      <c r="AI233">
+        <v>1.91</v>
+      </c>
+      <c r="AJ233">
+        <v>1.8</v>
+      </c>
+      <c r="AK233">
+        <v>1.3</v>
+      </c>
+      <c r="AL233">
+        <v>1.28</v>
+      </c>
+      <c r="AM233">
+        <v>1.67</v>
+      </c>
+      <c r="AN233">
+        <v>1.21</v>
+      </c>
+      <c r="AO233">
+        <v>1.21</v>
+      </c>
+      <c r="AP233">
+        <v>1.13</v>
+      </c>
+      <c r="AQ233">
+        <v>1.33</v>
+      </c>
+      <c r="AR233">
+        <v>1.44</v>
+      </c>
+      <c r="AS233">
+        <v>1.44</v>
+      </c>
+      <c r="AT233">
+        <v>2.88</v>
+      </c>
+      <c r="AU233">
+        <v>8</v>
+      </c>
+      <c r="AV233">
+        <v>5</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>8</v>
+      </c>
+      <c r="AY233">
+        <v>19</v>
+      </c>
+      <c r="AZ233">
+        <v>16</v>
+      </c>
+      <c r="BA233">
+        <v>3</v>
+      </c>
+      <c r="BB233">
+        <v>0</v>
+      </c>
+      <c r="BC233">
+        <v>3</v>
+      </c>
+      <c r="BD233">
+        <v>1.75</v>
+      </c>
+      <c r="BE233">
+        <v>7.5</v>
+      </c>
+      <c r="BF233">
+        <v>2.53</v>
+      </c>
+      <c r="BG233">
+        <v>1.55</v>
+      </c>
+      <c r="BH233">
+        <v>2.17</v>
+      </c>
+      <c r="BI233">
+        <v>2</v>
+      </c>
+      <c r="BJ233">
+        <v>1.69</v>
+      </c>
+      <c r="BK233">
+        <v>2.66</v>
+      </c>
+      <c r="BL233">
+        <v>1.37</v>
+      </c>
+      <c r="BM233">
+        <v>3.78</v>
+      </c>
+      <c r="BN233">
+        <v>1.19</v>
+      </c>
+      <c r="BO233">
+        <v>5.05</v>
+      </c>
+      <c r="BP233">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -49139,31 +49139,31 @@
         <v>1.94</v>
       </c>
       <c r="AU232">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV232">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW232">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AX232">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY232">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ232">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BA232">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB232">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC232">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD232">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="346">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['62', '65', '90']</t>
   </si>
   <si>
+    <t>['39', '90+2']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1410,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1666,7 +1669,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2284,7 +2287,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2696,7 +2699,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2777,7 +2780,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2902,7 +2905,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -2980,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
         <v>1.64</v>
@@ -3314,7 +3317,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3520,7 +3523,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3726,7 +3729,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -5168,7 +5171,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5246,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19">
         <v>3</v>
@@ -5455,7 +5458,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR20">
         <v>1.78</v>
@@ -6198,7 +6201,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6816,7 +6819,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7640,7 +7643,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7846,7 +7849,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8258,7 +8261,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8542,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ35">
         <v>0.27</v>
@@ -8751,7 +8754,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ36">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR36">
         <v>1.22</v>
@@ -9082,7 +9085,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9700,7 +9703,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9778,7 +9781,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -9906,7 +9909,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10112,7 +10115,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10318,7 +10321,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10524,7 +10527,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11142,7 +11145,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11429,7 +11432,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR49">
         <v>1.36</v>
@@ -11554,7 +11557,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11760,7 +11763,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12996,7 +12999,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13202,7 +13205,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13408,7 +13411,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13486,7 +13489,7 @@
         <v>1.5</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13614,7 +13617,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13820,7 +13823,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14232,7 +14235,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14438,7 +14441,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14644,7 +14647,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14850,7 +14853,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14931,7 +14934,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ66">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR66">
         <v>1.91</v>
@@ -15468,7 +15471,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15880,7 +15883,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16086,7 +16089,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16498,7 +16501,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16782,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ75">
         <v>0.93</v>
@@ -16910,7 +16913,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17197,7 +17200,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ77">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR77">
         <v>0.96</v>
@@ -17322,7 +17325,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17528,7 +17531,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17940,7 +17943,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18146,7 +18149,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18352,7 +18355,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18558,7 +18561,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18764,7 +18767,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19176,7 +19179,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19588,7 +19591,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19875,7 +19878,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ90">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -20000,7 +20003,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20078,7 +20081,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ91">
         <v>1.29</v>
@@ -20618,7 +20621,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21648,7 +21651,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21854,7 +21857,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -22060,7 +22063,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22266,7 +22269,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22472,7 +22475,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22550,7 +22553,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ103">
         <v>0.71</v>
@@ -23296,7 +23299,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23583,7 +23586,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ108">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR108">
         <v>0.6899999999999999</v>
@@ -23708,7 +23711,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24120,7 +24123,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24326,7 +24329,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25150,7 +25153,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25356,7 +25359,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25562,7 +25565,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25768,7 +25771,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25974,7 +25977,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26798,7 +26801,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27004,7 +27007,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27210,7 +27213,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27291,7 +27294,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ126">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR126">
         <v>1.56</v>
@@ -27494,7 +27497,7 @@
         <v>2.13</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ127">
         <v>1.71</v>
@@ -27622,7 +27625,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27828,7 +27831,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28240,7 +28243,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -29270,7 +29273,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29888,7 +29891,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30300,7 +30303,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30506,7 +30509,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30712,7 +30715,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30996,7 +30999,7 @@
         <v>2.11</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ144">
         <v>1.4</v>
@@ -31330,7 +31333,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31536,7 +31539,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31742,7 +31745,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31948,7 +31951,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32235,7 +32238,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ150">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR150">
         <v>1.62</v>
@@ -32360,7 +32363,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32566,7 +32569,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32772,7 +32775,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33184,7 +33187,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33802,7 +33805,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -34008,7 +34011,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34214,7 +34217,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34420,7 +34423,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -35038,7 +35041,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35244,7 +35247,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35325,7 +35328,7 @@
         <v>2</v>
       </c>
       <c r="AQ165">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR165">
         <v>1.65</v>
@@ -35656,7 +35659,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36274,7 +36277,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36352,7 +36355,7 @@
         <v>1.1</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ170">
         <v>1.33</v>
@@ -37098,7 +37101,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37304,7 +37307,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37922,7 +37925,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38003,7 +38006,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ178">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR178">
         <v>1.43</v>
@@ -38334,7 +38337,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38746,7 +38749,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38952,7 +38955,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39158,7 +39161,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39570,7 +39573,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39776,7 +39779,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39854,7 +39857,7 @@
         <v>1.27</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ187">
         <v>1.27</v>
@@ -39982,7 +39985,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40188,7 +40191,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -41218,7 +41221,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41630,7 +41633,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41836,7 +41839,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42866,7 +42869,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -42944,7 +42947,7 @@
         <v>2</v>
       </c>
       <c r="AP202">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ202">
         <v>2.14</v>
@@ -43278,7 +43281,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43359,7 +43362,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ204">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR204">
         <v>1.77</v>
@@ -43484,7 +43487,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43896,7 +43899,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44926,7 +44929,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45132,7 +45135,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45338,7 +45341,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45956,7 +45959,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46162,7 +46165,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46368,7 +46371,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q219">
         <v>6</v>
@@ -46446,7 +46449,7 @@
         <v>0.85</v>
       </c>
       <c r="AP219">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ219">
         <v>1</v>
@@ -46574,7 +46577,7 @@
         <v>231</v>
       </c>
       <c r="P220" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46861,7 +46864,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ221">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR221">
         <v>2.2</v>
@@ -46986,7 +46989,7 @@
         <v>233</v>
       </c>
       <c r="P222" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q222">
         <v>4.5</v>
@@ -47192,7 +47195,7 @@
         <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q223">
         <v>3.5</v>
@@ -47604,7 +47607,7 @@
         <v>234</v>
       </c>
       <c r="P225" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q225">
         <v>2.6</v>
@@ -48016,7 +48019,7 @@
         <v>235</v>
       </c>
       <c r="P227" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q227">
         <v>2.6</v>
@@ -48428,7 +48431,7 @@
         <v>236</v>
       </c>
       <c r="P229" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q229">
         <v>8</v>
@@ -49252,7 +49255,7 @@
         <v>182</v>
       </c>
       <c r="P233" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49409,6 +49412,212 @@
       </c>
       <c r="BP233">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7453916</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45752.52083333334</v>
+      </c>
+      <c r="F234">
+        <v>30</v>
+      </c>
+      <c r="G234" t="s">
+        <v>76</v>
+      </c>
+      <c r="H234" t="s">
+        <v>81</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>238</v>
+      </c>
+      <c r="P234" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q234">
+        <v>4.75</v>
+      </c>
+      <c r="R234">
+        <v>2</v>
+      </c>
+      <c r="S234">
+        <v>2.5</v>
+      </c>
+      <c r="T234">
+        <v>1.5</v>
+      </c>
+      <c r="U234">
+        <v>2.5</v>
+      </c>
+      <c r="V234">
+        <v>3.4</v>
+      </c>
+      <c r="W234">
+        <v>1.3</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.06</v>
+      </c>
+      <c r="Z234">
+        <v>3.82</v>
+      </c>
+      <c r="AA234">
+        <v>3.11</v>
+      </c>
+      <c r="AB234">
+        <v>2.06</v>
+      </c>
+      <c r="AC234">
+        <v>1.07</v>
+      </c>
+      <c r="AD234">
+        <v>7.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.4</v>
+      </c>
+      <c r="AF234">
+        <v>2.85</v>
+      </c>
+      <c r="AG234">
+        <v>2.12</v>
+      </c>
+      <c r="AH234">
+        <v>1.64</v>
+      </c>
+      <c r="AI234">
+        <v>2</v>
+      </c>
+      <c r="AJ234">
+        <v>1.73</v>
+      </c>
+      <c r="AK234">
+        <v>1.77</v>
+      </c>
+      <c r="AL234">
+        <v>1.28</v>
+      </c>
+      <c r="AM234">
+        <v>1.25</v>
+      </c>
+      <c r="AN234">
+        <v>1</v>
+      </c>
+      <c r="AO234">
+        <v>0.93</v>
+      </c>
+      <c r="AP234">
+        <v>1.13</v>
+      </c>
+      <c r="AQ234">
+        <v>0.87</v>
+      </c>
+      <c r="AR234">
+        <v>1.19</v>
+      </c>
+      <c r="AS234">
+        <v>1.34</v>
+      </c>
+      <c r="AT234">
+        <v>2.53</v>
+      </c>
+      <c r="AU234">
+        <v>9</v>
+      </c>
+      <c r="AV234">
+        <v>6</v>
+      </c>
+      <c r="AW234">
+        <v>5</v>
+      </c>
+      <c r="AX234">
+        <v>2</v>
+      </c>
+      <c r="AY234">
+        <v>16</v>
+      </c>
+      <c r="AZ234">
+        <v>9</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>8</v>
+      </c>
+      <c r="BC234">
+        <v>12</v>
+      </c>
+      <c r="BD234">
+        <v>2.53</v>
+      </c>
+      <c r="BE234">
+        <v>7.5</v>
+      </c>
+      <c r="BF234">
+        <v>1.75</v>
+      </c>
+      <c r="BG234">
+        <v>1.66</v>
+      </c>
+      <c r="BH234">
+        <v>2.14</v>
+      </c>
+      <c r="BI234">
+        <v>2.11</v>
+      </c>
+      <c r="BJ234">
+        <v>1.68</v>
+      </c>
+      <c r="BK234">
+        <v>2.75</v>
+      </c>
+      <c r="BL234">
+        <v>1.4</v>
+      </c>
+      <c r="BM234">
+        <v>3.78</v>
+      </c>
+      <c r="BN234">
+        <v>1.21</v>
+      </c>
+      <c r="BO234">
+        <v>5.35</v>
+      </c>
+      <c r="BP234">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['39', '90+2']</t>
   </si>
   <si>
+    <t>['2', '9', '11']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1052,6 +1055,12 @@
   </si>
   <si>
     <t>['8', '90+3']</t>
+  </si>
+  <si>
+    <t>['67', '74']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1669,7 +1678,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1747,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2">
         <v>1.29</v>
@@ -1956,7 +1965,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2159,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ4">
         <v>0.27</v>
@@ -2287,7 +2296,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2368,7 +2377,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2699,7 +2708,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2905,7 +2914,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3317,7 +3326,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3395,10 +3404,10 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3523,7 +3532,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3729,7 +3738,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3807,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ12">
         <v>1.4</v>
@@ -4840,7 +4849,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ17">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR17">
         <v>1.59</v>
@@ -5171,7 +5180,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -6073,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ23">
         <v>0.71</v>
@@ -6201,7 +6210,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6819,7 +6828,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7103,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ28">
         <v>1.07</v>
@@ -7309,7 +7318,7 @@
         <v>1.5</v>
       </c>
       <c r="AP29">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ29">
         <v>1.29</v>
@@ -7518,7 +7527,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ30">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7643,7 +7652,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7849,7 +7858,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8136,7 +8145,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ33">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR33">
         <v>1.82</v>
@@ -8261,7 +8270,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -9085,7 +9094,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9163,7 +9172,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
         <v>1.64</v>
@@ -9703,7 +9712,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9909,7 +9918,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9987,7 +9996,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10115,7 +10124,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10321,7 +10330,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10527,7 +10536,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -11145,7 +11154,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11226,7 +11235,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ48">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
         <v>1.07</v>
@@ -11557,7 +11566,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11763,7 +11772,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -11841,7 +11850,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51">
         <v>3</v>
@@ -12871,7 +12880,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ56">
         <v>0.93</v>
@@ -12999,7 +13008,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13205,7 +13214,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13286,7 +13295,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ58">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR58">
         <v>1.68</v>
@@ -13411,7 +13420,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13617,7 +13626,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13695,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ60">
         <v>0.71</v>
@@ -13823,7 +13832,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14235,7 +14244,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14441,7 +14450,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14647,7 +14656,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14853,7 +14862,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15140,7 +15149,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ67">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR67">
         <v>1.33</v>
@@ -15343,7 +15352,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ68">
         <v>0.93</v>
@@ -15471,7 +15480,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15755,7 +15764,7 @@
         <v>1.2</v>
       </c>
       <c r="AP70">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ70">
         <v>1.29</v>
@@ -15883,7 +15892,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16089,7 +16098,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16501,7 +16510,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16913,7 +16922,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -16994,7 +17003,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR76">
         <v>0</v>
@@ -17197,7 +17206,7 @@
         <v>0.2</v>
       </c>
       <c r="AP77">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ77">
         <v>0.87</v>
@@ -17325,7 +17334,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17531,7 +17540,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17612,7 +17621,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ79">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR79">
         <v>1.64</v>
@@ -17815,7 +17824,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80">
         <v>1.33</v>
@@ -17943,7 +17952,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18149,7 +18158,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18355,7 +18364,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18561,7 +18570,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18767,7 +18776,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19179,7 +19188,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19257,7 +19266,7 @@
         <v>0.8</v>
       </c>
       <c r="AP87">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ87">
         <v>0.71</v>
@@ -19591,7 +19600,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -20003,7 +20012,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20287,7 +20296,7 @@
         <v>1.83</v>
       </c>
       <c r="AP92">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ92">
         <v>1.64</v>
@@ -20621,7 +20630,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20702,7 +20711,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ94">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR94">
         <v>1.84</v>
@@ -21111,7 +21120,7 @@
         <v>0.17</v>
       </c>
       <c r="AP96">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96">
         <v>0.27</v>
@@ -21651,7 +21660,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21857,7 +21866,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -21938,7 +21947,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ100">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR100">
         <v>1.66</v>
@@ -22063,7 +22072,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22269,7 +22278,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22475,7 +22484,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22965,7 +22974,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ105">
         <v>0.93</v>
@@ -23171,7 +23180,7 @@
         <v>1.71</v>
       </c>
       <c r="AP106">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ106">
         <v>1.64</v>
@@ -23299,7 +23308,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23380,7 +23389,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ107">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR107">
         <v>1.95</v>
@@ -23711,7 +23720,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -23789,10 +23798,10 @@
         <v>2</v>
       </c>
       <c r="AP109">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ109">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR109">
         <v>1.11</v>
@@ -24123,7 +24132,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24329,7 +24338,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25153,7 +25162,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25359,7 +25368,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25565,7 +25574,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25771,7 +25780,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25977,7 +25986,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26801,7 +26810,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27007,7 +27016,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27213,7 +27222,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27500,7 +27509,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ127">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR127">
         <v>1.18</v>
@@ -27625,7 +27634,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27831,7 +27840,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27909,7 +27918,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28243,7 +28252,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28939,7 +28948,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ134">
         <v>1.27</v>
@@ -29145,7 +29154,7 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29273,7 +29282,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29351,7 +29360,7 @@
         <v>2</v>
       </c>
       <c r="AP136">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ136">
         <v>1.4</v>
@@ -29891,7 +29900,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -29972,7 +29981,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ139">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR139">
         <v>1.32</v>
@@ -30303,7 +30312,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30509,7 +30518,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30715,7 +30724,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -30796,7 +30805,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ143">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR143">
         <v>1.05</v>
@@ -31333,7 +31342,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31539,7 +31548,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31620,7 +31629,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ147">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -31745,7 +31754,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31951,7 +31960,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32235,7 +32244,7 @@
         <v>0.67</v>
       </c>
       <c r="AP150">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ150">
         <v>0.87</v>
@@ -32363,7 +32372,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32569,7 +32578,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32647,7 +32656,7 @@
         <v>3</v>
       </c>
       <c r="AP152">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ152">
         <v>3</v>
@@ -32775,7 +32784,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33187,7 +33196,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33474,7 +33483,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ156">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR156">
         <v>1.72</v>
@@ -33677,7 +33686,7 @@
         <v>0.44</v>
       </c>
       <c r="AP157">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ157">
         <v>0.93</v>
@@ -33805,7 +33814,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -33883,7 +33892,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ158">
         <v>1.33</v>
@@ -34011,7 +34020,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34217,7 +34226,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34423,7 +34432,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -35041,7 +35050,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35247,7 +35256,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35659,7 +35668,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -36149,10 +36158,10 @@
         <v>2</v>
       </c>
       <c r="AP169">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ169">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR169">
         <v>1.61</v>
@@ -36277,7 +36286,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36767,7 +36776,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ172">
         <v>1.27</v>
@@ -36976,7 +36985,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ173">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR173">
         <v>1.77</v>
@@ -37101,7 +37110,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37179,7 +37188,7 @@
         <v>1.1</v>
       </c>
       <c r="AP174">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ174">
         <v>1.07</v>
@@ -37307,7 +37316,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37925,7 +37934,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38212,7 +38221,7 @@
         <v>2</v>
       </c>
       <c r="AQ179">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR179">
         <v>1.67</v>
@@ -38337,7 +38346,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38621,7 +38630,7 @@
         <v>1.82</v>
       </c>
       <c r="AP181">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ181">
         <v>1.4</v>
@@ -38749,7 +38758,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38955,7 +38964,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39161,7 +39170,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39573,7 +39582,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39779,7 +39788,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39985,7 +39994,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40191,7 +40200,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40269,10 +40278,10 @@
         <v>2.09</v>
       </c>
       <c r="AP189">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ189">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR189">
         <v>2.16</v>
@@ -40681,7 +40690,7 @@
         <v>1.27</v>
       </c>
       <c r="AP191">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ191">
         <v>1.33</v>
@@ -41221,7 +41230,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41633,7 +41642,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41839,7 +41848,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -41920,7 +41929,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ197">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR197">
         <v>1.49</v>
@@ -42329,7 +42338,7 @@
         <v>1.25</v>
       </c>
       <c r="AP199">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ199">
         <v>1.07</v>
@@ -42869,7 +42878,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -42950,7 +42959,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ202">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR202">
         <v>1.22</v>
@@ -43153,7 +43162,7 @@
         <v>0.92</v>
       </c>
       <c r="AP203">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -43281,7 +43290,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43487,7 +43496,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43565,7 +43574,7 @@
         <v>1.25</v>
       </c>
       <c r="AP205">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ205">
         <v>1.27</v>
@@ -43899,7 +43908,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -44392,7 +44401,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ209">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR209">
         <v>1.19</v>
@@ -44929,7 +44938,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45135,7 +45144,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45341,7 +45350,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45419,7 +45428,7 @@
         <v>1.15</v>
       </c>
       <c r="AP214">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ214">
         <v>1.27</v>
@@ -45959,7 +45968,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46165,7 +46174,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46243,7 +46252,7 @@
         <v>1.38</v>
       </c>
       <c r="AP218">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ218">
         <v>1.27</v>
@@ -46371,7 +46380,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q219">
         <v>6</v>
@@ -46577,7 +46586,7 @@
         <v>231</v>
       </c>
       <c r="P220" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46861,7 +46870,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ221">
         <v>0.87</v>
@@ -46989,7 +46998,7 @@
         <v>233</v>
       </c>
       <c r="P222" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q222">
         <v>4.5</v>
@@ -47195,7 +47204,7 @@
         <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q223">
         <v>3.5</v>
@@ -47276,7 +47285,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ223">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR223">
         <v>1.65</v>
@@ -47607,7 +47616,7 @@
         <v>234</v>
       </c>
       <c r="P225" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q225">
         <v>2.6</v>
@@ -48019,7 +48028,7 @@
         <v>235</v>
       </c>
       <c r="P227" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q227">
         <v>2.6</v>
@@ -48431,7 +48440,7 @@
         <v>236</v>
       </c>
       <c r="P229" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q229">
         <v>8</v>
@@ -49255,7 +49264,7 @@
         <v>182</v>
       </c>
       <c r="P233" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49618,6 +49627,624 @@
       </c>
       <c r="BP234">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7453912</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F235">
+        <v>30</v>
+      </c>
+      <c r="G235" t="s">
+        <v>70</v>
+      </c>
+      <c r="H235" t="s">
+        <v>83</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>87</v>
+      </c>
+      <c r="P235" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q235">
+        <v>3.24</v>
+      </c>
+      <c r="R235">
+        <v>2.1</v>
+      </c>
+      <c r="S235">
+        <v>3</v>
+      </c>
+      <c r="T235">
+        <v>1.35</v>
+      </c>
+      <c r="U235">
+        <v>2.93</v>
+      </c>
+      <c r="V235">
+        <v>2.58</v>
+      </c>
+      <c r="W235">
+        <v>1.44</v>
+      </c>
+      <c r="X235">
+        <v>6.15</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>3.3</v>
+      </c>
+      <c r="AA235">
+        <v>3.4</v>
+      </c>
+      <c r="AB235">
+        <v>2.05</v>
+      </c>
+      <c r="AC235">
+        <v>1.02</v>
+      </c>
+      <c r="AD235">
+        <v>10</v>
+      </c>
+      <c r="AE235">
+        <v>1.2</v>
+      </c>
+      <c r="AF235">
+        <v>3.68</v>
+      </c>
+      <c r="AG235">
+        <v>1.8</v>
+      </c>
+      <c r="AH235">
+        <v>1.85</v>
+      </c>
+      <c r="AI235">
+        <v>1.59</v>
+      </c>
+      <c r="AJ235">
+        <v>2.15</v>
+      </c>
+      <c r="AK235">
+        <v>1.47</v>
+      </c>
+      <c r="AL235">
+        <v>1.27</v>
+      </c>
+      <c r="AM235">
+        <v>1.42</v>
+      </c>
+      <c r="AN235">
+        <v>1.86</v>
+      </c>
+      <c r="AO235">
+        <v>2.14</v>
+      </c>
+      <c r="AP235">
+        <v>1.73</v>
+      </c>
+      <c r="AQ235">
+        <v>2.2</v>
+      </c>
+      <c r="AR235">
+        <v>1.59</v>
+      </c>
+      <c r="AS235">
+        <v>1.27</v>
+      </c>
+      <c r="AT235">
+        <v>2.86</v>
+      </c>
+      <c r="AU235">
+        <v>-1</v>
+      </c>
+      <c r="AV235">
+        <v>-1</v>
+      </c>
+      <c r="AW235">
+        <v>-1</v>
+      </c>
+      <c r="AX235">
+        <v>-1</v>
+      </c>
+      <c r="AY235">
+        <v>-1</v>
+      </c>
+      <c r="AZ235">
+        <v>-1</v>
+      </c>
+      <c r="BA235">
+        <v>-1</v>
+      </c>
+      <c r="BB235">
+        <v>-1</v>
+      </c>
+      <c r="BC235">
+        <v>-1</v>
+      </c>
+      <c r="BD235">
+        <v>1.91</v>
+      </c>
+      <c r="BE235">
+        <v>7.5</v>
+      </c>
+      <c r="BF235">
+        <v>2.1</v>
+      </c>
+      <c r="BG235">
+        <v>1.34</v>
+      </c>
+      <c r="BH235">
+        <v>2.78</v>
+      </c>
+      <c r="BI235">
+        <v>1.65</v>
+      </c>
+      <c r="BJ235">
+        <v>2.05</v>
+      </c>
+      <c r="BK235">
+        <v>2.08</v>
+      </c>
+      <c r="BL235">
+        <v>1.6</v>
+      </c>
+      <c r="BM235">
+        <v>2.78</v>
+      </c>
+      <c r="BN235">
+        <v>1.34</v>
+      </c>
+      <c r="BO235">
+        <v>3.68</v>
+      </c>
+      <c r="BP235">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7453918</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F236">
+        <v>30</v>
+      </c>
+      <c r="G236" t="s">
+        <v>72</v>
+      </c>
+      <c r="H236" t="s">
+        <v>82</v>
+      </c>
+      <c r="I236">
+        <v>3</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>3</v>
+      </c>
+      <c r="L236">
+        <v>3</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>4</v>
+      </c>
+      <c r="O236" t="s">
+        <v>239</v>
+      </c>
+      <c r="P236" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q236">
+        <v>1.43</v>
+      </c>
+      <c r="R236">
+        <v>2.9</v>
+      </c>
+      <c r="S236">
+        <v>13.5</v>
+      </c>
+      <c r="T236">
+        <v>1.21</v>
+      </c>
+      <c r="U236">
+        <v>3.74</v>
+      </c>
+      <c r="V236">
+        <v>2.05</v>
+      </c>
+      <c r="W236">
+        <v>1.72</v>
+      </c>
+      <c r="X236">
+        <v>4.25</v>
+      </c>
+      <c r="Y236">
+        <v>1.17</v>
+      </c>
+      <c r="Z236">
+        <v>1.13</v>
+      </c>
+      <c r="AA236">
+        <v>9</v>
+      </c>
+      <c r="AB236">
+        <v>19</v>
+      </c>
+      <c r="AC236">
+        <v>1</v>
+      </c>
+      <c r="AD236">
+        <v>16</v>
+      </c>
+      <c r="AE236">
+        <v>1.06</v>
+      </c>
+      <c r="AF236">
+        <v>6</v>
+      </c>
+      <c r="AG236">
+        <v>1.36</v>
+      </c>
+      <c r="AH236">
+        <v>3</v>
+      </c>
+      <c r="AI236">
+        <v>2.32</v>
+      </c>
+      <c r="AJ236">
+        <v>1.51</v>
+      </c>
+      <c r="AK236">
+        <v>1</v>
+      </c>
+      <c r="AL236">
+        <v>1.04</v>
+      </c>
+      <c r="AM236">
+        <v>5.95</v>
+      </c>
+      <c r="AN236">
+        <v>2.71</v>
+      </c>
+      <c r="AO236">
+        <v>1.71</v>
+      </c>
+      <c r="AP236">
+        <v>2.73</v>
+      </c>
+      <c r="AQ236">
+        <v>1.6</v>
+      </c>
+      <c r="AR236">
+        <v>2.21</v>
+      </c>
+      <c r="AS236">
+        <v>1.41</v>
+      </c>
+      <c r="AT236">
+        <v>3.62</v>
+      </c>
+      <c r="AU236">
+        <v>-1</v>
+      </c>
+      <c r="AV236">
+        <v>-1</v>
+      </c>
+      <c r="AW236">
+        <v>-1</v>
+      </c>
+      <c r="AX236">
+        <v>-1</v>
+      </c>
+      <c r="AY236">
+        <v>-1</v>
+      </c>
+      <c r="AZ236">
+        <v>-1</v>
+      </c>
+      <c r="BA236">
+        <v>-1</v>
+      </c>
+      <c r="BB236">
+        <v>-1</v>
+      </c>
+      <c r="BC236">
+        <v>-1</v>
+      </c>
+      <c r="BD236">
+        <v>1.08</v>
+      </c>
+      <c r="BE236">
+        <v>13</v>
+      </c>
+      <c r="BF236">
+        <v>9</v>
+      </c>
+      <c r="BG236">
+        <v>1.27</v>
+      </c>
+      <c r="BH236">
+        <v>3.14</v>
+      </c>
+      <c r="BI236">
+        <v>1.51</v>
+      </c>
+      <c r="BJ236">
+        <v>2.26</v>
+      </c>
+      <c r="BK236">
+        <v>1.98</v>
+      </c>
+      <c r="BL236">
+        <v>1.82</v>
+      </c>
+      <c r="BM236">
+        <v>2.43</v>
+      </c>
+      <c r="BN236">
+        <v>1.44</v>
+      </c>
+      <c r="BO236">
+        <v>3.34</v>
+      </c>
+      <c r="BP236">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7453911</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45753.60416666666</v>
+      </c>
+      <c r="F237">
+        <v>30</v>
+      </c>
+      <c r="G237" t="s">
+        <v>78</v>
+      </c>
+      <c r="H237" t="s">
+        <v>71</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237" t="s">
+        <v>87</v>
+      </c>
+      <c r="P237" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q237">
+        <v>4.25</v>
+      </c>
+      <c r="R237">
+        <v>2.04</v>
+      </c>
+      <c r="S237">
+        <v>2.56</v>
+      </c>
+      <c r="T237">
+        <v>1.41</v>
+      </c>
+      <c r="U237">
+        <v>2.69</v>
+      </c>
+      <c r="V237">
+        <v>2.88</v>
+      </c>
+      <c r="W237">
+        <v>1.36</v>
+      </c>
+      <c r="X237">
+        <v>6.75</v>
+      </c>
+      <c r="Y237">
+        <v>1.04</v>
+      </c>
+      <c r="Z237">
+        <v>3.7</v>
+      </c>
+      <c r="AA237">
+        <v>3.3</v>
+      </c>
+      <c r="AB237">
+        <v>1.95</v>
+      </c>
+      <c r="AC237">
+        <v>1.02</v>
+      </c>
+      <c r="AD237">
+        <v>8.1</v>
+      </c>
+      <c r="AE237">
+        <v>1.28</v>
+      </c>
+      <c r="AF237">
+        <v>3.08</v>
+      </c>
+      <c r="AG237">
+        <v>1.91</v>
+      </c>
+      <c r="AH237">
+        <v>1.73</v>
+      </c>
+      <c r="AI237">
+        <v>1.77</v>
+      </c>
+      <c r="AJ237">
+        <v>1.89</v>
+      </c>
+      <c r="AK237">
+        <v>1.72</v>
+      </c>
+      <c r="AL237">
+        <v>1.28</v>
+      </c>
+      <c r="AM237">
+        <v>1.24</v>
+      </c>
+      <c r="AN237">
+        <v>0.79</v>
+      </c>
+      <c r="AO237">
+        <v>0.93</v>
+      </c>
+      <c r="AP237">
+        <v>0.8</v>
+      </c>
+      <c r="AQ237">
+        <v>0.93</v>
+      </c>
+      <c r="AR237">
+        <v>1.27</v>
+      </c>
+      <c r="AS237">
+        <v>1.17</v>
+      </c>
+      <c r="AT237">
+        <v>2.44</v>
+      </c>
+      <c r="AU237">
+        <v>-1</v>
+      </c>
+      <c r="AV237">
+        <v>-1</v>
+      </c>
+      <c r="AW237">
+        <v>-1</v>
+      </c>
+      <c r="AX237">
+        <v>-1</v>
+      </c>
+      <c r="AY237">
+        <v>-1</v>
+      </c>
+      <c r="AZ237">
+        <v>-1</v>
+      </c>
+      <c r="BA237">
+        <v>-1</v>
+      </c>
+      <c r="BB237">
+        <v>-1</v>
+      </c>
+      <c r="BC237">
+        <v>-1</v>
+      </c>
+      <c r="BD237">
+        <v>2.2</v>
+      </c>
+      <c r="BE237">
+        <v>7.5</v>
+      </c>
+      <c r="BF237">
+        <v>1.91</v>
+      </c>
+      <c r="BG237">
+        <v>1.37</v>
+      </c>
+      <c r="BH237">
+        <v>2.66</v>
+      </c>
+      <c r="BI237">
+        <v>1.7</v>
+      </c>
+      <c r="BJ237">
+        <v>1.98</v>
+      </c>
+      <c r="BK237">
+        <v>2.15</v>
+      </c>
+      <c r="BL237">
+        <v>1.56</v>
+      </c>
+      <c r="BM237">
+        <v>2.92</v>
+      </c>
+      <c r="BN237">
+        <v>1.31</v>
+      </c>
+      <c r="BO237">
+        <v>3.9</v>
+      </c>
+      <c r="BP237">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="351">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['2', '9', '11']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['3', '15', '45+3']</t>
   </si>
   <si>
@@ -1061,6 +1064,9 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['38', '76']</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP237"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1684,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1759,7 +1765,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2296,7 +2302,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2580,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6">
         <v>0.71</v>
@@ -2708,7 +2714,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2914,7 +2920,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3198,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3326,7 +3332,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3532,7 +3538,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3738,7 +3744,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4643,7 +4649,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR16">
         <v>1.02</v>
@@ -5180,7 +5186,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5464,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ20">
         <v>0.87</v>
@@ -5673,7 +5679,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5876,7 +5882,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ22">
         <v>1.64</v>
@@ -6210,7 +6216,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6828,7 +6834,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7321,7 +7327,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ29">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR29">
         <v>0.53</v>
@@ -7652,7 +7658,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7858,7 +7864,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -7936,7 +7942,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ32">
         <v>3</v>
@@ -8142,7 +8148,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ33">
         <v>1.6</v>
@@ -8270,7 +8276,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8969,7 +8975,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>1.6</v>
@@ -9094,7 +9100,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9587,7 +9593,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR40">
         <v>1.91</v>
@@ -9712,7 +9718,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9918,7 +9924,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9999,7 +10005,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR42">
         <v>0.6</v>
@@ -10124,7 +10130,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10330,7 +10336,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10536,7 +10542,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10820,7 +10826,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ46">
         <v>0.93</v>
@@ -11154,7 +11160,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11566,7 +11572,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11644,7 +11650,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ50">
         <v>1.4</v>
@@ -11772,7 +11778,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12265,7 +12271,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR53">
         <v>1.1</v>
@@ -12471,7 +12477,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ54">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR54">
         <v>1.46</v>
@@ -13008,7 +13014,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13214,7 +13220,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13420,7 +13426,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13626,7 +13632,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13832,7 +13838,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14116,7 +14122,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
         <v>0.27</v>
@@ -14244,7 +14250,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14322,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ63">
         <v>1.07</v>
@@ -14450,7 +14456,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14656,7 +14662,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14862,7 +14868,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15480,7 +15486,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15767,7 +15773,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ70">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR70">
         <v>2.49</v>
@@ -15892,7 +15898,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15973,7 +15979,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR71">
         <v>1.63</v>
@@ -16098,7 +16104,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16176,7 +16182,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ72">
         <v>1.27</v>
@@ -16510,7 +16516,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16922,7 +16928,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17334,7 +17340,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17540,7 +17546,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17952,7 +17958,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18158,7 +18164,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18364,7 +18370,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18570,7 +18576,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18776,7 +18782,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19060,7 +19066,7 @@
         <v>0.2</v>
       </c>
       <c r="AP86">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ86">
         <v>0.27</v>
@@ -19188,7 +19194,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19472,7 +19478,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ88">
         <v>0.93</v>
@@ -19600,7 +19606,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -19678,7 +19684,7 @@
         <v>1.2</v>
       </c>
       <c r="AP89">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ89">
         <v>1.27</v>
@@ -20012,7 +20018,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20093,7 +20099,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ91">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20505,7 +20511,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR93">
         <v>0</v>
@@ -20630,7 +20636,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -21660,7 +21666,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21866,7 +21872,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -22072,7 +22078,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22278,7 +22284,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22484,7 +22490,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22771,7 +22777,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR104">
         <v>1.79</v>
@@ -23308,7 +23314,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23386,7 +23392,7 @@
         <v>2.17</v>
       </c>
       <c r="AP107">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ107">
         <v>2.2</v>
@@ -23720,7 +23726,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24004,10 +24010,10 @@
         <v>1.29</v>
       </c>
       <c r="AP110">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR110">
         <v>1.53</v>
@@ -24132,7 +24138,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24338,7 +24344,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25162,7 +25168,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25368,7 +25374,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25574,7 +25580,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25780,7 +25786,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25986,7 +25992,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26810,7 +26816,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27016,7 +27022,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27222,7 +27228,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27300,7 +27306,7 @@
         <v>0.38</v>
       </c>
       <c r="AP126">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ126">
         <v>0.87</v>
@@ -27634,7 +27640,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27715,7 +27721,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ128">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR128">
         <v>1.28</v>
@@ -27840,7 +27846,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -27921,7 +27927,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR129">
         <v>1.62</v>
@@ -28252,7 +28258,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28536,7 +28542,7 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ132">
         <v>0.71</v>
@@ -29282,7 +29288,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29900,7 +29906,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30312,7 +30318,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30518,7 +30524,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30724,7 +30730,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31342,7 +31348,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31548,7 +31554,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31626,7 +31632,7 @@
         <v>1.89</v>
       </c>
       <c r="AP147">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ147">
         <v>1.6</v>
@@ -31754,7 +31760,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31960,7 +31966,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32038,7 +32044,7 @@
         <v>1.67</v>
       </c>
       <c r="AP149">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ149">
         <v>1.64</v>
@@ -32372,7 +32378,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32453,7 +32459,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR151">
         <v>1.68</v>
@@ -32578,7 +32584,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32784,7 +32790,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33071,7 +33077,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ154">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -33196,7 +33202,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33814,7 +33820,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -34020,7 +34026,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34226,7 +34232,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34432,7 +34438,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34922,7 +34928,7 @@
         <v>1.9</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ163">
         <v>1.4</v>
@@ -35050,7 +35056,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35256,7 +35262,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35668,7 +35674,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35746,7 +35752,7 @@
         <v>3</v>
       </c>
       <c r="AP167">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ167">
         <v>3</v>
@@ -36286,7 +36292,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -37110,7 +37116,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37316,7 +37322,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37603,7 +37609,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR176">
         <v>1.74</v>
@@ -37809,7 +37815,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ177">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR177">
         <v>1.08</v>
@@ -37934,7 +37940,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38346,7 +38352,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38758,7 +38764,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38964,7 +38970,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39042,7 +39048,7 @@
         <v>0.64</v>
       </c>
       <c r="AP183">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ183">
         <v>0.93</v>
@@ -39170,7 +39176,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39248,7 +39254,7 @@
         <v>1.27</v>
       </c>
       <c r="AP184">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ184">
         <v>1.07</v>
@@ -39582,7 +39588,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39788,7 +39794,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -39994,7 +40000,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40075,7 +40081,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR188">
         <v>1.79</v>
@@ -40200,7 +40206,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -41230,7 +41236,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41642,7 +41648,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41848,7 +41854,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42544,7 +42550,7 @@
         <v>1.42</v>
       </c>
       <c r="AP200">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ200">
         <v>1.33</v>
@@ -42878,7 +42884,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43165,7 +43171,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR203">
         <v>2.16</v>
@@ -43290,7 +43296,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43496,7 +43502,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43908,7 +43914,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -43989,7 +43995,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR207">
         <v>1.13</v>
@@ -44192,7 +44198,7 @@
         <v>1.42</v>
       </c>
       <c r="AP208">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ208">
         <v>1.27</v>
@@ -44938,7 +44944,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45144,7 +45150,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45350,7 +45356,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45968,7 +45974,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46049,7 +46055,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ217">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46174,7 +46180,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46380,7 +46386,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q219">
         <v>6</v>
@@ -46461,7 +46467,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ219">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR219">
         <v>1.23</v>
@@ -46586,7 +46592,7 @@
         <v>231</v>
       </c>
       <c r="P220" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46664,7 +46670,7 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ220">
         <v>0.93</v>
@@ -46998,7 +47004,7 @@
         <v>233</v>
       </c>
       <c r="P222" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q222">
         <v>4.5</v>
@@ -47204,7 +47210,7 @@
         <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q223">
         <v>3.5</v>
@@ -47282,7 +47288,7 @@
         <v>2.08</v>
       </c>
       <c r="AP223">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ223">
         <v>2.2</v>
@@ -47616,7 +47622,7 @@
         <v>234</v>
       </c>
       <c r="P225" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q225">
         <v>2.6</v>
@@ -47697,7 +47703,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ225">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR225">
         <v>1.67</v>
@@ -48028,7 +48034,7 @@
         <v>235</v>
       </c>
       <c r="P227" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q227">
         <v>2.6</v>
@@ -48440,7 +48446,7 @@
         <v>236</v>
       </c>
       <c r="P229" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q229">
         <v>8</v>
@@ -49264,7 +49270,7 @@
         <v>182</v>
       </c>
       <c r="P233" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49676,7 +49682,7 @@
         <v>87</v>
       </c>
       <c r="P235" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q235">
         <v>3.24</v>
@@ -49769,31 +49775,31 @@
         <v>2.86</v>
       </c>
       <c r="AU235">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV235">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW235">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX235">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY235">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ235">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA235">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB235">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC235">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD235">
         <v>1.91</v>
@@ -49882,7 +49888,7 @@
         <v>239</v>
       </c>
       <c r="P236" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q236">
         <v>1.43</v>
@@ -49975,31 +49981,31 @@
         <v>3.62</v>
       </c>
       <c r="AU236">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AV236">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW236">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AX236">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY236">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AZ236">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BA236">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB236">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC236">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD236">
         <v>1.08</v>
@@ -50181,31 +50187,31 @@
         <v>2.44</v>
       </c>
       <c r="AU237">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV237">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW237">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AX237">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY237">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AZ237">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA237">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB237">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC237">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD237">
         <v>2.2</v>
@@ -50245,6 +50251,418 @@
       </c>
       <c r="BP237">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7453914</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45754.54166666666</v>
+      </c>
+      <c r="F238">
+        <v>30</v>
+      </c>
+      <c r="G238" t="s">
+        <v>74</v>
+      </c>
+      <c r="H238" t="s">
+        <v>84</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>2</v>
+      </c>
+      <c r="N238">
+        <v>2</v>
+      </c>
+      <c r="O238" t="s">
+        <v>87</v>
+      </c>
+      <c r="P238" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q238">
+        <v>3</v>
+      </c>
+      <c r="R238">
+        <v>2.05</v>
+      </c>
+      <c r="S238">
+        <v>3.4</v>
+      </c>
+      <c r="T238">
+        <v>1.44</v>
+      </c>
+      <c r="U238">
+        <v>2.63</v>
+      </c>
+      <c r="V238">
+        <v>3.25</v>
+      </c>
+      <c r="W238">
+        <v>1.33</v>
+      </c>
+      <c r="X238">
+        <v>7.5</v>
+      </c>
+      <c r="Y238">
+        <v>1.07</v>
+      </c>
+      <c r="Z238">
+        <v>1.9</v>
+      </c>
+      <c r="AA238">
+        <v>3.29</v>
+      </c>
+      <c r="AB238">
+        <v>4.2</v>
+      </c>
+      <c r="AC238">
+        <v>1.02</v>
+      </c>
+      <c r="AD238">
+        <v>7.7</v>
+      </c>
+      <c r="AE238">
+        <v>1.29</v>
+      </c>
+      <c r="AF238">
+        <v>3.04</v>
+      </c>
+      <c r="AG238">
+        <v>1.85</v>
+      </c>
+      <c r="AH238">
+        <v>1.85</v>
+      </c>
+      <c r="AI238">
+        <v>1.8</v>
+      </c>
+      <c r="AJ238">
+        <v>1.91</v>
+      </c>
+      <c r="AK238">
+        <v>1.26</v>
+      </c>
+      <c r="AL238">
+        <v>1.29</v>
+      </c>
+      <c r="AM238">
+        <v>1.67</v>
+      </c>
+      <c r="AN238">
+        <v>1.36</v>
+      </c>
+      <c r="AO238">
+        <v>1</v>
+      </c>
+      <c r="AP238">
+        <v>1.27</v>
+      </c>
+      <c r="AQ238">
+        <v>1.13</v>
+      </c>
+      <c r="AR238">
+        <v>1.63</v>
+      </c>
+      <c r="AS238">
+        <v>1.51</v>
+      </c>
+      <c r="AT238">
+        <v>3.14</v>
+      </c>
+      <c r="AU238">
+        <v>3</v>
+      </c>
+      <c r="AV238">
+        <v>6</v>
+      </c>
+      <c r="AW238">
+        <v>8</v>
+      </c>
+      <c r="AX238">
+        <v>4</v>
+      </c>
+      <c r="AY238">
+        <v>15</v>
+      </c>
+      <c r="AZ238">
+        <v>12</v>
+      </c>
+      <c r="BA238">
+        <v>6</v>
+      </c>
+      <c r="BB238">
+        <v>4</v>
+      </c>
+      <c r="BC238">
+        <v>10</v>
+      </c>
+      <c r="BD238">
+        <v>1.64</v>
+      </c>
+      <c r="BE238">
+        <v>8</v>
+      </c>
+      <c r="BF238">
+        <v>2.67</v>
+      </c>
+      <c r="BG238">
+        <v>1.36</v>
+      </c>
+      <c r="BH238">
+        <v>2.7</v>
+      </c>
+      <c r="BI238">
+        <v>1.68</v>
+      </c>
+      <c r="BJ238">
+        <v>2.01</v>
+      </c>
+      <c r="BK238">
+        <v>2.14</v>
+      </c>
+      <c r="BL238">
+        <v>1.57</v>
+      </c>
+      <c r="BM238">
+        <v>2.88</v>
+      </c>
+      <c r="BN238">
+        <v>1.32</v>
+      </c>
+      <c r="BO238">
+        <v>3.85</v>
+      </c>
+      <c r="BP238">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7453913</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45754.54166666666</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="s">
+        <v>77</v>
+      </c>
+      <c r="H239" t="s">
+        <v>79</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
+        <v>240</v>
+      </c>
+      <c r="P239" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q239">
+        <v>1.91</v>
+      </c>
+      <c r="R239">
+        <v>2.38</v>
+      </c>
+      <c r="S239">
+        <v>6</v>
+      </c>
+      <c r="T239">
+        <v>1.33</v>
+      </c>
+      <c r="U239">
+        <v>3.25</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>6</v>
+      </c>
+      <c r="Y239">
+        <v>1.11</v>
+      </c>
+      <c r="Z239">
+        <v>1.55</v>
+      </c>
+      <c r="AA239">
+        <v>3.76</v>
+      </c>
+      <c r="AB239">
+        <v>6.3</v>
+      </c>
+      <c r="AC239">
+        <v>1.01</v>
+      </c>
+      <c r="AD239">
+        <v>12.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.18</v>
+      </c>
+      <c r="AF239">
+        <v>3.86</v>
+      </c>
+      <c r="AG239">
+        <v>1.8</v>
+      </c>
+      <c r="AH239">
+        <v>1.9</v>
+      </c>
+      <c r="AI239">
+        <v>1.91</v>
+      </c>
+      <c r="AJ239">
+        <v>1.8</v>
+      </c>
+      <c r="AK239">
+        <v>1.07</v>
+      </c>
+      <c r="AL239">
+        <v>1.16</v>
+      </c>
+      <c r="AM239">
+        <v>2.64</v>
+      </c>
+      <c r="AN239">
+        <v>1.36</v>
+      </c>
+      <c r="AO239">
+        <v>1.29</v>
+      </c>
+      <c r="AP239">
+        <v>1.47</v>
+      </c>
+      <c r="AQ239">
+        <v>1.2</v>
+      </c>
+      <c r="AR239">
+        <v>1.92</v>
+      </c>
+      <c r="AS239">
+        <v>1.19</v>
+      </c>
+      <c r="AT239">
+        <v>3.11</v>
+      </c>
+      <c r="AU239">
+        <v>4</v>
+      </c>
+      <c r="AV239">
+        <v>3</v>
+      </c>
+      <c r="AW239">
+        <v>8</v>
+      </c>
+      <c r="AX239">
+        <v>4</v>
+      </c>
+      <c r="AY239">
+        <v>17</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>3</v>
+      </c>
+      <c r="BB239">
+        <v>4</v>
+      </c>
+      <c r="BC239">
+        <v>7</v>
+      </c>
+      <c r="BD239">
+        <v>1.26</v>
+      </c>
+      <c r="BE239">
+        <v>9.5</v>
+      </c>
+      <c r="BF239">
+        <v>4.66</v>
+      </c>
+      <c r="BG239">
+        <v>1.36</v>
+      </c>
+      <c r="BH239">
+        <v>2.7</v>
+      </c>
+      <c r="BI239">
+        <v>1.67</v>
+      </c>
+      <c r="BJ239">
+        <v>2.03</v>
+      </c>
+      <c r="BK239">
+        <v>2.1</v>
+      </c>
+      <c r="BL239">
+        <v>1.59</v>
+      </c>
+      <c r="BM239">
+        <v>2.83</v>
+      </c>
+      <c r="BN239">
+        <v>1.33</v>
+      </c>
+      <c r="BO239">
+        <v>3.75</v>
+      </c>
+      <c r="BP239">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="354">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['2', '9', '11']</t>
   </si>
   <si>
+    <t>['14', '60', '73']</t>
+  </si>
+  <si>
     <t>['32']</t>
   </si>
   <si>
@@ -1067,6 +1070,12 @@
   </si>
   <si>
     <t>['38', '76']</t>
+  </si>
+  <si>
+    <t>['45+7', '68', '90+4']</t>
+  </si>
+  <si>
+    <t>['21', '33', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP239"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1684,7 +1693,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2302,7 +2311,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2380,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>1.6</v>
@@ -2589,7 +2598,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ6">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2714,7 +2723,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2792,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
         <v>0.87</v>
@@ -2920,7 +2929,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q8">
         <v>5.5</v>
@@ -3001,7 +3010,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3332,7 +3341,7 @@
         <v>87</v>
       </c>
       <c r="P10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -3538,7 +3547,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>2.75</v>
@@ -3744,7 +3753,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -4852,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ17">
         <v>1.6</v>
@@ -5058,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18">
         <v>0.27</v>
@@ -5186,7 +5195,7 @@
         <v>87</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19">
         <v>15</v>
@@ -5885,7 +5894,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ22">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6091,7 +6100,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
         <v>1.76</v>
@@ -6216,7 +6225,7 @@
         <v>103</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q24">
         <v>3.75</v>
@@ -6834,7 +6843,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -6912,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ27">
         <v>0.93</v>
@@ -7658,7 +7667,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q31">
         <v>3.2</v>
@@ -7864,7 +7873,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -8276,7 +8285,7 @@
         <v>87</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -8354,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>1.4</v>
@@ -9100,7 +9109,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9181,7 +9190,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR38">
         <v>1.63</v>
@@ -9384,7 +9393,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
         <v>1.33</v>
@@ -9718,7 +9727,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9924,7 +9933,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10130,7 +10139,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -10336,7 +10345,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -10542,7 +10551,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10623,7 +10632,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -11032,7 +11041,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ47">
         <v>0.27</v>
@@ -11160,7 +11169,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11572,7 +11581,7 @@
         <v>125</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11778,7 +11787,7 @@
         <v>87</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q51">
         <v>7.5</v>
@@ -12065,7 +12074,7 @@
         <v>2</v>
       </c>
       <c r="AQ52">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR52">
         <v>1.32</v>
@@ -12680,7 +12689,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ55">
         <v>1.27</v>
@@ -13014,7 +13023,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13092,7 +13101,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>1.33</v>
@@ -13220,7 +13229,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13426,7 +13435,7 @@
         <v>132</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>5</v>
@@ -13632,7 +13641,7 @@
         <v>87</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q60">
         <v>4</v>
@@ -13713,7 +13722,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ60">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR60">
         <v>0.73</v>
@@ -13838,7 +13847,7 @@
         <v>87</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>3</v>
@@ -14250,7 +14259,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14456,7 +14465,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -14662,7 +14671,7 @@
         <v>87</v>
       </c>
       <c r="P65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q65">
         <v>3.75</v>
@@ -14743,7 +14752,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR65">
         <v>1.31</v>
@@ -14868,7 +14877,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15486,7 +15495,7 @@
         <v>87</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>4.33</v>
@@ -15898,7 +15907,7 @@
         <v>139</v>
       </c>
       <c r="P71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16104,7 +16113,7 @@
         <v>140</v>
       </c>
       <c r="P72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16388,7 +16397,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ73">
         <v>1.27</v>
@@ -16516,7 +16525,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>1.95</v>
@@ -16597,7 +16606,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ74">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR74">
         <v>1.34</v>
@@ -16928,7 +16937,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -17006,7 +17015,7 @@
         <v>1.75</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ76">
         <v>2.2</v>
@@ -17340,7 +17349,7 @@
         <v>87</v>
       </c>
       <c r="P78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q78">
         <v>2.38</v>
@@ -17546,7 +17555,7 @@
         <v>145</v>
       </c>
       <c r="P79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
@@ -17958,7 +17967,7 @@
         <v>135</v>
       </c>
       <c r="P81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -18164,7 +18173,7 @@
         <v>146</v>
       </c>
       <c r="P82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q82">
         <v>1.73</v>
@@ -18370,7 +18379,7 @@
         <v>147</v>
       </c>
       <c r="P83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q83">
         <v>3.1</v>
@@ -18576,7 +18585,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q84">
         <v>8</v>
@@ -18782,7 +18791,7 @@
         <v>87</v>
       </c>
       <c r="P85" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18863,7 +18872,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ85">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>1.12</v>
@@ -19194,7 +19203,7 @@
         <v>150</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>1.36</v>
@@ -19275,7 +19284,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ87">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
         <v>2.4</v>
@@ -19606,7 +19615,7 @@
         <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>2.2</v>
@@ -20018,7 +20027,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>3.2</v>
@@ -20305,7 +20314,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ92">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20508,7 +20517,7 @@
         <v>0.67</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ93">
         <v>1.13</v>
@@ -20636,7 +20645,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94">
         <v>3.6</v>
@@ -20714,7 +20723,7 @@
         <v>2</v>
       </c>
       <c r="AP94">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
         <v>2.2</v>
@@ -21666,7 +21675,7 @@
         <v>158</v>
       </c>
       <c r="P99" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q99">
         <v>13</v>
@@ -21872,7 +21881,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q100">
         <v>2.38</v>
@@ -22078,7 +22087,7 @@
         <v>87</v>
       </c>
       <c r="P101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q101">
         <v>5.5</v>
@@ -22284,7 +22293,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -22490,7 +22499,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -22571,7 +22580,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR103">
         <v>1.2</v>
@@ -22774,7 +22783,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ104">
         <v>1.13</v>
@@ -23189,7 +23198,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ106">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR106">
         <v>2.08</v>
@@ -23314,7 +23323,7 @@
         <v>165</v>
       </c>
       <c r="P107" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23598,7 +23607,7 @@
         <v>0.29</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ108">
         <v>0.87</v>
@@ -23726,7 +23735,7 @@
         <v>87</v>
       </c>
       <c r="P109" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q109">
         <v>6</v>
@@ -24138,7 +24147,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24344,7 +24353,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q112">
         <v>4</v>
@@ -25168,7 +25177,7 @@
         <v>170</v>
       </c>
       <c r="P116" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q116">
         <v>2.05</v>
@@ -25374,7 +25383,7 @@
         <v>171</v>
       </c>
       <c r="P117" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>4</v>
@@ -25580,7 +25589,7 @@
         <v>87</v>
       </c>
       <c r="P118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q118">
         <v>7</v>
@@ -25786,7 +25795,7 @@
         <v>172</v>
       </c>
       <c r="P119" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q119">
         <v>3.25</v>
@@ -25992,7 +26001,7 @@
         <v>173</v>
       </c>
       <c r="P120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q120">
         <v>3.15</v>
@@ -26816,7 +26825,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q124">
         <v>3.25</v>
@@ -27022,7 +27031,7 @@
         <v>87</v>
       </c>
       <c r="P125" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q125">
         <v>3.85</v>
@@ -27100,10 +27109,10 @@
         <v>1.5</v>
       </c>
       <c r="AP125">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ125">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -27228,7 +27237,7 @@
         <v>110</v>
       </c>
       <c r="P126" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>1.77</v>
@@ -27640,7 +27649,7 @@
         <v>119</v>
       </c>
       <c r="P128" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27846,7 +27855,7 @@
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q129">
         <v>2.2</v>
@@ -28258,7 +28267,7 @@
         <v>87</v>
       </c>
       <c r="P131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -28336,7 +28345,7 @@
         <v>3</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ131">
         <v>3</v>
@@ -28545,7 +28554,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ132">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR132">
         <v>1.95</v>
@@ -28751,7 +28760,7 @@
         <v>2</v>
       </c>
       <c r="AQ133">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -29288,7 +29297,7 @@
         <v>182</v>
       </c>
       <c r="P136" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -29906,7 +29915,7 @@
         <v>87</v>
       </c>
       <c r="P139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q139">
         <v>5.5</v>
@@ -30318,7 +30327,7 @@
         <v>184</v>
       </c>
       <c r="P141" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q141">
         <v>2.4</v>
@@ -30524,7 +30533,7 @@
         <v>148</v>
       </c>
       <c r="P142" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30730,7 +30739,7 @@
         <v>185</v>
       </c>
       <c r="P143" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q143">
         <v>5.5</v>
@@ -31348,7 +31357,7 @@
         <v>188</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31429,7 +31438,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ146">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31554,7 +31563,7 @@
         <v>87</v>
       </c>
       <c r="P147" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31760,7 +31769,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q148">
         <v>8.5</v>
@@ -31838,7 +31847,7 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ148">
         <v>3</v>
@@ -31966,7 +31975,7 @@
         <v>190</v>
       </c>
       <c r="P149" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q149">
         <v>2.88</v>
@@ -32047,7 +32056,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ149">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR149">
         <v>2.02</v>
@@ -32378,7 +32387,7 @@
         <v>192</v>
       </c>
       <c r="P151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q151">
         <v>1.83</v>
@@ -32584,7 +32593,7 @@
         <v>87</v>
       </c>
       <c r="P152" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q152">
         <v>13</v>
@@ -32790,7 +32799,7 @@
         <v>92</v>
       </c>
       <c r="P153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -32868,7 +32877,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ153">
         <v>1.07</v>
@@ -33202,7 +33211,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>2.38</v>
@@ -33820,7 +33829,7 @@
         <v>196</v>
       </c>
       <c r="P158" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>1.53</v>
@@ -34026,7 +34035,7 @@
         <v>87</v>
       </c>
       <c r="P159" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34232,7 +34241,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q160">
         <v>3.25</v>
@@ -34438,7 +34447,7 @@
         <v>87</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q161">
         <v>4</v>
@@ -34725,7 +34734,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ162">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR162">
         <v>1.35</v>
@@ -35056,7 +35065,7 @@
         <v>199</v>
       </c>
       <c r="P164" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q164">
         <v>2.1</v>
@@ -35134,7 +35143,7 @@
         <v>0.4</v>
       </c>
       <c r="AP164">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ164">
         <v>0.93</v>
@@ -35262,7 +35271,7 @@
         <v>200</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q165">
         <v>1.8</v>
@@ -35674,7 +35683,7 @@
         <v>97</v>
       </c>
       <c r="P167" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q167">
         <v>6.5</v>
@@ -35961,7 +35970,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ168">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36292,7 +36301,7 @@
         <v>87</v>
       </c>
       <c r="P170" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q170">
         <v>3.75</v>
@@ -36576,7 +36585,7 @@
         <v>1.5</v>
       </c>
       <c r="AP171">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ171">
         <v>1.27</v>
@@ -37116,7 +37125,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q174">
         <v>3.4</v>
@@ -37322,7 +37331,7 @@
         <v>87</v>
       </c>
       <c r="P175" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q175">
         <v>2.38</v>
@@ -37940,7 +37949,7 @@
         <v>206</v>
       </c>
       <c r="P178" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>2.75</v>
@@ -38352,7 +38361,7 @@
         <v>87</v>
       </c>
       <c r="P180" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q180">
         <v>13</v>
@@ -38764,7 +38773,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q182">
         <v>1.83</v>
@@ -38970,7 +38979,7 @@
         <v>106</v>
       </c>
       <c r="P183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q183">
         <v>1.91</v>
@@ -39176,7 +39185,7 @@
         <v>189</v>
       </c>
       <c r="P184" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39463,7 +39472,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ185">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39588,7 +39597,7 @@
         <v>208</v>
       </c>
       <c r="P186" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q186">
         <v>2.88</v>
@@ -39669,7 +39678,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ186">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR186">
         <v>1.05</v>
@@ -39794,7 +39803,7 @@
         <v>87</v>
       </c>
       <c r="P187" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q187">
         <v>4.75</v>
@@ -40000,7 +40009,7 @@
         <v>87</v>
       </c>
       <c r="P188" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q188">
         <v>2</v>
@@ -40206,7 +40215,7 @@
         <v>209</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q189">
         <v>1.73</v>
@@ -40490,7 +40499,7 @@
         <v>1.18</v>
       </c>
       <c r="AP190">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ190">
         <v>0.93</v>
@@ -40902,7 +40911,7 @@
         <v>1.36</v>
       </c>
       <c r="AP192">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ192">
         <v>1.27</v>
@@ -41236,7 +41245,7 @@
         <v>212</v>
       </c>
       <c r="P194" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q194">
         <v>9.4</v>
@@ -41648,7 +41657,7 @@
         <v>214</v>
       </c>
       <c r="P196" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q196">
         <v>3.85</v>
@@ -41729,7 +41738,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ196">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR196">
         <v>1.72</v>
@@ -41854,7 +41863,7 @@
         <v>173</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q197">
         <v>3.25</v>
@@ -42759,7 +42768,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ201">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR201">
         <v>1.57</v>
@@ -42884,7 +42893,7 @@
         <v>119</v>
       </c>
       <c r="P202" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q202">
         <v>7</v>
@@ -43296,7 +43305,7 @@
         <v>219</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q204">
         <v>1.85</v>
@@ -43502,7 +43511,7 @@
         <v>220</v>
       </c>
       <c r="P205" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q205">
         <v>5.5</v>
@@ -43786,7 +43795,7 @@
         <v>1.08</v>
       </c>
       <c r="AP206">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ206">
         <v>0.93</v>
@@ -43914,7 +43923,7 @@
         <v>152</v>
       </c>
       <c r="P207" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -43992,7 +44001,7 @@
         <v>1.27</v>
       </c>
       <c r="AP207">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ207">
         <v>1.2</v>
@@ -44944,7 +44953,7 @@
         <v>87</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q212">
         <v>9.5</v>
@@ -45150,7 +45159,7 @@
         <v>225</v>
       </c>
       <c r="P213" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q213">
         <v>1.8</v>
@@ -45356,7 +45365,7 @@
         <v>226</v>
       </c>
       <c r="P214" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q214">
         <v>2.63</v>
@@ -45974,7 +45983,7 @@
         <v>189</v>
       </c>
       <c r="P217" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q217">
         <v>3</v>
@@ -46180,7 +46189,7 @@
         <v>229</v>
       </c>
       <c r="P218" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q218">
         <v>4.33</v>
@@ -46386,7 +46395,7 @@
         <v>230</v>
       </c>
       <c r="P219" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q219">
         <v>6</v>
@@ -46592,7 +46601,7 @@
         <v>231</v>
       </c>
       <c r="P220" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47004,7 +47013,7 @@
         <v>233</v>
       </c>
       <c r="P222" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q222">
         <v>4.5</v>
@@ -47085,7 +47094,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ222">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR222">
         <v>1.65</v>
@@ -47210,7 +47219,7 @@
         <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q223">
         <v>3.5</v>
@@ -47494,10 +47503,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP224">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ224">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR224">
         <v>1.16</v>
@@ -47622,7 +47631,7 @@
         <v>234</v>
       </c>
       <c r="P225" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q225">
         <v>2.6</v>
@@ -47700,7 +47709,7 @@
         <v>1.38</v>
       </c>
       <c r="AP225">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ225">
         <v>1.2</v>
@@ -48034,7 +48043,7 @@
         <v>235</v>
       </c>
       <c r="P227" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q227">
         <v>2.6</v>
@@ -48446,7 +48455,7 @@
         <v>236</v>
       </c>
       <c r="P229" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q229">
         <v>8</v>
@@ -49270,7 +49279,7 @@
         <v>182</v>
       </c>
       <c r="P233" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q233">
         <v>2.75</v>
@@ -49682,7 +49691,7 @@
         <v>87</v>
       </c>
       <c r="P235" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q235">
         <v>3.24</v>
@@ -49888,7 +49897,7 @@
         <v>239</v>
       </c>
       <c r="P236" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q236">
         <v>1.43</v>
@@ -50061,7 +50070,7 @@
         <v>69</v>
       </c>
       <c r="E237" s="2">
-        <v>45753.60416666666</v>
+        <v>45753.625</v>
       </c>
       <c r="F237">
         <v>30</v>
@@ -50300,7 +50309,7 @@
         <v>87</v>
       </c>
       <c r="P238" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q238">
         <v>3</v>
@@ -50464,7 +50473,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>7453913</v>
+        <v>7453915</v>
       </c>
       <c r="C239" t="s">
         <v>68</v>
@@ -50479,189 +50488,601 @@
         <v>30</v>
       </c>
       <c r="G239" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H239" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I239">
         <v>1</v>
       </c>
       <c r="J239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N239">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O239" t="s">
         <v>240</v>
       </c>
       <c r="P239" t="s">
-        <v>87</v>
+        <v>352</v>
       </c>
       <c r="Q239">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="R239">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S239">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T239">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U239">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V239">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="W239">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X239">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y239">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z239">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AA239">
-        <v>3.76</v>
+        <v>3.39</v>
       </c>
       <c r="AB239">
-        <v>6.3</v>
+        <v>3.93</v>
       </c>
       <c r="AC239">
         <v>1.01</v>
       </c>
       <c r="AD239">
+        <v>8.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.25</v>
+      </c>
+      <c r="AF239">
+        <v>3.28</v>
+      </c>
+      <c r="AG239">
+        <v>1.77</v>
+      </c>
+      <c r="AH239">
+        <v>1.98</v>
+      </c>
+      <c r="AI239">
+        <v>1.8</v>
+      </c>
+      <c r="AJ239">
+        <v>1.91</v>
+      </c>
+      <c r="AK239">
+        <v>1.22</v>
+      </c>
+      <c r="AL239">
+        <v>1.26</v>
+      </c>
+      <c r="AM239">
+        <v>1.79</v>
+      </c>
+      <c r="AN239">
+        <v>1.64</v>
+      </c>
+      <c r="AO239">
+        <v>0.71</v>
+      </c>
+      <c r="AP239">
+        <v>1.6</v>
+      </c>
+      <c r="AQ239">
+        <v>0.73</v>
+      </c>
+      <c r="AR239">
+        <v>1.76</v>
+      </c>
+      <c r="AS239">
+        <v>1.48</v>
+      </c>
+      <c r="AT239">
+        <v>3.24</v>
+      </c>
+      <c r="AU239">
+        <v>7</v>
+      </c>
+      <c r="AV239">
+        <v>7</v>
+      </c>
+      <c r="AW239">
+        <v>5</v>
+      </c>
+      <c r="AX239">
+        <v>2</v>
+      </c>
+      <c r="AY239">
+        <v>15</v>
+      </c>
+      <c r="AZ239">
+        <v>9</v>
+      </c>
+      <c r="BA239">
+        <v>4</v>
+      </c>
+      <c r="BB239">
+        <v>2</v>
+      </c>
+      <c r="BC239">
+        <v>6</v>
+      </c>
+      <c r="BD239">
+        <v>1.64</v>
+      </c>
+      <c r="BE239">
+        <v>8</v>
+      </c>
+      <c r="BF239">
+        <v>2.77</v>
+      </c>
+      <c r="BG239">
+        <v>1.32</v>
+      </c>
+      <c r="BH239">
+        <v>2.88</v>
+      </c>
+      <c r="BI239">
+        <v>1.6</v>
+      </c>
+      <c r="BJ239">
+        <v>2.08</v>
+      </c>
+      <c r="BK239">
+        <v>2.05</v>
+      </c>
+      <c r="BL239">
+        <v>1.65</v>
+      </c>
+      <c r="BM239">
+        <v>2.7</v>
+      </c>
+      <c r="BN239">
+        <v>1.36</v>
+      </c>
+      <c r="BO239">
+        <v>3.8</v>
+      </c>
+      <c r="BP239">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7453917</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45754.54166666666</v>
+      </c>
+      <c r="F240">
+        <v>30</v>
+      </c>
+      <c r="G240" t="s">
+        <v>73</v>
+      </c>
+      <c r="H240" t="s">
+        <v>85</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>2</v>
+      </c>
+      <c r="K240">
+        <v>2</v>
+      </c>
+      <c r="L240">
+        <v>1</v>
+      </c>
+      <c r="M240">
+        <v>3</v>
+      </c>
+      <c r="N240">
+        <v>4</v>
+      </c>
+      <c r="O240" t="s">
+        <v>226</v>
+      </c>
+      <c r="P240" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q240">
+        <v>0</v>
+      </c>
+      <c r="R240">
+        <v>0</v>
+      </c>
+      <c r="S240">
+        <v>0</v>
+      </c>
+      <c r="T240">
+        <v>0</v>
+      </c>
+      <c r="U240">
+        <v>0</v>
+      </c>
+      <c r="V240">
+        <v>0</v>
+      </c>
+      <c r="W240">
+        <v>0</v>
+      </c>
+      <c r="X240">
+        <v>0</v>
+      </c>
+      <c r="Y240">
+        <v>0</v>
+      </c>
+      <c r="Z240">
+        <v>7.1</v>
+      </c>
+      <c r="AA240">
+        <v>3.99</v>
+      </c>
+      <c r="AB240">
+        <v>1.47</v>
+      </c>
+      <c r="AC240">
+        <v>0</v>
+      </c>
+      <c r="AD240">
+        <v>0</v>
+      </c>
+      <c r="AE240">
+        <v>0</v>
+      </c>
+      <c r="AF240">
+        <v>0</v>
+      </c>
+      <c r="AG240">
+        <v>1.98</v>
+      </c>
+      <c r="AH240">
+        <v>1.77</v>
+      </c>
+      <c r="AI240">
+        <v>0</v>
+      </c>
+      <c r="AJ240">
+        <v>0</v>
+      </c>
+      <c r="AK240">
+        <v>0</v>
+      </c>
+      <c r="AL240">
+        <v>0</v>
+      </c>
+      <c r="AM240">
+        <v>0</v>
+      </c>
+      <c r="AN240">
+        <v>1.5</v>
+      </c>
+      <c r="AO240">
+        <v>1.64</v>
+      </c>
+      <c r="AP240">
+        <v>1.4</v>
+      </c>
+      <c r="AQ240">
+        <v>1.73</v>
+      </c>
+      <c r="AR240">
+        <v>1.14</v>
+      </c>
+      <c r="AS240">
+        <v>1.74</v>
+      </c>
+      <c r="AT240">
+        <v>2.88</v>
+      </c>
+      <c r="AU240">
+        <v>-1</v>
+      </c>
+      <c r="AV240">
+        <v>-1</v>
+      </c>
+      <c r="AW240">
+        <v>-1</v>
+      </c>
+      <c r="AX240">
+        <v>-1</v>
+      </c>
+      <c r="AY240">
+        <v>-1</v>
+      </c>
+      <c r="AZ240">
+        <v>-1</v>
+      </c>
+      <c r="BA240">
+        <v>-1</v>
+      </c>
+      <c r="BB240">
+        <v>-1</v>
+      </c>
+      <c r="BC240">
+        <v>-1</v>
+      </c>
+      <c r="BD240">
+        <v>0</v>
+      </c>
+      <c r="BE240">
+        <v>0</v>
+      </c>
+      <c r="BF240">
+        <v>0</v>
+      </c>
+      <c r="BG240">
+        <v>0</v>
+      </c>
+      <c r="BH240">
+        <v>0</v>
+      </c>
+      <c r="BI240">
+        <v>0</v>
+      </c>
+      <c r="BJ240">
+        <v>0</v>
+      </c>
+      <c r="BK240">
+        <v>0</v>
+      </c>
+      <c r="BL240">
+        <v>0</v>
+      </c>
+      <c r="BM240">
+        <v>0</v>
+      </c>
+      <c r="BN240">
+        <v>0</v>
+      </c>
+      <c r="BO240">
+        <v>0</v>
+      </c>
+      <c r="BP240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7453913</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45754.54166666666</v>
+      </c>
+      <c r="F241">
+        <v>30</v>
+      </c>
+      <c r="G241" t="s">
+        <v>77</v>
+      </c>
+      <c r="H241" t="s">
+        <v>79</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
+        <v>241</v>
+      </c>
+      <c r="P241" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q241">
+        <v>1.91</v>
+      </c>
+      <c r="R241">
+        <v>2.38</v>
+      </c>
+      <c r="S241">
+        <v>6</v>
+      </c>
+      <c r="T241">
+        <v>1.33</v>
+      </c>
+      <c r="U241">
+        <v>3.25</v>
+      </c>
+      <c r="V241">
+        <v>2.63</v>
+      </c>
+      <c r="W241">
+        <v>1.44</v>
+      </c>
+      <c r="X241">
+        <v>6</v>
+      </c>
+      <c r="Y241">
+        <v>1.11</v>
+      </c>
+      <c r="Z241">
+        <v>1.55</v>
+      </c>
+      <c r="AA241">
+        <v>3.76</v>
+      </c>
+      <c r="AB241">
+        <v>6.3</v>
+      </c>
+      <c r="AC241">
+        <v>1.01</v>
+      </c>
+      <c r="AD241">
         <v>12.5</v>
       </c>
-      <c r="AE239">
+      <c r="AE241">
         <v>1.18</v>
       </c>
-      <c r="AF239">
+      <c r="AF241">
         <v>3.86</v>
       </c>
-      <c r="AG239">
+      <c r="AG241">
         <v>1.8</v>
       </c>
-      <c r="AH239">
+      <c r="AH241">
         <v>1.9</v>
       </c>
-      <c r="AI239">
+      <c r="AI241">
         <v>1.91</v>
       </c>
-      <c r="AJ239">
+      <c r="AJ241">
         <v>1.8</v>
       </c>
-      <c r="AK239">
+      <c r="AK241">
         <v>1.07</v>
       </c>
-      <c r="AL239">
+      <c r="AL241">
         <v>1.16</v>
       </c>
-      <c r="AM239">
+      <c r="AM241">
         <v>2.64</v>
       </c>
-      <c r="AN239">
+      <c r="AN241">
         <v>1.36</v>
       </c>
-      <c r="AO239">
+      <c r="AO241">
         <v>1.29</v>
       </c>
-      <c r="AP239">
+      <c r="AP241">
         <v>1.47</v>
       </c>
-      <c r="AQ239">
+      <c r="AQ241">
         <v>1.2</v>
       </c>
-      <c r="AR239">
+      <c r="AR241">
         <v>1.92</v>
       </c>
-      <c r="AS239">
+      <c r="AS241">
         <v>1.19</v>
       </c>
-      <c r="AT239">
+      <c r="AT241">
         <v>3.11</v>
       </c>
-      <c r="AU239">
+      <c r="AU241">
         <v>4</v>
       </c>
-      <c r="AV239">
-        <v>3</v>
-      </c>
-      <c r="AW239">
+      <c r="AV241">
+        <v>3</v>
+      </c>
+      <c r="AW241">
         <v>8</v>
       </c>
-      <c r="AX239">
+      <c r="AX241">
         <v>4</v>
       </c>
-      <c r="AY239">
+      <c r="AY241">
         <v>17</v>
       </c>
-      <c r="AZ239">
+      <c r="AZ241">
         <v>10</v>
       </c>
-      <c r="BA239">
-        <v>3</v>
-      </c>
-      <c r="BB239">
+      <c r="BA241">
+        <v>3</v>
+      </c>
+      <c r="BB241">
         <v>4</v>
       </c>
-      <c r="BC239">
+      <c r="BC241">
         <v>7</v>
       </c>
-      <c r="BD239">
+      <c r="BD241">
         <v>1.26</v>
       </c>
-      <c r="BE239">
+      <c r="BE241">
         <v>9.5</v>
       </c>
-      <c r="BF239">
+      <c r="BF241">
         <v>4.66</v>
       </c>
-      <c r="BG239">
+      <c r="BG241">
         <v>1.36</v>
       </c>
-      <c r="BH239">
+      <c r="BH241">
         <v>2.7</v>
       </c>
-      <c r="BI239">
+      <c r="BI241">
         <v>1.67</v>
       </c>
-      <c r="BJ239">
+      <c r="BJ241">
         <v>2.03</v>
       </c>
-      <c r="BK239">
+      <c r="BK241">
         <v>2.1</v>
       </c>
-      <c r="BL239">
+      <c r="BL241">
         <v>1.59</v>
       </c>
-      <c r="BM239">
+      <c r="BM241">
         <v>2.83</v>
       </c>
-      <c r="BN239">
+      <c r="BN241">
         <v>1.33</v>
       </c>
-      <c r="BO239">
+      <c r="BO241">
         <v>3.75</v>
       </c>
-      <c r="BP239">
+      <c r="BP241">
         <v>1.21</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -50814,31 +50814,31 @@
         <v>2.88</v>
       </c>
       <c r="AU240">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV240">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AW240">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX240">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AY240">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ240">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="BA240">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB240">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BC240">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BD240">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Serbia SuperLiga_20242025.xlsx
@@ -1966,10 +1966,10 @@
         <v>3</v>
       </c>
       <c r="AY2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA2">
         <v>4</v>
@@ -2172,10 +2172,10 @@
         <v>7</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA3">
         <v>3</v>
@@ -2378,10 +2378,10 @@
         <v>5</v>
       </c>
       <c r="AY4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA4">
         <v>10</v>
@@ -2996,10 +2996,10 @@
         <v>2</v>
       </c>
       <c r="AY7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA7">
         <v>4</v>
@@ -3202,10 +3202,10 @@
         <v>5</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8">
         <v>1</v>
@@ -3408,10 +3408,10 @@
         <v>5</v>
       </c>
       <c r="AY9">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA9">
         <v>7</v>
@@ -3614,10 +3614,10 @@
         <v>6</v>
       </c>
       <c r="AY10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA10">
         <v>2</v>
@@ -3820,7 +3820,7 @@
         <v>2</v>
       </c>
       <c r="AY11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
         <v>4</v>
@@ -4232,10 +4232,10 @@
         <v>8</v>
       </c>
       <c r="AY13">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA13">
         <v>9</v>
@@ -4438,10 +4438,10 @@
         <v>6</v>
       </c>
       <c r="AY14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA14">
         <v>4</v>
@@ -4647,7 +4647,7 @@
         <v>6</v>
       </c>
       <c r="AZ15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4850,10 +4850,10 @@
         <v>5</v>
       </c>
       <c r="AY16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA16">
         <v>3</v>
@@ -5056,10 +5056,10 @@
         <v>5</v>
       </c>
       <c r="AY17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA17">
         <v>9</v>
@@ -5471,7 +5471,7 @@
         <v>6</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA19">
         <v>1</v>
@@ -5674,10 +5674,10 @@
         <v>5</v>
       </c>
       <c r="AY20">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA20">
         <v>5</v>
@@ -5880,10 +5880,10 @@
         <v>9</v>
       </c>
       <c r="AY21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ21">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA21">
         <v>2</v>
@@ -6086,10 +6086,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA22">
         <v>8</v>
@@ -6292,10 +6292,10 @@
         <v>3</v>
       </c>
       <c r="AY23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ23">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BA23">
         <v>3</v>
@@ -6498,10 +6498,10 @@
         <v>4</v>
       </c>
       <c r="AY24">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA24">
         <v>5</v>
@@ -6704,10 +6704,10 @@
         <v>3</v>
       </c>
       <c r="AY25">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA25">
         <v>2</v>
@@ -6910,10 +6910,10 @@
         <v>9</v>
       </c>
       <c r="AY26">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA26">
         <v>3</v>
@@ -7116,10 +7116,10 @@
         <v>3</v>
       </c>
       <c r="AY27">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA27">
         <v>10</v>
@@ -7528,10 +7528,10 @@
         <v>5</v>
       </c>
       <c r="AY29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA29">
         <v>2</v>
@@ -7734,10 +7734,10 @@
         <v>5</v>
       </c>
       <c r="AY30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ30">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA30">
         <v>1</v>
@@ -7940,10 +7940,10 @@
         <v>7</v>
       </c>
       <c r="AY31">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA31">
         <v>4</v>
@@ -8146,10 +8146,10 @@
         <v>10</v>
       </c>
       <c r="AY32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ32">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA32">
         <v>1</v>
@@ -8352,10 +8352,10 @@
         <v>1</v>
       </c>
       <c r="AY33">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA33">
         <v>6</v>
@@ -8764,10 +8764,10 @@
         <v>6</v>
       </c>
       <c r="AY35">
+        <v>7</v>
+      </c>
+      <c r="AZ35">
         <v>10</v>
-      </c>
-      <c r="AZ35">
-        <v>12</v>
       </c>
       <c r="BA35">
         <v>2</v>
@@ -8973,7 +8973,7 @@
         <v>5</v>
       </c>
       <c r="AZ36">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA36">
         <v>2</v>
@@ -9176,10 +9176,10 @@
         <v>2</v>
       </c>
       <c r="AY37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA37">
         <v>2</v>
@@ -9382,10 +9382,10 @@
         <v>7</v>
       </c>
       <c r="AY38">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ38">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA38">
         <v>5</v>
@@ -9794,10 +9794,10 @@
         <v>7</v>
       </c>
       <c r="AY40">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ40">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA40">
         <v>4</v>
@@ -10206,10 +10206,10 @@
         <v>5</v>
       </c>
       <c r="AY42">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA42">
         <v>2</v>
@@ -10412,10 +10412,10 @@
         <v>3</v>
       </c>
       <c r="AY43">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ43">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BA43">
         <v>7</v>
@@ -10618,10 +10618,10 @@
         <v>4</v>
       </c>
       <c r="AY44">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ44">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA44">
         <v>10</v>
@@ -10824,10 +10824,10 @@
         <v>8</v>
       </c>
       <c r="AY45">
+        <v>9</v>
+      </c>
+      <c r="AZ45">
         <v>12</v>
-      </c>
-      <c r="AZ45">
-        <v>14</v>
       </c>
       <c r="BA45">
         <v>8</v>
@@ -11030,10 +11030,10 @@
         <v>3</v>
       </c>
       <c r="AY46">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ46">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA46">
         <v>2</v>
@@ -11236,10 +11236,10 @@
         <v>6</v>
       </c>
       <c r="AY47">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ47">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA47">
         <v>10</v>
@@ -11442,10 +11442,10 @@
         <v>4</v>
       </c>
       <c r="AY48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA48">
         <v>2</v>
@@ -11648,10 +11648,10 @@
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ49">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA49">
         <v>4</v>
@@ -12060,10 +12060,10 @@
         <v>7</v>
       </c>
       <c r="AY51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ51">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA51">
         <v>2</v>
@@ -12266,10 +12266,10 @@
         <v>9</v>
       </c>
       <c r="AY52">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ52">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA52">
         <v>7</v>
@@ -12472,10 +12472,10 @@
         <v>5</v>
       </c>
       <c r="AY53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ53">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA53">
         <v>1</v>
@@ -12678,10 +12678,10 @@
         <v>7</v>
       </c>
       <c r="AY54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ54">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA54">
         <v>6</v>
@@ -12884,10 +12884,10 @@
         <v>1</v>
       </c>
       <c r="AY55">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AZ55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA55">
         <v>14</v>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="AY57">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ57">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA57">
         <v>6</v>
@@ -13502,10 +13502,10 @@
         <v>3</v>
       </c>
       <c r="AY58">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA58">
         <v>2</v>
@@ -13711,7 +13711,7 @@
         <v>11</v>
       </c>
       <c r="AZ59">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA59">
         <v>4</v>
@@ -13914,10 +13914,10 @@
         <v>5</v>
       </c>
       <c r="AY60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ60">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA60">
         <v>5</v>
@@ -14120,10 +14120,10 @@
         <v>8</v>
       </c>
       <c r="AY61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ61">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA61">
         <v>3</v>
@@ -14326,10 +14326,10 @@
         <v>3</v>
       </c>
       <c r="AY62">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AZ62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA62">
         <v>7</v>
@@ -14532,7 +14532,7 @@
         <v>4</v>
       </c>
       <c r="AY63">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ63">
         <v>11</v>
@@ -14944,10 +14944,10 @@
         <v>5</v>
       </c>
       <c r="AY65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ65">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA65">
         <v>2</v>
@@ -15150,10 +15150,10 @@
         <v>4</v>
       </c>
       <c r="AY66">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ66">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BA66">
         <v>4</v>
@@ -15356,10 +15356,10 @@
         <v>6</v>
       </c>
       <c r="AY67">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ67">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA67">
         <v>1</v>
@@ -15562,10 +15562,10 @@
         <v>2</v>
       </c>
       <c r="AY68">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ68">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA68">
         <v>5</v>
@@ -15771,7 +15771,7 @@
         <v>6</v>
       </c>
       <c r="AZ69">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA69">
         <v>7</v>
@@ -15974,10 +15974,10 @@
         <v>2</v>
       </c>
       <c r="AY70">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA70">
         <v>11</v>
@@ -16180,10 +16180,10 @@
         <v>4</v>
       </c>
       <c r="AY71">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ71">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA71">
         <v>5</v>
@@ -16386,10 +16386,10 @@
         <v>3</v>
       </c>
       <c r="AY72">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ72">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA72">
         <v>5</v>
@@ -16592,10 +16592,10 @@
         <v>4</v>
       </c>
       <c r="AY73">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ73">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA73">
         <v>3</v>
@@ -16798,10 +16798,10 @@
         <v>5</v>
       </c>
       <c r="AY74">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ74">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA74">
         <v>9</v>
@@ -17004,10 +17004,10 @@
         <v>4</v>
       </c>
       <c r="AY75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ75">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA75">
         <v>6</v>
@@ -17416,10 +17416,10 @@
         <v>3</v>
       </c>
       <c r="AY77">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ77">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA77">
         <v>1</v>
@@ -17622,10 +17622,10 @@
         <v>6</v>
       </c>
       <c r="AY78">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ78">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA78">
         <v>3</v>
@@ -17828,10 +17828,10 @@
         <v>6</v>
       </c>
       <c r="AY79">
+        <v>11</v>
+      </c>
+      <c r="AZ79">
         <v>15</v>
-      </c>
-      <c r="AZ79">
-        <v>20</v>
       </c>
       <c r="BA79">
         <v>4</v>
@@ -18034,10 +18034,10 @@
         <v>6</v>
       </c>
       <c r="AY80">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ80">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA80">
         <v>5</v>
@@ -18446,10 +18446,10 @@
         <v>3</v>
       </c>
       <c r="AY82">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA82">
         <v>3</v>
@@ -18652,10 +18652,10 @@
         <v>5</v>
       </c>
       <c r="AY83">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ83">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA83">
         <v>5</v>
@@ -18858,10 +18858,10 @@
         <v>3</v>
       </c>
       <c r="AY84">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ84">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA84">
         <v>5</v>
@@ -19064,10 +19064,10 @@
         <v>10</v>
       </c>
       <c r="AY85">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ85">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BA85">
         <v>3</v>
@@ -19270,7 +19270,7 @@
         <v>2</v>
       </c>
       <c r="AY86">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ86">
         <v>5</v>
@@ -20094,10 +20094,10 @@
         <v>3</v>
       </c>
       <c r="AY90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ90">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA90">
         <v>1</v>
@@ -20300,10 +20300,10 @@
         <v>4</v>
       </c>
       <c r="AY91">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ91">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA91">
         <v>3</v>
@@ -20506,10 +20506,10 @@
         <v>8</v>
       </c>
       <c r="AY92">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ92">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA92">
         <v>5</v>
@@ -20918,10 +20918,10 @@
         <v>1</v>
       </c>
       <c r="AY94">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ94">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA94">
         <v>9</v>
@@ -21536,10 +21536,10 @@
         <v>4</v>
       </c>
       <c r="AY97">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ97">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA97">
         <v>9</v>
@@ -21742,10 +21742,10 @@
         <v>9</v>
       </c>
       <c r="AY98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ98">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA98">
         <v>1</v>
@@ -21948,7 +21948,7 @@
         <v>1</v>
       </c>
       <c r="AY99">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ99">
         <v>6</v>
@@ -22154,10 +22154,10 @@
         <v>0</v>
       </c>
       <c r="AY100">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA100">
         <v>4</v>
@@ -22360,10 +22360,10 @@
         <v>5</v>
       </c>
       <c r="AY101">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ101">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA101">
         <v>4</v>
@@ -22772,10 +22772,10 @@
         <v>3</v>
       </c>
       <c r="AY103">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ103">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA103">
         <v>2</v>
@@ -22978,10 +22978,10 @@
         <v>7</v>
       </c>
       <c r="AY104">
+        <v>13</v>
+      </c>
+      <c r="AZ104">
         <v>14</v>
-      </c>
-      <c r="AZ104">
-        <v>21</v>
       </c>
       <c r="BA104">
         <v>7</v>
@@ -23184,10 +23184,10 @@
         <v>4</v>
       </c>
       <c r="AY105">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ105">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA105">
         <v>9</v>
@@ -23390,10 +23390,10 @@
         <v>1</v>
       </c>
       <c r="AY106">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AZ106">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA106">
         <v>12</v>
@@ -23596,10 +23596,10 @@
         <v>5</v>
       </c>
       <c r="AY107">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA107">
         <v>9</v>
@@ -24008,10 +24008,10 @@
         <v>2</v>
       </c>
       <c r="AY109">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ109">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA109">
         <v>4</v>
@@ -24214,7 +24214,7 @@
         <v>3</v>
       </c>
       <c r="AY110">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ110">
         <v>3</v>
@@ -24420,10 +24420,10 @@
         <v>3</v>
       </c>
       <c r="AY111">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ111">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA111">
         <v>6</v>
@@ -24626,10 +24626,10 @@
         <v>3</v>
       </c>
       <c r="AY112">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ112">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -25244,10 +25244,10 @@
         <v>3</v>
       </c>
       <c r="AY115">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ115">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>7</v>
@@ -25450,10 +25450,10 @@
         <v>2</v>
       </c>
       <c r="AY116">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA116">
         <v>4</v>
@@ -25656,10 +25656,10 @@
         <v>4</v>
       </c>
       <c r="AY117">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ117">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA117">
         <v>7</v>
@@ -25862,10 +25862,10 @@
         <v>12</v>
       </c>
       <c r="AY118">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ118">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA118">
         <v>0</v>
@@ -27304,10 +27304,10 @@
         <v>2</v>
       </c>
       <c r="AY125">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ125">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA125">
         <v>6</v>
@@ -27510,10 +27510,10 @@
         <v>4</v>
       </c>
       <c r="AY126">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AZ126">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA126">
         <v>11</v>
@@ -27716,10 +27716,10 @@
         <v>2</v>
       </c>
       <c r="AY127">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ127">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA127">
         <v>3</v>
@@ -27922,10 +27922,10 @@
         <v>1</v>
       </c>
       <c r="AY128">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ128">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA128">
         <v>5</v>
@@ -28128,10 +28128,10 @@
         <v>2</v>
       </c>
       <c r="AY129">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ129">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA129">
         <v>6</v>
@@ -28334,10 +28334,10 @@
         <v>2</v>
       </c>
       <c r="AY130">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA130">
         <v>6</v>
@@ -28746,10 +28746,10 @@
         <v>5</v>
       </c>
       <c r="AY132">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ132">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA132">
         <v>8</v>
@@ -28952,10 +28952,10 @@
         <v>5</v>
       </c>
       <c r="AY133">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ133">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -29158,10 +29158,10 @@
         <v>4</v>
       </c>
       <c r="AY134">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ134">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA134">
         <v>2</v>
@@ -29364,10 +29364,10 @@
         <v>0</v>
       </c>
       <c r="AY135">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA135">
         <v>6</v>
@@ -29576,13 +29576,13 @@
         <v>-1</v>
       </c>
       <c r="BA136">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BB136">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BC136">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BD136">
         <v>0</v>
@@ -29776,10 +29776,10 @@
         <v>3</v>
       </c>
       <c r="AY137">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA137">
         <v>4</v>
@@ -29985,7 +29985,7 @@
         <v>7</v>
       </c>
       <c r="AZ138">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA138">
         <v>5</v>
@@ -30188,10 +30188,10 @@
         <v>2</v>
       </c>
       <c r="AY139">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ139">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA139">
         <v>4</v>
@@ -30806,10 +30806,10 @@
         <v>5</v>
       </c>
       <c r="AY142">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ142">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA142">
         <v>5</v>
@@ -31012,10 +31012,10 @@
         <v>11</v>
       </c>
       <c r="AY143">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ143">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA143">
         <v>2</v>
@@ -31424,7 +31424,7 @@
         <v>4</v>
       </c>
       <c r="AY145">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ145">
         <v>7</v>
@@ -31630,10 +31630,10 @@
         <v>4</v>
       </c>
       <c r="AY146">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ146">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31836,10 +31836,10 @@
         <v>4</v>
       </c>
       <c r="AY147">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ147">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA147">
         <v>5</v>
@@ -32042,10 +32042,10 @@
         <v>3</v>
       </c>
       <c r="AY148">
+        <v>9</v>
+      </c>
+      <c r="AZ148">
         <v>14</v>
-      </c>
-      <c r="AZ148">
-        <v>16</v>
       </c>
       <c r="BA148">
         <v>2</v>
@@ -32248,10 +32248,10 @@
         <v>1</v>
       </c>
       <c r="AY149">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ149">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA149">
         <v>5</v>
@@ -32454,10 +32454,10 @@
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ150">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA150">
         <v>4</v>
@@ -32660,10 +32660,10 @@
         <v>3</v>
       </c>
       <c r="AY151">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ151">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA151">
         <v>5</v>
@@ -32866,10 +32866,10 @@
         <v>11</v>
       </c>
       <c r="AY152">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ152">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA152">
         <v>3</v>
@@ -33278,10 +33278,10 @@
         <v>3</v>
       </c>
       <c r="AY154">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ154">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA154">
         <v>6</v>
@@ -33484,10 +33484,10 @@
         <v>5</v>
       </c>
       <c r="AY155">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ155">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA155">
         <v>1</v>
@@ -33690,7 +33690,7 @@
         <v>2</v>
       </c>
       <c r="AY156">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ156">
         <v>6</v>
@@ -33896,10 +33896,10 @@
         <v>4</v>
       </c>
       <c r="AY157">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ157">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA157">
         <v>4</v>
@@ -34102,7 +34102,7 @@
         <v>3</v>
       </c>
       <c r="AY158">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ158">
         <v>8</v>
@@ -34308,10 +34308,10 @@
         <v>2</v>
       </c>
       <c r="AY159">
+        <v>7</v>
+      </c>
+      <c r="AZ159">
         <v>8</v>
-      </c>
-      <c r="AZ159">
-        <v>10</v>
       </c>
       <c r="BA159">
         <v>1</v>
@@ -34514,10 +34514,10 @@
         <v>3</v>
       </c>
       <c r="AY160">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ160">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA160">
         <v>3</v>
@@ -34720,10 +34720,10 @@
         <v>3</v>
       </c>
       <c r="AY161">
+        <v>6</v>
+      </c>
+      <c r="AZ161">
         <v>11</v>
-      </c>
-      <c r="AZ161">
-        <v>15</v>
       </c>
       <c r="BA161">
         <v>4</v>
@@ -35338,10 +35338,10 @@
         <v>5</v>
       </c>
       <c r="AY164">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ164">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA164">
         <v>7</v>
@@ -35544,10 +35544,10 @@
         <v>1</v>
       </c>
       <c r="AY165">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ165">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA165">
         <v>3</v>
@@ -35750,10 +35750,10 @@
         <v>6</v>
       </c>
       <c r="AY166">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ166">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA166">
         <v>4</v>
@@ -35956,10 +35956,10 @@
         <v>6</v>
       </c>
       <c r="AY167">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ167">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA167">
         <v>3</v>
@@ -36165,7 +36165,7 @@
         <v>7</v>
       </c>
       <c r="AZ168">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA168">
         <v>1</v>
@@ -36371,7 +36371,7 @@
         <v>13</v>
       </c>
       <c r="AZ169">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA169">
         <v>4</v>
@@ -36574,10 +36574,10 @@
         <v>9</v>
       </c>
       <c r="AY170">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ170">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA170">
         <v>3</v>
@@ -36986,10 +36986,10 @@
         <v>9</v>
       </c>
       <c r="AY172">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AZ172">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA172">
         <v>3</v>
@@ -37192,10 +37192,10 @@
         <v>2</v>
       </c>
       <c r="AY173">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ173">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA173">
         <v>5</v>
@@ -37401,7 +37401,7 @@
         <v>6</v>
       </c>
       <c r="AZ174">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA174">
         <v>6</v>
@@ -37810,7 +37810,7 @@
         <v>4</v>
       </c>
       <c r="AY176">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ176">
         <v>8</v>
@@ -38016,10 +38016,10 @@
         <v>1</v>
       </c>
       <c r="AY177">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ177">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA177">
         <v>1</v>
@@ -38222,7 +38222,7 @@
         <v>3</v>
       </c>
       <c r="AY178">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ178">
         <v>7</v>
@@ -39870,10 +39870,10 @@
         <v>4</v>
       </c>
       <c r="AY186">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ186">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA186">
         <v>6</v>
@@ -40076,10 +40076,10 @@
         <v>8</v>
       </c>
       <c r="AY187">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ187">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA187">
         <v>5</v>
@@ -40282,10 +40282,10 @@
         <v>6</v>
       </c>
       <c r="AY188">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ188">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA188">
         <v>5</v>
@@ -40903,7 +40903,7 @@
         <v>9</v>
       </c>
       <c r="AZ191">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA191">
         <v>3</v>
@@ -41106,10 +41106,10 @@
         <v>7</v>
       </c>
       <c r="AY192">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ192">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA192">
         <v>4</v>
@@ -41312,10 +41312,10 @@
         <v>4</v>
       </c>
       <c r="AY193">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ193">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA193">
         <v>3</v>
@@ -41521,7 +41521,7 @@
         <v>8</v>
       </c>
       <c r="AZ194">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA194">
         <v>4</v>
@@ -41930,10 +41930,10 @@
         <v>9</v>
       </c>
       <c r="AY196">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ196">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA196">
         <v>2</v>
@@ -42136,19 +42136,19 @@
         <v>1</v>
       </c>
       <c r="AY197">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ197">
         <v>11</v>
       </c>
       <c r="BA197">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB197">
         <v>6</v>
       </c>
       <c r="BC197">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD197">
         <v>1.64</v>
@@ -42342,10 +42342,10 @@
         <v>7</v>
       </c>
       <c r="AY198">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ198">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA198">
         <v>5</v>
@@ -42548,7 +42548,7 @@
         <v>4</v>
       </c>
       <c r="AY199">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ199">
         <v>6</v>
@@ -42754,7 +42754,7 @@
         <v>4</v>
       </c>
       <c r="AY200">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ200">
         <v>6</v>
@@ -42966,13 +42966,13 @@
         <v>13</v>
       </c>
       <c r="BA201">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB201">
         <v>5</v>
       </c>
       <c r="BC201">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD201">
         <v>0</v>
@@ -43166,7 +43166,7 @@
         <v>6</v>
       </c>
       <c r="AY202">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ202">
         <v>12</v>
@@ -43372,19 +43372,19 @@
         <v>3</v>
       </c>
       <c r="AY203">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA203">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BB203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC203">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BD203">
         <v>0</v>
@@ -43784,10 +43784,10 @@
         <v>11</v>
       </c>
       <c r="AY205">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ205">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA205">
         <v>3</v>
@@ -43990,10 +43990,10 @@
         <v>6</v>
       </c>
       <c r="AY206">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ206">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA206">
         <v>5</v>
@@ -44402,10 +44402,10 @@
         <v>8</v>
       </c>
       <c r="AY208">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ208">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA208">
         <v>1</v>
@@ -44814,10 +44814,10 @@
         <v>8</v>
       </c>
       <c r="AY210">
+        <v>8</v>
+      </c>
+      <c r="AZ210">
         <v>10</v>
-      </c>
-      <c r="AZ210">
-        <v>13</v>
       </c>
       <c r="BA210">
         <v>3</v>
@@ -45020,7 +45020,7 @@
         <v>3</v>
       </c>
       <c r="AY211">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ211">
         <v>13</v>
@@ -45226,7 +45226,7 @@
         <v>10</v>
       </c>
       <c r="AY212">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ212">
         <v>18</v>
@@ -45432,10 +45432,10 @@
         <v>4</v>
       </c>
       <c r="AY213">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ213">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA213">
         <v>1</v>
@@ -45641,7 +45641,7 @@
         <v>8</v>
       </c>
       <c r="AZ214">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA214">
         <v>5</v>
@@ -45850,13 +45850,13 @@
         <v>-1</v>
       </c>
       <c r="BA215">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BB215">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BC215">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BD215">
         <v>0</v>
@@ -46050,10 +46050,10 @@
         <v>6</v>
       </c>
       <c r="AY216">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ216">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA216">
         <v>4</v>
@@ -46256,10 +46256,10 @@
         <v>4</v>
       </c>
       <c r="AY217">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ217">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA217">
         <v>5</v>
@@ -46462,10 +46462,10 @@
         <v>12</v>
       </c>
       <c r="AY218">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ218">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BA218">
         <v>7</v>
@@ -47080,10 +47080,10 @@
         <v>2</v>
       </c>
       <c r="AY221">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ221">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA221">
         <v>11</v>
@@ -47904,10 +47904,10 @@
         <v>5</v>
       </c>
       <c r="AY225">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ225">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA225">
         <v>9</v>
@@ -48110,10 +48110,10 @@
         <v>4</v>
       </c>
       <c r="AY226">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ226">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA226">
         <v>3</v>
@@ -48316,7 +48316,7 @@
         <v>2</v>
       </c>
       <c r="AY227">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ227">
         <v>16</v>
@@ -48325,10 +48325,10 @@
         <v>5</v>
       </c>
       <c r="BB227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC227">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD227">
         <v>1.91</v>
@@ -48522,19 +48522,19 @@
         <v>7</v>
       </c>
       <c r="AY228">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ228">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA228">
         <v>5</v>
       </c>
       <c r="BB228">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC228">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD228">
         <v>1.64</v>
@@ -48731,7 +48731,7 @@
         <v>9</v>
       </c>
       <c r="AZ229">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BA229">
         <v>1</v>
@@ -48937,7 +48937,7 @@
         <v>12</v>
       </c>
       <c r="AZ230">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA230">
         <v>4</v>
@@ -49140,10 +49140,10 @@
         <v>4</v>
       </c>
       <c r="AY231">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ231">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA231">
         <v>7</v>
@@ -49552,10 +49552,10 @@
         <v>8</v>
       </c>
       <c r="AY233">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ233">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA233">
         <v>3</v>
@@ -49758,10 +49758,10 @@
         <v>2</v>
       </c>
       <c r="AY234">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ234">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA234">
         <v>4</v>
@@ -49964,10 +49964,10 @@
         <v>8</v>
       </c>
       <c r="AY235">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ235">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA235">
         <v>3</v>
@@ -50170,10 +50170,10 @@
         <v>7</v>
       </c>
       <c r="AY236">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AZ236">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA236">
         <v>6</v>
@@ -50376,10 +50376,10 @@
         <v>8</v>
       </c>
       <c r="AY237">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AZ237">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA237">
         <v>8</v>
@@ -50582,10 +50582,10 @@
         <v>4</v>
       </c>
       <c r="AY238">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ238">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA238">
         <v>3</v>
@@ -50994,7 +50994,7 @@
         <v>2</v>
       </c>
       <c r="AY240">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ240">
         <v>9</v>
@@ -51200,10 +51200,10 @@
         <v>4</v>
       </c>
       <c r="AY241">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ241">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA241">
         <v>6</v>
@@ -51406,10 +51406,10 @@
         <v>12</v>
       </c>
       <c r="AY242">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ242">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA242">
         <v>2</v>
@@ -51612,10 +51612,10 @@
         <v>4</v>
       </c>
       <c r="AY243">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ243">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA243">
         <v>6</v>
@@ -52848,10 +52848,10 @@
         <v>6</v>
       </c>
       <c r="AY249">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ249">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA249">
         <v>2</v>
@@ -54702,7 +54702,7 @@
         <v>5</v>
       </c>
       <c r="AY258">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ258">
         <v>8</v>
@@ -58204,7 +58204,7 @@
         <v>3</v>
       </c>
       <c r="AY275">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ275">
         <v>8</v>
@@ -62533,7 +62533,7 @@
         <v>11</v>
       </c>
       <c r="AZ296">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA296">
         <v>3</v>
